--- a/Output/Chandrashekhar Bawankule/extracted_links_Chandrashekhar Bawankule_failed_links.xlsx
+++ b/Output/Chandrashekhar Bawankule/extracted_links_Chandrashekhar Bawankule_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A385"/>
+  <dimension ref="A1:A396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,1785 +438,1785 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174008/</t>
+          <t>https://www.etvbharat.com/mr/!state/revenue-week-will-be-celebrate-in-the-maharashtra-in-1-to-7-august-says-minister-chandrashekhar-bawankule-maharashtra-news-mhs25073005592</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/154916/</t>
+          <t>https://mahasamvad.in/168550/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/159925/</t>
+          <t>https://mahasamvad.in/168121/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/157368/</t>
+          <t>https://mahasamvad.in/154916/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173290/</t>
+          <t>https://mahasamvad.in/174008/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/167394/</t>
+          <t>https://mahasamvad.in/159925/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/161858/</t>
+          <t>https://mahasamvad.in/157368/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170401/</t>
+          <t>https://mahasamvad.in/173290/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176111/</t>
+          <t>https://mahasamvad.in/167394/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/171657/</t>
+          <t>https://mahasamvad.in/161858/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/166188/</t>
+          <t>https://mahasamvad.in/176111/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/166744/</t>
+          <t>https://mahasamvad.in/170401/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173830/</t>
+          <t>https://mahasamvad.in/171657/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168197/</t>
+          <t>https://mahasamvad.in/166188/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/167498/</t>
+          <t>https://www.newsonair.gov.in/mr/farm-road/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172967/</t>
+          <t>https://mahasamvad.in/173830/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/165738/</t>
+          <t>https://mahasamvad.in/168197/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163316/</t>
+          <t>https://mahasamvad.in/167498/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173944/</t>
+          <t>https://mahasamvad.in/172967/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/166711/</t>
+          <t>https://mahasamvad.in/165738/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/167907/</t>
+          <t>https://mahasamvad.in/163316/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/167416/</t>
+          <t>https://mahasamvad.in/173944/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176970/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/3/9/Chandrashekhar-Bawankule-will-carry-out-comprehensive-development-of-Kamathi-city.html</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174937/</t>
+          <t>https://marathi.abplive.com/news/mumbai/micro-zoning-to-determine-rates-of-ready-reckoners-in-mumbai-revenue-minister-chandrashekhar-bawankule-decision-marathi-news-1352443</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176959/</t>
+          <t>https://mahasamvad.in/166711/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-news-state-governments-big-decision-regarding-land-fragmentation-high-level-committee-formed-to-make-reforms-83561</t>
+          <t>https://mahasamvad.in/167416/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/government-will-take-a-big-decision-for-snake-lovers-revenue-minister-bawankule-gave-information-8943735</t>
+          <t>https://mahasamvad.in/174937/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160422/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-news-state-governments-big-decision-regarding-land-fragmentation-high-level-committee-formed-to-make-reforms-83561</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175334/</t>
+          <t>https://marathi.ndtv.com/politics/government-will-take-a-big-decision-for-snake-lovers-revenue-minister-bawankule-gave-information-8943735</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/appointment-of-80-additional-district-collectors-in-the-state-a-big-decision-by-revenue-minister-chandrashekhar-bawankule-1355734</t>
+          <t>https://mahasamvad.in/160422/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/171768/</t>
+          <t>https://mahasamvad.in/167907/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/161982/</t>
+          <t>https://mahasamvad.in/176970/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nashik/chandrashekhar-bawankule-expressed-anger-on-phone-call-to-chandwad-tehsildar-regarding-working-complaints-pri/articleshow/121389576.cms</t>
+          <t>https://mahasamvad.in/175334/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176956/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/appointment-of-80-additional-district-collectors-in-the-state-a-big-decision-by-revenue-minister-chandrashekhar-bawankule-1355734</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/152385/</t>
+          <t>https://mahasamvad.in/171768/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/bjp-state-president-chandrashekhar-bawankule-apologized-to-chief-justice-bhushan-gavai-on-behalf-of-the-government/articleshow/121268071.cms</t>
+          <t>https://mahasamvad.in/176959/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168812/</t>
+          <t>https://mahasamvad.in/161982/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/government-benefits-will-reach-every-citizen-revenue-minister-chandrashekhar-bawankules-determination/01231556</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nashik/chandrashekhar-bawankule-expressed-anger-on-phone-call-to-chandwad-tehsildar-regarding-working-complaints-pri/articleshow/121389576.cms</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/revenue-minister-chandrashekhar-bawankules-call-to-chandwad-tehsildar-aggressive-reaction-over-complaints-in-bjp-janta-darbar-in-mumbai-video-goes-viral-maharashtra-politics-1361293</t>
+          <t>https://mahasamvad.in/152385/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-counterattack-after-uddhav-thackeray-criticism-of-pm-narendra-modi-u-turn-on-the-issue-of-farmer-loan-waiver-maharashtra-politics-marathi-news-1375550</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/bjp-state-president-chandrashekhar-bawankule-apologized-to-chief-justice-bhushan-gavai-on-behalf-of-the-government/articleshow/121268071.cms</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/151939/</t>
+          <t>https://mahasamvad.in/168812/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174605/</t>
+          <t>https://www.nagpurtoday.in/government-benefits-will-reach-every-citizen-revenue-minister-chandrashekhar-bawankules-determination/01231556</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/chandrasekhar-bawankule-felicitation-by-tuljapur-drugs-case-accused-sparks-backlash-9041887</t>
+          <t>https://www.mahasamvad.in/151939/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/30/revenue-department-to-implement-revenue-week-in-the-state-from-august-1.html</t>
+          <t>https://mahasamvad.in/176956/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/159732/</t>
+          <t>https://marathi.ndtv.com/politics/chandrasekhar-bawankule-felicitation-by-tuljapur-drugs-case-accused-sparks-backlash-9041887</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/151475/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/30/revenue-department-to-implement-revenue-week-in-the-state-from-august-1.html</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163322/</t>
+          <t>https://mahasamvad.in/159732/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/166742/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/4/revenue-minister-chandrashekhar-bawankule-makes-announcement-in-assembly-hints-at-action-against-eight-stamp-d.html</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/4/revenue-minister-chandrashekhar-bawankule-makes-announcement-in-assembly-hints-at-action-against-eight-stamp-d.html</t>
+          <t>https://mahasamvad.in/151475/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/bjp-does-not-do-low-level-acts-chandrashekhar-bawankule-rejects-allegations-in-praveen-gaikwad-attack-case-278013/amp/</t>
+          <t>https://mahasamvad.in/163322/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/revenue-minister-bawankule-announces-relaxation-fragmentation-law-50-lakh-farmers-relief-277582/amp/</t>
+          <t>https://www.mahasamvad.in/166742/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/166052/</t>
+          <t>https://www.etvbharat.com/mr/!state/minister-chandrashekhar-bawankule-criticizes-sharad-pawar-mandal-yatra-maharashtra-news-mhs25081000427</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/165886/</t>
+          <t>https://mahasamvad.in/174605/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/6/23/new-law-to-be-introduced-in-monsoon-session-said-chandrashekhar-bawankule.html</t>
+          <t>https://www.etvbharat.com/mr/!state/minister-chandrashekhar-bawankule-appeals-to-the-opposition-not-to-politicize-the-mumbai-train-accident-maharashtra-news-mhs25060906405</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/stamp-duty-of-rs-500-waived-for-various-certificates-including-caste-verification-income-certificate-chandrashekhar-bawankule-263813/</t>
+          <t>https://thefocusindia.com/maharashtra-news/revenue-minister-bawankule-announces-relaxation-fragmentation-law-50-lakh-farmers-relief-277582/amp/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/chandrashekhar-bawankule-assures-of-farmers-loan-waivers-after-proper-survey/articleshow/123184635.cms</t>
+          <t>https://mahasamvad.in/166052/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/buldana/revenue-minister-chandrashekhar-bawankule-fake-calling-and-ccheated-fraud-with-farmer/articleshow/123344845.cms</t>
+          <t>https://www.etvbharat.com/mr/!state/no-new-districts-will-be-created-in-the-state-for-the-time-being-says-revenue-minister-chandrashekhar-bawankule-maharashtra-news-mhs25012302825</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/22/revenue-department-to-implement-national-leader-to-father-of-the-nation-campaign-revenue-minister-chandrashekh.html</t>
+          <t>https://mahasamvad.in/165886/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176506/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/6/23/new-law-to-be-introduced-in-monsoon-session-said-chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-monsoon-session-2025-public-safety-bill-to-be-introduced-in-session-chandrashekhar-bawankule-80142</t>
+          <t>https://www.loksatta.com/pune/revenue-minister-chandrashekhar-bawankule-orders-action-against-guilty-officials-within-fifteen-days-pune-print-news-amy-95-5135372/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/prahar-activists-aggressive-against-chandrashekhar-bawankule-for-anti-farmer-remark-zws-70-5279759/</t>
+          <t>https://thefocusindia.com/maharashtra-news/stamp-duty-of-rs-500-waived-for-various-certificates-including-caste-verification-income-certificate-chandrashekhar-bawankule-263813/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nagpur/chandrashekhar-bawankule-order-to-file-fir-against-those-who-misuse-his-name-nagpur-crime-news-1375138</t>
+          <t>https://mahasamvad.in/173545/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/2/3/One-lakh-94-thousand-special-executive-officers-will-be-appointed-across-the-state-By-Chandrashekhar-Bawankule.html</t>
+          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-farmers-loan-waivers-farmers-who-drive-around-in-mercedes-lay-out-farm-house-1366570</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/165925/</t>
+          <t>https://marathi.abplive.com/news/dharashiv/revenue-minister-chandrashekhar-bawankule-publicly-felicitated-by-accused-out-on-bail-in-drug-case-1375621</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172338/</t>
+          <t>https://mahasamvad.in/163978/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/161979/</t>
+          <t>https://www.nagpurtoday.in/reconstruction-of-vidarbha-bhoodan-yagna-mandal-to-take-place-revenue-minister-chandrashekhar-bawankules-directive/02071130</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/crime/sambhajinagar-farmer-demand-money-hello-chandrashekhar-bawankule-pa-is-speaking-qr-sent-to-farmer-in-complaint-to-police-1377664</t>
+          <t>https://www.mahasamvad.in/173517/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-on-action-mode-against-sand-mafia-said-take-action-under-the-mpda-act-against-those-involved-in-illegal-sand-mining-and-transportation-in-buldhana-1376122</t>
+          <t>https://mahasamvad.in/169614/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/167615/</t>
+          <t>https://news18marathi.com/agriculture/revenue-department-under-leadership-revenue-minister-chandrashekhar-bawankule-has-taken-18-major-decisions-1413141.html</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/2/3/Chandrashekhar-Bawankule-brought-satisfaction-to-the-Mihan-project-victims.html</t>
+          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-on-stamp-paper-demand-in-e-service-centers-in-government-offices-is-illegal-information-from-revenue-minister-chandrashekhar-bawankule-maharashtra-politics-maharashtra-marathi-news-1362983</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/revenue-minister-chandrashekhar-bawankule-attend-district-planning-committee-meeting-in-solapur-district-884995.html</t>
+          <t>https://www.nagpurtoday.in/revenue-minister-and-guardian-minister-shri-taken-by-chandrasekhar-bawankule/06081251</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/171014/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B9%E0%A5%85%E0%A4%B2-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%B8-%E0%A4%B9%E0%A5%87%E0%A4%AC-%E0%A4%82%E0%A4%9A-%E0%A4%AA-%E0%A4%8F-%E0%A4%AC-%E0%A4%B2%E0%A4%A4-%E0%A4%AF-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%9C-%E0%A4%A8%E0%A4%97%E0%A4%B0%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%B2-%E0%A4%95%E0%A5%8D%E0%A4%AF%E0%A5%82%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%A0%E0%A4%B5%E0%A4%B2-%E0%A4%AA%E0%A5%88%E0%A4%B6-%E0%A4%82%E0%A4%9A-%E0%A4%AE-%E0%A4%97%E0%A4%A3-%E0%A4%AA-%E0%A4%B2-%E0%A4%B8-%E0%A4%A4-%E0%A4%A4%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%B0/ar-AA1KFEz1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/158981/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/2/3/One-lakh-94-thousand-special-executive-officers-will-be-appointed-across-the-state-By-Chandrashekhar-Bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrashekhar-bawankule-announcement-now-silt-soil-mud-stones-will-be-available-for-free-maharashtra-government-s-big-decision-1352610</t>
+          <t>https://mahasamvad.in/165925/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-news-revenue-minister-warns-of-strict-action-against-illegal-sand-mining-now-joint-action-by-police-and-revenue-dept-83488</t>
+          <t>https://mahasamvad.in/163171/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/151943/</t>
+          <t>https://mahasamvad.in/161979/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160518/</t>
+          <t>https://mahasamvad.in/161181/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/157532/</t>
+          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-on-action-mode-against-sand-mafia-said-take-action-under-the-mpda-act-against-those-involved-in-illegal-sand-mining-and-transportation-in-buldhana-1376122</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173912/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/2/3/Chandrashekhar-Bawankule-brought-satisfaction-to-the-Mihan-project-victims.html</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172002/</t>
+          <t>https://mahasamvad.in/167615/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/165774/</t>
+          <t>https://mahasamvad.in/158981/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/3/5/No-stamp-duty-for-affidavit-in-Maharashtra-Chandrashekhar-Bawankule.html</t>
+          <t>https://mahasamvad.in/171014/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163853/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-news-revenue-minister-warns-of-strict-action-against-illegal-sand-mining-now-joint-action-by-police-and-revenue-dept-83488</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174409/</t>
+          <t>https://mahasamvad.in/151943/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/164965/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/chandrashekhar-bawankule-assures-of-farmers-loan-waivers-after-proper-survey/articleshow/123184635.cms</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160286/</t>
+          <t>https://mahasamvad.in/172338/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174273/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/buldana/revenue-minister-chandrashekhar-bawankule-fake-calling-and-ccheated-fraud-with-farmer/articleshow/123344845.cms</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nashik/chandrashekhar-bawankule-big-statement-regarding-sudhakar-badgujar-entry-into-bjp-nashik-maharashtra-politics-marathi-news-1362706</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/22/revenue-department-to-implement-national-leader-to-father-of-the-nation-campaign-revenue-minister-chandrashekh.html</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
+          <t>https://mahasamvad.in/176506/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/31/congress-committed-an-unforgivable-crime-political-defamation-conspiracy-exposed-minister-chandrashekhar-bawan.html</t>
+          <t>https://www.loksatta.com/nagpur/prahar-activists-aggressive-against-chandrashekhar-bawankule-for-anti-farmer-remark-zws-70-5279759/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/revenue-minister-chandrashekhar-bawankule-informed-that-the-state-new-sand-policy-will-be-announced-soon-7948210</t>
+          <t>https://mahasamvad.in/160518/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/5/supreme-courts-decision-provides-justice-to-obcs-chandrashekhar-bawankule.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/will-action-be-taken-against-ranjitsinh-mohite-patil-for-anti-party-activities-bjp-state-presidents-bawankule-suggestive-statement-vd83</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168528/</t>
+          <t>https://mahasamvad.in/172002/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175785/</t>
+          <t>https://mahasamvad.in/165774/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-revenue-minister-chandrashekhar-bawankule-big-decision-students-stamp-duty-on-academic-affidavit-waived/articleshow/118747673.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/3/5/No-stamp-duty-for-affidavit-in-Maharashtra-Chandrashekhar-Bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176289/</t>
+          <t>https://mahasamvad.in/173912/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrashekhar-bawankule-says-opportunities-for-local-karyakarta-even-before-elections-appointment-of-1-lakh-94-thousand-seo-in-the-state-what-are-the-criteria-1342316</t>
+          <t>https://mahasamvad.in/172804/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/municipal-elections-in-april-may-information-from-bjp-state-president-chandrashekhar-bawankule-pune-print-news-apk-13-mrj-95-4895839/</t>
+          <t>https://mahasamvad.in/163853/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/business/real-estate-news/date-fixed-for-implementation-of-one-state-one-registration/articleshow/119943476.cms</t>
+          <t>https://mahasamvad.in/174409/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/jalna/farmers-flood-relief-funds-embezzled-in-jalna-revenue-minister-bawankule-orders-major-action-1375925</t>
+          <t>https://mahasamvad.in/164965/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/the-revenue-ministry-will-make-changes-to-the-rules-for-farm-roads-1317903.html</t>
+          <t>https://www.etvbharat.com/mr/!state/welcome-raj-thackeray-stance-in-hindi-context-chandrashekhar-bawankule-maharashtra-news-mhs25080403750</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/government-approved-1660-petrol-pumps-in-maharashtra-single-window-system-starts-know-how-to-apply-7822420</t>
+          <t>https://mahasamvad.in/160286/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/maharashtra-revenue-department-has-taken-5-major-decisions-marathi-agriculture-news-1401406.html</t>
+          <t>https://deshdoot.com/demand-for-stamp-paper-for-educational-certificates-and-affidavits-is-illegal/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-government-planning-for-new-gunthewari-law-will-introduce-bill-in-assembly-monsoon-session/articleshow/122052149.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-bawankule-kadu-row-revenue-minister-and-former-mla-clash-over-disabled-allowance-hike-and-farmers-issues-accusations-of-drama-exchanged-1374782</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/31/congress-committed-an-unforgivable-crime-political-defamation-conspiracy-exposed-minister-chandrashekhar-bawan.html</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/minister-chandrashekhar-bawankule-big-statement-about-farmers-loan-waiver/articleshow/123323729.cms</t>
+          <t>https://marathi.ndtv.com/politics/revenue-minister-chandrashekhar-bawankule-informed-that-the-state-new-sand-policy-will-be-announced-soon-7948210</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/162383/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/5/supreme-courts-decision-provides-justice-to-obcs-chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160516/</t>
+          <t>https://mahasamvad.in/174273/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170666/</t>
+          <t>https://mahasamvad.in/168528/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/31/62-officers-promoted-to-the-rank-of-naib-tehsildar-on-the-eve-of-revenue-day.html</t>
+          <t>https://mahasamvad.in/175785/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/164382/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-revenue-minister-chandrashekhar-bawankule-big-decision-students-stamp-duty-on-academic-affidavit-waived/articleshow/118747673.cms</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/159369/</t>
+          <t>https://mahasamvad.in/176289/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-leader-chandrashekhar-bawankule-explanation-on-viral-video-of-eknath-shinde/articleshow/122165237.cms</t>
+          <t>https://mahasamvad.in/172416/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/167572/</t>
+          <t>https://mahasamvad.in/174314/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160368/</t>
+          <t>https://news18marathi.com/maharashtra/dharashiv-tuljapur-drugs-case-main-accused-vinod-pintu-gangane-felicitates-minister-chandrashekhar-bawankule-1452942.html</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/strict-rules-now-for-birth-and-death-certificates-change-in-law-important-decision-of-revenue-minister-due-to-bangladeshi-in-mumbai-1348753</t>
+          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/chhatrapati-sambhajinagar-farmer-cheated-of-rs-4k-by-fake-call-claiming-to-be-chandrashekhar-bawankule-pa/articleshow/123360446.cms</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/5/case-registered-against-those-who-harassed-the-police-in-the-name-of-guardian-minister-bawankule.html</t>
+          <t>https://mahasamvad.in/161434/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/stamp-duty-of-500-on-affidavits-for-government-offices-waived-relief-for-lakhs-of-students-chanrashekhar-bavankule-decision-1347510</t>
+          <t>https://www.etvbharat.com/mr/!state/mla-shweta-mahales-devabhau-ladki-bahin-patsanstha-inaugurated-by-minister-chandrashekhar-bawankule-occasion-of-raksha-bandhan-maharashtra-news-mhs25080903763</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/attack-on-praveen-gaikwad-of-sambhaji-brigade-what-did-chandrashekhar-bawankule-say-ssb-93-5226647/</t>
+          <t>https://mahasamvad.in/174926/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/what-action-will-the-revenue-department-take-during-the-campaign-from-august-1-to-7-1447199.html</t>
+          <t>https://www.nagpurtoday.in/dont-politicize-pahalgam-attack-stand-with-the-government-chandrashekhar-bawankule-appeals/04232052</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/chandrashekhar-bawankule-revenue-department-setup-committee-fragmentation-of-land-report-will-came-in-15-days-1370434</t>
+          <t>https://mahasamvad.in/176273/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-land-measurement-maharashtra-government-fixed-fee-for-land-measurement-at-rs-200-benefit-to-farmers-for-division-of-land-73753</t>
+          <t>https://mahasamvad.in/169968/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/maharashtra-will-cancel-fake-birth-certificates-issued-to-illegal-bangladeshi-residents-says-minister-bawankule/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/minister-chandrashekhar-bawankule-big-statement-about-farmers-loan-waiver/articleshow/123323729.cms</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/159853/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/31/62-officers-promoted-to-the-rank-of-naib-tehsildar-on-the-eve-of-revenue-day.html</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/devendra-fadnavis-will-remain-chief-minister-till-2034-said-by-chandrakant-bawankule-eknath-shinde-reaction-on-statement/articleshow/120636714.cms</t>
+          <t>https://mahasamvad.in/170666/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/bjp-has-no-link-with-attack-on-sambhaji-brigade-leader-minister-bawankule-3628848</t>
+          <t>https://mahasamvad.in/159369/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/empty-out-the-congress-chandrashekhar-bawankule-tells-partymen-101746471227225.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-leader-chandrashekhar-bawankule-explanation-on-viral-video-of-eknath-shinde/articleshow/122165237.cms</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-revenue-minister-chandrashekhar-bawankule-implements-nagpur-model-for-farm-road-construction/ar-AA1yyeMo</t>
+          <t>https://mahasamvad.in/162383/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-urges-restraint-on-political-street-fights/articleshow/122819890.cms</t>
+          <t>https://mahasamvad.in/160516/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/sanjay-raut-can-not-decide-modis-tenure-maharashtra-bjp-president-chandrashekhar-bawankule-on-pms-retirement-23510710</t>
+          <t>https://mahasamvad.in/167572/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/maharashtra-minister-apologises-to-b-r-gavai-chief-justice-over-protocol-lapse-in-mumbai-8456034</t>
+          <t>https://mahasamvad.in/160368/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/govt-firm-on-purandar-airport-project-chandrashekhar-bawankule-101746466486230.html</t>
+          <t>https://mahasamvad.in/164382/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/maharashtra-bjp-chief-chandrashekhar-bawankule-urges-party-workers-to-empty-congress-induct-its-leaders-8334573</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/5/case-registered-against-those-who-harassed-the-police-in-the-name-of-guardian-minister-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-should-check-voter-lists-now-quips-chandrashekhar-bawankule/articleshow/123351307.cms</t>
+          <t>https://www.nagpurtoday.in/government-employees-will-be-threatened-those-who-run-away-from-the-office-are-no-longer-safe-directed-by-chandrasekhar-bawankule/04241205</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/confusion-in-bjp-over-induction-of-ex-sena-ubt-leader-bawankule-unaware-of-move-3589681</t>
+          <t>https://marathi.abplive.com/news/maharashtra/stamp-duty-of-500-on-affidavits-for-government-offices-waived-relief-for-lakhs-of-students-chanrashekhar-bavankule-decision-1347510</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/devendra-fadnavis-to-remain-maharashtra-cm-till-2034-says-chandrashekhar-bawankule-23527680</t>
+          <t>https://news18marathi.com/agriculture/what-action-will-the-revenue-department-take-during-the-campaign-from-august-1-to-7-1447199.html</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bawankule-meets-sulking-shirsat-amid-funds-diversion-controversy-101749670372918.html</t>
+          <t>https://www.etvbharat.com/mr/!state/sambhaji-brigade-pravin-gaikwad-press-conference-pune-alleges-devendra-fadnavis-and-chandrashekhar-bawankule-supports-deepak-kate-maharashtra-news-mhs25071605756</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/chandrashekhar-bawankule-welcomes-chhagan-bhujbals-induction-into-maharashtra-cabinet-calls-it-a-boost-for-govt-23547724</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-land-measurement-maharashtra-government-fixed-fee-for-land-measurement-at-rs-200-benefit-to-farmers-for-division-of-land-73753</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/no-75-year-age-rule-in-bjp-sanjay-raut-can-not-decide-modis-tenure-says-chandrashekhar-bawankule-3472151</t>
+          <t>https://www.mymahanagar.com/maharashtra/maharashtra-will-cancel-fake-birth-certificates-issued-to-illegal-bangladeshi-residents-says-minister-bawankule/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-plans-to-reform-modernise-revenue-dept-by-2029/articleshow/123067789.cms</t>
+          <t>https://marathi.ndtv.com/maharashtra/government-approved-1660-petrol-pumps-in-maharashtra-single-window-system-starts-know-how-to-apply-7822420</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-orders-crackdown-on-illegal-mining-craters-after-child-deaths/articleshow/122393943.cms</t>
+          <t>https://mahasamvad.in/159853/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
+          <t>https://marathi.indiatimes.com/business/real-estate-news/date-fixed-for-implementation-of-one-state-one-registration/articleshow/119943476.cms</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/chandrashekhar-bawankule-denies-making-calls-to-protect-deepak-kate-amid-solapur-assault-row-23584795</t>
+          <t>https://www.deccanherald.com/india/maharashtra/bjp-has-no-link-with-attack-on-sambhaji-brigade-leader-minister-bawankule-3628848</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/bawankule-assures-dialogue-with-farmers-amid-purandar-airport-land-acquisition-protests-101746380590787.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/empty-out-the-congress-chandrashekhar-bawankule-tells-partymen-101746471227225.html</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/no-salary-for-employees-without-face-app-attendance-says-maharashtra-revenue-minister-chandrashekhar-bawankule-2025-07-23-1000274</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-revenue-minister-chandrashekhar-bawankule-implements-nagpur-model-for-farm-road-construction/ar-AA1yyeMo</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/bawankule-urges-bjp-workers-to-induct-congress-leaders-empty-the-party-3524952</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-urges-restraint-on-political-street-fights/articleshow/122819890.cms</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-to-head-panel-on-farm-roads/articleshow/123103819.cms</t>
+          <t>https://www.ndtv.com/india-news/maharashtra-bjp-chief-chandrashekhar-bawankule-urges-party-workers-to-empty-congress-induct-its-leaders-8334573</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/infra-works-delay-bawankule-slams-nmc-over-non-utilisation-of-rs310cr/articleshow/122410221.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/govt-firm-on-purandar-airport-project-chandrashekhar-bawankule-101746466486230.html</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/bawankule-slams-pune-land-records-dept-hints-sit-probe-into-illegal-ownership-changes-101746467026560.html</t>
+          <t>https://www.ndtv.com/india-news/maharashtra-minister-apologises-to-b-r-gavai-chief-justice-over-protocol-lapse-in-mumbai-8456034</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-state-chief-asks-dhas-munde-to-bury-the-hatchet-101739560133748.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-should-check-voter-lists-now-quips-chandrashekhar-bawankule/articleshow/123351307.cms</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticizes-uddhav-for-opposing-maharashtra-security-bill/articleshow/122410846.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/confusion-in-bjp-over-induction-of-ex-sena-ubt-leader-bawankule-unaware-of-move-3589681</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/maharashtra-to-relax-fragmentation-law-sop-soon-bawankule/articleshow/122458237.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/devendra-fadnavis-to-remain-maharashtra-cm-till-2034-says-chandrashekhar-bawankule-23527680</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-congress-backs-rahul-gandhis-poll-rigging-allegations-demands-fadnavis-resignation-3601125</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bawankule-meets-sulking-shirsat-amid-funds-diversion-controversy-101749670372918.html</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/another-blow-to-shinde-bawankule-slams-cidco-over-naina-planning-101756150390930.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/our-caste-is-bjp-we-serve-the-nation-gadkari/articleshow/120044597.cms</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/no-blanket-farm-loan-waiver-only-the-most-distressed-to-get-it-bawankule/articleshow/123195407.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/chandrashekhar-bawankule-welcomes-chhagan-bhujbals-induction-into-maharashtra-cabinet-calls-it-a-boost-for-govt-23547724</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/no-75-year-retirement-rule-in-bjp-maharashtra-chief-counters-sanjay-raut-s-remark-on-modi-101743498262416.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/no-75-year-age-rule-in-bjp-sanjay-raut-can-not-decide-modis-tenure-says-chandrashekhar-bawankule-3472151</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/politics/india-bloc-disintegrating-as-it-doesn-t-have-ideology-bjp-s-bawankule-125011300459_1.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/ravindra-chavan-set-to-head-maha-bjp-says-bawankule/articleshow/121504377.cms</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/no-biometric-attendance-system-no-salary-for-amravati-state-govt-employees-bawankule/articleshow/122789185.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/maharashtra-ministers-reach-agreement-on-key-welfare-issues-after-bawankule-led-talks/articleshow/122256747.cms</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/politics/nagpur-violence-bjp-s-bawankule-calls-for-peace-as-police-detain-over-20-125031800026_1.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-plans-to-reform-modernise-revenue-dept-by-2029/articleshow/123067789.cms</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/bawankule-urges-bjp-cadre-to-bring-in-congress-leaders-empty-the-party-101746466905147.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/state-to-soon-have-a-new-artificial-sand-policy-bawankule/articleshow/120441502.cms</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/bawankule-faces-flak-for-sharing-stage-with-accused-in-tuljapur-drugs-case/articleshow/123196303.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-hints-at-major-land-law-reform-amend-plot-size-restrictions/articleshow/122032769.cms</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://realty.economictimes.indiatimes.com/news/allied-industries/free-sand-royalty-receipts-to-be-delivered-to-beneficiaries-of-housing-schemes-maharashtra-revenue-minister/121176284</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/the-nomadic-community-will-get-ration-anywhere-in-the-state-says-revenue-minister-chandrashekhar-bawankule/articleshow/121208499.cms</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/govt-panel-to-conduct-survey-to-identify-farmers-in-need-of-loan-waiver-in-maharashtra-says-bjp-minister-bawankule/articleshow/123169142.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/maharashtra-special-public-security-bill-2024-tabled-to-tackle-urban-naxalism-8852342</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/macau-jibe-to-advt-row-cong-bjp-maha-chiefs-in-war-of-words/articleshow/120529370.cms</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/ravindra-chavan-to-be-new-bjp-chief-for-maharashtra-3609432</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/saamanas-writings-are-damaging-uddhav-says-bawankule-amid-row-over-phule-comments/articleshow/120289982.cms</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/6/3-booked-for-threatening-cops-using-name-of-bawankule.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/chandrashekhar-bawankule-denies-making-calls-to-protect-deepak-kate-amid-solapur-assault-row-23584795</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-calls-rahul-gandhis-caste-census-push-too-late-to-matter/articleshow/122925629.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/bawankule-assures-dialogue-with-farmers-amid-purandar-airport-land-acquisition-protests-101746380590787.html</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/part-of-maharashtras-tradition-chandrashekhar-bawankule-responds-to-uddhav-thackerays-praise-for-cm-fadnavis20250723103612</t>
+          <t>https://www.indiatvnews.com/maharashtra/no-salary-for-employees-without-face-app-attendance-says-maharashtra-revenue-minister-chandrashekhar-bawankule-2025-07-23-1000274</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/no-one-will-dare-maharashtra-plans-tough-law-against-religious-conversions-revenue-minister-tells-assembly-uike-pledges-to-bring-converted-tribals-back/articleshow/122363837.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-pushes-for-speedy-execution-of-pench-irri-schemes/articleshow/120215813.cms</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-govt-to-bring-strict-anti-conversion-law-minister-3622288</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/infra-works-delay-bawankule-slams-nmc-over-non-utilisation-of-rs310cr/articleshow/122410221.cms</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/10-crore-tree-plantation-drive-a-shared-responsbility-reiterates-bawankule/articleshow/122423491.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-quashes-rift-rumours-asserts-mahayuti-will-contest-local-polls-unitedly/articleshow/121448703.cms</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/india/politics/maharashtra-bjp-chief-chandrashekhar-bawankule-congress-remark-poaching-leaders-controversy-19599239.htm</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/bawankule-slams-pune-land-records-dept-hints-sit-probe-into-illegal-ownership-changes-101746467026560.html</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/maharashtra-cabinet-reshuffle-buzz-final-decision-rests-with-cm-fadnavis-says-bawankule-101753525179967.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/bawankule-asks-for-alternatives-as-meeting-with-farmers-over-purandar-airport-ends-in-stalemate/articleshow/120909800.cms</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/maha-govt-plans-new-land-acquisition-rules-to-speed-up-projects-assure-farmers-fair-compensation/articleshow/123144329.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-state-chief-asks-dhas-munde-to-bury-the-hatchet-101739560133748.html</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-assures-timely-relief-for-rain-hit-farmers-as-per-norms/articleshow/120074385.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/maharashtra-to-relax-fragmentation-law-sop-soon-bawankule/articleshow/122458237.cms</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-hits-back-at-uddhav-calls-his-marathi-stand-political-drama-ahead-of-polls/07051714</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-congress-backs-rahul-gandhis-poll-rigging-allegations-demands-fadnavis-resignation-3601125</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/08/05/nagpur-case-filed-against-three-for-misusing-minister-chandrashekhar-bawankules-name-to-intimidate-police-at-friendship-day-party/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/who-reads-saamana-who-listens-to-them-asks-bawankule/articleshow/121541164.cms</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/rahul-gandhis-vote-theft-claims-are-baseless-childish-chandrashekhar-bawankule-23588752</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/another-blow-to-shinde-bawankule-slams-cidco-over-naina-planning-101756150390930.html</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ladki-bahin-gets-336cr-from-tribal-dept-min-denies/articleshow/121385494.cms</t>
+          <t>https://www.business-standard.com/politics/india-bloc-disintegrating-as-it-doesn-t-have-ideology-bjp-s-bawankule-125011300459_1.html</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-meets-protesting-bachchu-kadu-cong-backs-his-stir/articleshow/121836362.cms</t>
+          <t>https://www.hindustantimes.com/india-news/no-75-year-retirement-rule-in-bjp-maharashtra-chief-counters-sanjay-raut-s-remark-on-modi-101743498262416.html</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/needy-farmers-to-get-loan-waiver-not-those-building-farmhouses-bungalows-minister-bawankule-3683575</t>
+          <t>https://www.business-standard.com/politics/nagpur-violence-bjp-s-bawankule-calls-for-peace-as-police-detain-over-20-125031800026_1.html</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/farmers-demand-land-return-from-reliance-sez-bawankule-seeks-report/24555620250403</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-takes-stock-of-damage-caused-due-to-unseasonal-rain/articleshow/121580211.cms</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/chandrashekhar-bawankule-welcomes-ncps-chhagan-bhujbal-in-maharashtra-cabinet-calls-it-a-boost-for-govt20250520094044</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-probe-illegal-transfer-of-1-628-land-parcels-to-nontribals-101752087826955.html</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-promises-sop-in-3-months-to-resolve-zudpi-jungle-land-issue-in-vidarbha/articleshow/122394160.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/bawankule-urges-bjp-cadre-to-bring-in-congress-leaders-empty-the-party-101746466905147.html</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/pune-dist-admin-to-meet-villagers-on-purandar-airport-next-week-101747166217162.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/raj-thackeray-uddhav-thackeray-victory-rally-no-traffic-diversions-for-sena-mns-rally-23583195</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-to-appoint-rss-workers-as-pas-to-its-ministers-101737571872713.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-directs-nmc-to-repair-roads-immediately/articleshow/121893777.cms</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/velhe-taluka-in-pune-district-renamed-as-rajgad-announces-maharashtra-minister-bawankule-3691509</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-warns-against-lapses-in-koradi-textile-project/articleshow/122212627.cms</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/gym-owner-faces-case-for-online-content-against-bawankule/articleshow/123395126.cms</t>
+          <t>https://www.ndtv.com/india-news/maharashtra-special-public-security-bill-2024-tabled-to-tackle-urban-naxalism-8852342</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-to-allow-hoardings-on-vacant-land-owned-by-govt-bawankule-101750872010984.html</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/bawankule-faces-flak-for-sharing-stage-with-accused-in-tuljapur-drugs-case/articleshow/123196303.cms</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/50-of-bhandara-city-located-on-nazul-land-govt-to-regularize-these-properties-bawankule/articleshow/123103215.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/clear-pending-water-projects-on-priority-bawankule/articleshow/122077229.cms</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-to-enact-law-against-religious-conversions-demolish-illegal-churches-in-tribal-districts-101752088546524.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/no-one-will-dare-maharashtra-plans-tough-law-against-religious-conversions-revenue-minister-tells-assembly-uike-pledges-to-bring-converted-tribals-back/articleshow/122363837.cms</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/act-against-illegal-plotting-mining-in-yeolewadi-kondhwa-katraj-areas-bawankule-101748459992922.html</t>
+          <t>https://www.aninews.in/news/national/general-news/part-of-maharashtras-tradition-chandrashekhar-bawankule-responds-to-uddhav-thackerays-praise-for-cm-fadnavis20250723103612</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/hc-acquits-all-2006-train-blasts-accused-maharashtra-govt-will-study-order-says-chandrashekhar-bawankule-23585741</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-govt-to-bring-strict-anti-conversion-law-minister-3622288</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/maharashtra-govt-to-relax-land-fragmentation-law-subdivided-plots-up-to-jan-1-to-become-legal/articleshow/122343682.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-assures-timely-relief-for-rain-hit-farmers-as-per-norms/articleshow/120074385.cms</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/maharashtra-govt-to-legalise-subdivided-land-plots-formed-till-jan-1-2025-125070900961_1.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/10-crore-tree-plantation-drive-a-shared-responsbility-reiterates-bawankule/articleshow/122423491.cms</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/file-criminal-cases-against-those-blocking-farm-roads-bawankule/02071333</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-sets-july-15-deadline-for-document-distribution-to-all-dnts/articleshow/121347284.cms</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/short-videos/trending/vaibhav-naik-news-uddhav-thackeray-s-shiladhar-chandrashekhar-bawankule-meets-n18s-1070283.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-tells-every-dept-to-set-up-nurseries-on-its-land/articleshow/122410853.cms</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-fires-back-at-rahul-over-voter-surge-claim-was-there-a-scam-in-2009-too/06071145</t>
+          <t>https://www.cnbctv18.com/india/politics/maharashtra-bjp-chief-chandrashekhar-bawankule-congress-remark-poaching-leaders-controversy-19599239.htm</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://realty.economictimes.indiatimes.com/news/infrastructure/maharashtra-government-to-begin-campaign-from-april-1-to-update-7/12-land-title-records/119479129</t>
+          <t>https://www.nagpurtoday.in/bawankule-hits-back-at-uddhav-calls-his-marathi-stand-political-drama-ahead-of-polls/07051714</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-tightens-rules-for-birth-death-certificates-for-foreign-nationals-23498903</t>
+          <t>https://thelivenagpur.com/2025/08/05/nagpur-case-filed-against-three-for-misusing-minister-chandrashekhar-bawankules-name-to-intimidate-police-at-friendship-day-party/</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/maharashtra-govt-to-have-single-window-system-for-approval-process-of-1660-petrol-pumps-enn25022807370</t>
+          <t>https://m.economictimes.com/news/india/maharashtra-govt-starts-second-phase-of-land-title-updating/articleshow/120827478.cms</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/modi-is-not-a-show-he-is-a-roadshow-of-development-bawankule-slams-rahul/07261259</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/rahul-gandhis-vote-theft-claims-are-baseless-childish-chandrashekhar-bawankule-23588752</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/now-sand-mafias-to-face-criminal-charges-not-just-fines-bawankule/07181631</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ladki-bahin-gets-336cr-from-tribal-dept-min-denies/articleshow/121385494.cms</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/rahul-gandhis-remark-on-govts-foreign-policy-unfortunate-maharashtra-bjp-chief-bawankule20250524112058</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-meets-protesting-bachchu-kadu-cong-backs-his-stir/articleshow/121836362.cms</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/are-congress-leaders-trying-to-exonerate-terrorists-maharashtra-bjp-president-on-wadettiwars-remark20250429084410/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/needy-farmers-to-get-loan-waiver-not-those-building-farmhouses-bungalows-minister-bawankule-3683575</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-slams-uddhav-thackeray-calls-him-leader-of-aurangzeb-fan-club/03281015</t>
+          <t>https://www.nagpurtoday.in/bawankule-hits-back-at-raut-over-his-outburst-against-sharad-pawar/02131733</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankules-sharp-attack-on-uddhav-rakes-up-rs-100-crore-extortion-case/08111455</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-promises-sop-in-3-months-to-resolve-zudpi-jungle-land-issue-in-vidarbha/articleshow/122394160.cms</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/article/maharashtra-launches-one-district-one-registration-scheme-for-property-23535200</t>
+          <t>https://aninews.in/news/national/politics/chandrashekhar-bawankule-welcomes-ncps-chhagan-bhujbal-in-maharashtra-cabinet-calls-it-a-boost-for-govt20250520094044/</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/maharashtra-govt-forms-sit-to-probe-delayed-birth-death-certificates-125012500183_1.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/shinde-mahajan-were-in-kashmir-to-serve-not-score-points-bawankule/articleshow/120629012.cms</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/08/10/guardian-minister-bawankule-orders-high-level-inquiry-into-koradi-incident/</t>
+          <t>https://www.nagpurtoday.in/rahul-gandhi-lacks-mentality-to-accept-defeat-bawankule/02071649</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-minister-bawankule-asks-bmc-to-halt-its-demolition-drive-in-north-mumbai-till-ganeshotsav-23590378</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/in-direct-public-outreach-bawankule-holds-3rd-janata-darbar-in-a-month/articleshow/121553803.cms</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/friendship-day-party-controversy-vedant-chhabria-says-sorry-to-bawankule-in-exclusive-nagpur-today-video/08090717</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-to-enact-law-against-religious-conversions-demolish-illegal-churches-in-tribal-districts-101752088546524.html</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/resolve-citizens-grievances-promptly-and-effectively-bawankule-directs-officials/06021151</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/social-media-influencers-on-radar-strict-monitoring-for-ram-navami-bawankule/articleshow/120024432.cms</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/7/29/noted-author-shubhangi-bhadbhade-passes-away.html</t>
+          <t>https://m.economictimes.com/news/india/maharashtra-govt-to-relax-land-fragmentation-law-subdivided-plots-up-to-jan-1-to-become-legal/articleshow/122343682.cms</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://timesproperty.com/news/post/maha-govt-to-launch-vertical-7-12-document-system-for-multi-floor-homes-blid10102</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/divisional-revenue-commissionerate-to-be-set-up-in-latur-or-nanded-chandrashekhar-bawankule-23489288</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/rahul-gandhi-is-troubled-by-electoral-defeats-maharashtra-bjp-chief-on-election-rigging-allegations20250607234624/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/government-to-remove-non-agricultural-land-use-requirement-for-industries-101738952544368.html</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/07/bom21-mh-farmers-loan-waiver-bawankule.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/hc-acquits-all-2006-train-blasts-accused-maharashtra-govt-will-study-order-says-chandrashekhar-bawankule-23585741</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-slams-congress-for-questioning-operation-sindoor/07291623</t>
+          <t>https://telanganatoday.com/maharashtra-minister-declares-14-villages-from-telangana-would-be-merged-with-chandrapur-district</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/the-constitution-is-the-backbone-of-indias-development-maharashtra-minister-bawankule-pays-tribute-to-dr-ambedkar-in-nagpur/04141639</t>
+          <t>https://www.aninews.in/news/national/general-news/rahul-gandhi-should-felicitate-pm-modi-openly-maharashtra-bjp-president-bawankule-on-centres-decision-for-caste-census20250501135229</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-cabinet-meet-ndas-vice-presidential-candidate-c-p-radhakrishnan-in-mumbai-23591080</t>
+          <t>https://www.business-standard.com/india-news/maharashtra-govt-to-legalise-subdivided-land-plots-formed-till-jan-1-2025-125070900961_1.html</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/nagpur-violence-bjps-bawankule-calls-for-peace-as-maharashtra-police-detain-over-2020250318003909/</t>
+          <t>https://www.nagpurtoday.in/file-criminal-cases-against-those-blocking-farm-roads-bawankule/02071333</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/maharashtra-urban-naxal-bill-opposition-raises-concerns-public-security-bill-2729057-2025-05-22</t>
+          <t>https://lokmat.news18.com/short-videos/trending/vaibhav-naik-news-uddhav-thackeray-s-shiladhar-chandrashekhar-bawankule-meets-n18s-1070283.html</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/west-nagpur-mla-thakre-exposes-pmay-scam-bawankule-asks-housing-minister-to-order-probe/06051215</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-approves-policy-for-promoting-artificial-sand-101747164656571.html</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/koradi-temple-gate-collapse-guardian-minister-orders-probe-assures-action/08101755</t>
+          <t>https://www.nagpurtoday.in/bawankule-fires-back-at-rahul-over-voter-surge-claim-was-there-a-scam-in-2009-too/06071145</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/05/14/kamptee-hospital-to-get-50-more-beds-6-acres-land-allotted-bawankule/</t>
+          <t>https://www.etvbharat.com/en/!state/maharashtra-govt-to-have-single-window-system-for-approval-process-of-1660-petrol-pumps-enn25022807370</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/drinking-water-crisis-in-nagpur-district-to-be-resolved-soon-bawankule/04261228</t>
+          <t>https://www.etvbharat.com/en/!state/maharashtra-govt-will-take-balanced-decision-on-temple-inam-land-issue-says-bawankule-enn25032407754</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-inspects-farm-access-road-in-katol-stresses-quality-execution/05311731</t>
+          <t>https://www.nagpurtoday.in/big-relief-for-students-citizens-bawankule-announces-waiver-of-rs-500-stamp-duty-for-affidavits/03051617</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.sarkaritel.com/maha-govt-to-launch-online-property-registration-from-may-1/</t>
+          <t>https://www.aninews.in/news/national/politics/rahul-gandhis-remark-on-govts-foreign-policy-unfortunate-maharashtra-bjp-chief-bawankule20250524112058</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/land-measurement-for-division-in-maharashtra-now-at-rs-200-23548697</t>
+          <t>https://thelivenagpur.com/2025/08/10/guardian-minister-bawankule-orders-high-level-inquiry-into-koradi-incident/</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/04/very-shameless-statement-chandrashekhar-bawankule-slams-vijay-wadettiwars-remark-on-pahalgam-attack/</t>
+          <t>https://www.nagpurtoday.in/bawankule-discusses-issue-of-encroachment-on-rural-roads/01211724</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://www.nagpurtrends.com/articles/central-jail-to-be-relocated-near-babhulkheda-says-bawankule-jE4hdD</t>
+          <t>https://timesproperty.com/news/post/maha-govt-to-launch-vertical-7-12-document-system-for-multi-floor-homes-blid10102</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-maharashtra-minister-bawankules-call-to-empty-congress-sparks-debate-clarifies-stance-amid-opposition-criticism/</t>
+          <t>https://www.sarkaritel.com/maha-govt-to-launch-online-property-registration-from-may-1/</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ravindra-chavan-set-to-head-maha-bjp-says-bawankule/articleshow/121504377.cms</t>
+          <t>https://www.moneycontrol.com/news/india/7-11-train-blasts-maharashtra-govt-will-study-acquittal-order-before-deciding-next-legal-step-13304293.html</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/state-to-soon-have-a-new-artificial-sand-policy-bawankule/articleshow/120441502.cms</t>
+          <t>https://www.thehitavada.com/Encyc/2025/1/28/Finally-Somalwada-underpass-to-be-inaugurated-today.html</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/our-caste-is-bjp-we-serve-the-nation-gadkari/articleshow/120044597.cms</t>
+          <t>https://www.cnbctv18.com/india/maharashtra-mandates-3-metre-width-for-farm-roads-other-rights-in-land-records-ws-l-19609629.htm</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/owners-willingly-giving-up-land-for-civic-projects-in-maharashtra-may-receive-additional-benefits-says-chandrashekhar-bawankule/articleshow/119555188.cms</t>
+          <t>https://thenewsmill.com/2025/04/very-shameless-statement-chandrashekhar-bawankule-slams-vijay-wadettiwars-remark-on-pahalgam-attack/</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-hints-at-major-land-law-reform-amend-plot-size-restrictions/articleshow/122032769.cms</t>
+          <t>https://www.nagpurtrends.com/articles/chandrashekhar-bawankule-to-unfurl-tricolour-at-nagpurs-republic-day-kG2xyj</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-pushes-for-speedy-execution-of-pench-irri-schemes/articleshow/120215813.cms</t>
+          <t>https://www.punekarnews.in/pune-maharashtra-minister-bawankules-call-to-empty-congress-sparks-debate-clarifies-stance-amid-opposition-criticism/</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-mahayuti-expansion-only-after-consensus-among-allies/articleshow/117496923.cms</t>
+          <t>https://www.punekarnews.in/pune-revenue-minister-chandrashekhar-bawankule-promises-best-compensation-for-purandar-airport-land-acquisition/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/maharashtra-ministers-reach-agreement-on-key-welfare-issues-after-bawankule-led-talks/articleshow/122256747.cms</t>
+          <t>https://www.punekarnews.in/pune-revenue-minister-chandrashekhar-bawankule-backs-purandar-airport-urges-farmers-to-voice-grievances-directly/</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/maharashtras-love-jihad-law-to-be-strictest-in-india-minister-chandrashekhar-bawankule/articleshow/118295093.cms</t>
+          <t>https://www.socialnews.xyz/?p=6725428</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-warns-against-lapses-in-koradi-textile-project/articleshow/122212627.cms</t>
+          <t>https://www.mypunepulse.com/pune-crackdown-ordered-on-illegal-plotting-and-mining-in-yeolewadi-kondhwa-and-katraj-minister-bawankule/</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/saamanas-writings-are-damaging-uddhav-says-bawankule-amid-row-over-phule-comments/articleshow/120289982.cms</t>
+          <t>https://timesofindia.indiatimes.com/entertainment/events/chandrashekhar-bawankules-initiative-brings-a-timeless-epic-to-life/articleshow/117122781.cms</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/the-nomadic-community-will-get-ration-anywhere-in-the-state-says-revenue-minister-chandrashekhar-bawankule/articleshow/121208499.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/functionaries-fret-as-bawankule-welcomes-members-from-oppn-parties/articleshow/121683858.cms</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/drones-to-monitor-illegal-mining-across-maha-bawankule/articleshow/119269920.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-orders-crackdown-on-illegal-mining-craters-after-child-deaths/articleshow/122393943.cms</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/who-reads-saamana-who-listens-to-them-asks-bawankule/articleshow/121541164.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/owners-willingly-giving-up-land-for-civic-projects-in-maharashtra-may-receive-additional-benefits-says-chandrashekhar-bawankule/articleshow/119555188.cms</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/bawankule-asks-for-alternatives-as-meeting-with-farmers-over-purandar-airport-ends-in-stalemate/articleshow/120909800.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-mahayuti-expansion-only-after-consensus-among-allies/articleshow/117496923.cms</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-quashes-rift-rumours-asserts-mahayuti-will-contest-local-polls-unitedly/articleshow/121448703.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/maharashtras-love-jihad-law-to-be-strictest-in-india-minister-chandrashekhar-bawankule/articleshow/118295093.cms</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/probe-rauts-book-for-remarks-on-judicial-process-bawankule/articleshow/121219474.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-condemns-kharges-kumbh-mela-comments-demands-apology/articleshow/117652890.cms</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-takes-stock-of-damage-caused-due-to-unseasonal-rain/articleshow/121580211.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-to-head-panel-on-farm-roads/articleshow/123103819.cms</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/maharashtra-govt-starts-second-phase-of-land-title-updating/articleshow/120827478.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pending-maharera-recovery-cases-to-be-disposed-of-within-3-months-bawankule/articleshow/118947932.cms</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-directs-nmc-to-repair-roads-immediately/articleshow/121893777.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticizes-uddhav-for-opposing-maharashtra-security-bill/articleshow/122410846.cms</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/people-will-decide-when-modi-should-retire-not-sanjay-raut-bawankule/articleshow/119881247.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/probe-rauts-book-for-remarks-on-judicial-process-bawankule/articleshow/121219474.cms</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/clear-pending-water-projects-on-priority-bawankule/articleshow/122077229.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/people-will-decide-when-modi-should-retire-not-sanjay-raut-bawankule/articleshow/119881247.cms</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-probe-illegal-transfer-of-1-628-land-parcels-to-nontribals-101752087826955.html</t>
+          <t>https://www.hindustantimes.com/india-news/maharashtra-cabinet-reshuffle-buzz-final-decision-rests-with-cm-fadnavis-says-bawankule-101753525179967.html</t>
         </is>
       </c>
     </row>
@@ -2237,889 +2237,966 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/bjp-targeting-1-5-cr-party-members-in-maha-ahead-of-civic-polls-bawankule/articleshow/118309658.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bhandara-illegal-sand-mining-2-revenue-officers-suspended/articleshow/120138193.cms</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-for-death-penalty-to-beed-sarpanchs-killers/articleshow/118338664.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/oppn-drags-fadnavis-into-koratkar-row-bjp-denies-ties-101743273793055.html</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://manufacturing.economictimes.indiatimes.com/news/industry/rs-1200-cr-sought-for-nagpur-rs-600-crore-for-amravati/117907831</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/state-govt-bawankule-behind-ink-attack-pravin-gaikwad/articleshow/122592422.cms</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/revenue-minister-orders-demolition-of-unauthorised-bungalows-in-mumbai-two-officials-suspended-for-crz-map-manipulation/articleshow/118855995.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/our-doors-are-open-for-badgujar-bawankule/articleshow/121655948.cms</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/raj-thackeray-uddhav-thackeray-victory-rally-no-traffic-diversions-for-sena-mns-rally-23583195</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/bjp-targeting-1-5-cr-party-members-in-maha-ahead-of-civic-polls-bawankule/articleshow/118309658.cms</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/government-to-remove-non-agricultural-land-use-requirement-for-industries-101738952544368.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-to-appoint-rss-workers-as-pas-to-its-ministers-101737571872713.html</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-approves-policy-for-promoting-artificial-sand-101747164656571.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/maha-govt-allows-24-hour-sand-transport/articleshow/122256742.cms</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/shinde-mahajan-were-in-kashmir-to-serve-not-score-points-bawankule/articleshow/120629012.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/law-on-land-fragmentation-to-be-scrapped/articleshow/122349434.cms</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/resolve-public-issues-on-priority-bawankule-directs-administration/03241323</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/voter-increase-in-kamptee-due-to-rapid-urbanization-bawankule-on-rahul-allegations/articleshow/121699423.cms</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/in-direct-public-outreach-bawankule-holds-3rd-janata-darbar-in-a-month/articleshow/121553803.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/gym-owner-faces-case-for-online-content-against-bawankule/articleshow/123395126.cms</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/tatkare-bawankule-push-for-rapid-launch-of-womens-employment-hub-in-koradi/articleshow/121347327.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/50-of-bhandara-city-located-on-nazul-land-govt-to-regularize-these-properties-bawankule/articleshow/123103215.cms</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/politics/rahul-gandhis-remark-on-govts-foreign-policy-unfortunate-maharashtra-bjp-chief-bawankule20250524112058/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/revenue-minister-orders-demolition-of-unauthorised-bungalows-in-mumbai-two-officials-suspended-for-crz-map-manipulation/articleshow/118855995.cms</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/sports/cricketer-kedar-jadhav-joins-bjp/2446677</t>
+          <t>https://www.nagpurtoday.in/resolve-public-issues-on-priority-bawankule-directs-administration/03241323</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-discusses-issue-of-encroachment-on-rural-roads/01211724</t>
+          <t>https://realty.economictimes.indiatimes.com/news/infrastructure/maharashtra-government-to-begin-campaign-from-april-1-to-update-7/12-land-title-records/119479129</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/on-fast-track-bawankule-sets-deadlines-for-nagpurs-development-projects/01231314</t>
+          <t>https://www.business-standard.com/pti-stories/national/maharashtra-govt-plans-to-curb-illegal-sand-mining-through-drone-based-surveys-125060600147_1.html</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-hails-union-budget-calls-it-a-strong-pillar-for-indias-future/02011547</t>
+          <t>https://www.nagpurtoday.in/bawankule-to-opposition-show-proof-or-stop-defaming/07211731</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-dares-rahul-gandhi-to-contest-from-kamptee-in-2029-assembly-poll/02101325</t>
+          <t>https://www.nagpurtoday.in/bawankule-slams-uddhav-thackeray-calls-him-leader-of-aurangzeb-fan-club/03281015</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/now-get-stamp-papers-by-paying-fees-online-in-maharashtra-bawankule/03251300</t>
+          <t>https://www.nagpurtoday.in/friendship-day-party-controversy-vedant-chhabria-says-sorry-to-bawankule-in-exclusive-nagpur-today-video/08090717</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/07/part-of-maharashtras-tradition-chandrashekhar-bawankule-responds-to-uddhav-thackerays-praise-for-cm-fadnavis/</t>
+          <t>https://www.nagpurtoday.in/drones-to-keep-an-eye-on-illegal-mining-across-maharashtra-bawankule/03211218</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-revenue-minister-chandrashekhar-bawankule-promises-best-compensation-for-purandar-airport-land-acquisition/</t>
+          <t>https://www.nagpurtoday.in/friendship-day-bash-turns-chaotic-main-bawankule-se-baat-kar-leta-hoon-organisers-threat-to-cops-caught-on-camera/08050821</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-chandrashekhar-bawankule-celebrates-bjps-victory-in-delhi-elections-challenges-rahul-gandhi-to-run-against-him/</t>
+          <t>https://www.nagpurtoday.in/dont-repeat-my-mistakes-nitin-gadkaris-candid-advice-to-bawankule-on-caste-based-politics/04071557</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-revenue-minister-chandrashekhar-bawankule-backs-purandar-airport-urges-farmers-to-voice-grievances-directly/</t>
+          <t>https://www.nagpurtoday.in/on-fast-track-bawankule-sets-deadlines-for-nagpurs-development-projects/01231314</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/maha-govt-to-reclaim-encroached-private-temple-lands-from-waqf-board-bawankule/03221140</t>
+          <t>https://www.nagpurtoday.in/koradi-temple-gate-collapse-guardian-minister-orders-probe-assures-action/08101755</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-crackdown-ordered-on-illegal-plotting-and-mining-in-yeolewadi-kondhwa-and-katraj-minister-bawankule/</t>
+          <t>https://www.nagpurtoday.in/lets-work-towards-a-developed-maharashtra-urges-nagpur-guardian-minister-bawankule/01271530</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/lets-work-towards-a-developed-maharashtra-urges-nagpur-guardian-minister-bawankule/01271530</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-govt-to-cancel-42-000-fake-birth-certificates-of-illegal-bangladeshi-nationals-by-aug-15-23587269</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/bawankule-hits-back-at-rahul-over-poll-charges-says-he-should-worry-more-about-congress-survival-3402034</t>
+          <t>https://www.aninews.in/news/national/general-news/rahul-gandhi-is-troubled-by-electoral-defeats-maharashtra-bjp-chief-on-election-rigging-allegations20250607234624/</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/megha-engineering-infrastructure-fined-rs-94-crore-for-illegal-excavation-maharashtra-minister/articleshow/122393487.cms</t>
+          <t>https://www.nagpurtoday.in/modi-is-not-a-show-he-is-a-roadshow-of-development-bawankule-slams-rahul/07261259</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/rahul-needs-to-come-out-of-dark-shadow-of-defeat-bawankule-on-his-match-fixing-remark-3575806</t>
+          <t>https://www.nagpurtoday.in/govts-benefits-will-reach-every-citizen-asserts-revenue-minister-bawankule/01231600</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/no-right-maharashtra-bjp-chiefs-dig-at-rahul-gandhi-on-caste-census-timeline-demand-101746088832797.html</t>
+          <t>https://www.nagpurtoday.in/the-constitution-is-the-backbone-of-indias-development-maharashtra-minister-bawankule-pays-tribute-to-dr-ambedkar-in-nagpur/04141639</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/oppn-drags-fadnavis-into-koratkar-row-bjp-denies-ties-101743273793055.html</t>
+          <t>https://www.nagpurtoday.in/bawankule-hails-union-budget-calls-it-a-strong-pillar-for-indias-future/02011547</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/rahul-gandhi-has-lost-the-plot-says-bawankule-denies-dig-at-bachchu-kadu/articleshow/123103074.cms</t>
+          <t>https://www.nagpurtoday.in/bawankule-slams-congress-for-questioning-operation-sindoor/07291623</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/state-govt-bawankule-behind-ink-attack-pravin-gaikwad/articleshow/122592422.cms</t>
+          <t>https://www.nagpurtoday.in/bawankule-dares-rahul-gandhi-to-contest-from-kamptee-in-2029-assembly-poll/02101325</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/childish-move-bjp-slams-entitled-dynast-rahul-gandhi-over-eci-allegations-maharashtra-polls-101749324813073.html</t>
+          <t>https://www.nagpurtoday.in/drinking-water-crisis-in-nagpur-district-to-be-resolved-soon-bawankule/04261228</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/former-cricketer-kedar-jadhav-joins-bjp-3484153</t>
+          <t>https://www.nagpurtoday.in/bawankule-inspects-farm-access-road-in-katol-stresses-quality-execution/05311731</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/no-discord-in-maha-yuti-govt-bawankule-dismisses-reports-of-credit-game-over-pahalgam-rescue-op-3510596</t>
+          <t>https://www.nagpurtoday.in/now-get-stamp-papers-by-paying-fees-online-in-maharashtra-bawankule/03251300</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/encroachment-visible-on-govt-land-no-fake-docus-used-bawankule/articleshow/122394983.cms</t>
+          <t>https://thenewsmill.com/2025/07/part-of-maharashtras-tradition-chandrashekhar-bawankule-responds-to-uddhav-thackerays-praise-for-cm-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/take-strict-action-against-illegal-soil-transportation-embezzlement-of-royalties-in-thane-bawankule-to-officials-23515104</t>
+          <t>https://thenewsmill.com/2025/05/chandrashekhar-bawankule-welcomes-ncps-chhagan-bhujbal-in-maharashtra-cabinet-calls-it-a-boost-for-govt/</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/govt-with-you-bawankule-assures-matangs-seeking-sub-quota-benefits-101747768592892.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/shiv-sena-ubt-has-realised-its-blunder-of-breaking-alliance-with-bjp-and-siding-with-congress-bawankule-3351296</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/pti-stories/national/maharashtra-govt-plans-to-curb-illegal-sand-mining-through-drone-based-surveys-125060600147_1.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/bawankule-hits-back-at-rahul-over-poll-charges-says-he-should-worry-more-about-congress-survival-3402034</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/ajit-pawar-defends-decision-to-divert-sc-st-funds-to-ladki-bahin-scheme-101746385156890.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/megha-engineering-infrastructure-fined-rs-94-crore-for-illegal-excavation-maharashtra-minister/articleshow/122393487.cms</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/illegal-building-that-came-up-on-land-of-ambedkar-heir-in-kalyan-demolished-plot-reclaimed-minister/articleshow/122420767.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/rahul-needs-to-come-out-of-dark-shadow-of-defeat-bawankule-on-his-match-fixing-remark-3575806</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/nagpur-violence-over-50-persons-held-5-firs-lodged-3451085</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/no-blanket-farm-loan-waiver-only-the-most-distressed-to-get-it-bawankule/articleshow/123195407.cms</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/hc-acquits-all-2006-train-blasts-accused-maharashtra-govt-will-study-order-says-chandrashekhar-bawankule-23585741</t>
+          <t>https://www.hindustantimes.com/india-news/no-right-maharashtra-bjp-chiefs-dig-at-rahul-gandhi-on-caste-census-timeline-demand-101746088832797.html</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/politics/rahul-upset-over-electoral-losses-maharashtra-bjp-chief-on-rigging-claims-125060700848_1.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-calls-rahul-gandhis-caste-census-push-too-late-to-matter/articleshow/122925629.cms</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-pushes-for-people-centric-development-weekly-village-visits-fast-track-projects-under-annual-plan/articleshow/123127176.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/rahul-gandhi-has-lost-the-plot-says-bawankule-denies-dig-at-bachchu-kadu/articleshow/123103074.cms</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/not-right-to-cast-doubt-on-vp-dhankhars-resignation-bjp-leader-bawankule-3641964</t>
+          <t>https://realty.economictimes.indiatimes.com/news/allied-industries/free-sand-royalty-receipts-to-be-delivered-to-beneficiaries-of-housing-schemes-maharashtra-revenue-minister/121176284</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/article/dhankhars-resignation-bjp-dismisses-congress-doubts-cites-spotless-life-23585910</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/maha-govt-plans-new-land-acquisition-rules-to-speed-up-projects-assure-farmers-fair-compensation/articleshow/123144329.cms</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-orders-bulldozer-on-illegal-lawns-houses-in-futala-lake-area-in-nagpur/02131731</t>
+          <t>https://www.hindustantimes.com/india-news/childish-move-bjp-slams-entitled-dynast-rahul-gandhi-over-eci-allegations-maharashtra-polls-101749324813073.html</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://realty.economictimes.indiatimes.com/news/infrastructure/maharashtra-government-plans-to-curb-illegal-sand-mining-through-drones/121687914</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/no-biometric-attendance-system-no-salary-for-amravati-state-govt-employees-bawankule/articleshow/122789185.cms</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/no-funds-diverted-from-other-departments-for-ladki-bahin-scheme-says-bawankule-23565529</t>
+          <t>https://www.deccanherald.com/india/maharashtra/former-cricketer-kedar-jadhav-joins-bjp-3484153</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/14-telangana-villages-will-be-merged-in-maharashtra-enn25071602801</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-to-allow-hoardings-on-vacant-land-owned-by-govt-bawankule-101750872010984.html</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/do-not-raze-unauthorised-houses-during-ganesh-festival-minister-orders-authorities/2840776</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/govt-panel-to-conduct-survey-to-identify-farmers-in-need-of-loan-waiver-in-maharashtra-says-bjp-minister-bawankule/articleshow/123169142.cms</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cuts-red-tape-waives-rs-500-stamp-duty-on-affidavits-23495197</t>
+          <t>https://www.deccanherald.com/india/maharashtra/no-discord-in-maha-yuti-govt-bawankule-dismisses-reports-of-credit-game-over-pahalgam-rescue-op-3510596</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/good-news-maharashtra-waives-%E2%82%B9500-stamp-duty-on-affidavits-major-relief-for-students-citizens/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/encroachment-visible-on-govt-land-no-fake-docus-used-bawankule/articleshow/122394983.cms</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/news/fake-birth-certificates-of-bangladeshis-to-be-cancelled-mahaminister-says-42000-forged-documents-were-issued-to-illegal-immigrants-with-tehsildars-help-to-be-nullified-by-august-15-135565530.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/take-strict-action-against-illegal-soil-transportation-embezzlement-of-royalties-in-thane-bawankule-to-officials-23515104</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/much-awaited-nmc-elections-likely-by-october-bawankule/06031614</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/act-against-illegal-plotting-mining-in-yeolewadi-kondhwa-katraj-areas-bawankule-101748459992922.html</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/sc-verdict-on-obc-reservation-expected-soon-says-revenue-minister-chandrashekhar-bawankule-in-pune/</t>
+          <t>https://manufacturing.economictimes.indiatimes.com/news/industry/rs-1200-cr-sought-for-nagpur-rs-600-crore-for-amravati/117907831</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-on-ladki-bahin-yojana-if-men-have-taken-money-than-file-case-and-the-money-should-also-be-recovered-revenue-minister-instructions-1372671</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-will-cancel-fake-birth-certificates-issued-to-illegal-bangladeshi-residents-state-minister-bawankule-3656548</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/chandrashekhar-bawankule-not-aware-of-sudhakar-badgujars-entry-into-bjp-8687548</t>
+          <t>https://www.ndtv.com/india-news/maharashtra-revenue-department-goes-hi-tech-to-ensure-employee-attendance-8944686</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-farmers-loan-waivers-farmers-who-drive-around-in-mercedes-lay-out-farm-house-1366570</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/govt-with-you-bawankule-assures-matangs-seeking-sub-quota-benefits-101747768592892.html</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrashekhar-bawankule-on-mohite-patil-solapur-news-revenue-minister-chandrashekhar-bawankule-response-to-a-question-asked-regarding-bjp-mla-ranjitsinh-mohite-patil-1361514</t>
+          <t>https://www.deccanherald.com/india/maharashtra/ravindra-chavan-to-be-new-bjp-chief-for-maharashtra-3609432</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrashekhar-bawankule-solapur-visit-sand-instructions-to-chandrashekhar-bawankule-officials-regarding-sand-policy-1361488</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/ajit-pawar-defends-decision-to-divert-sc-st-funds-to-ladki-bahin-scheme-101746385156890.html</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/ncp-sharad-chandra-pawar-party-state-president-jayant-patil-and-bjp-state-president-chandrashekhar-bawankule-met-in-mumbai-1360571</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/illegal-building-that-came-up-on-land-of-ambedkar-heir-in-kalyan-demolished-plot-reclaimed-minister/articleshow/122420767.cms</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-said-morning-did-not-know-about-sudhakar-badgujar-entry-into-the-party-but-he-entered-in-his-presence-marathi-news-1364737</t>
+          <t>https://www.business-standard.com/politics/rahul-upset-over-electoral-losses-maharashtra-bjp-chief-on-rigging-claims-125060700848_1.html</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrashekhar-bawankule-tweet-12-senior-officers-of-the-revenue-department-promoted-by-the-public-service-commission-given-ias-status-by-the-center-1369895</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-pushes-for-people-centric-development-weekly-village-visits-fast-track-projects-under-annual-plan/articleshow/123127176.cms</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/revenue-minister-chandrashekhar-bawankule-important-orders-to-sub-divisional-officer-and-tehsildar-1373523.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/not-right-to-cast-doubt-on-vp-dhankhars-resignation-bjp-leader-bawankule-3641964</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174314/</t>
+          <t>https://www.indiatoday.in/india/law-news/story/supreme-court-status-quo-order-bale-shah-peer-dargah-demolition-2727320-2025-05-20</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172891/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/velhe-taluka-in-pune-district-renamed-as-rajgad-announces-maharashtra-minister-bawankule-3691509</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/maharashtra-government-forms-committee-for-farmers-loan-waiver-minister-appeals-to-avoid-haste-in-protests-vsb99</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-minister-bawankule-asks-bmc-to-halt-its-demolition-drive-in-north-mumbai-till-ganeshotsav-23590378</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/maharashtra-politics-chandrashekhar-bawankule-big-statement-order-to-bjp-office-bearers-dismantle-congress-1398359.html</t>
+          <t>https://aninews.in/news/national/politics/rahul-gandhis-remark-on-govts-foreign-policy-unfortunate-maharashtra-bjp-chief-bawankule20250524112058/</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/emotional-letter-from-ex-bjp-maharashtra-president-chandrashekhar-bawankule-now-ravindra-chavhan-new-state-bjp-presdent-1367444</t>
+          <t>https://www.mid-day.com/news/india-news/article/maharashtra-launches-one-district-one-registration-scheme-for-property-23535200</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174971/</t>
+          <t>https://www.business-standard.com/india-news/maharashtra-govt-forms-sit-to-probe-delayed-birth-death-certificates-125012500183_1.html</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/sambhaji-brigade-leader-pravin-gaikwad-press-conference-says-devendra-fadnavis-and-chandrashekhar-bawankule-supports-deepak-kate-1370337</t>
+          <t>https://www.nagpurtoday.in/now-sand-mafias-to-face-criminal-charges-not-just-fines-bawankule/07181631</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/169614/</t>
+          <t>https://realty.economictimes.indiatimes.com/news/infrastructure/maharashtra-government-plans-to-curb-illegal-sand-mining-through-drones/121687914</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173287/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/no-funds-diverted-from-other-departments-for-ladki-bahin-scheme-says-bawankule-23565529</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176273/</t>
+          <t>https://www.nagpurtoday.in/sc-verdict-on-zudpi-jungle-opens-doors-to-vidarbhas-all-round-development-jobs-bawankule/05231117</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-bjp-state-president-election-process-begins-chandrashekar-bawankule-defends-public-safety-bill-1367078</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-tightens-rules-for-birth-death-certificates-for-foreign-nationals-23498903</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/169968/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cuts-red-tape-waives-rs-500-stamp-duty-on-affidavits-23495197</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-immediate-suspension-of-the-tehsildars-who-sang-when-will-action-be-taken-against-the-dysp-anant-kulkarni-who-kicked-1377733</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/land-measurement-for-division-in-maharashtra-now-at-rs-200-23548697</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-criticized-on-eknath-khadse-over-girish-mahajan-and-rameshwar-naik-prafull-lodha-file-complaint-demand-maharashtra-marathi-news-1371612</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/bjp-gets-1-crore-new-members-across-maharashtra-23482502</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/amravati-koundanyapur-to-get-connected-to-shaktipeeth-highway-for-pilgrims-announcement-by-chandrashekhar-bawankule-mma-73-vsd-99-5188294/</t>
+          <t>https://www.mypunepulse.com/pune-bawankule-calls-for-dialogue-as-farmers-protest-purandar-airport-land-acquisition/</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/minister-bawankule-questions-opposition-silence-on-honeytrap-claims-vsb99</t>
+          <t>https://www.mypunepulse.com/no-face-app-no-salary-maharashtra-govt-makes-digital-attendance-compulsory-for-revenue-employees/</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172168/</t>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/news/fake-birth-certificates-of-bangladeshis-to-be-cancelled-mahaminister-says-42000-forged-documents-were-issued-to-illegal-immigrants-with-tehsildars-help-to-be-nullified-by-august-15-135565530.html</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170687/</t>
+          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-on-ladki-bahin-yojana-if-men-have-taken-money-than-file-case-and-the-money-should-also-be-recovered-revenue-minister-instructions-1372671</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172900/</t>
+          <t>https://marathi.ndtv.com/cities/chandrashekhar-bawankule-not-aware-of-sudhakar-badgujars-entry-into-bjp-8687548</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175339/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/chandrashekhar-bawankule-tweet-12-senior-officers-of-the-revenue-department-promoted-by-the-public-service-commission-given-ias-status-by-the-center-1369895</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/167780/</t>
+          <t>https://news18marathi.com/maharashtra/revenue-minister-chandrashekhar-bawankule-important-orders-to-sub-divisional-officer-and-tehsildar-1373523.html</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/chandrashekhar-bawankule-reaction-on-bjp-leader-babanrao-lonikar-statement/articleshow/122091225.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/chandrashekhar-bawankule-on-sharad-pawar-minister-chandrashekhar-bawankule-criticism-on-sharad-pawar-s-mandal-yatra-1376056</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra-politics-revenue-minister-chandrashekhar-bawankule-mediation-in-the-issue-of-the-disabled-and-successful-solution-after-six-ministers-discuss-1367752</t>
+          <t>https://mahasamvad.in/172891/</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-leader-chandrashekhar-bawankule-denied-allegations-of-sushma-andhare-having-connection-with-sambhaji-brigade-pravin-gaikwad-attack-1369812</t>
+          <t>https://marathi.ndtv.com/maharashtra/maharashtra-politics-chandrashekhar-bawankule-big-statement-about-ban-sanjay-rauts-narkatla-swarg-book-8430233</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/dharashiv/revenue-minister-chandrashekhar-bawankule-publicly-felicitated-by-accused-out-on-bail-in-drug-case-1375621</t>
+          <t>https://www.tv9marathi.com/videos/maharashtra-politics-chandrashekhar-bawankule-big-statement-order-to-bjp-office-bearers-dismantle-congress-1398359.html</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/no-one-can-steal-funds-from-tribal-and-social-departments-devendra-fadnavis-will-not-allow-injustice-to-happen-says-chandrashekhar-bawankule-1363646</t>
+          <t>https://www.esakal.com/vidarbha/maharashtra-government-forms-committee-for-farmers-loan-waiver-minister-appeals-to-avoid-haste-in-protests-vsb99</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/26/chandrashekhar-bawankule-on-congress-obc.html</t>
+          <t>https://www.loksatta.com/nagpur/wardha-officials-under-pressure-after-bawankules-warning-revenue-department-shaken-by-strict-action-vsd-99-5284677/</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/uddhav-thackeray-fears-that-mumbai-municipal-corporation-will-be-taken-away-from-him-says-chandrashekhar-bawankule-maharashtra-news-mhs25080703834</t>
+          <t>https://mahasamvad.in/174971/</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-praises-pm-narendra-modi-for-operation-sindoor/videoshow/121133822.cms</t>
+          <t>https://marathi.abplive.com/news/politics/sambhaji-brigade-leader-pravin-gaikwad-press-conference-says-devendra-fadnavis-and-chandrashekhar-bawankule-supports-deepak-kate-1370337</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/revenue-minister-chandrashekhar-bawankule-announced-in-the-legislative-assembly-that-an-inquiry-will-be-conducted-through-a-commissioner-phm-00-5217343/</t>
+          <t>https://mahasamvad.in/173287/</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/173517/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-bjp-state-president-election-process-begins-chandrashekar-bawankule-defends-public-safety-bill-1367078</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/chandrasekhar-bawankule-orders-tehsildars-to-retrieve-42000-cancelled-birth-certificates-by-august-15-1372656</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/chandrashekhar-bawankule-reaction-on-bjp-leader-babanrao-lonikar-statement/articleshow/122091225.cms</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/22-day-old-baby-saved-after-severe-burns-minister-intervenes-vsb99</t>
+          <t>https://marathi.abplive.com/news/maharashtra-politics-revenue-minister-chandrashekhar-bawankule-mediation-in-the-issue-of-the-disabled-and-successful-solution-after-six-ministers-discuss-1367752</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/5/it-is-unfortunate-for-this-country-that-such-an-immature-opposition-leader.html</t>
+          <t>https://mahasamvad.in/170687/</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B9%E0%A5%85%E0%A4%B2-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%B8-%E0%A4%B9%E0%A5%87%E0%A4%AC-%E0%A4%82%E0%A4%9A-%E0%A4%AA-%E0%A4%8F-%E0%A4%AC-%E0%A4%B2%E0%A4%A4-%E0%A4%AF-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%9C-%E0%A4%A8%E0%A4%97%E0%A4%B0%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%B2-%E0%A4%95%E0%A5%8D%E0%A4%AF%E0%A5%82%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%A0%E0%A4%B5%E0%A4%B2-%E0%A4%AA%E0%A5%88%E0%A4%B6-%E0%A4%82%E0%A4%9A-%E0%A4%AE-%E0%A4%97%E0%A4%A3-%E0%A4%AA-%E0%A4%B2-%E0%A4%B8-%E0%A4%A4-%E0%A4%A4%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%B0/ar-AA1KFEz1</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/minister-bawankule-questions-opposition-silence-on-honeytrap-claims-vsb99</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-on-malegaon-blast-case-verdict-the-truth-has-come-out-in-the-malegaon-case-now-congress-should-apologize-demands-chandrashekhar-bawankule-1373804</t>
+          <t>https://mahasamvad.in/172900/</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-criticized-on-rahul-gandhi-over-criticized-pm-narendra-modi-statement-maharashtra-marathi-news-1372638</t>
+          <t>https://mahasamvad.in/172168/</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/chandrashekhar-bawankule-bjp-explanation-on-remarks-over-splitting-congress-in-maharshtra-politics/articleshow/120903323.cms</t>
+          <t>https://marathi.abplive.com/news/bacchu-kadu-response-to-chandrashekhar-bawankule-criticism-over-farmers-loan-waiver-issue-maharashtra-politics-marathi-news-1374715</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrashekhar-bawankule-amravati-news-bjp-minister-chandrashekhar-bawankule-criticizes-on-congress-amravati-1377470</t>
+          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-says-revenue-department-faceapp-registration-is-mandatory-for-everyone-from-talatha-to-dy-collector-1372159</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/minister-chandrashekhar-bawankule-orders-officers-to-involve-public-representative-in-work/articleshow/123099445.cms</t>
+          <t>https://marathi.ndtv.com/maharashtra/maharashtra-politics-chandrashekhar-bawankule-take-strict-action-on-pwd-department-scam-sting-operation-7921778</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/26/chandrashekhar-bawankule-rahul-gandhi-narendra-modi.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/1/strict-action-will-be-taken-against-illegal-sand-miners-on-wardha-river-revenue-minister-chandrashekhar-bawank.html</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174403/</t>
+          <t>https://www.tv9marathi.com/videos/chandrashekhar-bawankule-response-sanjay-raut-criticism-1374675.html</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173545/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/nagpur-news-saw-the-news-on-abp-majha-chandrashekhar-bawankule-immediately-took-note-with-the-help-of-nitin-gadkari-road-issue-was-resolved-in-an-instant-1377264</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/video/chandrashekhar-bawankule-meets-bacchu-kadu/914920</t>
+          <t>https://marathi.ndtv.com/cities/chandrashekhar-bawankule-on-raj-thackeray-hindi-language-natioanl-education-policy-8201539</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nashik/bjp-chandrashekhar-bawankule-says-code-of-conduct-will-in-august-for-upcoming-municipal-elections-2025-pri/articleshow/121662946.cms</t>
+          <t>https://mahasamvad.in/175339/</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/revenue-minister-chandrashekhar-bawankule-announded-cancelled-tukde-ban-act-maharashtra-govt-big-decision-1432122.html</t>
+          <t>https://mahasamvad.in/168918/</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-voter-list-deletion-allegations-congress-accuses-sanket-bawankule-of-deleting-thousands-of-voter-names-in-kamthi-assembly-constituency-1378709</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/26/chandrashekhar-bawankule-on-congress-obc.html</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/1/committee-formed-under-the-chairmanship-of-revenue-minister-bawankule.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-praises-pm-narendra-modi-for-operation-sindoor/videoshow/121133822.cms</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/sudhakar-badgujar-join-bjp-chandrashekhar-bawankule-reaction-1425349.html</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/chandrashekhar-bawankule-calls-terrorists-naxalites-gaffe-sk95</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/3/28/The-baby-s-life-was-saved-by-the-initiative-of-Guardian-Minister-Chandrashekhar-Bawankule-.html</t>
+          <t>https://www.loksatta.com/mumbai/revenue-minister-chandrashekhar-bawankule-announced-in-the-legislative-assembly-that-an-inquiry-will-be-conducted-through-a-commissioner-phm-00-5217343/</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/will-the-amravati-airport-be-inaugurated-on-31-march-2025-says-guardian-minister-chandrashekhar-bawankule-maharashtra-news-mhs25032804267</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-bawankule-kadu-row-revenue-minister-and-former-mla-clash-over-disabled-allowance-hike-and-farmers-issues-accusations-of-drama-exchanged-1374782</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nasik/casino-photo-controversy-shivsena-ubt-sanjay-raut-bjp-dispute-between-sudhakar-badgujar-and-chandrashekhar-bawankule-nashik-marathi-news-1364674</t>
+          <t>https://mahasamvad.in/172725/</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-uddhav-thackeray-and-bawankule-engage-in-twitter-spat-as-shiv-sena-workers-join-bjp-due-to-leader-unavailability-in-maharashtra-politics-1369935</t>
+          <t>https://deshdoot.com/revenue-minister-chandrashekhar-bawankule-to-visit-nashik-on-saturday/</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/buldana/chandrashekhar-bawankule-criticizes-sharad-pawar-over-obc-mandal-yatra/videoshow/123213597.cms</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/22-day-old-baby-saved-after-severe-burns-minister-intervenes-vsb99</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/honey-trap-case-chandrashekhar-bawankule-explanation-nagpur-ssb-93-5243624/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/5/it-is-unfortunate-for-this-country-that-such-an-immature-opposition-leader.html</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168121/</t>
+          <t>https://marathi.abplive.com/news/politics/sudhakar-badgujar-bjp-party-joining-ceremony-chandrashekhar-bawankule-statement-create-confusion-1364657</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-on-agriculture-minister-manikrao-kokate-statement-say-if-agriculture-ministerhas-said-anything-we-will-apologize-on-behalf-of-the-government-maharashtra-politics-1352861</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/chandrashekhar-bawankule-bjp-explanation-on-remarks-over-splitting-congress-in-maharshtra-politics/articleshow/120903323.cms</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168550/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/chandrashekhar-bawankule-amravati-news-bjp-minister-chandrashekhar-bawankule-criticizes-on-congress-amravati-1377470</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/2-former-mlas-and-former-minister-son-join-bjp-chandrashekhar-bawankule-said-2-big-entries-from-congress-soon-aslo-kolhapur-shahapur-and-srirampur-1354545</t>
+          <t>https://www.nagpurtoday.in/revenue-minister-chandrasekhar-bawankules-announcement-in-the-legislative-assembly-action-against-wrongdoers/03201828</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrashekhar-bawankule-on-uddhav-thackeray-in-mumbai-bjp-state-president-chandrashekhar-bawankule-criticizes-on-uddhav-thackeray-1354721</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/26/chandrashekhar-bawankule-rahul-gandhi-narendra-modi.html</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/politics-heat-up-over-honey-trap-allegations-minister-chandrashekhar-bawankule-open-challenge-to-opponents-in-nagpur-maharashtra-news-mhs25072104965</t>
+          <t>https://mahasamvad.in/174403/</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>https://zeenews.india.com/marathi/video/chandrashekhar-bawankule-meets-bacchu-kadu/914920</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/nashik/bjp-chandrashekhar-bawankule-says-code-of-conduct-will-in-august-for-upcoming-municipal-elections-2025-pri/articleshow/121662946.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>https://news18marathi.com/maharashtra/revenue-minister-chandrashekhar-bawankule-announded-cancelled-tukde-ban-act-maharashtra-govt-big-decision-1432122.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-voter-list-deletion-allegations-congress-accuses-sanket-bawankule-of-deleting-thousands-of-voter-names-in-kamthi-assembly-constituency-1378709</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/1/committee-formed-under-the-chairmanship-of-revenue-minister-bawankule.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/3/28/The-baby-s-life-was-saved-by-the-initiative-of-Guardian-Minister-Chandrashekhar-Bawankule-.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/pune/maharashtra-revenue-minister-admits-large-encroachment-on-government-land-pune-print-news-ocd-94-5205178/</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/amravati/news/guardian-minister-chandrashekhar-bawankule-announced-a-solar-pump-that-provides-electricity-for-12-hours-a-12-foot-road-and-goods-distribution-under-the-vayoshree-yojana-135151355.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-on-jayant-patil-resigns-shashikant-shinde-new-state-president-of-sharad-pawar-ncp-maharashtra-politics-maharashtra-marathi-news-1369487</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-on-agriculture-minister-manikrao-kokate-statement-say-if-agriculture-ministerhas-said-anything-we-will-apologize-on-behalf-of-the-government-maharashtra-politics-1352861</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/maharashtra/chandrashekhar-bawankule-on-uddhav-thackeray-in-mumbai-bjp-state-president-chandrashekhar-bawankule-criticizes-on-uddhav-thackeray-1354721</t>
         </is>
       </c>
     </row>

--- a/Output/Chandrashekhar Bawankule/extracted_links_Chandrashekhar Bawankule_failed_links.xlsx
+++ b/Output/Chandrashekhar Bawankule/extracted_links_Chandrashekhar Bawankule_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A396"/>
+  <dimension ref="A1:A375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,2758 +445,2611 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168550/</t>
+          <t>https://mahasamvad.in/174008/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168121/</t>
+          <t>https://www.newsonair.gov.in/mr/farm-road/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/154916/</t>
+          <t>https://mahasamvad.in/173290/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174008/</t>
+          <t>https://mahasamvad.in/176111/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/159925/</t>
+          <t>https://mahasamvad.in/173830/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/157368/</t>
+          <t>https://mahasamvad.in/172967/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173290/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/3/9/Chandrashekhar-Bawankule-will-carry-out-comprehensive-development-of-Kamathi-city.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/167394/</t>
+          <t>https://mahasamvad.in/173944/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/161858/</t>
+          <t>https://marathi.ndtv.com/politics/government-will-take-a-big-decision-for-snake-lovers-revenue-minister-bawankule-gave-information-8943735</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176111/</t>
+          <t>https://mahasamvad.in/176970/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170401/</t>
+          <t>https://mahasamvad.in/174937/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/171657/</t>
+          <t>https://mahasamvad.in/176959/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/166188/</t>
+          <t>https://mahasamvad.in/175334/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/mr/farm-road/</t>
+          <t>https://mahasamvad.in/171768/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173830/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nashik/chandrashekhar-bawankule-expressed-anger-on-phone-call-to-chandwad-tehsildar-regarding-working-complaints-pri/articleshow/121389576.cms</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168197/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/bjp-state-president-chandrashekhar-bawankule-apologized-to-chief-justice-bhushan-gavai-on-behalf-of-the-government/articleshow/121268071.cms</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/167498/</t>
+          <t>https://www.nagpurtoday.in/government-benefits-will-reach-every-citizen-revenue-minister-chandrashekhar-bawankules-determination/01231556</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172967/</t>
+          <t>https://marathi.abplive.com/news/revenue-minister-chandrashekhar-bawankules-call-to-chandwad-tehsildar-aggressive-reaction-over-complaints-in-bjp-janta-darbar-in-mumbai-video-goes-viral-maharashtra-politics-1361293</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/165738/</t>
+          <t>https://mahasamvad.in/176956/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163316/</t>
+          <t>https://marathi.ndtv.com/politics/chandrasekhar-bawankule-felicitation-by-tuljapur-drugs-case-accused-sparks-backlash-9041887</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173944/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/30/revenue-department-to-implement-revenue-week-in-the-state-from-august-1.html</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/3/9/Chandrashekhar-Bawankule-will-carry-out-comprehensive-development-of-Kamathi-city.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/4/revenue-minister-chandrashekhar-bawankule-makes-announcement-in-assembly-hints-at-action-against-eight-stamp-d.html</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/micro-zoning-to-determine-rates-of-ready-reckoners-in-mumbai-revenue-minister-chandrashekhar-bawankule-decision-marathi-news-1352443</t>
+          <t>https://mahasamvad.in/174605/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/166711/</t>
+          <t>https://www.etvbharat.com/mr/!state/minister-chandrashekhar-bawankule-appeals-to-the-opposition-not-to-politicize-the-mumbai-train-accident-maharashtra-news-mhs25060906405</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/167416/</t>
+          <t>https://thefocusindia.com/maharashtra-news/revenue-minister-bawankule-announces-relaxation-fragmentation-law-50-lakh-farmers-relief-277582/amp/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174937/</t>
+          <t>https://thefocusindia.com/maharashtra-news/bjp-does-not-do-low-level-acts-chandrashekhar-bawankule-rejects-allegations-in-praveen-gaikwad-attack-case-278013/amp/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-news-state-governments-big-decision-regarding-land-fragmentation-high-level-committee-formed-to-make-reforms-83561</t>
+          <t>https://www.mahasamvad.in/166742/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/government-will-take-a-big-decision-for-snake-lovers-revenue-minister-bawankule-gave-information-8943735</t>
+          <t>https://www.etvbharat.com/mr/!state/no-new-districts-will-be-created-in-the-state-for-the-time-being-says-revenue-minister-chandrashekhar-bawankule-maharashtra-news-mhs25012302825</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160422/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/6/23/new-law-to-be-introduced-in-monsoon-session-said-chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/167907/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/drone-watch-on-illegal-minor-mineral-mining-important-decision-of-revenue-minister-bawankule-1362804</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176970/</t>
+          <t>https://mahasamvad.in/173545/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175334/</t>
+          <t>https://thefocusindia.com/maharashtra-news/stamp-duty-of-rs-500-waived-for-various-certificates-including-caste-verification-income-certificate-chandrashekhar-bawankule-263813/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/appointment-of-80-additional-district-collectors-in-the-state-a-big-decision-by-revenue-minister-chandrashekhar-bawankule-1355734</t>
+          <t>https://marathi.abplive.com/news/dharashiv/revenue-minister-chandrashekhar-bawankule-publicly-felicitated-by-accused-out-on-bail-in-drug-case-1375621</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/171768/</t>
+          <t>https://www.nagpurtoday.in/reconstruction-of-vidarbha-bhoodan-yagna-mandal-to-take-place-revenue-minister-chandrashekhar-bawankules-directive/02071130</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176959/</t>
+          <t>https://www.mahasamvad.in/173517/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/161982/</t>
+          <t>https://www.mahasamvad.in/169614/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nashik/chandrashekhar-bawankule-expressed-anger-on-phone-call-to-chandwad-tehsildar-regarding-working-complaints-pri/articleshow/121389576.cms</t>
+          <t>https://news18marathi.com/agriculture/revenue-department-under-leadership-revenue-minister-chandrashekhar-bawankule-has-taken-18-major-decisions-1413141.html</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/152385/</t>
+          <t>https://www.nagpurtoday.in/revenue-minister-and-guardian-minister-shri-taken-by-chandrasekhar-bawankule/06081251</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/bjp-state-president-chandrashekhar-bawankule-apologized-to-chief-justice-bhushan-gavai-on-behalf-of-the-government/articleshow/121268071.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B9%E0%A5%85%E0%A4%B2-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%B8-%E0%A4%B9%E0%A5%87%E0%A4%AC-%E0%A4%82%E0%A4%9A-%E0%A4%AA-%E0%A4%8F-%E0%A4%AC-%E0%A4%B2%E0%A4%A4-%E0%A4%AF-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%9C-%E0%A4%A8%E0%A4%97%E0%A4%B0%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%B2-%E0%A4%95%E0%A5%8D%E0%A4%AF%E0%A5%82%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%A0%E0%A4%B5%E0%A4%B2-%E0%A4%AA%E0%A5%88%E0%A4%B6-%E0%A4%82%E0%A4%9A-%E0%A4%AE-%E0%A4%97%E0%A4%A3-%E0%A4%AA-%E0%A4%B2-%E0%A4%B8-%E0%A4%A4-%E0%A4%A4%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%B0/ar-AA1KFEz1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168812/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/2/3/One-lakh-94-thousand-special-executive-officers-will-be-appointed-across-the-state-By-Chandrashekhar-Bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/government-benefits-will-reach-every-citizen-revenue-minister-chandrashekhar-bawankules-determination/01231556</t>
+          <t>https://marathi.abplive.com/crime/sambhajinagar-farmer-demand-money-hello-chandrashekhar-bawankule-pa-is-speaking-qr-sent-to-farmer-in-complaint-to-police-1377664</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/151939/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/2/3/Chandrashekhar-Bawankule-brought-satisfaction-to-the-Mihan-project-victims.html</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176956/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/chandrashekhar-bawankule-assures-of-farmers-loan-waivers-after-proper-survey/articleshow/123184635.cms</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/chandrasekhar-bawankule-felicitation-by-tuljapur-drugs-case-accused-sparks-backlash-9041887</t>
+          <t>https://marathi.indiatimes.com/maharashtra/buldana/revenue-minister-chandrashekhar-bawankule-fake-calling-and-ccheated-fraud-with-farmer/articleshow/123344845.cms</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/30/revenue-department-to-implement-revenue-week-in-the-state-from-august-1.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/22/revenue-department-to-implement-national-leader-to-father-of-the-nation-campaign-revenue-minister-chandrashekh.html</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/159732/</t>
+          <t>https://mahasamvad.in/176506/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/4/revenue-minister-chandrashekhar-bawankule-makes-announcement-in-assembly-hints-at-action-against-eight-stamp-d.html</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-news-revenue-minister-warns-of-strict-action-against-illegal-sand-mining-now-joint-action-by-police-and-revenue-dept-83488</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/151475/</t>
+          <t>https://mahasamvad.in/171014/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163322/</t>
+          <t>https://mahasamvad.in/165774/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/166742/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/3/5/No-stamp-duty-for-affidavit-in-Maharashtra-Chandrashekhar-Bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/minister-chandrashekhar-bawankule-criticizes-sharad-pawar-mandal-yatra-maharashtra-news-mhs25081000427</t>
+          <t>https://www.loksatta.com/nagpur/maharashtra-public-security-act-for-naxal-crackdown-chandrashekhar-bawankule-statement-vsd-99-5223733/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174605/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/31/congress-committed-an-unforgivable-crime-political-defamation-conspiracy-exposed-minister-chandrashekhar-bawan.html</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/minister-chandrashekhar-bawankule-appeals-to-the-opposition-not-to-politicize-the-mumbai-train-accident-maharashtra-news-mhs25060906405</t>
+          <t>https://marathi.ndtv.com/politics/revenue-minister-chandrashekhar-bawankule-informed-that-the-state-new-sand-policy-will-be-announced-soon-7948210</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/revenue-minister-bawankule-announces-relaxation-fragmentation-law-50-lakh-farmers-relief-277582/amp/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/5/supreme-courts-decision-provides-justice-to-obcs-chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/166052/</t>
+          <t>https://mahasamvad.in/176289/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/no-new-districts-will-be-created-in-the-state-for-the-time-being-says-revenue-minister-chandrashekhar-bawankule-maharashtra-news-mhs25012302825</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-revenue-minister-chandrashekhar-bawankule-big-decision-students-stamp-duty-on-academic-affidavit-waived/articleshow/118747673.cms</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/165886/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/chhatrapati-sambhajinagar-farmer-cheated-of-rs-4k-by-fake-call-claiming-to-be-chandrashekhar-bawankule-pa/articleshow/123360446.cms</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/6/23/new-law-to-be-introduced-in-monsoon-session-said-chandrashekhar-bawankule.html</t>
+          <t>https://news18marathi.com/maharashtra/dharashiv-tuljapur-drugs-case-main-accused-vinod-pintu-gangane-felicitates-minister-chandrashekhar-bawankule-1452942.html</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/revenue-minister-chandrashekhar-bawankule-orders-action-against-guilty-officials-within-fifteen-days-pune-print-news-amy-95-5135372/</t>
+          <t>https://mahasamvad.in/172416/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/stamp-duty-of-rs-500-waived-for-various-certificates-including-caste-verification-income-certificate-chandrashekhar-bawankule-263813/</t>
+          <t>https://www.tv9marathi.com/maharashtra/mumbai/devendra-fadnavis-will-be-the-chief-minister-till-2034-chandrashekhar-bawankule-prediction-deputy-cm-eknath-shinde-big-reaction-in-one-word-1392298.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173545/</t>
+          <t>https://www.nagpurtoday.in/dont-politicize-pahalgam-attack-stand-with-the-government-chandrashekhar-bawankule-appeals/04232052</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-farmers-loan-waivers-farmers-who-drive-around-in-mercedes-lay-out-farm-house-1366570</t>
+          <t>https://mahasamvad.in/176273/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/dharashiv/revenue-minister-chandrashekhar-bawankule-publicly-felicitated-by-accused-out-on-bail-in-drug-case-1375621</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/minister-chandrashekhar-bawankule-big-statement-about-farmers-loan-waiver/articleshow/123323729.cms</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163978/</t>
+          <t>https://mahasamvad.in/174314/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/reconstruction-of-vidarbha-bhoodan-yagna-mandal-to-take-place-revenue-minister-chandrashekhar-bawankules-directive/02071130</t>
+          <t>https://mahasamvad.in/174926/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/173517/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/31/62-officers-promoted-to-the-rank-of-naib-tehsildar-on-the-eve-of-revenue-day.html</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/169614/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-leader-chandrashekhar-bawankule-explanation-on-viral-video-of-eknath-shinde/articleshow/122165237.cms</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/revenue-department-under-leadership-revenue-minister-chandrashekhar-bawankule-has-taken-18-major-decisions-1413141.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/5/case-registered-against-those-who-harassed-the-police-in-the-name-of-guardian-minister-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-on-stamp-paper-demand-in-e-service-centers-in-government-offices-is-illegal-information-from-revenue-minister-chandrashekhar-bawankule-maharashtra-politics-maharashtra-marathi-news-1362983</t>
+          <t>https://marathi.ndtv.com/maharashtra/government-approved-1660-petrol-pumps-in-maharashtra-single-window-system-starts-know-how-to-apply-7822420</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/revenue-minister-and-guardian-minister-shri-taken-by-chandrasekhar-bawankule/06081251</t>
+          <t>https://marathi.indiatimes.com/business/real-estate-news/date-fixed-for-implementation-of-one-state-one-registration/articleshow/119943476.cms</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B9%E0%A5%85%E0%A4%B2-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%B8-%E0%A4%B9%E0%A5%87%E0%A4%AC-%E0%A4%82%E0%A4%9A-%E0%A4%AA-%E0%A4%8F-%E0%A4%AC-%E0%A4%B2%E0%A4%A4-%E0%A4%AF-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%9C-%E0%A4%A8%E0%A4%97%E0%A4%B0%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%B2-%E0%A4%95%E0%A5%8D%E0%A4%AF%E0%A5%82%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%A0%E0%A4%B5%E0%A4%B2-%E0%A4%AA%E0%A5%88%E0%A4%B6-%E0%A4%82%E0%A4%9A-%E0%A4%AE-%E0%A4%97%E0%A4%A3-%E0%A4%AA-%E0%A4%B2-%E0%A4%B8-%E0%A4%A4-%E0%A4%A4%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%B0/ar-AA1KFEz1</t>
+          <t>https://www.nagpurtoday.in/decision-to-relax-fragmentation-law/07091622</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/2/3/One-lakh-94-thousand-special-executive-officers-will-be-appointed-across-the-state-By-Chandrashekhar-Bawankule.html</t>
+          <t>https://civicmirror.in/maharashtra/temple-land-transactions-should-be-stopped-to-next-government-order-revenue-minister-chandrashekhar-bawankule-instructs/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/165925/</t>
+          <t>https://news18marathi.com/agriculture/the-revenue-ministry-will-make-changes-to-the-rules-for-farm-roads-1317903.html</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163171/</t>
+          <t>https://news18marathi.com/agriculture/maharashtra-revenue-department-has-taken-5-major-decisions-marathi-agriculture-news-1401406.html</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/161979/</t>
+          <t>https://marathi.abplive.com/news/jalna/farmers-flood-relief-funds-embezzled-in-jalna-revenue-minister-bawankule-orders-major-action-1375925</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/161181/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-government-planning-for-new-gunthewari-law-will-introduce-bill-in-assembly-monsoon-session/articleshow/122052149.cms</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-on-action-mode-against-sand-mafia-said-take-action-under-the-mpda-act-against-those-involved-in-illegal-sand-mining-and-transportation-in-buldhana-1376122</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-bawankule-kadu-row-revenue-minister-and-former-mla-clash-over-disabled-allowance-hike-and-farmers-issues-accusations-of-drama-exchanged-1374782</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/2/3/Chandrashekhar-Bawankule-brought-satisfaction-to-the-Mihan-project-victims.html</t>
+          <t>https://civicmirror.in/news/fadnavis-governmen-big-decision-guntha-tukdebandi-kayda/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/167615/</t>
+          <t>https://news18marathi.com/maharashtra/ias-vikas-kharge-taken-charge-additional-chief-secretary-of-revenue-department-1447633.html</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/158981/</t>
+          <t>https://marathi.abplive.com/news/pune/pune-velhe-taluka-name-change-as-rajgad-by-maharashtra-government-central-government-give-approval-1378588</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/171014/</t>
+          <t>https://www.tarunbharat.com/then-action-must-be-taken-against-those-officials-too/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-news-revenue-minister-warns-of-strict-action-against-illegal-sand-mining-now-joint-action-by-police-and-revenue-dept-83488</t>
+          <t>https://thefocusindia.com/maharashtra-news/appointment-of-80-additional-district-collectors-in-the-state-promotion-of-deputy-district-collectors-269014/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/151943/</t>
+          <t>https://www.nagpurtoday.in/governments-big-decision-rs-500-stamp-duty-waived-off-for-affidavit-revenue-minister-bawankule-announced/03051341</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/chandrashekhar-bawankule-assures-of-farmers-loan-waivers-after-proper-survey/articleshow/123184635.cms</t>
+          <t>https://www.nagpurtoday.in/separate-dcp-office-to-be-established-in-kamath-minister-bawankule-gave-instructions-to-the-planning-authorities/03171903</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172338/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/amravati/cm-devendra-fadnavis-big-decision-on-bachchu-kadu-demand-about-farmer-loan-waiver/articleshow/121832462.cms</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/buldana/revenue-minister-chandrashekhar-bawankule-fake-calling-and-ccheated-fraud-with-farmer/articleshow/123344845.cms</t>
+          <t>https://www.nagpurtoday.in/let-the-sub-capital-nagpur-get-the-status-of-an-international-metropolis-in-five-years/05022100</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/22/revenue-department-to-implement-national-leader-to-father-of-the-nation-campaign-revenue-minister-chandrashekh.html</t>
+          <t>https://www.nagpurtoday.in/govts-benefits-will-reach-every-citizen-asserts-revenue-minister-bawankule/01231600</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176506/</t>
+          <t>https://news18marathi.com/agriculture/state-government-to-bring-new-law-regarding-temple-land-marathi-agriculture-news-1361595.html</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/prahar-activists-aggressive-against-chandrashekhar-bawankule-for-anti-farmer-remark-zws-70-5279759/</t>
+          <t>https://deshonnati.com/revenue-minister-chandrasekhar-bawankule-department/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160518/</t>
+          <t>https://www.marathiebatmya.com/political/chandrashekhar-bawankule-orders-submit-a-proposal-for-the-junction-midc/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/will-action-be-taken-against-ranjitsinh-mohite-patil-for-anti-party-activities-bjp-state-presidents-bawankule-suggestive-statement-vd83</t>
+          <t>https://civicmirror.in/news/maharashtra-or-shrubs-will-provide-relief-to-families-on-forest-land-revenue-minister-bawankule/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172002/</t>
+          <t>https://marathi.timesnownews.com/maharashtra/revenue-minister-on-action-mode-against-sand-mafia-register-cases-under-mpda-act-against-those-involved-in-illegal-sand-mining-article-152439491</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/165774/</t>
+          <t>https://www.marathiebatmya.com/political/chandrasekhar-bawankule-assured-24-hours-sand-transportation-allowed/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/3/5/No-stamp-duty-for-affidavit-in-Maharashtra-Chandrashekhar-Bawankule.html</t>
+          <t>https://lokmanthan.com/the-industries-department-should-submit-a-proposal-for-the-required-land-for-the-proposed-junction-midc-revenue-minister-chandrashekhar-bawankule/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173912/</t>
+          <t>https://civicmirror.in/maharashtra/buldhana-file-cases-under-mpda-act-against-those-involved-in-illegal-sand-mining-and-transportation-in-the-district-revenue-minister-chandrashekhar-bawankule/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172804/</t>
+          <t>https://www.nagpurtoday.in/maharashtra-has-not-forgotten-who-is-the-chieftain-of-extortion-revenue-minister-bawankule-attacked-uddhav-thackeray/08111447</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163853/</t>
+          <t>https://www.marathiebatmya.com/political/chandrashekhar-bawankule-assures-no-one-will-be-homeless-in-a-bushy-forest-area/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174409/</t>
+          <t>https://deshonnati.com/chandrasekhar-bawankule-revenue-department-implement/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/164965/</t>
+          <t>https://www.dainikprabhat.com/revenue-minister-has-taken-a-big-decision-regarding-heir-registration/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/welcome-raj-thackeray-stance-in-hindi-context-chandrashekhar-bawankule-maharashtra-news-mhs25080403750</t>
+          <t>https://marathi.timesnownews.com/maharashtra/farm-roads-will-now-be-twelve-feet-wide-revenue-department-took-big-decision-article-151701949</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160286/</t>
+          <t>https://www.marathiebatmya.com/political/chandrasekhar-bawankule-announced-repeal-of-tukde-bandi-law-in-urban-areas/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/demand-for-stamp-paper-for-educational-certificates-and-affidavits-is-illegal/</t>
+          <t>https://www.marathiebatmya.com/political/efforts-to-make-the-revenue-department-more-efficient-with-the-help-of-technology/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
+          <t>https://lokmanthan.com/shrimant-chhatrapati-shivaji-maharaj-maharajswa-samadhan-camp-campaign-now-at-mandal-level-revenue-minister-bawankule/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/31/congress-committed-an-unforgivable-crime-political-defamation-conspiracy-exposed-minister-chandrashekhar-bawan.html</t>
+          <t>https://www.timemaharashtra.com/politics/chandrashekhar-bawankule-on-uddhav-thackeray-thackerays-criticism-of-fadnavis-bawankules-attack-on-thackeray/128784/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/revenue-minister-chandrashekhar-bawankule-informed-that-the-state-new-sand-policy-will-be-announced-soon-7948210</t>
+          <t>https://buldanalive.com/buldhana/prepare-proposal-to-give-25-per-cent-additional/cid16646943.htm</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/5/supreme-courts-decision-provides-justice-to-obcs-chandrashekhar-bawankule.html</t>
+          <t>https://krushimarathi.com/noc-hassle-while-building-a-house-is-over-historic-decision-of-the-revenue-department/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174273/</t>
+          <t>https://www.dainikprabhat.com/big-relief-from-state-government-waiver-of-stamp-duty-of-rs-500-for-affidavit/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168528/</t>
+          <t>https://www.dainikprabhat.com/maharashtra-scraps-land-fragmentation-law-relief-farmers/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175785/</t>
+          <t>https://www.berartimes.com/vidarbha/207471/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-revenue-minister-chandrashekhar-bawankule-big-decision-students-stamp-duty-on-academic-affidavit-waived/articleshow/118747673.cms</t>
+          <t>https://ahmednagarlive24.com/spacial/government-employee-news-so-maharashtra-state-government-employees-will-not-get-their-salary-for-august-2025/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176289/</t>
+          <t>https://dainikekmat.com/minister-bawankule-publicly-felicitated-by-accused-in-drug-case/112805/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172416/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/bjp-has-no-link-with-attack-on-sambhaji-brigade-leader-minister-bawankule-3628848</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174314/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/govt-firm-on-purandar-airport-project-chandrashekhar-bawankule-101746466486230.html</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/dharashiv-tuljapur-drugs-case-main-accused-vinod-pintu-gangane-felicitates-minister-chandrashekhar-bawankule-1452942.html</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-revenue-minister-chandrashekhar-bawankule-implements-nagpur-model-for-farm-road-construction/ar-AA1yyeMo</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/chhatrapati-sambhajinagar-farmer-cheated-of-rs-4k-by-fake-call-claiming-to-be-chandrashekhar-bawankule-pa/articleshow/123360446.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-urges-restraint-on-political-street-fights/articleshow/122819890.cms</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/161434/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/sanjay-raut-can-not-decide-modis-tenure-maharashtra-bjp-president-chandrashekhar-bawankule-on-pms-retirement-23510710</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/mla-shweta-mahales-devabhau-ladki-bahin-patsanstha-inaugurated-by-minister-chandrashekhar-bawankule-occasion-of-raksha-bandhan-maharashtra-news-mhs25080903763</t>
+          <t>https://www.ndtv.com/india-news/maharashtra-minister-apologises-to-b-r-gavai-chief-justice-over-protocol-lapse-in-mumbai-8456034</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174926/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/empty-out-the-congress-chandrashekhar-bawankule-tells-partymen-101746471227225.html</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/dont-politicize-pahalgam-attack-stand-with-the-government-chandrashekhar-bawankule-appeals/04232052</t>
+          <t>https://www.ndtv.com/india-news/maharashtra-bjp-chief-chandrashekhar-bawankule-urges-party-workers-to-empty-congress-induct-its-leaders-8334573</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176273/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-should-check-voter-lists-now-quips-chandrashekhar-bawankule/articleshow/123351307.cms</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/169968/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/confusion-in-bjp-over-induction-of-ex-sena-ubt-leader-bawankule-unaware-of-move-3589681</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/minister-chandrashekhar-bawankule-big-statement-about-farmers-loan-waiver/articleshow/123323729.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/devendra-fadnavis-to-remain-maharashtra-cm-till-2034-says-chandrashekhar-bawankule-23527680</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/31/62-officers-promoted-to-the-rank-of-naib-tehsildar-on-the-eve-of-revenue-day.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bawankule-meets-sulking-shirsat-amid-funds-diversion-controversy-101749670372918.html</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170666/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/no-75-year-age-rule-in-bjp-sanjay-raut-can-not-decide-modis-tenure-says-chandrashekhar-bawankule-3472151</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/159369/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/ravindra-chavan-set-to-head-maha-bjp-says-bawankule/articleshow/121504377.cms</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-leader-chandrashekhar-bawankule-explanation-on-viral-video-of-eknath-shinde/articleshow/122165237.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/maharashtra-ministers-reach-agreement-on-key-welfare-issues-after-bawankule-led-talks/articleshow/122256747.cms</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/162383/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-plans-to-reform-modernise-revenue-dept-by-2029/articleshow/123067789.cms</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160516/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/state-to-soon-have-a-new-artificial-sand-policy-bawankule/articleshow/120441502.cms</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/167572/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/chandrashekhar-bawankule-denies-making-calls-to-protect-deepak-kate-amid-solapur-assault-row-23584795</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160368/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-hints-at-major-land-law-reform-amend-plot-size-restrictions/articleshow/122032769.cms</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/164382/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/the-nomadic-community-will-get-ration-anywhere-in-the-state-says-revenue-minister-chandrashekhar-bawankule/articleshow/121208499.cms</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/5/case-registered-against-those-who-harassed-the-police-in-the-name-of-guardian-minister-bawankule.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/government-employees-will-be-threatened-those-who-run-away-from-the-office-are-no-longer-safe-directed-by-chandrasekhar-bawankule/04241205</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/macau-jibe-to-advt-row-cong-bjp-maha-chiefs-in-war-of-words/articleshow/120529370.cms</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/stamp-duty-of-500-on-affidavits-for-government-offices-waived-relief-for-lakhs-of-students-chanrashekhar-bavankule-decision-1347510</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/bawankule-assures-dialogue-with-farmers-amid-purandar-airport-land-acquisition-protests-101746380590787.html</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/what-action-will-the-revenue-department-take-during-the-campaign-from-august-1-to-7-1447199.html</t>
+          <t>https://www.indiatvnews.com/maharashtra/no-salary-for-employees-without-face-app-attendance-says-maharashtra-revenue-minister-chandrashekhar-bawankule-2025-07-23-1000274</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/sambhaji-brigade-pravin-gaikwad-press-conference-pune-alleges-devendra-fadnavis-and-chandrashekhar-bawankule-supports-deepak-kate-maharashtra-news-mhs25071605756</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/infra-works-delay-bawankule-slams-nmc-over-non-utilisation-of-rs310cr/articleshow/122410221.cms</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-land-measurement-maharashtra-government-fixed-fee-for-land-measurement-at-rs-200-benefit-to-farmers-for-division-of-land-73753</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-quashes-rift-rumours-asserts-mahayuti-will-contest-local-polls-unitedly/articleshow/121448703.cms</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/maharashtra-will-cancel-fake-birth-certificates-issued-to-illegal-bangladeshi-residents-says-minister-bawankule/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/bawankule-slams-pune-land-records-dept-hints-sit-probe-into-illegal-ownership-changes-101746467026560.html</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/government-approved-1660-petrol-pumps-in-maharashtra-single-window-system-starts-know-how-to-apply-7822420</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/bawankule-asks-for-alternatives-as-meeting-with-farmers-over-purandar-airport-ends-in-stalemate/articleshow/120909800.cms</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/159853/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-state-chief-asks-dhas-munde-to-bury-the-hatchet-101739560133748.html</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/business/real-estate-news/date-fixed-for-implementation-of-one-state-one-registration/articleshow/119943476.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/maharashtra-to-relax-fragmentation-law-sop-soon-bawankule/articleshow/122458237.cms</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/bjp-has-no-link-with-attack-on-sambhaji-brigade-leader-minister-bawankule-3628848</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-congress-backs-rahul-gandhis-poll-rigging-allegations-demands-fadnavis-resignation-3601125</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/empty-out-the-congress-chandrashekhar-bawankule-tells-partymen-101746471227225.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/who-reads-saamana-who-listens-to-them-asks-bawankule/articleshow/121541164.cms</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-revenue-minister-chandrashekhar-bawankule-implements-nagpur-model-for-farm-road-construction/ar-AA1yyeMo</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/another-blow-to-shinde-bawankule-slams-cidco-over-naina-planning-101756150390930.html</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-urges-restraint-on-political-street-fights/articleshow/122819890.cms</t>
+          <t>https://www.hindustantimes.com/india-news/no-75-year-retirement-rule-in-bjp-maharashtra-chief-counters-sanjay-raut-s-remark-on-modi-101743498262416.html</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/maharashtra-bjp-chief-chandrashekhar-bawankule-urges-party-workers-to-empty-congress-induct-its-leaders-8334573</t>
+          <t>https://www.business-standard.com/politics/nagpur-violence-bjp-s-bawankule-calls-for-peace-as-police-detain-over-20-125031800026_1.html</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/govt-firm-on-purandar-airport-project-chandrashekhar-bawankule-101746466486230.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-takes-stock-of-damage-caused-due-to-unseasonal-rain/articleshow/121580211.cms</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/maharashtra-minister-apologises-to-b-r-gavai-chief-justice-over-protocol-lapse-in-mumbai-8456034</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/bawankule-urges-bjp-cadre-to-bring-in-congress-leaders-empty-the-party-101746466905147.html</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-should-check-voter-lists-now-quips-chandrashekhar-bawankule/articleshow/123351307.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-probe-illegal-transfer-of-1-628-land-parcels-to-nontribals-101752087826955.html</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/confusion-in-bjp-over-induction-of-ex-sena-ubt-leader-bawankule-unaware-of-move-3589681</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/raj-thackeray-uddhav-thackeray-victory-rally-no-traffic-diversions-for-sena-mns-rally-23583195</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/devendra-fadnavis-to-remain-maharashtra-cm-till-2034-says-chandrashekhar-bawankule-23527680</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-directs-nmc-to-repair-roads-immediately/articleshow/121893777.cms</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bawankule-meets-sulking-shirsat-amid-funds-diversion-controversy-101749670372918.html</t>
+          <t>https://www.msn.com/en-in/news/India/no-affidavit-on-500-stamp-paper-for-students-says-revenue-minister-chandrashekhar-bawankule/ar-AA1AjwfL</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/our-caste-is-bjp-we-serve-the-nation-gadkari/articleshow/120044597.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-warns-against-lapses-in-koradi-textile-project/articleshow/122212627.cms</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/chandrashekhar-bawankule-welcomes-chhagan-bhujbals-induction-into-maharashtra-cabinet-calls-it-a-boost-for-govt-23547724</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/very-shameless-statement-chandrashekhar-bawankule-slams-vijay-wadettiwars-remark-on-pahalgam-terror-attack-23530298</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/no-75-year-age-rule-in-bjp-sanjay-raut-can-not-decide-modis-tenure-says-chandrashekhar-bawankule-3472151</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/bawankule-faces-flak-for-sharing-stage-with-accused-in-tuljapur-drugs-case/articleshow/123196303.cms</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ravindra-chavan-set-to-head-maha-bjp-says-bawankule/articleshow/121504377.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/ravindra-chavan-to-be-new-bjp-chief-for-maharashtra-3609432</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/maharashtra-ministers-reach-agreement-on-key-welfare-issues-after-bawankule-led-talks/articleshow/122256747.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/clear-pending-water-projects-on-priority-bawankule/articleshow/122077229.cms</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-plans-to-reform-modernise-revenue-dept-by-2029/articleshow/123067789.cms</t>
+          <t>https://www.indiatoday.in/india/story/maharashtra-to-bring-anti-conversion-law-investigate-unauthorised-churches-2753435-2025-07-09</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/state-to-soon-have-a-new-artificial-sand-policy-bawankule/articleshow/120441502.cms</t>
+          <t>https://www.ndtv.com/india-news/maharashtra-special-public-security-bill-2024-tabled-to-tackle-urban-naxalism-8852342</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-hints-at-major-land-law-reform-amend-plot-size-restrictions/articleshow/122032769.cms</t>
+          <t>https://m.economictimes.com/news/india/maharashtra-govt-starts-second-phase-of-land-title-updating/articleshow/120827478.cms</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/the-nomadic-community-will-get-ration-anywhere-in-the-state-says-revenue-minister-chandrashekhar-bawankule/articleshow/121208499.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/no-one-will-dare-maharashtra-plans-tough-law-against-religious-conversions-revenue-minister-tells-assembly-uike-pledges-to-bring-converted-tribals-back/articleshow/122363837.cms</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
+          <t>https://www.aninews.in/news/national/general-news/part-of-maharashtras-tradition-chandrashekhar-bawankule-responds-to-uddhav-thackerays-praise-for-cm-fadnavis20250723103612</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/macau-jibe-to-advt-row-cong-bjp-maha-chiefs-in-war-of-words/articleshow/120529370.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-govt-to-bring-strict-anti-conversion-law-minister-3622288</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/saamanas-writings-are-damaging-uddhav-says-bawankule-amid-row-over-phule-comments/articleshow/120289982.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/maha-govt-plans-new-land-acquisition-rules-to-speed-up-projects-assure-farmers-fair-compensation/articleshow/123144329.cms</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/chandrashekhar-bawankule-denies-making-calls-to-protect-deepak-kate-amid-solapur-assault-row-23584795</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/rahul-gandhis-vote-theft-claims-are-baseless-childish-chandrashekhar-bawankule-23588752</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/bawankule-assures-dialogue-with-farmers-amid-purandar-airport-land-acquisition-protests-101746380590787.html</t>
+          <t>https://www.cnbctv18.com/india/politics/maharashtra-bjp-chief-chandrashekhar-bawankule-congress-remark-poaching-leaders-controversy-19599239.htm</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/no-salary-for-employees-without-face-app-attendance-says-maharashtra-revenue-minister-chandrashekhar-bawankule-2025-07-23-1000274</t>
+          <t>https://www.nagpurtoday.in/bawankule-hits-back-at-uddhav-calls-his-marathi-stand-political-drama-ahead-of-polls/07051714</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-pushes-for-speedy-execution-of-pench-irri-schemes/articleshow/120215813.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/10-crore-tree-plantation-drive-a-shared-responsbility-reiterates-bawankule/articleshow/122423491.cms</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/infra-works-delay-bawankule-slams-nmc-over-non-utilisation-of-rs310cr/articleshow/122410221.cms</t>
+          <t>https://thelivenagpur.com/2025/08/05/nagpur-case-filed-against-three-for-misusing-minister-chandrashekhar-bawankules-name-to-intimidate-police-at-friendship-day-party/</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-quashes-rift-rumours-asserts-mahayuti-will-contest-local-polls-unitedly/articleshow/121448703.cms</t>
+          <t>https://www.hindustantimes.com/india-news/no-right-maharashtra-bjp-chiefs-dig-at-rahul-gandhi-on-caste-census-timeline-demand-101746088832797.html</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/bawankule-slams-pune-land-records-dept-hints-sit-probe-into-illegal-ownership-changes-101746467026560.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/no-discord-in-maha-yuti-govt-bawankule-dismisses-reports-of-credit-game-over-pahalgam-rescue-op-3510596</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/bawankule-asks-for-alternatives-as-meeting-with-farmers-over-purandar-airport-ends-in-stalemate/articleshow/120909800.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/encroachment-visible-on-govt-land-no-fake-docus-used-bawankule/articleshow/122394983.cms</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-state-chief-asks-dhas-munde-to-bury-the-hatchet-101739560133748.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/take-strict-action-against-illegal-soil-transportation-embezzlement-of-royalties-in-thane-bawankule-to-officials-23515104</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/maharashtra-to-relax-fragmentation-law-sop-soon-bawankule/articleshow/122458237.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/needy-farmers-to-get-loan-waiver-not-those-building-farmhouses-bungalows-minister-bawankule-3683575</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-congress-backs-rahul-gandhis-poll-rigging-allegations-demands-fadnavis-resignation-3601125</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/state-govt-bawankule-behind-ink-attack-pravin-gaikwad/articleshow/122592422.cms</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/who-reads-saamana-who-listens-to-them-asks-bawankule/articleshow/121541164.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-pushes-for-people-centric-development-weekly-village-visits-fast-track-projects-under-annual-plan/articleshow/123127176.cms</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/another-blow-to-shinde-bawankule-slams-cidco-over-naina-planning-101756150390930.html</t>
+          <t>https://www.newsband.in/article_detail/rss-chiefs-anecdote-on-75-sparks-political-speculation-bjp-dismisses-retirement-talk</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/politics/india-bloc-disintegrating-as-it-doesn-t-have-ideology-bjp-s-bawankule-125011300459_1.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-promises-sop-in-3-months-to-resolve-zudpi-jungle-land-issue-in-vidarbha/articleshow/122394160.cms</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/no-75-year-retirement-rule-in-bjp-maharashtra-chief-counters-sanjay-raut-s-remark-on-modi-101743498262416.html</t>
+          <t>https://aninews.in/news/national/politics/chandrashekhar-bawankule-welcomes-ncps-chhagan-bhujbal-in-maharashtra-cabinet-calls-it-a-boost-for-govt20250520094044/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/politics/nagpur-violence-bjp-s-bawankule-calls-for-peace-as-police-detain-over-20-125031800026_1.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-to-appoint-rss-workers-as-pas-to-its-ministers-101737571872713.html</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-takes-stock-of-damage-caused-due-to-unseasonal-rain/articleshow/121580211.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/velhe-taluka-in-pune-district-renamed-as-rajgad-announces-maharashtra-minister-bawankule-3691509</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-probe-illegal-transfer-of-1-628-land-parcels-to-nontribals-101752087826955.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/gym-owner-faces-case-for-online-content-against-bawankule/articleshow/123395126.cms</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/bawankule-urges-bjp-cadre-to-bring-in-congress-leaders-empty-the-party-101746466905147.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-to-allow-hoardings-on-vacant-land-owned-by-govt-bawankule-101750872010984.html</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/raj-thackeray-uddhav-thackeray-victory-rally-no-traffic-diversions-for-sena-mns-rally-23583195</t>
+          <t>https://www.nagpurtoday.in/bawankule-slams-uddhav-thackeray-over-saamana-says-political-relevance-under-threat/04141830</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-directs-nmc-to-repair-roads-immediately/articleshow/121893777.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/act-against-illegal-plotting-mining-in-yeolewadi-kondhwa-katraj-areas-bawankule-101748459992922.html</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-warns-against-lapses-in-koradi-textile-project/articleshow/122212627.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/50-of-bhandara-city-located-on-nazul-land-govt-to-regularize-these-properties-bawankule/articleshow/123103215.cms</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/maharashtra-special-public-security-bill-2024-tabled-to-tackle-urban-naxalism-8852342</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-to-enact-law-against-religious-conversions-demolish-illegal-churches-in-tribal-districts-101752088546524.html</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/bawankule-faces-flak-for-sharing-stage-with-accused-in-tuljapur-drugs-case/articleshow/123196303.cms</t>
+          <t>https://m.economictimes.com/news/india/maharashtra-govt-to-relax-land-fragmentation-law-subdivided-plots-up-to-jan-1-to-become-legal/articleshow/122343682.cms</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/clear-pending-water-projects-on-priority-bawankule/articleshow/122077229.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-orders-probe-into-bid-to-usurp-42-acre-of-forest-land-in-nagpur-three-clerks-suspended-101746816714894.html</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/no-one-will-dare-maharashtra-plans-tough-law-against-religious-conversions-revenue-minister-tells-assembly-uike-pledges-to-bring-converted-tribals-back/articleshow/122363837.cms</t>
+          <t>https://www.nagpurtoday.in/bawankule-to-opposition-show-proof-or-stop-defaming/07211731</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/part-of-maharashtras-tradition-chandrashekhar-bawankule-responds-to-uddhav-thackerays-praise-for-cm-fadnavis20250723103612</t>
+          <t>https://www.hindustantimes.com/india-news/childish-move-bjp-slams-entitled-dynast-rahul-gandhi-over-eci-allegations-maharashtra-polls-101749324813073.html</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-govt-to-bring-strict-anti-conversion-law-minister-3622288</t>
+          <t>https://www.etvbharat.com/en/!state/14-telangana-villages-will-be-merged-in-maharashtra-enn25071602801</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-assures-timely-relief-for-rain-hit-farmers-as-per-norms/articleshow/120074385.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/government-to-remove-non-agricultural-land-use-requirement-for-industries-101738952544368.html</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/10-crore-tree-plantation-drive-a-shared-responsbility-reiterates-bawankule/articleshow/122423491.cms</t>
+          <t>https://theprint.in/india/attack-on-sambhaji-brigade-leader-made-no-calls-to-save-accused-says-bawankule/2690539/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-sets-july-15-deadline-for-document-distribution-to-all-dnts/articleshow/121347284.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/divisional-revenue-commissionerate-to-be-set-up-in-latur-or-nanded-chandrashekhar-bawankule-23489288</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-tells-every-dept-to-set-up-nurseries-on-its-land/articleshow/122410853.cms</t>
+          <t>https://www.ptinews.com/story/national/bawankule-s-statement-about-case-involving-navneet-rana-misleading-cong-writes-to-ec-sc/1389710</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/india/politics/maharashtra-bjp-chief-chandrashekhar-bawankule-congress-remark-poaching-leaders-controversy-19599239.htm</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/hc-acquits-all-2006-train-blasts-accused-maharashtra-govt-will-study-order-says-chandrashekhar-bawankule-23585741</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-hits-back-at-uddhav-calls-his-marathi-stand-political-drama-ahead-of-polls/07051714</t>
+          <t>https://www.ptinews.com/story/national/bjp-has-no-link-with-attack-on-sambhaji-brigade-leader-minister-bawankule/2725525</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/08/05/nagpur-case-filed-against-three-for-misusing-minister-chandrashekhar-bawankules-name-to-intimidate-police-at-friendship-day-party/</t>
+          <t>https://www.aninews.in/news/national/general-news/why-did-he-not-lodge-a-complaint-at-the-police-station-on-the-same-day-bjps-bawankule-over-sharad-pawars-claims20250809213444/</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/maharashtra-govt-starts-second-phase-of-land-title-updating/articleshow/120827478.cms</t>
+          <t>https://www.thehitavada.com/Encyc/2025/1/24/Central-Jail-to-be-shifted-near-Babhulkheda-Bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/rahul-gandhis-vote-theft-claims-are-baseless-childish-chandrashekhar-bawankule-23588752</t>
+          <t>https://www.business-standard.com/pti-stories/national/maharashtra-govt-plans-to-curb-illegal-sand-mining-through-drone-based-surveys-125060600147_1.html</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ladki-bahin-gets-336cr-from-tribal-dept-min-denies/articleshow/121385494.cms</t>
+          <t>https://www.thehitavada.com/Encyc/2025/3/3/Devpt-works-worth-Rs-164-61-cr-for-Dhapewada-kick-off.html</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-meets-protesting-bachchu-kadu-cong-backs-his-stir/articleshow/121836362.cms</t>
+          <t>https://www.thehitavada.com/Encyc/2025/2/2/Rs-2-065-cr-approved-by-District-Planning-Committee-for-2025-26.html</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/needy-farmers-to-get-loan-waiver-not-those-building-farmhouses-bungalows-minister-bawankule-3683575</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/koradi-to-get-butterfly-garden-7d-theatre-worlds-tallest-hanuman-statue-bawankule/articleshow/122844552.cms</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-hits-back-at-raut-over-his-outburst-against-sharad-pawar/02131733</t>
+          <t>https://www.business-standard.com/india-news/maharashtra-govt-to-legalise-subdivided-land-plots-formed-till-jan-1-2025-125070900961_1.html</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-promises-sop-in-3-months-to-resolve-zudpi-jungle-land-issue-in-vidarbha/articleshow/122394160.cms</t>
+          <t>https://lokmat.news18.com/short-videos/trending/vaibhav-naik-news-uddhav-thackeray-s-shiladhar-chandrashekhar-bawankule-meets-n18s-1070283.html</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/politics/chandrashekhar-bawankule-welcomes-ncps-chhagan-bhujbal-in-maharashtra-cabinet-calls-it-a-boost-for-govt20250520094044/</t>
+          <t>https://www.nagpurtoday.in/no-loan-waiver-for-farmhouse-or-mercedes-owners-bawankule-clarifies-policy-for-needy-farmers-only/06280958</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/shinde-mahajan-were-in-kashmir-to-serve-not-score-points-bawankule/articleshow/120629012.cms</t>
+          <t>https://www.nagpurtoday.in/bawankule-fires-back-at-rahul-over-voter-surge-claim-was-there-a-scam-in-2009-too/06071145</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/rahul-gandhi-lacks-mentality-to-accept-defeat-bawankule/02071649</t>
+          <t>https://realty.economictimes.indiatimes.com/news/infrastructure/maharashtra-government-to-begin-campaign-from-april-1-to-update-7/12-land-title-records/119479129</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/in-direct-public-outreach-bawankule-holds-3rd-janata-darbar-in-a-month/articleshow/121553803.cms</t>
+          <t>https://aninews.in/news/national/general-news/are-congress-leaders-trying-to-exonerate-terrorists-maharashtra-bjp-president-on-wadettiwars-remark20250429084410/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-to-enact-law-against-religious-conversions-demolish-illegal-churches-in-tribal-districts-101752088546524.html</t>
+          <t>https://www.nagpurtoday.in/modi-is-not-a-show-he-is-a-roadshow-of-development-bawankule-slams-rahul/07261259</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/social-media-influencers-on-radar-strict-monitoring-for-ram-navami-bawankule/articleshow/120024432.cms</t>
+          <t>https://www.nagpurtoday.in/now-sand-mafias-to-face-criminal-charges-not-just-fines-bawankule/07181631</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/maharashtra-govt-to-relax-land-fragmentation-law-subdivided-plots-up-to-jan-1-to-become-legal/articleshow/122343682.cms</t>
+          <t>https://www.nagpurtoday.in/friendship-day-party-controversy-vedant-chhabria-says-sorry-to-bawankule-in-exclusive-nagpur-today-video/08090717</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/divisional-revenue-commissionerate-to-be-set-up-in-latur-or-nanded-chandrashekhar-bawankule-23489288</t>
+          <t>https://www.aninews.in/news/national/politics/rahul-gandhis-remark-on-govts-foreign-policy-unfortunate-maharashtra-bjp-chief-bawankule20250524112058</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/government-to-remove-non-agricultural-land-use-requirement-for-industries-101738952544368.html</t>
+          <t>https://www.nagpurtoday.in/bawankules-sharp-attack-on-uddhav-rakes-up-rs-100-crore-extortion-case/08111455</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/hc-acquits-all-2006-train-blasts-accused-maharashtra-govt-will-study-order-says-chandrashekhar-bawankule-23585741</t>
+          <t>https://www.mid-day.com/news/india-news/article/maharashtra-launches-one-district-one-registration-scheme-for-property-23535200</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://telanganatoday.com/maharashtra-minister-declares-14-villages-from-telangana-would-be-merged-with-chandrapur-district</t>
+          <t>https://thelivenagpur.com/2025/08/10/guardian-minister-bawankule-orders-high-level-inquiry-into-koradi-incident/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/rahul-gandhi-should-felicitate-pm-modi-openly-maharashtra-bjp-president-bawankule-on-centres-decision-for-caste-census20250501135229</t>
+          <t>https://www.nagpurtoday.in/resolve-citizens-grievances-promptly-and-effectively-bawankule-directs-officials/06021151</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/maharashtra-govt-to-legalise-subdivided-land-plots-formed-till-jan-1-2025-125070900961_1.html</t>
+          <t>https://timesproperty.com/news/post/maha-govt-to-launch-vertical-7-12-document-system-for-multi-floor-homes-blid10102</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/file-criminal-cases-against-those-blocking-farm-roads-bawankule/02071333</t>
+          <t>https://www.aninews.in/news/national/general-news/rahul-gandhi-is-troubled-by-electoral-defeats-maharashtra-bjp-chief-on-election-rigging-allegations20250607234624/</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/short-videos/trending/vaibhav-naik-news-uddhav-thackeray-s-shiladhar-chandrashekhar-bawankule-meets-n18s-1070283.html</t>
+          <t>https://www.nagpurtoday.in/friendship-day-bash-turns-chaotic-main-bawankule-se-baat-kar-leta-hoon-organisers-threat-to-cops-caught-on-camera/08050821</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-approves-policy-for-promoting-artificial-sand-101747164656571.html</t>
+          <t>https://www.nagpurtoday.in/video-bawankule-unfurled-tricolour-at-kasturchand-park/01260936</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-fires-back-at-rahul-over-voter-surge-claim-was-there-a-scam-in-2009-too/06071145</t>
+          <t>https://www.nagpurtoday.in/bachchu-kadu-ends-stir-in-amravati-after-bawankules-assurances/06141705</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/maharashtra-govt-to-have-single-window-system-for-approval-process-of-1660-petrol-pumps-enn25022807370</t>
+          <t>https://www.nagpurtoday.in/bawankule-slams-congress-for-questioning-operation-sindoor/07291623</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/maharashtra-govt-will-take-balanced-decision-on-temple-inam-land-issue-says-bawankule-enn25032407754</t>
+          <t>https://www.nagpurtoday.in/the-constitution-is-the-backbone-of-indias-development-maharashtra-minister-bawankule-pays-tribute-to-dr-ambedkar-in-nagpur/04141639</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/big-relief-for-students-citizens-bawankule-announces-waiver-of-rs-500-stamp-duty-for-affidavits/03051617</t>
+          <t>https://www.nagpurtoday.in/bring-entire-city-under-cctv-surveillance-guardian-minister-chandrashekhar-bawankules-directive/04121754</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/rahul-gandhis-remark-on-govts-foreign-policy-unfortunate-maharashtra-bjp-chief-bawankule20250524112058</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-cabinet-meet-ndas-vice-presidential-candidate-c-p-radhakrishnan-in-mumbai-23591080</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/08/10/guardian-minister-bawankule-orders-high-level-inquiry-into-koradi-incident/</t>
+          <t>https://www.nagpurtoday.in/west-nagpur-mla-thakre-exposes-pmay-scam-bawankule-asks-housing-minister-to-order-probe/06051215</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-discusses-issue-of-encroachment-on-rural-roads/01211724</t>
+          <t>https://www.nagpurtoday.in/koradi-temple-gate-collapse-guardian-minister-orders-probe-assures-action/08101755</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://timesproperty.com/news/post/maha-govt-to-launch-vertical-7-12-document-system-for-multi-floor-homes-blid10102</t>
+          <t>https://www.nagpurtoday.in/nagpur-man-booked-for-defaming-minister-bawankule-on-social-media/08200806</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://www.sarkaritel.com/maha-govt-to-launch-online-property-registration-from-may-1/</t>
+          <t>https://thelivenagpur.com/2025/05/14/kamptee-hospital-to-get-50-more-beds-6-acres-land-allotted-bawankule/</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/7-11-train-blasts-maharashtra-govt-will-study-acquittal-order-before-deciding-next-legal-step-13304293.html</t>
+          <t>https://www.nagpurtoday.in/drinking-water-crisis-in-nagpur-district-to-be-resolved-soon-bawankule/04261228</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/1/28/Finally-Somalwada-underpass-to-be-inaugurated-today.html</t>
+          <t>https://www.sarkaritel.com/maha-govt-to-launch-online-property-registration-from-may-1/</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/india/maharashtra-mandates-3-metre-width-for-farm-roads-other-rights-in-land-records-ws-l-19609629.htm</t>
+          <t>https://www.nagpurtoday.in/bawankule-inspects-farm-access-road-in-katol-stresses-quality-execution/05311731</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/04/very-shameless-statement-chandrashekhar-bawankule-slams-vijay-wadettiwars-remark-on-pahalgam-attack/</t>
+          <t>https://www.nagpurtrends.com/articles/chandrashekhar-bawankule-to-unfurl-tricolour-at-nagpurs-republic-day-kG2xyj</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://www.nagpurtrends.com/articles/chandrashekhar-bawankule-to-unfurl-tricolour-at-nagpurs-republic-day-kG2xyj</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-orders-crackdown-on-illegal-mining-craters-after-child-deaths/articleshow/122393943.cms</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-maharashtra-minister-bawankules-call-to-empty-congress-sparks-debate-clarifies-stance-amid-opposition-criticism/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-to-head-panel-on-farm-roads/articleshow/123103819.cms</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-revenue-minister-chandrashekhar-bawankule-promises-best-compensation-for-purandar-airport-land-acquisition/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticizes-uddhav-for-opposing-maharashtra-security-bill/articleshow/122410846.cms</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-revenue-minister-chandrashekhar-bawankule-backs-purandar-airport-urges-farmers-to-voice-grievances-directly/</t>
+          <t>https://www.hindustantimes.com/india-news/maharashtra-cabinet-reshuffle-buzz-final-decision-rests-with-cm-fadnavis-says-bawankule-101753525179967.html</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/?p=6725428</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/maha-finalizes-new-policy-to-regulate-hoardings-on-government-land/articleshow/122098695.cms</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-crackdown-ordered-on-illegal-plotting-and-mining-in-yeolewadi-kondhwa-and-katraj-minister-bawankule/</t>
+          <t>https://www.ptinews.com/story/business/megha-engineering-infrastructure-fined-rs-94-crore-for-illegal-excavation-maharashtra-minister/2719861</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/entertainment/events/chandrashekhar-bawankules-initiative-brings-a-timeless-epic-to-life/articleshow/117122781.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/90-water-conservation-structures-non-functional-bawankule/articleshow/121711476.cms</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/functionaries-fret-as-bawankule-welcomes-members-from-oppn-parties/articleshow/121683858.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/oppn-drags-fadnavis-into-koratkar-row-bjp-denies-ties-101743273793055.html</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-orders-crackdown-on-illegal-mining-craters-after-child-deaths/articleshow/122393943.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-assures-timely-relief-for-rain-hit-farmers-as-per-norms/articleshow/120074385.cms</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/owners-willingly-giving-up-land-for-civic-projects-in-maharashtra-may-receive-additional-benefits-says-chandrashekhar-bawankule/articleshow/119555188.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bhandara-illegal-sand-mining-2-revenue-officers-suspended/articleshow/120138193.cms</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-mahayuti-expansion-only-after-consensus-among-allies/articleshow/117496923.cms</t>
+          <t>https://www.nagpurtoday.in/bawankule-hits-back-at-raut-over-his-outburst-against-sharad-pawar/02131733</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/maharashtras-love-jihad-law-to-be-strictest-in-india-minister-chandrashekhar-bawankule/articleshow/118295093.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-meets-protesting-bachchu-kadu-cong-backs-his-stir/articleshow/121836362.cms</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-condemns-kharges-kumbh-mela-comments-demands-apology/articleshow/117652890.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/our-doors-are-open-for-badgujar-bawankule/articleshow/121655948.cms</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-to-head-panel-on-farm-roads/articleshow/123103819.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/bjp-targeting-1-5-cr-party-members-in-maha-ahead-of-civic-polls-bawankule/articleshow/118309658.cms</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pending-maharera-recovery-cases-to-be-disposed-of-within-3-months-bawankule/articleshow/118947932.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/shiv-sena-minister-meets-raj-thackeray-at-his-mumbai-residence-3417200</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticizes-uddhav-for-opposing-maharashtra-security-bill/articleshow/122410846.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/maha-govt-allows-24-hour-sand-transport/articleshow/122256742.cms</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/probe-rauts-book-for-remarks-on-judicial-process-bawankule/articleshow/121219474.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ladki-bahin-gets-336cr-from-tribal-dept-min-denies/articleshow/121385494.cms</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/people-will-decide-when-modi-should-retire-not-sanjay-raut-bawankule/articleshow/119881247.cms</t>
+          <t>https://www.nagpurtoday.in/nagpur-violence-bawankule-meets-injured-police-officers-personnel-in-hospital/03182025</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/maharashtra-cabinet-reshuffle-buzz-final-decision-rests-with-cm-fadnavis-says-bawankule-101753525179967.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/law-on-land-fragmentation-to-be-scrapped/articleshow/122349434.cms</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/megha-engineering-infrastructure-fined-rs-94-crore-for-illegal-excavation-maharashtra-minister/2719861</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-sets-july-15-deadline-for-document-distribution-to-all-dnts/articleshow/121347284.cms</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/90-water-conservation-structures-non-functional-bawankule/articleshow/121711476.cms</t>
+          <t>https://www.nagpurtoday.in/rahul-gandhi-lacks-mentality-to-accept-defeat-bawankule/02071649</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bhandara-illegal-sand-mining-2-revenue-officers-suspended/articleshow/120138193.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/revenue-minister-orders-demolition-of-unauthorised-bungalows-in-mumbai-two-officials-suspended-for-crz-map-manipulation/articleshow/118855995.cms</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/oppn-drags-fadnavis-into-koratkar-row-bjp-denies-ties-101743273793055.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-approves-policy-for-promoting-artificial-sand-101747164656571.html</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/state-govt-bawankule-behind-ink-attack-pravin-gaikwad/articleshow/122592422.cms</t>
+          <t>https://www.nagpurtoday.in/resolve-public-issues-on-priority-bawankule-directs-administration/03241323</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/our-doors-are-open-for-badgujar-bawankule/articleshow/121655948.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/in-direct-public-outreach-bawankule-holds-3rd-janata-darbar-in-a-month/articleshow/121553803.cms</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/bjp-targeting-1-5-cr-party-members-in-maha-ahead-of-civic-polls-bawankule/articleshow/118309658.cms</t>
+          <t>https://www.nagpurtoday.in/big-relief-for-students-citizens-bawankule-announces-waiver-of-rs-500-stamp-duty-for-affidavits/03051617</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-to-appoint-rss-workers-as-pas-to-its-ministers-101737571872713.html</t>
+          <t>https://www.nagpurtoday.in/dont-repeat-my-mistakes-nitin-gadkaris-candid-advice-to-bawankule-on-caste-based-politics/04071557</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/maha-govt-allows-24-hour-sand-transport/articleshow/122256742.cms</t>
+          <t>https://www.nagpurtoday.in/drones-to-keep-an-eye-on-illegal-mining-across-maharashtra-bawankule/03211218</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/law-on-land-fragmentation-to-be-scrapped/articleshow/122349434.cms</t>
+          <t>https://www.nagpurtoday.in/lets-work-towards-a-developed-maharashtra-urges-nagpur-guardian-minister-bawankule/01271530</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/voter-increase-in-kamptee-due-to-rapid-urbanization-bawankule-on-rahul-allegations/articleshow/121699423.cms</t>
+          <t>https://www.nagpurtoday.in/vidarbha-bhoodan-yagna-mandal-to-be-revamped-bawankule/02071335</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/gym-owner-faces-case-for-online-content-against-bawankule/articleshow/123395126.cms</t>
+          <t>https://www.nagpurtoday.in/bawankule-hails-union-budget-calls-it-a-strong-pillar-for-indias-future/02011547</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/50-of-bhandara-city-located-on-nazul-land-govt-to-regularize-these-properties-bawankule/articleshow/123103215.cms</t>
+          <t>https://www.nagpurtoday.in/bawankule-dares-rahul-gandhi-to-contest-from-kamptee-in-2029-assembly-poll/02101325</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/revenue-minister-orders-demolition-of-unauthorised-bungalows-in-mumbai-two-officials-suspended-for-crz-map-manipulation/articleshow/118855995.cms</t>
+          <t>https://www.nagpurtoday.in/bawankule-seeks-probe-into-sanjay-rauts-book-over-comments-on-judiciary/05171156</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/resolve-public-issues-on-priority-bawankule-directs-administration/03241323</t>
+          <t>https://www.aninews.in/news/national/politics/double-engine-govt-working-in-peoples-best-interests-new-maharashtra-bjp-chief-ravindra-chavan20250702021253</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://realty.economictimes.indiatimes.com/news/infrastructure/maharashtra-government-to-begin-campaign-from-april-1-to-update-7/12-land-title-records/119479129</t>
+          <t>https://thenewsmill.com/2025/07/part-of-maharashtras-tradition-chandrashekhar-bawankule-responds-to-uddhav-thackerays-praise-for-cm-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/pti-stories/national/maharashtra-govt-plans-to-curb-illegal-sand-mining-through-drone-based-surveys-125060600147_1.html</t>
+          <t>https://thenewsmill.com/2025/04/very-shameless-statement-chandrashekhar-bawankule-slams-vijay-wadettiwars-remark-on-pahalgam-attack/</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-to-opposition-show-proof-or-stop-defaming/07211731</t>
+          <t>https://thenewsmill.com/2025/05/chandrashekhar-bawankule-welcomes-ncps-chhagan-bhujbal-in-maharashtra-cabinet-calls-it-a-boost-for-govt/</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-slams-uddhav-thackeray-calls-him-leader-of-aurangzeb-fan-club/03281015</t>
+          <t>https://news.abplive.com/cities/bjp-has-no-rule-of-retirement-at-75-raut-can-t-decide-modi-s-tenure-maharashtra-bjp-chief-1762084</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/friendship-day-party-controversy-vedant-chhabria-says-sorry-to-bawankule-in-exclusive-nagpur-today-video/08090717</t>
+          <t>https://www.punekarnews.in/pune-maharashtra-minister-bawankules-call-to-empty-congress-sparks-debate-clarifies-stance-amid-opposition-criticism/</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/drones-to-keep-an-eye-on-illegal-mining-across-maharashtra-bawankule/03211218</t>
+          <t>https://www.punekarnews.in/pune-revenue-minister-chandrashekhar-bawankule-promises-best-compensation-for-purandar-airport-land-acquisition/</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/friendship-day-bash-turns-chaotic-main-bawankule-se-baat-kar-leta-hoon-organisers-threat-to-cops-caught-on-camera/08050821</t>
+          <t>https://www.punekarnews.in/pune-revenue-minister-chandrashekhar-bawankule-backs-purandar-airport-urges-farmers-to-voice-grievances-directly/</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/dont-repeat-my-mistakes-nitin-gadkaris-candid-advice-to-bawankule-on-caste-based-politics/04071557</t>
+          <t>https://www.mypunepulse.com/good-news-maharashtra-waives-%E2%82%B9500-stamp-duty-on-affidavits-major-relief-for-students-citizens/</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/on-fast-track-bawankule-sets-deadlines-for-nagpurs-development-projects/01231314</t>
+          <t>https://www.mypunepulse.com/pune-crackdown-ordered-on-illegal-plotting-and-mining-in-yeolewadi-kondhwa-and-katraj-minister-bawankule/</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/koradi-temple-gate-collapse-guardian-minister-orders-probe-assures-action/08101755</t>
+          <t>https://www.nagpurtoday.in/bawankule-congratulates-gadkari-for-receiving-lokmanya-tilak-national-award/07231655</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/lets-work-towards-a-developed-maharashtra-urges-nagpur-guardian-minister-bawankule/01271530</t>
+          <t>https://www.orissapost.com/cricketer-kedar-jadhav-joins-bjp/</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-govt-to-cancel-42-000-fake-birth-certificates-of-illegal-bangladeshi-nationals-by-aug-15-23587269</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/our-caste-is-bjp-we-serve-the-nation-gadkari/articleshow/120044597.cms</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/rahul-gandhi-is-troubled-by-electoral-defeats-maharashtra-bjp-chief-on-election-rigging-allegations20250607234624/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/bawankule-hits-back-at-rahul-over-poll-charges-says-he-should-worry-more-about-congress-survival-3402034</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/modi-is-not-a-show-he-is-a-roadshow-of-development-bawankule-slams-rahul/07261259</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/functionaries-fret-as-bawankule-welcomes-members-from-oppn-parties/articleshow/121683858.cms</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/govts-benefits-will-reach-every-citizen-asserts-revenue-minister-bawankule/01231600</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/owners-willingly-giving-up-land-for-civic-projects-in-maharashtra-may-receive-additional-benefits-says-chandrashekhar-bawankule/articleshow/119555188.cms</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/the-constitution-is-the-backbone-of-indias-development-maharashtra-minister-bawankule-pays-tribute-to-dr-ambedkar-in-nagpur/04141639</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-condemns-kharges-kumbh-mela-comments-demands-apology/articleshow/117652890.cms</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-hails-union-budget-calls-it-a-strong-pillar-for-indias-future/02011547</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/prevent-floods-conserve-water-bawankule-to-nmc/articleshow/119353591.cms</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-slams-congress-for-questioning-operation-sindoor/07291623</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/saamanas-writings-are-damaging-uddhav-says-bawankule-amid-row-over-phule-comments/articleshow/120289982.cms</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-dares-rahul-gandhi-to-contest-from-kamptee-in-2029-assembly-poll/02101325</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-mahayuti-expansion-only-after-consensus-among-allies/articleshow/117496923.cms</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/drinking-water-crisis-in-nagpur-district-to-be-resolved-soon-bawankule/04261228</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/maharashtras-love-jihad-law-to-be-strictest-in-india-minister-chandrashekhar-bawankule/articleshow/118295093.cms</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-inspects-farm-access-road-in-katol-stresses-quality-execution/05311731</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-calls-rahul-gandhis-caste-census-push-too-late-to-matter/articleshow/122925629.cms</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/now-get-stamp-papers-by-paying-fees-online-in-maharashtra-bawankule/03251300</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/rahul-gandhi-has-lost-the-plot-says-bawankule-denies-dig-at-bachchu-kadu/articleshow/123103074.cms</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/07/part-of-maharashtras-tradition-chandrashekhar-bawankule-responds-to-uddhav-thackerays-praise-for-cm-fadnavis/</t>
+          <t>https://realty.economictimes.indiatimes.com/news/allied-industries/free-sand-royalty-receipts-to-be-delivered-to-beneficiaries-of-housing-schemes-maharashtra-revenue-minister/121176284</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/05/chandrashekhar-bawankule-welcomes-ncps-chhagan-bhujbal-in-maharashtra-cabinet-calls-it-a-boost-for-govt/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-tells-every-dept-to-set-up-nurseries-on-its-land/articleshow/122410853.cms</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/shiv-sena-ubt-has-realised-its-blunder-of-breaking-alliance-with-bjp-and-siding-with-congress-bawankule-3351296</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/no-biometric-attendance-system-no-salary-for-amravati-state-govt-employees-bawankule/articleshow/122789185.cms</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/bawankule-hits-back-at-rahul-over-poll-charges-says-he-should-worry-more-about-congress-survival-3402034</t>
+          <t>https://www.deccanherald.com/india/maharashtra/former-cricketer-kedar-jadhav-joins-bjp-3484153</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/megha-engineering-infrastructure-fined-rs-94-crore-for-illegal-excavation-maharashtra-minister/articleshow/122393487.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/govt-panel-to-conduct-survey-to-identify-farmers-in-need-of-loan-waiver-in-maharashtra-says-bjp-minister-bawankule/articleshow/123169142.cms</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/rahul-needs-to-come-out-of-dark-shadow-of-defeat-bawankule-on-his-match-fixing-remark-3575806</t>
+          <t>https://www.deccanherald.com/india/maharashtra/rss-holds-two-day-brainstorming-session-with-bjp-allied-outfits-3362607</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/no-blanket-farm-loan-waiver-only-the-most-distressed-to-get-it-bawankule/articleshow/123195407.cms</t>
+          <t>https://www.ndtv.com/india-news/maharashtra-revenue-department-goes-hi-tech-to-ensure-employee-attendance-8944686</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/no-right-maharashtra-bjp-chiefs-dig-at-rahul-gandhi-on-caste-census-timeline-demand-101746088832797.html</t>
+          <t>https://manufacturing.economictimes.indiatimes.com/news/industry/rs-1200-cr-sought-for-nagpur-rs-600-crore-for-amravati/117907831</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-calls-rahul-gandhis-caste-census-push-too-late-to-matter/articleshow/122925629.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-will-cancel-fake-birth-certificates-issued-to-illegal-bangladeshi-residents-state-minister-bawankule-3656548</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/rahul-gandhi-has-lost-the-plot-says-bawankule-denies-dig-at-bachchu-kadu/articleshow/123103074.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/govt-with-you-bawankule-assures-matangs-seeking-sub-quota-benefits-101747768592892.html</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://realty.economictimes.indiatimes.com/news/allied-industries/free-sand-royalty-receipts-to-be-delivered-to-beneficiaries-of-housing-schemes-maharashtra-revenue-minister/121176284</t>
+          <t>https://www.deccanherald.com/india/maharashtra/in-politics-role-keeps-changing-cm-fadnavis-3512825</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/maha-govt-plans-new-land-acquisition-rules-to-speed-up-projects-assure-farmers-fair-compensation/articleshow/123144329.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/social-media-influencers-on-radar-strict-monitoring-for-ram-navami-bawankule/articleshow/120024432.cms</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/childish-move-bjp-slams-entitled-dynast-rahul-gandhi-over-eci-allegations-maharashtra-polls-101749324813073.html</t>
+          <t>https://www.business-standard.com/politics/rahul-upset-over-electoral-losses-maharashtra-bjp-chief-on-rigging-claims-125060700848_1.html</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/no-biometric-attendance-system-no-salary-for-amravati-state-govt-employees-bawankule/articleshow/122789185.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/bawankule-denies-transfer-of-funds-for-ladki-bahin-scheme-from-tribal-development-dept/articleshow/121385644.cms</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/former-cricketer-kedar-jadhav-joins-bjp-3484153</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/tatkare-bawankule-push-for-rapid-launch-of-womens-employment-hub-in-koradi/articleshow/121347327.cms</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-to-allow-hoardings-on-vacant-land-owned-by-govt-bawankule-101750872010984.html</t>
+          <t>https://www.thehitavada.com/Encyc/2025/5/5/%E2%80%98One-district,-One-Registration-for-property-commences-in-Mah.html</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/govt-panel-to-conduct-survey-to-identify-farmers-in-need-of-loan-waiver-in-maharashtra-says-bjp-minister-bawankule/articleshow/123169142.cms</t>
+          <t>https://www.nagpurtoday.in/sc-verdict-on-zudpi-jungle-opens-doors-to-vidarbhas-all-round-development-jobs-bawankule/05231117</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/no-discord-in-maha-yuti-govt-bawankule-dismisses-reports-of-credit-game-over-pahalgam-rescue-op-3510596</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cuts-red-tape-waives-rs-500-stamp-duty-on-affidavits-23495197</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/encroachment-visible-on-govt-land-no-fake-docus-used-bawankule/articleshow/122394983.cms</t>
+          <t>https://www.aninews.in/news/national/general-news/nagpur-fire-maharashtra-govt-announce-rs-5-lakh-to-each-victims-family20250412202335/</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/take-strict-action-against-illegal-soil-transportation-embezzlement-of-royalties-in-thane-bawankule-to-officials-23515104</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/bjp-gets-1-crore-new-members-across-maharashtra-23482502</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/act-against-illegal-plotting-mining-in-yeolewadi-kondhwa-katraj-areas-bawankule-101748459992922.html</t>
+          <t>https://www.mypunepulse.com/pune-bawankule-calls-for-dialogue-as-farmers-protest-purandar-airport-land-acquisition/</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://manufacturing.economictimes.indiatimes.com/news/industry/rs-1200-cr-sought-for-nagpur-rs-600-crore-for-amravati/117907831</t>
+          <t>https://www.mypunepulse.com/no-face-app-no-salary-maharashtra-govt-makes-digital-attendance-compulsory-for-revenue-employees/</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-will-cancel-fake-birth-certificates-issued-to-illegal-bangladeshi-residents-state-minister-bawankule-3656548</t>
+          <t>https://www.nagpurtoday.in/mastermind-behind-nagpur-violence-will-be-identified-bawankule/03181157</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/maharashtra-revenue-department-goes-hi-tech-to-ensure-employee-attendance-8944686</t>
+          <t>https://www.socialnews.xyz/?p=6725428</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/govt-with-you-bawankule-assures-matangs-seeking-sub-quota-benefits-101747768592892.html</t>
+          <t>https://marathi.ndtv.com/cities/chandrashekhar-bawankule-not-aware-of-sudhakar-badgujars-entry-into-bjp-8687548</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/ravindra-chavan-to-be-new-bjp-chief-for-maharashtra-3609432</t>
+          <t>https://mahasamvad.in/174409/</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/ajit-pawar-defends-decision-to-divert-sc-st-funds-to-ladki-bahin-scheme-101746385156890.html</t>
+          <t>https://news18marathi.com/maharashtra/revenue-minister-chandrashekhar-bawankule-important-orders-to-sub-divisional-officer-and-tehsildar-1373523.html</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/illegal-building-that-came-up-on-land-of-ambedkar-heir-in-kalyan-demolished-plot-reclaimed-minister/articleshow/122420767.cms</t>
+          <t>https://mahasamvad.in/171657/</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/politics/rahul-upset-over-electoral-losses-maharashtra-bjp-chief-on-rigging-claims-125060700848_1.html</t>
+          <t>https://mahasamvad.in/170401/</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-pushes-for-people-centric-development-weekly-village-visits-fast-track-projects-under-annual-plan/articleshow/123127176.cms</t>
+          <t>https://mahasamvad.in/172891/</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/not-right-to-cast-doubt-on-vp-dhankhars-resignation-bjp-leader-bawankule-3641964</t>
+          <t>https://marathi.abplive.com/news/maharashtra/chandrashekhar-bawankule-on-sharad-pawar-minister-chandrashekhar-bawankule-criticism-on-sharad-pawar-s-mandal-yatra-1376056</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/law-news/story/supreme-court-status-quo-order-bale-shah-peer-dargah-demolition-2727320-2025-05-20</t>
+          <t>https://marathi.ndtv.com/maharashtra/maharashtra-politics-chandrashekhar-bawankule-big-statement-about-ban-sanjay-rauts-narkatla-swarg-book-8430233</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/velhe-taluka-in-pune-district-renamed-as-rajgad-announces-maharashtra-minister-bawankule-3691509</t>
+          <t>https://www.esakal.com/vidarbha/maharashtra-government-forms-committee-for-farmers-loan-waiver-minister-appeals-to-avoid-haste-in-protests-vsb99</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-minister-bawankule-asks-bmc-to-halt-its-demolition-drive-in-north-mumbai-till-ganeshotsav-23590378</t>
+          <t>https://mahasamvad.in/175785/</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/politics/rahul-gandhis-remark-on-govts-foreign-policy-unfortunate-maharashtra-bjp-chief-bawankule20250524112058/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-bjp-state-president-election-process-begins-chandrashekar-bawankule-defends-public-safety-bill-1367078</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/article/maharashtra-launches-one-district-one-registration-scheme-for-property-23535200</t>
+          <t>https://mahasamvad.in/174971/</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/maharashtra-govt-forms-sit-to-probe-delayed-birth-death-certificates-125012500183_1.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/chandrashekhar-bawankule-reaction-on-bjp-leader-babanrao-lonikar-statement/articleshow/122091225.cms</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/now-sand-mafias-to-face-criminal-charges-not-just-fines-bawankule/07181631</t>
+          <t>https://marathi.abplive.com/news/maharashtra-politics-revenue-minister-chandrashekhar-bawankule-mediation-in-the-issue-of-the-disabled-and-successful-solution-after-six-ministers-discuss-1367752</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>https://realty.economictimes.indiatimes.com/news/infrastructure/maharashtra-government-plans-to-curb-illegal-sand-mining-through-drones/121687914</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/minister-bawankule-questions-opposition-silence-on-honeytrap-claims-vsb99</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/no-funds-diverted-from-other-departments-for-ladki-bahin-scheme-says-bawankule-23565529</t>
+          <t>https://mahasamvad.in/173287/</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/sc-verdict-on-zudpi-jungle-opens-doors-to-vidarbhas-all-round-development-jobs-bawankule/05231117</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/1/strict-action-will-be-taken-against-illegal-sand-miners-on-wardha-river-revenue-minister-chandrashekhar-bawank.html</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-tightens-rules-for-birth-death-certificates-for-foreign-nationals-23498903</t>
+          <t>https://www.loksatta.com/pune/chandrashekhar-bawankule-confesses-illegal-hill-breaking-in-pune-district-pune-print-news-apk-13-zws-70-5222016/</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cuts-red-tape-waives-rs-500-stamp-duty-on-affidavits-23495197</t>
+          <t>https://marathi.ndtv.com/maharashtra/maharashtra-politics-chandrashekhar-bawankule-take-strict-action-on-pwd-department-scam-sting-operation-7921778</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/land-measurement-for-division-in-maharashtra-now-at-rs-200-23548697</t>
+          <t>https://mahasamvad.in/170687/</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/bjp-gets-1-crore-new-members-across-maharashtra-23482502</t>
+          <t>https://mahasamvad.in/172168/</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-bawankule-calls-for-dialogue-as-farmers-protest-purandar-airport-land-acquisition/</t>
+          <t>https://mahasamvad.in/172900/</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/no-face-app-no-salary-maharashtra-govt-makes-digital-attendance-compulsory-for-revenue-employees/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/nagpur-news-saw-the-news-on-abp-majha-chandrashekhar-bawankule-immediately-took-note-with-the-help-of-nitin-gadkari-road-issue-was-resolved-in-an-instant-1377264</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/news/fake-birth-certificates-of-bangladeshis-to-be-cancelled-mahaminister-says-42000-forged-documents-were-issued-to-illegal-immigrants-with-tehsildars-help-to-be-nullified-by-august-15-135565530.html</t>
+          <t>https://mahasamvad.in/170632/</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-on-ladki-bahin-yojana-if-men-have-taken-money-than-file-case-and-the-money-should-also-be-recovered-revenue-minister-instructions-1372671</t>
+          <t>https://mahasamvad.in/175339/</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/chandrashekhar-bawankule-not-aware-of-sudhakar-badgujars-entry-into-bjp-8687548</t>
+          <t>https://mahasamvad.in/170666/</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrashekhar-bawankule-tweet-12-senior-officers-of-the-revenue-department-promoted-by-the-public-service-commission-given-ias-status-by-the-center-1369895</t>
+          <t>https://www.nagpurtoday.in/government-employees-will-be-threatened-those-who-run-away-from-the-office-are-no-longer-safe-directed-by-chandrasekhar-bawankule/04241205</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/revenue-minister-chandrashekhar-bawankule-important-orders-to-sub-divisional-officer-and-tehsildar-1373523.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/26/chandrashekhar-bawankule-on-congress-obc.html</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrashekhar-bawankule-on-sharad-pawar-minister-chandrashekhar-bawankule-criticism-on-sharad-pawar-s-mandal-yatra-1376056</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-praises-pm-narendra-modi-for-operation-sindoor/videoshow/121133822.cms</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172891/</t>
+          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-explained-the-maths-bmc-elections-raj-thackeray-mns-we-are-prepared-for-51-percent-votes-bjp-response-to-thackeray-alliance-1374778</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/maharashtra-politics-chandrashekhar-bawankule-big-statement-about-ban-sanjay-rauts-narkatla-swarg-book-8430233</t>
+          <t>https://mahasamvad.in/172725/</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/maharashtra-politics-chandrashekhar-bawankule-big-statement-order-to-bjp-office-bearers-dismantle-congress-1398359.html</t>
+          <t>https://deshdoot.com/revenue-minister-chandrashekhar-bawankule-to-visit-nashik-on-saturday/</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/maharashtra-government-forms-committee-for-farmers-loan-waiver-minister-appeals-to-avoid-haste-in-protests-vsb99</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/5/it-is-unfortunate-for-this-country-that-such-an-immature-opposition-leader.html</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/wardha-officials-under-pressure-after-bawankules-warning-revenue-department-shaken-by-strict-action-vsd-99-5284677/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-news-state-governments-big-decision-regarding-land-fragmentation-high-level-committee-formed-to-make-reforms-83561</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174971/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/chandrashekhar-bawankule-amravati-news-bjp-minister-chandrashekhar-bawankule-criticizes-on-congress-amravati-1377470</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/sambhaji-brigade-leader-pravin-gaikwad-press-conference-says-devendra-fadnavis-and-chandrashekhar-bawankule-supports-deepak-kate-1370337</t>
+          <t>https://www.nagpurtoday.in/revenue-minister-chandrasekhar-bawankules-announcement-in-the-legislative-assembly-action-against-wrongdoers/03201828</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173287/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/26/chandrashekhar-bawankule-rahul-gandhi-narendra-modi.html</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-bjp-state-president-election-process-begins-chandrashekar-bawankule-defends-public-safety-bill-1367078</t>
+          <t>https://mahasamvad.in/174403/</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/chandrashekhar-bawankule-reaction-on-bjp-leader-babanrao-lonikar-statement/articleshow/122091225.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nashik/bjp-chandrashekhar-bawankule-says-code-of-conduct-will-in-august-for-upcoming-municipal-elections-2025-pri/articleshow/121662946.cms</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra-politics-revenue-minister-chandrashekhar-bawankule-mediation-in-the-issue-of-the-disabled-and-successful-solution-after-six-ministers-discuss-1367752</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-voter-list-deletion-allegations-congress-accuses-sanket-bawankule-of-deleting-thousands-of-voter-names-in-kamthi-assembly-constituency-1378709</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170687/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/1/committee-formed-under-the-chairmanship-of-revenue-minister-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/minister-bawankule-questions-opposition-silence-on-honeytrap-claims-vsb99</t>
+          <t>https://news18marathi.com/maharashtra/revenue-minister-chandrashekhar-bawankule-announded-cancelled-tukde-ban-act-maharashtra-govt-big-decision-1432122.html</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172900/</t>
+          <t>https://www.tv9marathi.com/videos/sudhakar-badgujar-join-bjp-chandrashekhar-bawankule-reaction-1425349.html</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172168/</t>
+          <t>https://www.tarunbharat.com/information-from-revenue-minister-chandrashekhar-bawankule-in-amboli/</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/bacchu-kadu-response-to-chandrashekhar-bawankule-criticism-over-farmers-loan-waiver-issue-maharashtra-politics-marathi-news-1374715</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-uddhav-thackeray-and-bawankule-engage-in-twitter-spat-as-shiv-sena-workers-join-bjp-due-to-leader-unavailability-in-maharashtra-politics-1369935</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-says-revenue-department-faceapp-registration-is-mandatory-for-everyone-from-talatha-to-dy-collector-1372159</t>
+          <t>https://mahasamvad.in/168121/</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/maharashtra-politics-chandrashekhar-bawankule-take-strict-action-on-pwd-department-scam-sting-operation-7921778</t>
+          <t>https://mahasamvad.in/168550/</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/1/strict-action-will-be-taken-against-illegal-sand-miners-on-wardha-river-revenue-minister-chandrashekhar-bawank.html</t>
+          <t>https://mahasamvad.in/167416/</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/chandrashekhar-bawankule-response-sanjay-raut-criticism-1374675.html</t>
+          <t>https://mahasamvad.in/169614/</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/nagpur-news-saw-the-news-on-abp-majha-chandrashekhar-bawankule-immediately-took-note-with-the-help-of-nitin-gadkari-road-issue-was-resolved-in-an-instant-1377264</t>
+          <t>https://mahasamvad.in/166188/</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/chandrashekhar-bawankule-on-raj-thackeray-hindi-language-natioanl-education-policy-8201539</t>
+          <t>https://mahasamvad.in/167907/</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175339/</t>
+          <t>https://mahasamvad.in/167498/</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168918/</t>
+          <t>https://mahasamvad.in/166711/</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/26/chandrashekhar-bawankule-on-congress-obc.html</t>
+          <t>https://mahasamvad.in/168197/</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-praises-pm-narendra-modi-for-operation-sindoor/videoshow/121133822.cms</t>
+          <t>https://mahasamvad.in/160422/</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/chandrashekhar-bawankule-calls-terrorists-naxalites-gaffe-sk95</t>
+          <t>https://marathi.abplive.com/news/mumbai/micro-zoning-to-determine-rates-of-ready-reckoners-in-mumbai-revenue-minister-chandrashekhar-bawankule-decision-marathi-news-1352443</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/revenue-minister-chandrashekhar-bawankule-announced-in-the-legislative-assembly-that-an-inquiry-will-be-conducted-through-a-commissioner-phm-00-5217343/</t>
+          <t>https://mahasamvad.in/165886/</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-bawankule-kadu-row-revenue-minister-and-former-mla-clash-over-disabled-allowance-hike-and-farmers-issues-accusations-of-drama-exchanged-1374782</t>
-        </is>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/172725/</t>
-        </is>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>https://deshdoot.com/revenue-minister-chandrashekhar-bawankule-to-visit-nashik-on-saturday/</t>
-        </is>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/22-day-old-baby-saved-after-severe-burns-minister-intervenes-vsb99</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/5/it-is-unfortunate-for-this-country-that-such-an-immature-opposition-leader.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/politics/sudhakar-badgujar-bjp-party-joining-ceremony-chandrashekhar-bawankule-statement-create-confusion-1364657</t>
-        </is>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/chandrashekhar-bawankule-bjp-explanation-on-remarks-over-splitting-congress-in-maharshtra-politics/articleshow/120903323.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrashekhar-bawankule-amravati-news-bjp-minister-chandrashekhar-bawankule-criticizes-on-congress-amravati-1377470</t>
-        </is>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>https://www.nagpurtoday.in/revenue-minister-chandrasekhar-bawankules-announcement-in-the-legislative-assembly-action-against-wrongdoers/03201828</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/26/chandrashekhar-bawankule-rahul-gandhi-narendra-modi.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/174403/</t>
-        </is>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>https://zeenews.india.com/marathi/video/chandrashekhar-bawankule-meets-bacchu-kadu/914920</t>
-        </is>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nashik/bjp-chandrashekhar-bawankule-says-code-of-conduct-will-in-august-for-upcoming-municipal-elections-2025-pri/articleshow/121662946.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>https://news18marathi.com/maharashtra/revenue-minister-chandrashekhar-bawankule-announded-cancelled-tukde-ban-act-maharashtra-govt-big-decision-1432122.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-voter-list-deletion-allegations-congress-accuses-sanket-bawankule-of-deleting-thousands-of-voter-names-in-kamthi-assembly-constituency-1378709</t>
-        </is>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/1/committee-formed-under-the-chairmanship-of-revenue-minister-bawankule.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/3/28/The-baby-s-life-was-saved-by-the-initiative-of-Guardian-Minister-Chandrashekhar-Bawankule-.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>https://www.loksatta.com/pune/maharashtra-revenue-minister-admits-large-encroachment-on-government-land-pune-print-news-ocd-94-5205178/</t>
-        </is>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/amravati/news/guardian-minister-chandrashekhar-bawankule-announced-a-solar-pump-that-provides-electricity-for-12-hours-a-12-foot-road-and-goods-distribution-under-the-vayoshree-yojana-135151355.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-on-jayant-patil-resigns-shashikant-shinde-new-state-president-of-sharad-pawar-ncp-maharashtra-politics-maharashtra-marathi-news-1369487</t>
-        </is>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-on-agriculture-minister-manikrao-kokate-statement-say-if-agriculture-ministerhas-said-anything-we-will-apologize-on-behalf-of-the-government-maharashtra-politics-1352861</t>
-        </is>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrashekhar-bawankule-on-uddhav-thackeray-in-mumbai-bjp-state-president-chandrashekhar-bawankule-criticizes-on-uddhav-thackeray-1354721</t>
+          <t>https://mahasamvad.in/172338/</t>
         </is>
       </c>
     </row>

--- a/Output/Chandrashekhar Bawankule/extracted_links_Chandrashekhar Bawankule_failed_links.xlsx
+++ b/Output/Chandrashekhar Bawankule/extracted_links_Chandrashekhar Bawankule_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A375"/>
+  <dimension ref="A1:A364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,1498 +438,1498 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/revenue-week-will-be-celebrate-in-the-maharashtra-in-1-to-7-august-says-minister-chandrashekhar-bawankule-maharashtra-news-mhs25073005592</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/revenue-minister-chandrashekhar-bawankule-on-staff-officers-staying-at-headquarters-134898981.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174008/</t>
+          <t>https://www.etvbharat.com/mr/!state/revenue-week-will-be-celebrate-in-the-maharashtra-in-1-to-7-august-says-minister-chandrashekhar-bawankule-maharashtra-news-mhs25073005592</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/mr/farm-road/</t>
+          <t>https://mahasamvad.in/168550/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173290/</t>
+          <t>https://mahasamvad.in/168121/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176111/</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtara-revenue-minister-chandrashekhar-bawankule-on-sindhudurg-tourism-tour-rds-00-5299511/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173830/</t>
+          <t>https://mahasamvad.in/174008/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172967/</t>
+          <t>https://mahasamvad.in/173290/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/3/9/Chandrashekhar-Bawankule-will-carry-out-comprehensive-development-of-Kamathi-city.html</t>
+          <t>https://www.loksatta.com/pune/revenue-minister-chandrashekhar-bawankule-warned-revenue-officials-pune-print-news-ccm-82-mrj-95-4819166/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173944/</t>
+          <t>https://mahasamvad.in/176111/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/government-will-take-a-big-decision-for-snake-lovers-revenue-minister-bawankule-gave-information-8943735</t>
+          <t>https://mahasamvad.in/170401/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176970/</t>
+          <t>https://mahasamvad.in/171657/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174937/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/30/revenue-department-to-implement-revenue-week-in-the-state-from-august-1.html</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176959/</t>
+          <t>https://www.lokmat.com/nagpur/any-party-entry-will-be-possible-only-after-discussions-on-the-platform-of-the-mahayuti-revenue-minister-chandrashekhar-bawankule-said-a-a653/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175334/</t>
+          <t>https://mahasamvad.in/166188/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/171768/</t>
+          <t>https://mahasamvad.in/168197/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nashik/chandrashekhar-bawankule-expressed-anger-on-phone-call-to-chandwad-tehsildar-regarding-working-complaints-pri/articleshow/121389576.cms</t>
+          <t>https://mahasamvad.in/167498/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/bjp-state-president-chandrashekhar-bawankule-apologized-to-chief-justice-bhushan-gavai-on-behalf-of-the-government/articleshow/121268071.cms</t>
+          <t>https://mahasamvad.in/165738/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/government-benefits-will-reach-every-citizen-revenue-minister-chandrashekhar-bawankules-determination/01231556</t>
+          <t>https://mahasamvad.in/173830/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/revenue-minister-chandrashekhar-bawankules-call-to-chandwad-tehsildar-aggressive-reaction-over-complaints-in-bjp-janta-darbar-in-mumbai-video-goes-viral-maharashtra-politics-1361293</t>
+          <t>https://mahasamvad.in/172967/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176956/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/3/9/Chandrashekhar-Bawankule-will-carry-out-comprehensive-development-of-Kamathi-city.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/chandrasekhar-bawankule-felicitation-by-tuljapur-drugs-case-accused-sparks-backlash-9041887</t>
+          <t>https://marathi.abplive.com/news/mumbai/micro-zoning-to-determine-rates-of-ready-reckoners-in-mumbai-revenue-minister-chandrashekhar-bawankule-decision-marathi-news-1352443</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/30/revenue-department-to-implement-revenue-week-in-the-state-from-august-1.html</t>
+          <t>https://mahasamvad.in/173944/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/4/revenue-minister-chandrashekhar-bawankule-makes-announcement-in-assembly-hints-at-action-against-eight-stamp-d.html</t>
+          <t>https://marathi.ndtv.com/politics/government-will-take-a-big-decision-for-snake-lovers-revenue-minister-bawankule-gave-information-8943735</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174605/</t>
+          <t>https://mahasamvad.in/166711/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/minister-chandrashekhar-bawankule-appeals-to-the-opposition-not-to-politicize-the-mumbai-train-accident-maharashtra-news-mhs25060906405</t>
+          <t>https://mahasamvad.in/167416/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/revenue-minister-bawankule-announces-relaxation-fragmentation-law-50-lakh-farmers-relief-277582/amp/</t>
+          <t>https://mahasamvad.in/167907/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/bjp-does-not-do-low-level-acts-chandrashekhar-bawankule-rejects-allegations-in-praveen-gaikwad-attack-case-278013/amp/</t>
+          <t>https://mahasamvad.in/176970/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/166742/</t>
+          <t>https://mahasamvad.in/174937/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/no-new-districts-will-be-created-in-the-state-for-the-time-being-says-revenue-minister-chandrashekhar-bawankule-maharashtra-news-mhs25012302825</t>
+          <t>https://mahasamvad.in/176959/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/6/23/new-law-to-be-introduced-in-monsoon-session-said-chandrashekhar-bawankule.html</t>
+          <t>https://mahasamvad.in/171768/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/drone-watch-on-illegal-minor-mineral-mining-important-decision-of-revenue-minister-bawankule-1362804</t>
+          <t>https://mahasamvad.in/175334/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173545/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/appointment-of-80-additional-district-collectors-in-the-state-a-big-decision-by-revenue-minister-chandrashekhar-bawankule-1355734</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/stamp-duty-of-rs-500-waived-for-various-certificates-including-caste-verification-income-certificate-chandrashekhar-bawankule-263813/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nashik/chandrashekhar-bawankule-expressed-anger-on-phone-call-to-chandwad-tehsildar-regarding-working-complaints-pri/articleshow/121389576.cms</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/dharashiv/revenue-minister-chandrashekhar-bawankule-publicly-felicitated-by-accused-out-on-bail-in-drug-case-1375621</t>
+          <t>https://marathi.abplive.com/news/revenue-minister-chandrashekhar-bawankules-call-to-chandwad-tehsildar-aggressive-reaction-over-complaints-in-bjp-janta-darbar-in-mumbai-video-goes-viral-maharashtra-politics-1361293</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/reconstruction-of-vidarbha-bhoodan-yagna-mandal-to-take-place-revenue-minister-chandrashekhar-bawankules-directive/02071130</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/bjp-state-president-chandrashekhar-bawankule-apologized-to-chief-justice-bhushan-gavai-on-behalf-of-the-government/articleshow/121268071.cms</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/173517/</t>
+          <t>https://www.newsonair.gov.in/mr/farm-road/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/169614/</t>
+          <t>https://mahasamvad.in/176956/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/revenue-department-under-leadership-revenue-minister-chandrashekhar-bawankule-has-taken-18-major-decisions-1413141.html</t>
+          <t>https://marathi.ndtv.com/politics/chandrasekhar-bawankule-felicitation-by-tuljapur-drugs-case-accused-sparks-backlash-9041887</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/revenue-minister-and-guardian-minister-shri-taken-by-chandrasekhar-bawankule/06081251</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/4/revenue-minister-chandrashekhar-bawankule-makes-announcement-in-assembly-hints-at-action-against-eight-stamp-d.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B9%E0%A5%85%E0%A4%B2-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%B8-%E0%A4%B9%E0%A5%87%E0%A4%AC-%E0%A4%82%E0%A4%9A-%E0%A4%AA-%E0%A4%8F-%E0%A4%AC-%E0%A4%B2%E0%A4%A4-%E0%A4%AF-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%9C-%E0%A4%A8%E0%A4%97%E0%A4%B0%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%B2-%E0%A4%95%E0%A5%8D%E0%A4%AF%E0%A5%82%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%A0%E0%A4%B5%E0%A4%B2-%E0%A4%AA%E0%A5%88%E0%A4%B6-%E0%A4%82%E0%A4%9A-%E0%A4%AE-%E0%A4%97%E0%A4%A3-%E0%A4%AA-%E0%A4%B2-%E0%A4%B8-%E0%A4%A4-%E0%A4%A4%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%B0/ar-AA1KFEz1</t>
+          <t>https://mahasamvad.in/174605/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/2/3/One-lakh-94-thousand-special-executive-officers-will-be-appointed-across-the-state-By-Chandrashekhar-Bawankule.html</t>
+          <t>https://marathi.abplive.com/news/nagpur/chandrashekhar-bawankule-order-to-file-fir-against-those-who-misuse-his-name-nagpur-crime-news-1375138</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/crime/sambhajinagar-farmer-demand-money-hello-chandrashekhar-bawankule-pa-is-speaking-qr-sent-to-farmer-in-complaint-to-police-1377664</t>
+          <t>https://www.etvbharat.com/mr/!state/minister-chandrashekhar-bawankule-appeals-to-the-opposition-not-to-politicize-the-mumbai-train-accident-maharashtra-news-mhs25060906405</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/2/3/Chandrashekhar-Bawankule-brought-satisfaction-to-the-Mihan-project-victims.html</t>
+          <t>https://thefocusindia.com/maharashtra-news/revenue-minister-bawankule-announces-relaxation-fragmentation-law-50-lakh-farmers-relief-277582/amp/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/chandrashekhar-bawankule-assures-of-farmers-loan-waivers-after-proper-survey/articleshow/123184635.cms</t>
+          <t>https://thefocusindia.com/maharashtra-news/bjp-does-not-do-low-level-acts-chandrashekhar-bawankule-rejects-allegations-in-praveen-gaikwad-attack-case-278013/amp/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/buldana/revenue-minister-chandrashekhar-bawankule-fake-calling-and-ccheated-fraud-with-farmer/articleshow/123344845.cms</t>
+          <t>https://www.mahasamvad.in/166742/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/22/revenue-department-to-implement-national-leader-to-father-of-the-nation-campaign-revenue-minister-chandrashekh.html</t>
+          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-farmers-loan-waivers-farmers-who-drive-around-in-mercedes-lay-out-farm-house-1366570</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176506/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/4/sub-divisional-officer-suspended-in-land-scam-case-revenue-minister-chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-news-revenue-minister-warns-of-strict-action-against-illegal-sand-mining-now-joint-action-by-police-and-revenue-dept-83488</t>
+          <t>https://www.etvbharat.com/mr/!state/no-new-districts-will-be-created-in-the-state-for-the-time-being-says-revenue-minister-chandrashekhar-bawankule-maharashtra-news-mhs25012302825</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/171014/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/6/23/new-law-to-be-introduced-in-monsoon-session-said-chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/165774/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/drone-watch-on-illegal-minor-mineral-mining-important-decision-of-revenue-minister-bawankule-1362804</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/3/5/No-stamp-duty-for-affidavit-in-Maharashtra-Chandrashekhar-Bawankule.html</t>
+          <t>https://mahasamvad.in/173545/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/maharashtra-public-security-act-for-naxal-crackdown-chandrashekhar-bawankule-statement-vsd-99-5223733/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/announcement-to-repeal-the-tukde-ban-act-revenue-minister-chandrashekhar-bawankule-big-decision-maha-vikas-aghadi-also-welcomes-the-decision-1368855</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/31/congress-committed-an-unforgivable-crime-political-defamation-conspiracy-exposed-minister-chandrashekhar-bawan.html</t>
+          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-criticized-on-rahul-gandhi-over-criticized-pm-narendra-modi-statement-maharashtra-marathi-news-1372638</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/revenue-minister-chandrashekhar-bawankule-informed-that-the-state-new-sand-policy-will-be-announced-soon-7948210</t>
+          <t>https://mahasamvad.in/165886/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/5/supreme-courts-decision-provides-justice-to-obcs-chandrashekhar-bawankule.html</t>
+          <t>https://marathi.abplive.com/news/dharashiv/revenue-minister-chandrashekhar-bawankule-publicly-felicitated-by-accused-out-on-bail-in-drug-case-1375621</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176289/</t>
+          <t>https://www.mahasamvad.in/173517/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-revenue-minister-chandrashekhar-bawankule-big-decision-students-stamp-duty-on-academic-affidavit-waived/articleshow/118747673.cms</t>
+          <t>https://www.mahasamvad.in/169614/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/chhatrapati-sambhajinagar-farmer-cheated-of-rs-4k-by-fake-call-claiming-to-be-chandrashekhar-bawankule-pa/articleshow/123360446.cms</t>
+          <t>https://news18marathi.com/agriculture/revenue-department-under-leadership-revenue-minister-chandrashekhar-bawankule-has-taken-18-major-decisions-1413141.html</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/dharashiv-tuljapur-drugs-case-main-accused-vinod-pintu-gangane-felicitates-minister-chandrashekhar-bawankule-1452942.html</t>
+          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-on-stamp-paper-demand-in-e-service-centers-in-government-offices-is-illegal-information-from-revenue-minister-chandrashekhar-bawankule-maharashtra-politics-maharashtra-marathi-news-1362983</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172416/</t>
+          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-counterattack-after-uddhav-thackeray-criticism-of-pm-narendra-modi-u-turn-on-the-issue-of-farmer-loan-waiver-maharashtra-politics-marathi-news-1375550</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/mumbai/devendra-fadnavis-will-be-the-chief-minister-till-2034-chandrashekhar-bawankule-prediction-deputy-cm-eknath-shinde-big-reaction-in-one-word-1392298.html</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B9%E0%A5%85%E0%A4%B2-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%B8-%E0%A4%B9%E0%A5%87%E0%A4%AC-%E0%A4%82%E0%A4%9A-%E0%A4%AA-%E0%A4%8F-%E0%A4%AC-%E0%A4%B2%E0%A4%A4-%E0%A4%AF-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%9C-%E0%A4%A8%E0%A4%97%E0%A4%B0%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%B2-%E0%A4%95%E0%A5%8D%E0%A4%AF%E0%A5%82%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%A0%E0%A4%B5%E0%A4%B2-%E0%A4%AA%E0%A5%88%E0%A4%B6-%E0%A4%82%E0%A4%9A-%E0%A4%AE-%E0%A4%97%E0%A4%A3-%E0%A4%AA-%E0%A4%B2-%E0%A4%B8-%E0%A4%A4-%E0%A4%A4%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%B0/ar-AA1KFEz1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/dont-politicize-pahalgam-attack-stand-with-the-government-chandrashekhar-bawankule-appeals/04232052</t>
+          <t>https://mahasamvad.in/163978/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176273/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/2/3/One-lakh-94-thousand-special-executive-officers-will-be-appointed-across-the-state-By-Chandrashekhar-Bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/minister-chandrashekhar-bawankule-big-statement-about-farmers-loan-waiver/articleshow/123323729.cms</t>
+          <t>https://agrowon.esakal.com/agro-special/file-criminal-cases-against-those-who-close-farms-revenue-minister-chandrashekhar-bawankule-orders-srs92</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174314/</t>
+          <t>https://mahasamvad.in/165932/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174926/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/22/revenue-department-to-implement-national-leader-to-father-of-the-nation-campaign-revenue-minister-chandrashekh.html</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/31/62-officers-promoted-to-the-rank-of-naib-tehsildar-on-the-eve-of-revenue-day.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/2/3/Chandrashekhar-Bawankule-brought-satisfaction-to-the-Mihan-project-victims.html</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-leader-chandrashekhar-bawankule-explanation-on-viral-video-of-eknath-shinde/articleshow/122165237.cms</t>
+          <t>https://mahasamvad.in/165925/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/5/case-registered-against-those-who-harassed-the-police-in-the-name-of-guardian-minister-bawankule.html</t>
+          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-on-action-mode-against-sand-mafia-said-take-action-under-the-mpda-act-against-those-involved-in-illegal-sand-mining-and-transportation-in-buldhana-1376122</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/government-approved-1660-petrol-pumps-in-maharashtra-single-window-system-starts-know-how-to-apply-7822420</t>
+          <t>https://mahasamvad.in/167615/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/business/real-estate-news/date-fixed-for-implementation-of-one-state-one-registration/articleshow/119943476.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/buldana/revenue-minister-chandrashekhar-bawankule-fake-calling-and-ccheated-fraud-with-farmer/articleshow/123344845.cms</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/decision-to-relax-fragmentation-law/07091622</t>
+          <t>https://mahasamvad.in/171014/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/temple-land-transactions-should-be-stopped-to-next-government-order-revenue-minister-chandrashekhar-bawankule-instructs/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/chandrashekhar-bawankule-assures-of-farmers-loan-waivers-after-proper-survey/articleshow/123184635.cms</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/the-revenue-ministry-will-make-changes-to-the-rules-for-farm-roads-1317903.html</t>
+          <t>https://marathi.abplive.com/crime/sambhajinagar-farmer-demand-money-hello-chandrashekhar-bawankule-pa-is-speaking-qr-sent-to-farmer-in-complaint-to-police-1377664</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/maharashtra-revenue-department-has-taken-5-major-decisions-marathi-agriculture-news-1401406.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/chandrashekhar-bawankule-announcement-now-silt-soil-mud-stones-will-be-available-for-free-maharashtra-government-s-big-decision-1352610</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/jalna/farmers-flood-relief-funds-embezzled-in-jalna-revenue-minister-bawankule-orders-major-action-1375925</t>
+          <t>https://mahasamvad.in/176506/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-government-planning-for-new-gunthewari-law-will-introduce-bill-in-assembly-monsoon-session/articleshow/122052149.cms</t>
+          <t>https://mahasamvad.in/172338/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-bawankule-kadu-row-revenue-minister-and-former-mla-clash-over-disabled-allowance-hike-and-farmers-issues-accusations-of-drama-exchanged-1374782</t>
+          <t>https://mahasamvad.in/173912/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/fadnavis-governmen-big-decision-guntha-tukdebandi-kayda/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/3/5/No-stamp-duty-for-affidavit-in-Maharashtra-Chandrashekhar-Bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/ias-vikas-kharge-taken-charge-additional-chief-secretary-of-revenue-department-1447633.html</t>
+          <t>https://mahasamvad.in/165774/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/pune-velhe-taluka-name-change-as-rajgad-by-maharashtra-government-central-government-give-approval-1378588</t>
+          <t>https://mahasamvad.in/172804/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/then-action-must-be-taken-against-those-officials-too/</t>
+          <t>https://mahasamvad.in/163853/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/appointment-of-80-additional-district-collectors-in-the-state-promotion-of-deputy-district-collectors-269014/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/3/21/Implementation-of-Pratyay-online-system-under-the-guidance-of-Revenue-Minister-Chandrashekhar-Bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/governments-big-decision-rs-500-stamp-duty-waived-off-for-affidavit-revenue-minister-bawankule-announced/03051341</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-demands-to-check-voter-lists-against-congress-allegations/articleshow/123356783.cms</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/separate-dcp-office-to-be-established-in-kamath-minister-bawankule-gave-instructions-to-the-planning-authorities/03171903</t>
+          <t>https://marathi.abplive.com/news/nashik/chandrashekhar-bawankule-big-statement-regarding-sudhakar-badgujar-entry-into-bjp-nashik-maharashtra-politics-marathi-news-1362706</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/amravati/cm-devendra-fadnavis-big-decision-on-bachchu-kadu-demand-about-farmer-loan-waiver/articleshow/121832462.cms</t>
+          <t>https://deshdoot.com/demand-for-stamp-paper-for-educational-certificates-and-affidavits-is-illegal/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/let-the-sub-capital-nagpur-get-the-status-of-an-international-metropolis-in-five-years/05022100</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/31/congress-committed-an-unforgivable-crime-political-defamation-conspiracy-exposed-minister-chandrashekhar-bawan.html</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/govts-benefits-will-reach-every-citizen-asserts-revenue-minister-bawankule/01231600</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/5/supreme-courts-decision-provides-justice-to-obcs-chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/state-government-to-bring-new-law-regarding-temple-land-marathi-agriculture-news-1361595.html</t>
+          <t>https://mahasamvad.in/168528/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/revenue-minister-chandrasekhar-bawankule-department/</t>
+          <t>https://marathi.ndtv.com/politics/revenue-minister-chandrashekhar-bawankule-informed-that-the-state-new-sand-policy-will-be-announced-soon-7948210</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/chandrashekhar-bawankule-orders-submit-a-proposal-for-the-junction-midc/</t>
+          <t>https://mahasamvad.in/164965/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/maharashtra-or-shrubs-will-provide-relief-to-families-on-forest-land-revenue-minister-bawankule/</t>
+          <t>https://mahasamvad.in/176289/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/revenue-minister-on-action-mode-against-sand-mafia-register-cases-under-mpda-act-against-those-involved-in-illegal-sand-mining-article-152439491</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-revenue-minister-chandrashekhar-bawankule-big-decision-students-stamp-duty-on-academic-affidavit-waived/articleshow/118747673.cms</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/chandrasekhar-bawankule-assured-24-hours-sand-transportation-allowed/</t>
+          <t>https://mahasamvad.in/174409/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/the-industries-department-should-submit-a-proposal-for-the-required-land-for-the-proposed-junction-midc-revenue-minister-chandrashekhar-bawankule/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/chandrashekhar-bawankule-says-opportunities-for-local-karyakarta-even-before-elections-appointment-of-1-lakh-94-thousand-seo-in-the-state-what-are-the-criteria-1342316</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/buldhana-file-cases-under-mpda-act-against-those-involved-in-illegal-sand-mining-and-transportation-in-the-district-revenue-minister-chandrashekhar-bawankule/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/chhatrapati-sambhajinagar-farmer-cheated-of-rs-4k-by-fake-call-claiming-to-be-chandrashekhar-bawankule-pa/articleshow/123360446.cms</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/maharashtra-has-not-forgotten-who-is-the-chieftain-of-extortion-revenue-minister-bawankule-attacked-uddhav-thackeray/08111447</t>
+          <t>https://news18marathi.com/maharashtra/dharashiv-tuljapur-drugs-case-main-accused-vinod-pintu-gangane-felicitates-minister-chandrashekhar-bawankule-1452942.html</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/chandrashekhar-bawankule-assures-no-one-will-be-homeless-in-a-bushy-forest-area/</t>
+          <t>https://mahasamvad.in/172416/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/chandrasekhar-bawankule-revenue-department-implement/</t>
+          <t>https://www.tv9marathi.com/maharashtra/mumbai/devendra-fadnavis-will-be-the-chief-minister-till-2034-chandrashekhar-bawankule-prediction-deputy-cm-eknath-shinde-big-reaction-in-one-word-1392298.html</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/revenue-minister-has-taken-a-big-decision-regarding-heir-registration/</t>
+          <t>https://www.nagpurtoday.in/dont-politicize-pahalgam-attack-stand-with-the-government-chandrashekhar-bawankule-appeals/04232052</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/farm-roads-will-now-be-twelve-feet-wide-revenue-department-took-big-decision-article-151701949</t>
+          <t>https://mahasamvad.in/174314/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/chandrasekhar-bawankule-announced-repeal-of-tukde-bandi-law-in-urban-areas/</t>
+          <t>https://sarkarnama.esakal.com/ampstories/web-stories/devendra-fadnavis-government-big-decision-for-farmers-in-assembly-session-tukda-bandi-law-cancelled-dk88</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/efforts-to-make-the-revenue-department-more-efficient-with-the-help-of-technology/</t>
+          <t>https://mahasamvad.in/169968/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/shrimant-chhatrapati-shivaji-maharaj-maharajswa-samadhan-camp-campaign-now-at-mandal-level-revenue-minister-bawankule/</t>
+          <t>https://mahasamvad.in/174926/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/chandrashekhar-bawankule-on-uddhav-thackeray-thackerays-criticism-of-fadnavis-bawankules-attack-on-thackeray/128784/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/31/62-officers-promoted-to-the-rank-of-naib-tehsildar-on-the-eve-of-revenue-day.html</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://buldanalive.com/buldhana/prepare-proposal-to-give-25-per-cent-additional/cid16646943.htm</t>
+          <t>https://mahasamvad.in/170666/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://krushimarathi.com/noc-hassle-while-building-a-house-is-over-historic-decision-of-the-revenue-department/</t>
+          <t>https://civicmirror.in/maharashtra/buldhana-file-cases-under-mpda-act-against-those-involved-in-illegal-sand-mining-and-transportation-in-the-district-revenue-minister-chandrashekhar-bawankule/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/big-relief-from-state-government-waiver-of-stamp-duty-of-rs-500-for-affidavit/</t>
+          <t>https://mahasamvad.in/167572/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/maharashtra-scraps-land-fragmentation-law-relief-farmers/</t>
+          <t>https://marathi.abplive.com/news/politics/chandrasekhar-bawankule-spoke-clearly-on-anna-hazare-demand-over-dhananjay-munde-and-manikrao-kokate-resign-cabinet-post-maharashtra-marathi-news-1345621</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.berartimes.com/vidarbha/207471/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/strict-rules-now-for-birth-and-death-certificates-change-in-law-important-decision-of-revenue-minister-due-to-bangladeshi-in-mumbai-1348753</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://ahmednagarlive24.com/spacial/government-employee-news-so-maharashtra-state-government-employees-will-not-get-their-salary-for-august-2025/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/5/case-registered-against-those-who-harassed-the-police-in-the-name-of-guardian-minister-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/minister-bawankule-publicly-felicitated-by-accused-in-drug-case/112805/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/stamp-duty-of-500-on-affidavits-for-government-offices-waived-relief-for-lakhs-of-students-chanrashekhar-bavankule-decision-1347510</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/bjp-has-no-link-with-attack-on-sambhaji-brigade-leader-minister-bawankule-3628848</t>
+          <t>https://news18marathi.com/agriculture/what-action-will-the-revenue-department-take-during-the-campaign-from-august-1-to-7-1447199.html</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/govt-firm-on-purandar-airport-project-chandrashekhar-bawankule-101746466486230.html</t>
+          <t>https://www.mahasamvad.in/page/355/?m=0</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-revenue-minister-chandrashekhar-bawankule-implements-nagpur-model-for-farm-road-construction/ar-AA1yyeMo</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-government-planning-for-new-gunthewari-law-will-introduce-bill-in-assembly-monsoon-session/articleshow/122052149.cms</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-urges-restraint-on-political-street-fights/articleshow/122819890.cms</t>
+          <t>https://www.mymahanagar.com/maharashtra/maharashtra-will-cancel-fake-birth-certificates-issued-to-illegal-bangladeshi-residents-says-minister-bawankule/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/sanjay-raut-can-not-decide-modis-tenure-maharashtra-bjp-president-chandrashekhar-bawankule-on-pms-retirement-23510710</t>
+          <t>https://marathi.ndtv.com/maharashtra/government-approved-1660-petrol-pumps-in-maharashtra-single-window-system-starts-know-how-to-apply-7822420</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/maharashtra-minister-apologises-to-b-r-gavai-chief-justice-over-protocol-lapse-in-mumbai-8456034</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-land-measurement-maharashtra-government-fixed-fee-for-land-measurement-at-rs-200-benefit-to-farmers-for-division-of-land-73753</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/empty-out-the-congress-chandrashekhar-bawankule-tells-partymen-101746471227225.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/minister-chandrashekhar-bawankule-big-statement-about-farmers-loan-waiver/articleshow/123323729.cms</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/maharashtra-bjp-chief-chandrashekhar-bawankule-urges-party-workers-to-empty-congress-induct-its-leaders-8334573</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/pakistani-nationals-must-leave-india-chandrashekhar-bawankule-vsb99</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-should-check-voter-lists-now-quips-chandrashekhar-bawankule/articleshow/123351307.cms</t>
+          <t>https://marathi.indiatimes.com/business/real-estate-news/date-fixed-for-implementation-of-one-state-one-registration/articleshow/119943476.cms</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/confusion-in-bjp-over-induction-of-ex-sena-ubt-leader-bawankule-unaware-of-move-3589681</t>
+          <t>https://news18marathi.com/agriculture/the-revenue-ministry-will-make-changes-to-the-rules-for-farm-roads-1317903.html</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/devendra-fadnavis-to-remain-maharashtra-cm-till-2034-says-chandrashekhar-bawankule-23527680</t>
+          <t>https://civicmirror.in/maharashtra/temple-land-transactions-should-be-stopped-to-next-government-order-revenue-minister-chandrashekhar-bawankule-instructs/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bawankule-meets-sulking-shirsat-amid-funds-diversion-controversy-101749670372918.html</t>
+          <t>https://news18marathi.com/agriculture/maharashtra-revenue-department-has-taken-5-major-decisions-marathi-agriculture-news-1401406.html</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/no-75-year-age-rule-in-bjp-sanjay-raut-can-not-decide-modis-tenure-says-chandrashekhar-bawankule-3472151</t>
+          <t>https://marathi.abplive.com/news/jalna/farmers-flood-relief-funds-embezzled-in-jalna-revenue-minister-bawankule-orders-major-action-1375925</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ravindra-chavan-set-to-head-maha-bjp-says-bawankule/articleshow/121504377.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/maharashtra-revenue-minister-chandrashekhar-bawankule-informed-that-caste-wise-census-will-be-conducted-in-2027-pri/articleshow/120884066.cms</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/maharashtra-ministers-reach-agreement-on-key-welfare-issues-after-bawankule-led-talks/articleshow/122256747.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/6/23/raiba-imandar-film-release.html</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-plans-to-reform-modernise-revenue-dept-by-2029/articleshow/123067789.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/farm-roads-passing-through-agricultural-embankments-will-now-be-twelve-feet-wide-1360495</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/state-to-soon-have-a-new-artificial-sand-policy-bawankule/articleshow/120441502.cms</t>
+          <t>https://news18marathi.com/maharashtra/ias-vikas-kharge-taken-charge-additional-chief-secretary-of-revenue-department-1447633.html</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/chandrashekhar-bawankule-denies-making-calls-to-protect-deepak-kate-amid-solapur-assault-row-23584795</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-bawankule-kadu-row-revenue-minister-and-former-mla-clash-over-disabled-allowance-hike-and-farmers-issues-accusations-of-drama-exchanged-1374782</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-hints-at-major-land-law-reform-amend-plot-size-restrictions/articleshow/122032769.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/bjp-has-no-link-with-attack-on-sambhaji-brigade-leader-minister-bawankule-3628848</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/the-nomadic-community-will-get-ration-anywhere-in-the-state-says-revenue-minister-chandrashekhar-bawankule/articleshow/121208499.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/govt-firm-on-purandar-airport-project-chandrashekhar-bawankule-101746466486230.html</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-revenue-minister-chandrashekhar-bawankule-implements-nagpur-model-for-farm-road-construction/ar-AA1yyeMo</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/macau-jibe-to-advt-row-cong-bjp-maha-chiefs-in-war-of-words/articleshow/120529370.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-urges-restraint-on-political-street-fights/articleshow/122819890.cms</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/bawankule-assures-dialogue-with-farmers-amid-purandar-airport-land-acquisition-protests-101746380590787.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/sanjay-raut-can-not-decide-modis-tenure-maharashtra-bjp-president-chandrashekhar-bawankule-on-pms-retirement-23510710</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/no-salary-for-employees-without-face-app-attendance-says-maharashtra-revenue-minister-chandrashekhar-bawankule-2025-07-23-1000274</t>
+          <t>https://www.ndtv.com/india-news/maharashtra-minister-apologises-to-b-r-gavai-chief-justice-over-protocol-lapse-in-mumbai-8456034</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/infra-works-delay-bawankule-slams-nmc-over-non-utilisation-of-rs310cr/articleshow/122410221.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/empty-out-the-congress-chandrashekhar-bawankule-tells-partymen-101746471227225.html</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-quashes-rift-rumours-asserts-mahayuti-will-contest-local-polls-unitedly/articleshow/121448703.cms</t>
+          <t>https://www.ndtv.com/india-news/maharashtra-bjp-chief-chandrashekhar-bawankule-urges-party-workers-to-empty-congress-induct-its-leaders-8334573</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/bawankule-slams-pune-land-records-dept-hints-sit-probe-into-illegal-ownership-changes-101746467026560.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/congress-should-check-voter-lists-now-quips-chandrashekhar-bawankule/articleshow/123351307.cms</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/bawankule-asks-for-alternatives-as-meeting-with-farmers-over-purandar-airport-ends-in-stalemate/articleshow/120909800.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/confusion-in-bjp-over-induction-of-ex-sena-ubt-leader-bawankule-unaware-of-move-3589681</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-state-chief-asks-dhas-munde-to-bury-the-hatchet-101739560133748.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/devendra-fadnavis-to-remain-maharashtra-cm-till-2034-says-chandrashekhar-bawankule-23527680</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/maharashtra-to-relax-fragmentation-law-sop-soon-bawankule/articleshow/122458237.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bawankule-meets-sulking-shirsat-amid-funds-diversion-controversy-101749670372918.html</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-congress-backs-rahul-gandhis-poll-rigging-allegations-demands-fadnavis-resignation-3601125</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/chandrashekhar-bawankule-welcomes-chhagan-bhujbals-induction-into-maharashtra-cabinet-calls-it-a-boost-for-govt-23547724</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/who-reads-saamana-who-listens-to-them-asks-bawankule/articleshow/121541164.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/no-75-year-age-rule-in-bjp-sanjay-raut-can-not-decide-modis-tenure-says-chandrashekhar-bawankule-3472151</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/another-blow-to-shinde-bawankule-slams-cidco-over-naina-planning-101756150390930.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/maharashtra-ministers-reach-agreement-on-key-welfare-issues-after-bawankule-led-talks/articleshow/122256747.cms</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/no-75-year-retirement-rule-in-bjp-maharashtra-chief-counters-sanjay-raut-s-remark-on-modi-101743498262416.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-orders-crackdown-on-illegal-mining-craters-after-child-deaths/articleshow/122393943.cms</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/politics/nagpur-violence-bjp-s-bawankule-calls-for-peace-as-police-detain-over-20-125031800026_1.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-plans-to-reform-modernise-revenue-dept-by-2029/articleshow/123067789.cms</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-takes-stock-of-damage-caused-due-to-unseasonal-rain/articleshow/121580211.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-dubs-kadus-protest-as-hypocritical/articleshow/122305534.cms</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/bawankule-urges-bjp-cadre-to-bring-in-congress-leaders-empty-the-party-101746466905147.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/chandrashekhar-bawankule-denies-making-calls-to-protect-deepak-kate-amid-solapur-assault-row-23584795</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-probe-illegal-transfer-of-1-628-land-parcels-to-nontribals-101752087826955.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-hints-at-major-land-law-reform-amend-plot-size-restrictions/articleshow/122032769.cms</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/raj-thackeray-uddhav-thackeray-victory-rally-no-traffic-diversions-for-sena-mns-rally-23583195</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/bawankule-assures-dialogue-with-farmers-amid-purandar-airport-land-acquisition-protests-101746380590787.html</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-directs-nmc-to-repair-roads-immediately/articleshow/121893777.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/infra-works-delay-bawankule-slams-nmc-over-non-utilisation-of-rs310cr/articleshow/122410221.cms</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/no-affidavit-on-500-stamp-paper-for-students-says-revenue-minister-chandrashekhar-bawankule/ar-AA1AjwfL</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/bawankule-slams-pune-land-records-dept-hints-sit-probe-into-illegal-ownership-changes-101746467026560.html</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-warns-against-lapses-in-koradi-textile-project/articleshow/122212627.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/rahul-needs-to-come-out-of-dark-shadow-of-defeat-bawankule-on-his-match-fixing-remark-3575806</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/very-shameless-statement-chandrashekhar-bawankule-slams-vijay-wadettiwars-remark-on-pahalgam-terror-attack-23530298</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-state-chief-asks-dhas-munde-to-bury-the-hatchet-101739560133748.html</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/bawankule-faces-flak-for-sharing-stage-with-accused-in-tuljapur-drugs-case/articleshow/123196303.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticizes-uddhav-for-opposing-maharashtra-security-bill/articleshow/122410846.cms</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/ravindra-chavan-to-be-new-bjp-chief-for-maharashtra-3609432</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/maharashtra-to-relax-fragmentation-law-sop-soon-bawankule/articleshow/122458237.cms</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/clear-pending-water-projects-on-priority-bawankule/articleshow/122077229.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-congress-backs-rahul-gandhis-poll-rigging-allegations-demands-fadnavis-resignation-3601125</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/maharashtra-to-bring-anti-conversion-law-investigate-unauthorised-churches-2753435-2025-07-09</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-to-head-panel-on-farm-roads/articleshow/123103819.cms</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/maharashtra-special-public-security-bill-2024-tabled-to-tackle-urban-naxalism-8852342</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/no-blanket-farm-loan-waiver-only-the-most-distressed-to-get-it-bawankule/articleshow/123195407.cms</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/maharashtra-govt-starts-second-phase-of-land-title-updating/articleshow/120827478.cms</t>
+          <t>https://www.business-standard.com/politics/india-bloc-disintegrating-as-it-doesn-t-have-ideology-bjp-s-bawankule-125011300459_1.html</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/no-one-will-dare-maharashtra-plans-tough-law-against-religious-conversions-revenue-minister-tells-assembly-uike-pledges-to-bring-converted-tribals-back/articleshow/122363837.cms</t>
+          <t>https://www.hindustantimes.com/india-news/no-75-year-retirement-rule-in-bjp-maharashtra-chief-counters-sanjay-raut-s-remark-on-modi-101743498262416.html</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/part-of-maharashtras-tradition-chandrashekhar-bawankule-responds-to-uddhav-thackerays-praise-for-cm-fadnavis20250723103612</t>
+          <t>https://www.business-standard.com/politics/nagpur-violence-bjp-s-bawankule-calls-for-peace-as-police-detain-over-20-125031800026_1.html</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-govt-to-bring-strict-anti-conversion-law-minister-3622288</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/seize-assets-of-school-directors-in-shalarth-id-scam-bawankule/articleshow/123371134.cms</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/maha-govt-plans-new-land-acquisition-rules-to-speed-up-projects-assure-farmers-fair-compensation/articleshow/123144329.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/bawankule-urges-bjp-cadre-to-bring-in-congress-leaders-empty-the-party-101746466905147.html</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/rahul-gandhis-vote-theft-claims-are-baseless-childish-chandrashekhar-bawankule-23588752</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-probe-illegal-transfer-of-1-628-land-parcels-to-nontribals-101752087826955.html</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/india/politics/maharashtra-bjp-chief-chandrashekhar-bawankule-congress-remark-poaching-leaders-controversy-19599239.htm</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-directs-nmc-to-repair-roads-immediately/articleshow/121893777.cms</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-hits-back-at-uddhav-calls-his-marathi-stand-political-drama-ahead-of-polls/07051714</t>
+          <t>https://www.aninews.in/news/national/general-news/very-shameless-statement-chandrashekhar-bawankule-slams-vijay-wadettiwars-remark-on-pahalgam-attack20250429092821</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/10-crore-tree-plantation-drive-a-shared-responsbility-reiterates-bawankule/articleshow/122423491.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/raj-thackeray-uddhav-thackeray-victory-rally-no-traffic-diversions-for-sena-mns-rally-23583195</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/08/05/nagpur-case-filed-against-three-for-misusing-minister-chandrashekhar-bawankules-name-to-intimidate-police-at-friendship-day-party/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-warns-against-lapses-in-koradi-textile-project/articleshow/122212627.cms</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/no-right-maharashtra-bjp-chiefs-dig-at-rahul-gandhi-on-caste-census-timeline-demand-101746088832797.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/very-shameless-statement-chandrashekhar-bawankule-slams-vijay-wadettiwars-remark-on-pahalgam-terror-attack-23530298</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/no-discord-in-maha-yuti-govt-bawankule-dismisses-reports-of-credit-game-over-pahalgam-rescue-op-3510596</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/clear-pending-water-projects-on-priority-bawankule/articleshow/122077229.cms</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/encroachment-visible-on-govt-land-no-fake-docus-used-bawankule/articleshow/122394983.cms</t>
+          <t>https://realty.economictimes.indiatimes.com/news/allied-industries/free-sand-royalty-receipts-to-be-delivered-to-beneficiaries-of-housing-schemes-maharashtra-revenue-minister/121176284</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/take-strict-action-against-illegal-soil-transportation-embezzlement-of-royalties-in-thane-bawankule-to-officials-23515104</t>
+          <t>https://www.deccanherald.com/india/maharashtra/ravindra-chavan-to-be-new-bjp-chief-for-maharashtra-3609432</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/needy-farmers-to-get-loan-waiver-not-those-building-farmhouses-bungalows-minister-bawankule-3683575</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/bawankule-faces-flak-for-sharing-stage-with-accused-in-tuljapur-drugs-case/articleshow/123196303.cms</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/state-govt-bawankule-behind-ink-attack-pravin-gaikwad/articleshow/122592422.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/rahul-gandhi-has-lost-the-plot-says-bawankule-denies-dig-at-bachchu-kadu/articleshow/123103074.cms</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-pushes-for-people-centric-development-weekly-village-visits-fast-track-projects-under-annual-plan/articleshow/123127176.cms</t>
+          <t>https://www.ndtv.com/india-news/maharashtra-special-public-security-bill-2024-tabled-to-tackle-urban-naxalism-8852342</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/rss-chiefs-anecdote-on-75-sparks-political-speculation-bjp-dismisses-retirement-talk</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-calls-rahul-gandhis-caste-census-push-too-late-to-matter/articleshow/122925629.cms</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-promises-sop-in-3-months-to-resolve-zudpi-jungle-land-issue-in-vidarbha/articleshow/122394160.cms</t>
+          <t>https://m.economictimes.com/news/india/maharashtra-govt-starts-second-phase-of-land-title-updating/articleshow/120827478.cms</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/politics/chandrashekhar-bawankule-welcomes-ncps-chhagan-bhujbal-in-maharashtra-cabinet-calls-it-a-boost-for-govt20250520094044/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/no-one-will-dare-maharashtra-plans-tough-law-against-religious-conversions-revenue-minister-tells-assembly-uike-pledges-to-bring-converted-tribals-back/articleshow/122363837.cms</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-to-appoint-rss-workers-as-pas-to-its-ministers-101737571872713.html</t>
+          <t>https://www.aninews.in/news/national/general-news/part-of-maharashtras-tradition-chandrashekhar-bawankule-responds-to-uddhav-thackerays-praise-for-cm-fadnavis20250723103612</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/velhe-taluka-in-pune-district-renamed-as-rajgad-announces-maharashtra-minister-bawankule-3691509</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/6/3-booked-for-threatening-cops-using-name-of-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/gym-owner-faces-case-for-online-content-against-bawankule/articleshow/123395126.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-govt-to-bring-strict-anti-conversion-law-minister-3622288</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-to-allow-hoardings-on-vacant-land-owned-by-govt-bawankule-101750872010984.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/take-strict-action-against-illegal-soil-transportation-embezzlement-of-royalties-in-thane-bawankule-to-officials-23515104</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-slams-uddhav-thackeray-over-saamana-says-political-relevance-under-threat/04141830</t>
+          <t>https://www.cnbctv18.com/india/politics/maharashtra-bjp-chief-chandrashekhar-bawankule-congress-remark-poaching-leaders-controversy-19599239.htm</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/act-against-illegal-plotting-mining-in-yeolewadi-kondhwa-katraj-areas-bawankule-101748459992922.html</t>
+          <t>https://www.nagpurtoday.in/bawankule-hits-back-at-uddhav-calls-his-marathi-stand-political-drama-ahead-of-polls/07051714</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/50-of-bhandara-city-located-on-nazul-land-govt-to-regularize-these-properties-bawankule/articleshow/123103215.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/10-crore-tree-plantation-drive-a-shared-responsbility-reiterates-bawankule/articleshow/122423491.cms</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-to-enact-law-against-religious-conversions-demolish-illegal-churches-in-tribal-districts-101752088546524.html</t>
+          <t>https://www.hindustantimes.com/india-news/no-right-maharashtra-bjp-chiefs-dig-at-rahul-gandhi-on-caste-census-timeline-demand-101746088832797.html</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/maharashtra-govt-to-relax-land-fragmentation-law-subdivided-plots-up-to-jan-1-to-become-legal/articleshow/122343682.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-meets-protesting-bachchu-kadu-cong-backs-his-stir/articleshow/121836362.cms</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-orders-probe-into-bid-to-usurp-42-acre-of-forest-land-in-nagpur-three-clerks-suspended-101746816714894.html</t>
+          <t>https://www.hindustantimes.com/india-news/maharashtra-cabinet-reshuffle-buzz-final-decision-rests-with-cm-fadnavis-says-bawankule-101753525179967.html</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-to-opposition-show-proof-or-stop-defaming/07211731</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/maha-finalizes-new-policy-to-regulate-hoardings-on-government-land/articleshow/122098695.cms</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/childish-move-bjp-slams-entitled-dynast-rahul-gandhi-over-eci-allegations-maharashtra-polls-101749324813073.html</t>
+          <t>https://thelivenagpur.com/2025/08/05/nagpur-case-filed-against-three-for-misusing-minister-chandrashekhar-bawankules-name-to-intimidate-police-at-friendship-day-party/</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/14-telangana-villages-will-be-merged-in-maharashtra-enn25071602801</t>
+          <t>https://www.deccanherald.com/india/maharashtra/needy-farmers-to-get-loan-waiver-not-those-building-farmhouses-bungalows-minister-bawankule-3683575</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/government-to-remove-non-agricultural-land-use-requirement-for-industries-101738952544368.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-pushes-for-people-centric-development-weekly-village-visits-fast-track-projects-under-annual-plan/articleshow/123127176.cms</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/attack-on-sambhaji-brigade-leader-made-no-calls-to-save-accused-says-bawankule/2690539/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-promises-sop-in-3-months-to-resolve-zudpi-jungle-land-issue-in-vidarbha/articleshow/122394160.cms</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/divisional-revenue-commissionerate-to-be-set-up-in-latur-or-nanded-chandrashekhar-bawankule-23489288</t>
+          <t>https://aninews.in/news/national/politics/chandrashekhar-bawankule-welcomes-ncps-chhagan-bhujbal-in-maharashtra-cabinet-calls-it-a-boost-for-govt20250520094044/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/bawankule-s-statement-about-case-involving-navneet-rana-misleading-cong-writes-to-ec-sc/1389710</t>
+          <t>https://theprint.in/india/confusion-in-bjp-over-induction-of-ex-sena-ubt-leader-bawankule-unaware-of-move/2660709/</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/hc-acquits-all-2006-train-blasts-accused-maharashtra-govt-will-study-order-says-chandrashekhar-bawankule-23585741</t>
+          <t>https://www.deccanherald.com/india/maharashtra/velhe-taluka-in-pune-district-renamed-as-rajgad-announces-maharashtra-minister-bawankule-3691509</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/bjp-has-no-link-with-attack-on-sambhaji-brigade-leader-minister-bawankule/2725525</t>
+          <t>https://m.economictimes.com/news/india/maharashtra-govt-to-relax-land-fragmentation-law-subdivided-plots-up-to-jan-1-to-become-legal/articleshow/122343682.cms</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/why-did-he-not-lodge-a-complaint-at-the-police-station-on-the-same-day-bjps-bawankule-over-sharad-pawars-claims20250809213444/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-to-enact-law-against-religious-conversions-demolish-illegal-churches-in-tribal-districts-101752088546524.html</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/1/24/Central-Jail-to-be-shifted-near-Babhulkheda-Bawankule.html</t>
+          <t>https://www.nagpurtoday.in/bawankule-to-opposition-show-proof-or-stop-defaming/07211731</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/pti-stories/national/maharashtra-govt-plans-to-curb-illegal-sand-mining-through-drone-based-surveys-125060600147_1.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/government-to-remove-non-agricultural-land-use-requirement-for-industries-101738952544368.html</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/3/3/Devpt-works-worth-Rs-164-61-cr-for-Dhapewada-kick-off.html</t>
+          <t>https://www.hindustantimes.com/india-news/childish-move-bjp-slams-entitled-dynast-rahul-gandhi-over-eci-allegations-maharashtra-polls-101749324813073.html</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/2/2/Rs-2-065-cr-approved-by-District-Planning-Committee-for-2025-26.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/divisional-revenue-commissionerate-to-be-set-up-in-latur-or-nanded-chandrashekhar-bawankule-23489288</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/koradi-to-get-butterfly-garden-7d-theatre-worlds-tallest-hanuman-statue-bawankule/articleshow/122844552.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/hc-acquits-all-2006-train-blasts-accused-maharashtra-govt-will-study-order-says-chandrashekhar-bawankule-23585741</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/maharashtra-govt-to-legalise-subdivided-land-plots-formed-till-jan-1-2025-125070900961_1.html</t>
+          <t>https://www.ptinews.com/story/national/bjp-has-no-link-with-attack-on-sambhaji-brigade-leader-minister-bawankule/2725525</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/short-videos/trending/vaibhav-naik-news-uddhav-thackeray-s-shiladhar-chandrashekhar-bawankule-meets-n18s-1070283.html</t>
+          <t>https://www.theweek.in/news/india/2025/07/02/illegal-sand-mining-in-wardha-river-maharashtra-minister-chandrashekhar-bawankule-warns-strict-action.html</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/no-loan-waiver-for-farmhouse-or-mercedes-owners-bawankule-clarifies-policy-for-needy-farmers-only/06280958</t>
+          <t>https://www.business-standard.com/india-news/maharashtra-govt-to-legalise-subdivided-land-plots-formed-till-jan-1-2025-125070900961_1.html</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-fires-back-at-rahul-over-voter-surge-claim-was-there-a-scam-in-2009-too/06071145</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-approves-policy-for-promoting-artificial-sand-101747164656571.html</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://realty.economictimes.indiatimes.com/news/infrastructure/maharashtra-government-to-begin-campaign-from-april-1-to-update-7/12-land-title-records/119479129</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-tightens-rules-for-birth-death-certificates-for-foreign-nationals-23498903</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/are-congress-leaders-trying-to-exonerate-terrorists-maharashtra-bjp-president-on-wadettiwars-remark20250429084410/</t>
+          <t>https://lokmat.news18.com/short-videos/trending/vaibhav-naik-news-uddhav-thackeray-s-shiladhar-chandrashekhar-bawankule-meets-n18s-1070283.html</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/modi-is-not-a-show-he-is-a-roadshow-of-development-bawankule-slams-rahul/07261259</t>
+          <t>https://www.nagpurtoday.in/resolve-public-issues-on-priority-bawankule-directs-administration/03241323</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/now-sand-mafias-to-face-criminal-charges-not-just-fines-bawankule/07181631</t>
+          <t>https://www.etvbharat.com/en/!state/maharashtra-govt-to-have-single-window-system-for-approval-process-of-1660-petrol-pumps-enn25022807370</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/friendship-day-party-controversy-vedant-chhabria-says-sorry-to-bawankule-in-exclusive-nagpur-today-video/08090717</t>
+          <t>https://www.mid-day.com/news/india-news/article/maharashtra-launches-one-district-one-registration-scheme-for-property-23535200</t>
         </is>
       </c>
     </row>
@@ -1943,1113 +1943,1036 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankules-sharp-attack-on-uddhav-rakes-up-rs-100-crore-extortion-case/08111455</t>
+          <t>https://thelivenagpur.com/2025/08/10/guardian-minister-bawankule-orders-high-level-inquiry-into-koradi-incident/</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/article/maharashtra-launches-one-district-one-registration-scheme-for-property-23535200</t>
+          <t>https://timesproperty.com/news/post/maha-govt-to-launch-vertical-7-12-document-system-for-multi-floor-homes-blid10102</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/08/10/guardian-minister-bawankule-orders-high-level-inquiry-into-koradi-incident/</t>
+          <t>https://www.aninews.in/news/national/general-news/rahul-gandhi-is-troubled-by-electoral-defeats-maharashtra-bjp-chief-on-election-rigging-allegations20250607234624/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/resolve-citizens-grievances-promptly-and-effectively-bawankule-directs-officials/06021151</t>
+          <t>https://www.nagpurtoday.in/govts-benefits-will-reach-every-citizen-asserts-revenue-minister-bawankule/01231600</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://timesproperty.com/news/post/maha-govt-to-launch-vertical-7-12-document-system-for-multi-floor-homes-blid10102</t>
+          <t>https://www.nagpurtoday.in/bawankule-dares-rahul-gandhi-to-contest-from-kamptee-in-2029-assembly-poll/02101325</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/rahul-gandhi-is-troubled-by-electoral-defeats-maharashtra-bjp-chief-on-election-rigging-allegations20250607234624/</t>
+          <t>https://www.thehitavada.com/Encyc/2025/6/29/Constitution-Preamble-Park-will-spread-awareness-about-Constitutional-values-in-citizens--CJI-Gavai.html</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/friendship-day-bash-turns-chaotic-main-bawankule-se-baat-kar-leta-hoon-organisers-threat-to-cops-caught-on-camera/08050821</t>
+          <t>https://www.nagpurtoday.in/koradi-temple-gate-collapse-guardian-minister-orders-probe-assures-action/08101755</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/video-bawankule-unfurled-tricolour-at-kasturchand-park/01260936</t>
+          <t>https://www.sarkaritel.com/maha-govt-to-launch-online-property-registration-from-may-1/</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bachchu-kadu-ends-stir-in-amravati-after-bawankules-assurances/06141705</t>
+          <t>https://www.nagpurtrends.com/articles/chandrashekhar-bawankule-to-unfurl-tricolour-at-nagpurs-republic-day-kG2xyj</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-slams-congress-for-questioning-operation-sindoor/07291623</t>
+          <t>https://www.devdiscourse.com/article/law-order/3548164-maharashtra-minister-halts-demolitions-for-ganesh-festival</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/the-constitution-is-the-backbone-of-indias-development-maharashtra-minister-bawankule-pays-tribute-to-dr-ambedkar-in-nagpur/04141639</t>
+          <t>https://organiser.org/2025/07/12/302369/bharat/maharashtra-government-to-enact-stringent-anti-conversion-law-illegal-churches-set-for-demolition/</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bring-entire-city-under-cctv-surveillance-guardian-minister-chandrashekhar-bawankules-directive/04121754</t>
+          <t>https://www.mypunepulse.com/pune-news-municipal-elections-likely-in-april-may-in-maharashtra-bjp-state-president-chandrashekhar-bawankule/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cm-fadnavis-cabinet-meet-ndas-vice-presidential-candidate-c-p-radhakrishnan-in-mumbai-23591080</t>
+          <t>https://www.punekarnews.in/pune-maharashtra-minister-bawankules-call-to-empty-congress-sparks-debate-clarifies-stance-amid-opposition-criticism/</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/west-nagpur-mla-thakre-exposes-pmay-scam-bawankule-asks-housing-minister-to-order-probe/06051215</t>
+          <t>https://www.punekarnews.in/pune-revenue-minister-chandrashekhar-bawankule-promises-best-compensation-for-purandar-airport-land-acquisition/</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/koradi-temple-gate-collapse-guardian-minister-orders-probe-assures-action/08101755</t>
+          <t>https://www.punekarnews.in/pune-revenue-minister-chandrashekhar-bawankule-backs-purandar-airport-urges-farmers-to-voice-grievances-directly/</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/nagpur-man-booked-for-defaming-minister-bawankule-on-social-media/08200806</t>
+          <t>https://www.mypunepulse.com/pune-crackdown-ordered-on-illegal-plotting-and-mining-in-yeolewadi-kondhwa-and-katraj-minister-bawankule/</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/05/14/kamptee-hospital-to-get-50-more-beds-6-acres-land-allotted-bawankule/</t>
+          <t>https://www.nagpurtrends.com/articles/central-jail-to-be-relocated-near-babhulkheda-says-bawankule-jE4hdD?utm_source=website&amp;utm_medium=homepage&amp;utm_name=slider</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/drinking-water-crisis-in-nagpur-district-to-be-resolved-soon-bawankule/04261228</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/functionaries-fret-as-bawankule-welcomes-members-from-oppn-parties/articleshow/121683858.cms</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://www.sarkaritel.com/maha-govt-to-launch-online-property-registration-from-may-1/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-takes-stock-of-damage-caused-due-to-unseasonal-rain/articleshow/121580211.cms</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-inspects-farm-access-road-in-katol-stresses-quality-execution/05311731</t>
+          <t>https://www.ptinews.com/story/business/megha-engineering-infrastructure-fined-rs-94-crore-for-illegal-excavation-maharashtra-minister/2719861</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://www.nagpurtrends.com/articles/chandrashekhar-bawankule-to-unfurl-tricolour-at-nagpurs-republic-day-kG2xyj</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/oppn-drags-fadnavis-into-koratkar-row-bjp-denies-ties-101743273793055.html</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-orders-crackdown-on-illegal-mining-craters-after-child-deaths/articleshow/122393943.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/state-govt-bawankule-behind-ink-attack-pravin-gaikwad/articleshow/122592422.cms</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-to-head-panel-on-farm-roads/articleshow/123103819.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/our-doors-are-open-for-badgujar-bawankule/articleshow/121655948.cms</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticizes-uddhav-for-opposing-maharashtra-security-bill/articleshow/122410846.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-to-appoint-rss-workers-as-pas-to-its-ministers-101737571872713.html</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/maharashtra-cabinet-reshuffle-buzz-final-decision-rests-with-cm-fadnavis-says-bawankule-101753525179967.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/voter-increase-in-kamptee-due-to-rapid-urbanization-bawankule-on-rahul-allegations/articleshow/121699423.cms</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/maha-finalizes-new-policy-to-regulate-hoardings-on-government-land/articleshow/122098695.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/gym-owner-faces-case-for-online-content-against-bawankule/articleshow/123395126.cms</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/megha-engineering-infrastructure-fined-rs-94-crore-for-illegal-excavation-maharashtra-minister/2719861</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-to-allow-hoardings-on-vacant-land-owned-by-govt-bawankule-101750872010984.html</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/90-water-conservation-structures-non-functional-bawankule/articleshow/121711476.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/50-of-bhandara-city-located-on-nazul-land-govt-to-regularize-these-properties-bawankule/articleshow/123103215.cms</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/oppn-drags-fadnavis-into-koratkar-row-bjp-denies-ties-101743273793055.html</t>
+          <t>https://realty.economictimes.indiatimes.com/news/infrastructure/maharashtra-government-to-begin-campaign-from-april-1-to-update-7/12-land-title-records/119479129</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-assures-timely-relief-for-rain-hit-farmers-as-per-norms/articleshow/120074385.cms</t>
+          <t>https://www.business-standard.com/pti-stories/national/maharashtra-govt-plans-to-curb-illegal-sand-mining-through-drone-based-surveys-125060600147_1.html</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bhandara-illegal-sand-mining-2-revenue-officers-suspended/articleshow/120138193.cms</t>
+          <t>https://www.indiatoday.in/india/law-news/story/supreme-court-status-quo-order-bale-shah-peer-dargah-demolition-2727320-2025-05-20</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-hits-back-at-raut-over-his-outburst-against-sharad-pawar/02131733</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-minister-bawankule-asks-bmc-to-halt-its-demolition-drive-in-north-mumbai-till-ganeshotsav-23590378</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-meets-protesting-bachchu-kadu-cong-backs-his-stir/articleshow/121836362.cms</t>
+          <t>https://www.nagpurtoday.in/dont-repeat-my-mistakes-nitin-gadkaris-candid-advice-to-bawankule-on-caste-based-politics/04071557</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/our-doors-are-open-for-badgujar-bawankule/articleshow/121655948.cms</t>
+          <t>https://www.nagpurtoday.in/friendship-day-bash-turns-chaotic-main-bawankule-se-baat-kar-leta-hoon-organisers-threat-to-cops-caught-on-camera/08050821</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/bjp-targeting-1-5-cr-party-members-in-maha-ahead-of-civic-polls-bawankule/articleshow/118309658.cms</t>
+          <t>https://www.thehansindia.com/news/national/twelve-officers-from-maharashtra-promoted-to-the-indian-administrative-service-987949</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/shiv-sena-minister-meets-raj-thackeray-at-his-mumbai-residence-3417200</t>
+          <t>https://www.nagpurtoday.in/now-sand-mafias-to-face-criminal-charges-not-just-fines-bawankule/07181631</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/maha-govt-allows-24-hour-sand-transport/articleshow/122256742.cms</t>
+          <t>https://www.nagpurtoday.in/the-constitution-is-the-backbone-of-indias-development-maharashtra-minister-bawankule-pays-tribute-to-dr-ambedkar-in-nagpur/04141639</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ladki-bahin-gets-336cr-from-tribal-dept-min-denies/articleshow/121385494.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/land-measurement-for-division-in-maharashtra-now-at-rs-200-23548697</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/nagpur-violence-bawankule-meets-injured-police-officers-personnel-in-hospital/03182025</t>
+          <t>https://www.ptinews.com/story/national/Do-not-raze-unauthorised-houses-during-Ganesh-festival-Minister-orders-authorities/2840776</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/law-on-land-fragmentation-to-be-scrapped/articleshow/122349434.cms</t>
+          <t>https://www.nagpurtoday.in/congress-must-decide-how-much-more-insult-it-can-tolerate-from-shiv-sena-ubt-bawankule/07071926</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-sets-july-15-deadline-for-document-distribution-to-all-dnts/articleshow/121347284.cms</t>
+          <t>https://www.nagpurtoday.in/women-should-leverage-govt-schemes-through-shgs-to-become-self-reliant-bawankule/03251428</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/rahul-gandhi-lacks-mentality-to-accept-defeat-bawankule/02071649</t>
+          <t>https://www.nagpurtoday.in/now-get-stamp-papers-by-paying-fees-online-in-maharashtra-bawankule/03251300</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/revenue-minister-orders-demolition-of-unauthorised-bungalows-in-mumbai-two-officials-suspended-for-crz-map-manipulation/articleshow/118855995.cms</t>
+          <t>https://www.sarkaritel.com/maha-govt-to-launch-online-property-registration-from-may-1/</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-approves-policy-for-promoting-artificial-sand-101747164656571.html</t>
+          <t>https://thenewsmill.com/2025/07/part-of-maharashtras-tradition-chandrashekhar-bawankule-responds-to-uddhav-thackerays-praise-for-cm-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/resolve-public-issues-on-priority-bawankule-directs-administration/03241323</t>
+          <t>https://thenewsmill.com/2025/05/chandrashekhar-bawankule-welcomes-ncps-chhagan-bhujbal-in-maharashtra-cabinet-calls-it-a-boost-for-govt/</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/in-direct-public-outreach-bawankule-holds-3rd-janata-darbar-in-a-month/articleshow/121553803.cms</t>
+          <t>https://www.socialnews.xyz/?p=6563311</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/big-relief-for-students-citizens-bawankule-announces-waiver-of-rs-500-stamp-duty-for-affidavits/03051617</t>
+          <t>https://www.socialnews.xyz/?p=6725428</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/dont-repeat-my-mistakes-nitin-gadkaris-candid-advice-to-bawankule-on-caste-based-politics/04071557</t>
+          <t>https://timesofindia.indiatimes.com/entertainment/events/chandrashekhar-bawankules-initiative-brings-a-timeless-epic-to-life/articleshow/117122781.cms</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/drones-to-keep-an-eye-on-illegal-mining-across-maharashtra-bawankule/03211218</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/ravindra-chavan-set-to-head-maha-bjp-says-bawankule/articleshow/121504377.cms</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/lets-work-towards-a-developed-maharashtra-urges-nagpur-guardian-minister-bawankule/01271530</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/our-caste-is-bjp-we-serve-the-nation-gadkari/articleshow/120044597.cms</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/vidarbha-bhoodan-yagna-mandal-to-be-revamped-bawankule/02071335</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/state-to-soon-have-a-new-artificial-sand-policy-bawankule/articleshow/120441502.cms</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-hails-union-budget-calls-it-a-strong-pillar-for-indias-future/02011547</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/owners-willingly-giving-up-land-for-civic-projects-in-maharashtra-may-receive-additional-benefits-says-chandrashekhar-bawankule/articleshow/119555188.cms</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-dares-rahul-gandhi-to-contest-from-kamptee-in-2029-assembly-poll/02101325</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/bawankule-asks-for-alternatives-as-meeting-with-farmers-over-purandar-airport-ends-in-stalemate/articleshow/120909800.cms</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-seeks-probe-into-sanjay-rauts-book-over-comments-on-judiciary/05171156</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-condemns-kharges-kumbh-mela-comments-demands-apology/articleshow/117652890.cms</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/double-engine-govt-working-in-peoples-best-interests-new-maharashtra-bjp-chief-ravindra-chavan20250702021253</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/prevent-floods-conserve-water-bawankule-to-nmc/articleshow/119353591.cms</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/07/part-of-maharashtras-tradition-chandrashekhar-bawankule-responds-to-uddhav-thackerays-praise-for-cm-fadnavis/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/saamanas-writings-are-damaging-uddhav-says-bawankule-amid-row-over-phule-comments/articleshow/120289982.cms</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/04/very-shameless-statement-chandrashekhar-bawankule-slams-vijay-wadettiwars-remark-on-pahalgam-attack/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-mahayuti-expansion-only-after-consensus-among-allies/articleshow/117496923.cms</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/05/chandrashekhar-bawankule-welcomes-ncps-chhagan-bhujbal-in-maharashtra-cabinet-calls-it-a-boost-for-govt/</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/maharashtras-love-jihad-law-to-be-strictest-in-india-minister-chandrashekhar-bawankule/articleshow/118295093.cms</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/cities/bjp-has-no-rule-of-retirement-at-75-raut-can-t-decide-modi-s-tenure-maharashtra-bjp-chief-1762084</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/who-reads-saamana-who-listens-to-them-asks-bawankule/articleshow/121541164.cms</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-maharashtra-minister-bawankules-call-to-empty-congress-sparks-debate-clarifies-stance-amid-opposition-criticism/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-pushes-for-speedy-execution-of-pench-irri-schemes/articleshow/120215813.cms</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-revenue-minister-chandrashekhar-bawankule-promises-best-compensation-for-purandar-airport-land-acquisition/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/drones-to-monitor-illegal-mining-across-maha-bawankule/articleshow/119269920.cms</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-revenue-minister-chandrashekhar-bawankule-backs-purandar-airport-urges-farmers-to-voice-grievances-directly/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/the-nomadic-community-will-get-ration-anywhere-in-the-state-says-revenue-minister-chandrashekhar-bawankule/articleshow/121208499.cms</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/good-news-maharashtra-waives-%E2%82%B9500-stamp-duty-on-affidavits-major-relief-for-students-citizens/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/minister-bawankule-bjp-ready-for-upcominglocal-body-elections/articleshow/121504003.cms</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-crackdown-ordered-on-illegal-plotting-and-mining-in-yeolewadi-kondhwa-and-katraj-minister-bawankule/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/macau-jibe-to-advt-row-cong-bjp-maha-chiefs-in-war-of-words/articleshow/120529370.cms</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-congratulates-gadkari-for-receiving-lokmanya-tilak-national-award/07231655</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pending-maharera-recovery-cases-to-be-disposed-of-within-3-months-bawankule/articleshow/118947932.cms</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://www.orissapost.com/cricketer-kedar-jadhav-joins-bjp/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/probe-rauts-book-for-remarks-on-judicial-process-bawankule/articleshow/121219474.cms</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/our-caste-is-bjp-we-serve-the-nation-gadkari/articleshow/120044597.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/people-will-decide-when-modi-should-retire-not-sanjay-raut-bawankule/articleshow/119881247.cms</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/bawankule-hits-back-at-rahul-over-poll-charges-says-he-should-worry-more-about-congress-survival-3402034</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/bjp-targeting-1-5-cr-party-members-in-maha-ahead-of-civic-polls-bawankule/articleshow/118309658.cms</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/functionaries-fret-as-bawankule-welcomes-members-from-oppn-parties/articleshow/121683858.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-quashes-rift-rumours-asserts-mahayuti-will-contest-local-polls-unitedly/articleshow/121448703.cms</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/owners-willingly-giving-up-land-for-civic-projects-in-maharashtra-may-receive-additional-benefits-says-chandrashekhar-bawankule/articleshow/119555188.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-assures-timely-relief-for-rain-hit-farmers-as-per-norms/articleshow/120074385.cms</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-condemns-kharges-kumbh-mela-comments-demands-apology/articleshow/117652890.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ladki-bahin-gets-336cr-from-tribal-dept-min-denies/articleshow/121385494.cms</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/prevent-floods-conserve-water-bawankule-to-nmc/articleshow/119353591.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-sets-july-15-deadline-for-document-distribution-to-all-dnts/articleshow/121347284.cms</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/saamanas-writings-are-damaging-uddhav-says-bawankule-amid-row-over-phule-comments/articleshow/120289982.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/revenue-minister-orders-demolition-of-unauthorised-bungalows-in-mumbai-two-officials-suspended-for-crz-map-manipulation/articleshow/118855995.cms</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-mahayuti-expansion-only-after-consensus-among-allies/articleshow/117496923.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/revenue-dept-must-implement-digital-initiatives-to-resolve-pending-cases-immediately-bawankule/articleshow/119990325.cms</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/maharashtras-love-jihad-law-to-be-strictest-in-india-minister-chandrashekhar-bawankule/articleshow/118295093.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/govt-with-you-bawankule-assures-matangs-seeking-sub-quota-benefits-101747768592892.html</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-calls-rahul-gandhis-caste-census-push-too-late-to-matter/articleshow/122925629.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/in-direct-public-outreach-bawankule-holds-3rd-janata-darbar-in-a-month/articleshow/121553803.cms</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/rahul-gandhi-has-lost-the-plot-says-bawankule-denies-dig-at-bachchu-kadu/articleshow/123103074.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/social-media-influencers-on-radar-strict-monitoring-for-ram-navami-bawankule/articleshow/120024432.cms</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://realty.economictimes.indiatimes.com/news/allied-industries/free-sand-royalty-receipts-to-be-delivered-to-beneficiaries-of-housing-schemes-maharashtra-revenue-minister/121176284</t>
+          <t>https://www.business-standard.com/politics/rahul-upset-over-electoral-losses-maharashtra-bjp-chief-on-rigging-claims-125060700848_1.html</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-tells-every-dept-to-set-up-nurseries-on-its-land/articleshow/122410853.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/bawankule-denies-transfer-of-funds-for-ladki-bahin-scheme-from-tribal-development-dept/articleshow/121385644.cms</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/no-biometric-attendance-system-no-salary-for-amravati-state-govt-employees-bawankule/articleshow/122789185.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/tatkare-bawankule-push-for-rapid-launch-of-womens-employment-hub-in-koradi/articleshow/121347327.cms</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/former-cricketer-kedar-jadhav-joins-bjp-3484153</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-offers-relief-to-plot-holders-in-kamptee-cantonment-land-dispute/articleshow/121346411.cms</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/govt-panel-to-conduct-survey-to-identify-farmers-in-need-of-loan-waiver-in-maharashtra-says-bjp-minister-bawankule/articleshow/123169142.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/koradi-to-get-butterfly-garden-7d-theatre-worlds-tallest-hanuman-statue-bawankule/articleshow/122844552.cms</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/rss-holds-two-day-brainstorming-session-with-bjp-allied-outfits-3362607</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/no-funds-diverted-from-other-departments-for-ladki-bahin-scheme-says-bawankule-23565529</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/maharashtra-revenue-department-goes-hi-tech-to-ensure-employee-attendance-8944686</t>
+          <t>https://www.business-standard.com/industry/agriculture/maharashtra-farmers-compensation-unseasonal-rain-damage-relief-amravati-125053001729_1.html</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://manufacturing.economictimes.indiatimes.com/news/industry/rs-1200-cr-sought-for-nagpur-rs-600-crore-for-amravati/117907831</t>
+          <t>https://www.mypunepulse.com/pune-bawankule-calls-for-dialogue-as-farmers-protest-purandar-airport-land-acquisition/</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-will-cancel-fake-birth-certificates-issued-to-illegal-bangladeshi-residents-state-minister-bawankule-3656548</t>
+          <t>https://www.mypunepulse.com/good-news-maharashtra-waives-%E2%82%B9500-stamp-duty-on-affidavits-major-relief-for-students-citizens/</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/govt-with-you-bawankule-assures-matangs-seeking-sub-quota-benefits-101747768592892.html</t>
+          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-on-ladki-bahin-yojana-if-men-have-taken-money-than-file-case-and-the-money-should-also-be-recovered-revenue-minister-instructions-1372671</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/in-politics-role-keeps-changing-cm-fadnavis-3512825</t>
+          <t>https://marathi.abplive.com/news/maharashtra/chandrashekhar-bawankule-tweet-12-senior-officers-of-the-revenue-department-promoted-by-the-public-service-commission-given-ias-status-by-the-center-1369895</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/social-media-influencers-on-radar-strict-monitoring-for-ram-navami-bawankule/articleshow/120024432.cms</t>
+          <t>https://marathi.ndtv.com/cities/chandrashekhar-bawankule-not-aware-of-sudhakar-badgujars-entry-into-bjp-8687548</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/politics/rahul-upset-over-electoral-losses-maharashtra-bjp-chief-on-rigging-claims-125060700848_1.html</t>
+          <t>https://news18marathi.com/maharashtra/revenue-minister-chandrashekhar-bawankule-important-orders-to-sub-divisional-officer-and-tehsildar-1373523.html</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/bawankule-denies-transfer-of-funds-for-ladki-bahin-scheme-from-tribal-development-dept/articleshow/121385644.cms</t>
+          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-says-revenue-department-faceapp-registration-is-mandatory-for-everyone-from-talatha-to-dy-collector-1372159</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/tatkare-bawankule-push-for-rapid-launch-of-womens-employment-hub-in-koradi/articleshow/121347327.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/chandrashekhar-bawankule-on-sharad-pawar-minister-chandrashekhar-bawankule-criticism-on-sharad-pawar-s-mandal-yatra-1376056</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/5/5/%E2%80%98One-district,-One-Registration-for-property-commences-in-Mah.html</t>
+          <t>https://mahasamvad.in/174971/</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/sc-verdict-on-zudpi-jungle-opens-doors-to-vidarbhas-all-round-development-jobs-bawankule/05231117</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-leader-chandrashekhar-bawankule-denied-allegations-of-sushma-andhare-having-connection-with-sambhaji-brigade-pravin-gaikwad-attack-1369812</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cuts-red-tape-waives-rs-500-stamp-duty-on-affidavits-23495197</t>
+          <t>https://marathi.ndtv.com/maharashtra/maharashtra-politics-chandrashekhar-bawankule-big-statement-about-ban-sanjay-rauts-narkatla-swarg-book-8430233</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/nagpur-fire-maharashtra-govt-announce-rs-5-lakh-to-each-victims-family20250412202335/</t>
+          <t>https://mahasamvad.in/172891/</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/bjp-gets-1-crore-new-members-across-maharashtra-23482502</t>
+          <t>https://www.esakal.com/vidarbha/maharashtra-government-forms-committee-for-farmers-loan-waiver-minister-appeals-to-avoid-haste-in-protests-vsb99</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-bawankule-calls-for-dialogue-as-farmers-protest-purandar-airport-land-acquisition/</t>
+          <t>https://marathi.abplive.com/news/politics/emotional-letter-from-ex-bjp-maharashtra-president-chandrashekhar-bawankule-now-ravindra-chavhan-new-state-bjp-presdent-1367444</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/no-face-app-no-salary-maharashtra-govt-makes-digital-attendance-compulsory-for-revenue-employees/</t>
+          <t>https://marathi.abplive.com/news/politics/sambhaji-brigade-leader-pravin-gaikwad-press-conference-says-devendra-fadnavis-and-chandrashekhar-bawankule-supports-deepak-kate-1370337</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/mastermind-behind-nagpur-violence-will-be-identified-bawankule/03181157</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-bjp-state-president-election-process-begins-chandrashekar-bawankule-defends-public-safety-bill-1367078</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/?p=6725428</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/chandrashekhar-bawankule-reaction-on-bjp-leader-babanrao-lonikar-statement/articleshow/122091225.cms</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/chandrashekhar-bawankule-not-aware-of-sudhakar-badgujars-entry-into-bjp-8687548</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/chandrashekhar-bawankule-apologize-for-manikrao-kokates-statement-134778297.html</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174409/</t>
+          <t>https://marathi.abplive.com/news/maharashtra-politics-revenue-minister-chandrashekhar-bawankule-mediation-in-the-issue-of-the-disabled-and-successful-solution-after-six-ministers-discuss-1367752</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/revenue-minister-chandrashekhar-bawankule-important-orders-to-sub-divisional-officer-and-tehsildar-1373523.html</t>
+          <t>https://mahasamvad.in/175785/</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/171657/</t>
+          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-criticized-on-eknath-khadse-over-girish-mahajan-and-rameshwar-naik-prafull-lodha-file-complaint-demand-maharashtra-marathi-news-1371612</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170401/</t>
+          <t>https://mahasamvad.in/176273/</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172891/</t>
+          <t>https://mahasamvad.in/173287/</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrashekhar-bawankule-on-sharad-pawar-minister-chandrashekhar-bawankule-criticism-on-sharad-pawar-s-mandal-yatra-1376056</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/chandrashekhar-bawankule-on-purandar-airport-survey-stopped-farmer-issue-134969709.html</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/maharashtra-politics-chandrashekhar-bawankule-big-statement-about-ban-sanjay-rauts-narkatla-swarg-book-8430233</t>
+          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-immediate-suspension-of-the-tehsildars-who-sang-when-will-action-be-taken-against-the-dysp-anant-kulkarni-who-kicked-1377733</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/maharashtra-government-forms-committee-for-farmers-loan-waiver-minister-appeals-to-avoid-haste-in-protests-vsb99</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/chandrashekhar-bawankule-farmer-loan-waiver-shinde-delhi-visit-135625935.html</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175785/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/1/strict-action-will-be-taken-against-illegal-sand-miners-on-wardha-river-revenue-minister-chandrashekhar-bawank.html</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-bjp-state-president-election-process-begins-chandrashekar-bawankule-defends-public-safety-bill-1367078</t>
+          <t>https://marathi.ndtv.com/maharashtra/maharashtra-politics-chandrashekhar-bawankule-take-strict-action-on-pwd-department-scam-sting-operation-7921778</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174971/</t>
+          <t>https://mahasamvad.in/172168/</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/chandrashekhar-bawankule-reaction-on-bjp-leader-babanrao-lonikar-statement/articleshow/122091225.cms</t>
+          <t>https://mahasamvad.in/172900/</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra-politics-revenue-minister-chandrashekhar-bawankule-mediation-in-the-issue-of-the-disabled-and-successful-solution-after-six-ministers-discuss-1367752</t>
+          <t>https://mahasamvad.in/175339/</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/minister-bawankule-questions-opposition-silence-on-honeytrap-claims-vsb99</t>
+          <t>https://mahasamvad.in/168918/</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173287/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/26/chandrashekhar-bawankule-on-congress-obc.html</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/1/strict-action-will-be-taken-against-illegal-sand-miners-on-wardha-river-revenue-minister-chandrashekhar-bawank.html</t>
+          <t>https://marathi.abplive.com/news/bacchu-kadu-response-to-chandrashekhar-bawankule-criticism-over-farmers-loan-waiver-issue-maharashtra-politics-marathi-news-1374715</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrashekhar-bawankule-confesses-illegal-hill-breaking-in-pune-district-pune-print-news-apk-13-zws-70-5222016/</t>
+          <t>https://www.lokmat.com/maharashtra/land-seized-by-builder-returned-to-babasaheb-ambedkars-heirs-says-chandrashekhar-bawankule-a-a629/amp/</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/maharashtra-politics-chandrashekhar-bawankule-take-strict-action-on-pwd-department-scam-sting-operation-7921778</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/aurangabad/jalna/news/inam-land-in-khanepuri-is-in-the-possession-of-the-temple-an-important-decision-by-revenue-minister-chandrashekhar-bawankule-134611955.html</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170687/</t>
+          <t>https://mahasamvad.in/172725/</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172168/</t>
+          <t>https://deshdoot.com/revenue-minister-chandrashekhar-bawankule-to-visit-nashik-on-saturday/</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172900/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/5/it-is-unfortunate-for-this-country-that-such-an-immature-opposition-leader.html</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/nagpur-news-saw-the-news-on-abp-majha-chandrashekhar-bawankule-immediately-took-note-with-the-help-of-nitin-gadkari-road-issue-was-resolved-in-an-instant-1377264</t>
+          <t>https://marathi.abplive.com/news/mumbai/chandrasekhar-bawankule-orders-tehsildars-to-retrieve-42000-cancelled-birth-certificates-by-august-15-1372656</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170632/</t>
+          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-on-malegaon-blast-case-verdict-the-truth-has-come-out-in-the-malegaon-case-now-congress-should-apologize-demands-chandrashekhar-bawankule-1373804</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175339/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/chandrashekhar-bawankule-amravati-news-bjp-minister-chandrashekhar-bawankule-criticizes-on-congress-amravati-1377470</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170666/</t>
+          <t>https://www.nagpurtoday.in/revenue-minister-chandrasekhar-bawankules-announcement-in-the-legislative-assembly-action-against-wrongdoers/03201828</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/government-employees-will-be-threatened-those-who-run-away-from-the-office-are-no-longer-safe-directed-by-chandrasekhar-bawankule/04241205</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/chandrashekhar-bawankule-order-to-try-split-congress-and-join-congress-workers-in-bjp/articleshow/120875259.cms</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/26/chandrashekhar-bawankule-on-congress-obc.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/26/chandrashekhar-bawankule-rahul-gandhi-narendra-modi.html</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-praises-pm-narendra-modi-for-operation-sindoor/videoshow/121133822.cms</t>
+          <t>https://mahasamvad.in/174403/</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-explained-the-maths-bmc-elections-raj-thackeray-mns-we-are-prepared-for-51-percent-votes-bjp-response-to-thackeray-alliance-1374778</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/1/committee-formed-under-the-chairmanship-of-revenue-minister-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172725/</t>
+          <t>https://news18marathi.com/maharashtra/revenue-minister-chandrashekhar-bawankule-announded-cancelled-tukde-ban-act-maharashtra-govt-big-decision-1432122.html</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/revenue-minister-chandrashekhar-bawankule-to-visit-nashik-on-saturday/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-voter-list-deletion-allegations-congress-accuses-sanket-bawankule-of-deleting-thousands-of-voter-names-in-kamthi-assembly-constituency-1378709</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/5/it-is-unfortunate-for-this-country-that-such-an-immature-opposition-leader.html</t>
+          <t>https://marathi.abplive.com/news/politics/chandrashekhar-bawankule-on-jayant-patil-resigns-shashikant-shinde-new-state-president-of-sharad-pawar-ncp-maharashtra-politics-maharashtra-marathi-news-1369487</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-news-state-governments-big-decision-regarding-land-fragmentation-high-level-committee-formed-to-make-reforms-83561</t>
+          <t>https://www.tarunbharat.com/information-from-revenue-minister-chandrashekhar-bawankule-in-amboli/</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrashekhar-bawankule-amravati-news-bjp-minister-chandrashekhar-bawankule-criticizes-on-congress-amravati-1377470</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-uddhav-thackeray-and-bawankule-engage-in-twitter-spat-as-shiv-sena-workers-join-bjp-due-to-leader-unavailability-in-maharashtra-politics-1369935</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/revenue-minister-chandrasekhar-bawankules-announcement-in-the-legislative-assembly-action-against-wrongdoers/03201828</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/minister-bawankule-questions-opposition-silence-on-honeytrap-claims-vsb99</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/26/chandrashekhar-bawankule-rahul-gandhi-narendra-modi.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/buldana/chandrashekhar-bawankule-criticizes-sharad-pawar-over-obc-mandal-yatra/videoshow/123213597.cms</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174403/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/25/special-committee-for-manmad-indore-railway-land-acquisition-revenue-minister-bawankules-instructions-for-re-s.html</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nashik/bjp-chandrashekhar-bawankule-says-code-of-conduct-will-in-august-for-upcoming-municipal-elections-2025-pri/articleshow/121662946.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/wardha/revenue-minister-chandrashekhar-bawankule-gave-clear-indication-will-govt-waive-off-loans-to-farmers-pri/articleshow/120634173.cms</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-voter-list-deletion-allegations-congress-accuses-sanket-bawankule-of-deleting-thousands-of-voter-names-in-kamthi-assembly-constituency-1378709</t>
+          <t>https://www.mahamtb.com/Encyc/2025/6/4/Chandrashekhar-Bawankule-expressed-his-determination-to-revenue-administration.html</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/1/committee-formed-under-the-chairmanship-of-revenue-minister-bawankule.html</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/bawankule-condemns-attack-pravin-gaikwad-deepak-kate-statement-135459180.html</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/revenue-minister-chandrashekhar-bawankule-announded-cancelled-tukde-ban-act-maharashtra-govt-big-decision-1432122.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/nagpur-news-saw-the-news-on-abp-majha-chandrashekhar-bawankule-immediately-took-note-with-the-help-of-nitin-gadkari-road-issue-was-resolved-in-an-instant-1377264</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/sudhakar-badgujar-join-bjp-chandrashekhar-bawankule-reaction-1425349.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/3/27/loan-available-on-Occupier-Class-2-land-Chandrashekhar-Bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/information-from-revenue-minister-chandrashekhar-bawankule-in-amboli/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/3/24/State-government-takes-concrete-steps-regarding-temple-land-donation-By-Chandrashekhar-Bawankule-.html</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-uddhav-thackeray-and-bawankule-engage-in-twitter-spat-as-shiv-sena-workers-join-bjp-due-to-leader-unavailability-in-maharashtra-politics-1369935</t>
+          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-on-agriculture-minister-manikrao-kokate-statement-say-if-agriculture-ministerhas-said-anything-we-will-apologize-on-behalf-of-the-government-maharashtra-politics-1352861</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168121/</t>
+          <t>https://marathi.abplive.com/news/politics/2-former-mlas-and-former-minister-son-join-bjp-chandrashekhar-bawankule-said-2-big-entries-from-congress-soon-aslo-kolhapur-shahapur-and-srirampur-1354545</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168550/</t>
-        </is>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/167416/</t>
-        </is>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/169614/</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/166188/</t>
-        </is>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/167907/</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/167498/</t>
-        </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/166711/</t>
-        </is>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/168197/</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/160422/</t>
-        </is>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/mumbai/micro-zoning-to-determine-rates-of-ready-reckoners-in-mumbai-revenue-minister-chandrashekhar-bawankule-decision-marathi-news-1352443</t>
-        </is>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/165886/</t>
-        </is>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/172338/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/chandrashekhar-bawankule-on-uddhav-thackeray-in-mumbai-bjp-state-president-chandrashekhar-bawankule-criticizes-on-uddhav-thackeray-1354721</t>
         </is>
       </c>
     </row>

--- a/Output/Chandrashekhar Bawankule/extracted_links_Chandrashekhar Bawankule_failed_links.xlsx
+++ b/Output/Chandrashekhar Bawankule/extracted_links_Chandrashekhar Bawankule_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A162"/>
+  <dimension ref="A1:A151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,1127 +438,1050 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178088/</t>
+          <t>https://mahasamvad.in/179502/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AA-%E0%A4%A3%E0%A4%82%E0%A4%A6-%E0%A4%AE%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%9A-%E0%A4%AE%E0%A5%87%E0%A4%97-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AF-%E0%A4%97-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%9D%E0%A4%97%E0%A4%A1-%E0%A4%B8%E0%A5%81%E0%A4%9F%E0%A4%A3-%E0%A4%B0-%E0%A4%AE%E0%A4%B9%E0%A4%B8%E0%A5%82%E0%A4%B2-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AE-%E0%A4%A0-%E0%A4%98-%E0%A4%B7%E0%A4%A3/ar-AA1MeEni</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/land-approved-for-bhandara-judges-residence-revenue-minister-chandrashekhar-bawankules-initiative.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178012/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AA-%E0%A4%A3%E0%A4%82%E0%A4%A6-%E0%A4%AE%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%9A-%E0%A4%AE%E0%A5%87%E0%A4%97-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AF-%E0%A4%97-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%9D%E0%A4%97%E0%A4%A1-%E0%A4%B8%E0%A5%81%E0%A4%9F%E0%A4%A3-%E0%A4%B0-%E0%A4%AE%E0%A4%B9%E0%A4%B8%E0%A5%82%E0%A4%B2-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AE-%E0%A4%A0-%E0%A4%98-%E0%A4%B7%E0%A4%A3/ar-AA1MeEni?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/twitter-war-breaks-out-between-rohit-pawar-and-chandrashekhar-bawankule-over-megha-engineering/920492/</t>
+          <t>https://mahasamvad.in/179430/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/resolve-the-sand-issue-in-konkan-within-three-months/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/21/maharashtra-knows-what-lights-vadettiwar-lit-when-he-was-a-minister-minister-chandrashekhar-bawankule-criticiz.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/politics/rohit-pawar-challenge-accepted-twitter-proof-devabhau-advertisment/</t>
+          <t>https://mahasamvad.in/178572/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/10/?m=0</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%AA%E0%A4%B9-%E0%A4%B2%E0%A4%82-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4%E0%A5%8D%E0%A4%AF%E0%A5%81%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B0-%E0%A4%95-%E0%A4%81%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B8%E0%A4%9A-%E0%A4%89%E0%A4%B2%E0%A5%8D%E0%A4%B2%E0%A5%87%E0%A4%96-%E0%A4%95%E0%A4%B0%E0%A4%A4-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1yazrQ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/campaign-unveiled-to-boost-baliraja-farmroad-initiativeset-to-minimize-future-conflicts</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-state-new-district-and-taluka-formation-the-map-of-maharashtra-will-change-81-new-talukas-and-20-districts-will-be-created-in-maharashtra/940852/amp</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-launches-chief-minister-baliraja-panand-road-scheme-125091000009_1.html</t>
+          <t>https://www.adharnewsnetwork.com/2025/09/chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/rohit-pawar-on-bawankule-rohit-pawar-again-targeted-revenue-minister-chandrashekhar-bawankule-said-the-suspension-of-engineering-fine-is-a-fine/131885/</t>
+          <t>https://deshonnati.com/officials-should-act-without-condoning-any-wrongdoing/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/chandrasekhar-bawankule-and-ncps-rohit-pawar-questioned-eachother/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/farmers-in-tribal-areas-can-lease-land-to-private-parties-bawankule/articleshow/124004941.cms</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/chandrasekhar-bawankule-said-there-will-be-no-injustice-to-obcs/</t>
+          <t>https://www.devdiscourse.com/article/entertainment/3634952-controversy-brews-over-garba-entry-restrictions-amidst-navratri-celebrations?amp</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/rohit-pawar-rohit-pawar-made-serious-allegations-against-revenue-minister-chandrashekhar-bawankule-said-i-without-evidence/131714/</t>
+          <t>https://www.business-standard.com/india-news/maha-govt-to-allow-tribal-farmers-to-lease-land-to-private-firms-minister-125092000372_1.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/review-of-the-work-of-konkan-revenue-department-chandrashekhar-bawankule-directs-that-the-revenue-system-should-utilize-its-capabilities/132124/</t>
+          <t>https://www.ptinews.com/editor-detail/Tribals-in-Maharashtra-can-now-lease-barren-land-to-private-entities;-govt-to-bring-law-Minister/2932964</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/prove-the-allegations-or-else-retire-from-politics-chandrashekhar-bawankules-direct-challenge-to-rohit-pawar/131706/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.berartimes.com/vidarbha/216208/</t>
+          <t>https://www.ptinews.com/story/national/maharashtra-obc-panel-orders-strict-scrutiny-of-caste-certificates-clears-rs-2-933cr-pending-funds/2920779</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/sena-ubt-criticises-govt-over-match-bawankule-hits-back/articleshow/123887314.cms</t>
+          <t>https://www.devdiscourse.com/article/business/3634504-empowering-maharashtras-tribal-farmers-leasing-land-for-agriculture-and-mining?amp</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/entertainment/southcinema/bawankule-announces-kalamkari-garment-cluster-in-koradi/ar-AA1Mqj9x</t>
+          <t>https://timesofindia.indiatimes.com/india/vhp-issues-hindus-only-diktat-for-garba-bawankule-backs-organisers-rights-wadettiwar-slams-move/articleshow/124014945.cms</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/govt-to-firmly-defend-maratha-and-obc-quotas-bawankule/articleshow/123752163.cms</t>
+          <t>https://www.ptinews.com/editor-detail/vhp-issues--hindus-only--diktat-for-garba;-bawankule-backs-organisers--rights--wadettiwar-slams-move/2932800</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/other/megha-engineering-fined-rs-94-6-crore-for-illegal-mining-in-maharashtra-s-jalna/ar-AA1Iroje?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.ptinews.com/editor-detail/vhp-issues--hindus-only--diktat-for-garba;-bjp-minister-backs-organisers--rights--cong-slams-move/2934001</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/look-beyond-roads-focus-on-health-edu-development-in-villages-bawankule-to-zp/articleshow/123793225.cms</t>
+          <t>https://www.ptinews.com/story/national/No-opposition-to-Badgujar-s-induction-into-BJP-Fadnavis/2655228</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/no-injustice-to-obcs-kunbi-certificates-to-be-issued-only-after-due-verification-bawankule/ar-AA1Mh8fw</t>
+          <t>https://www.devdiscourse.com/article/headlines/3634796-maharashtras-road-to-prosperity-revamping-farm-access-for-farmers?amp</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/no-injustice-to-obcs-accept-only-verified-records-for-maratha-kunbi-certificate-bawankule/articleshow/123816212.cms</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/20/bom22-mh-tribals-land-lease.amp.html</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/clear-health-proposals-in-nagpur-amravati-melghat-bawankule/articleshow/123816301.cms</t>
+          <t>https://www.devdiscourse.com/article/law-order/3634600-maharashtras-new-lease-law-a-boon-or-bane-for-tribal-farmers?amp</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/bawankule-gave-firm-rs90cr-penalty-waiver-in-poll-bonds-favouritism-rohit/articleshow/123772937.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-minister-chhagan-bhujbal-demands-verification-of-obc-certificates-issued-to-maratha-community-23594340</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-hits-back-at-oppn-targeting-cm-over-devabhau-advt/articleshow/123772690.cms</t>
+          <t>https://www.socialnews.xyz/?p=6725428</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-announces-kalamkari-garment-cluster-in-koradi/articleshow/123853712.cms</t>
+          <t>https://www.devdiscourse.com/article/headlines/3634796-maharashtras-road-to-prosperity-revamping-farm-access-for-farmers</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/obc-communitys-concerns-over-reservation-will-not-be-ignored-minister-pankaja-munde/2901852</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-soon-allow-private-entities-to-lease-tribal-lands-101758396296809-amp.html</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/no-injustice-to-obcs-kunbi-certificates-to-be-issued-only-after-due-verification-bawankule/ar-AA1Mh8fw?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.hindustantimes.com/india-news/for-hindu-only-garba-vhp-sets-entry-norms-check-aadhaar-apply-tilak-101758363132840-amp.html</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/no-injustice-to-obcs-kunbi-certificates-to-be-issued-only-after-due-verification-bawankule/2902881</t>
+          <t>https://www.msn.com/mr-in/news/other/chandrashekhar-bawankule-%E0%A4%95%E0%A5%81%E0%A4%A3-%E0%A4%B9-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9C%E0%A4%96%E0%A4%AE%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%AE-%E0%A4%A0-%E0%A4%9A-%E0%A4%B3%E0%A5%82-%E0%A4%A8%E0%A4%AF%E0%A5%87-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%95-%E0%A4%9F%E0%A5%87-%E0%A4%95-%E0%A4%B9-%E0%A4%AC-%E0%A4%B2%E0%A4%B2%E0%A5%87-%E0%A4%85%E0%A4%B8%E0%A4%A4-%E0%A4%B2-%E0%A4%A4%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%A4%E0%A4%B0%E0%A5%8D%E0%A4%AB%E0%A5%87-%E0%A4%86%E0%A4%AE%E0%A5%8D%E0%A4%B9-%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%AE-%E0%A4%AE-%E0%A4%97%E0%A5%82-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%87%E0%A4%96%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87/ar-AA1Cn5Cg?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/sena-ubt-criticises-govt-over-match-bawankule-hits-back/amp_articleshow/123887314.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/maharashtra-manoj-jarange-govt-at-odds-over-obc-certificates-for-marathas-23593384</t>
+          <t>https://marathi.indiatimes.com/e-paper/chandrashekhar-bawankules-important-instructions-for-water-resource-conservation-in-nagpur/articleshow/123916999.cms</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/177929/</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/guardian-minister-chandrashekhar-bawankule-thanks-govt-for-upgrading-nagpurs-religious-sites-sdj87</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/10/there-will-be-no-injustice-to-obcs-no-false-records-important-decision-taken-in-the-cabinet-sub-committee-meet.html</t>
+          <t>https://mahasamvad.in/178575/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/maratha-arakashan-%E0%A4%B9%E0%A5%88%E0%A4%A6%E0%A4%B0-%E0%A4%AC-%E0%A4%A6-%E0%A4%97%E0%A5%85%E0%A4%9D%E0%A5%87%E0%A4%9F-%E0%A4%AF%E0%A4%B0%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%A8-%E0%A4%82%E0%A4%A6-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3%E0%A5%82%E0%A4%A8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AE-%E0%A4%A3%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%A8-%E0%A4%B9-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%87%E0%A4%96%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87/ar-AA1LXgLq</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%B8%E0%A5%81%E0%A4%B0%E0%A5%82%E0%A4%9A-%E0%A4%B0-%E0%A4%B9%E0%A4%A3-%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1zbVuE?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-will-discuss-with-chhagan-bhujbal-in-meeting-regarding-obc-community-demands/videoshow/123779234.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/nagpur-political-news-%E0%A4%95%E0%A5%87%E0%A4%B5%E0%A4%B3-%E0%A4%97%E0%A5%85%E0%A4%9D%E0%A5%87%E0%A4%9F%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%A8-%E0%A4%82%E0%A4%A6-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3%E0%A5%82%E0%A4%A8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AE-%E0%A4%A3%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%A8-%E0%A4%B9-%E0%A4%AE%E0%A4%B9%E0%A4%B8%E0%A5%82%E0%A4%B2%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87/ar-AA1LZyoY?cvid=68bc9315762a4b358cad5b270e1111ac&amp;ocid=wispr&amp;apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/chandrasekhar-bawankule-you-cannot-get-caste-certificate-with-sword-at-officers-throat-283530/</t>
+          <t>https://marathi.abplive.com/news/gadchiroli/gadchiroli-non-tribals-will-able-to-take-tribal-lands-on-lease-revenue-minister-chandrashekhar-bawankule-marathi-news-1385320</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/rohit-pawar-chandrashekhar-bawankule-dispute-mega-engineering-fine-135880348.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/gadchiroli/revenue-minister-chandrashekhar-bawankule-announces-that-tribal-lands-can-be-given-on-lease/articleshow/124010200.cms</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/177925/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/minister-chandrashekhar-bawankule-gives-important-instructions-to-officers-about-maratha-kunbi-certificate-distribution/articleshow/123922415.cms</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/topics/chandrashekhar-bawankule/</t>
+          <t>https://agrowon.esakal.com/agro-special/maharashtra-plans-20-new-districts-and-81-talukas-revenue-minister-bawankule-mj18</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/video/obcs-will-not-be-treated-unfairly-chandrasekhar-bawankule-answer-to-laxman-haka/939237</t>
+          <t>https://marathi.ndtv.com/videos/bawankule-no-tickets-for-those-who-follow-leaders-bawankule-warns-997430</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/maratha-aarkshan-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%8D%E0%A4%A8-%E0%A4%B6-%E0%A4%B8%E0%A4%A8-%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%AF-%E0%A4%B2%E0%A4%AF-%E0%A4%A8-%E0%A4%B2%E0%A4%A2-%E0%A4%88%E0%A4%B9-%E0%A4%B2%E0%A4%A2%E0%A5%87%E0%A4%B2-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%87%E0%A4%96%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87/ar-AA1M3rCj</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A8-%E0%A4%AF%E0%A4%AE-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%89%E0%A4%B2%E0%A5%8D%E0%A4%B2%E0%A4%82%E0%A4%98%E0%A4%A8-%E0%A4%95%E0%A5%87%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%B5-%E0%A4%B3%E0%A5%82-%E0%A4%A1%E0%A5%87%E0%A4%AA-%E0%A4%B0%E0%A4%A6%E0%A5%8D%E0%A4%A6/ar-AA1Df6na?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/good-news-for-farmers-chief-minister-baliraja-panand-roads-scheme-in-maharashtra-chandrashekhar-bawankule-difficulties-will-be-resolved-roads-will-be-built-up-to-the-fields-1382855</t>
+          <t>https://mahasamvad.in/178893/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/rohit-pawar-slams-chandrashekhar-bawankule-megha-engineering-fine-controversy-135892296.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-obc-sub-committee-big-decision-on-kunbi-certificate-distribution-to-maratha-community/articleshow/123921757.cms</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/nagpur/news/nagpur-bawankule-pawar-advertisement-controversy-update-135869808.html</t>
+          <t>https://news18marathi.com/maharashtra/revenue-minister-chandrashekhar-bawankule-has-made-murum-mining-royalty-free-1484899.html</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/bharatiya-janata-party-leader-and-minister-chandrashekhar-bawankule-said-that-uddhav-thackeray-has-no-moral-right-to-speak-on-ind-vs-pak-match/921394/</t>
+          <t>https://agrowon.esakal.com/agro-special/maharashtra-to-make-1100-government-services-online-by-may-cm-fadnavis-mj18</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/revenue-minister-chandrashekhar-bawankule-directs-the-administration-to-find-a-solution-to-the-complex-issue-of-sand-temples-and-ancestral-lands-in-the-konkan-region/920713/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-chandrashekhar-bawankule-on-local-body-elections-tickets-via-internal-survey-public-opinion-to-decide-not-loyalty-to-leaders-amid-chandrapur-groupism-1385779/amp</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/minister-chandrashekhar-bawankule-on-obc-reservation-slams-vijay-wadettiwar/919460/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-shivbhojan-thali-scheme-to-continue-minister-bawankule-announces-200-crore-approval-for-maharashtra-s-affordable-meal-program-1385482/amp</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/jalna-news-%E0%A4%86%E0%A4%AE%E0%A4%A6-%E0%A4%B0-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B5%E0%A4%B0-%E0%A4%B2-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%96-%E0%A4%9F-%E0%A4%B2-%E0%A4%A3-%E0%A4%95%E0%A4%B0/ar-AA1MeEhz</t>
+          <t>https://www.msn.com/mr-in/news/other/dhananjay-deshmukh-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%AD%E0%A5%82%E0%A4%AE-%E0%A4%95-%E0%A4%AE-%E0%A4%82%E0%A4%A1-%E0%A4%AF%E0%A4%B2-%E0%A4%B9%E0%A4%B5-%E0%A4%B9-%E0%A4%A4-%E0%A4%A7%E0%A4%A8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%A6%E0%A5%87%E0%A4%B6%E0%A4%AE%E0%A5%81%E0%A4%96-%E0%A4%82%E0%A4%A8-%E0%A4%B5%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%95%E0%A5%87%E0%A4%B2-%E0%A4%96%E0%A4%82%E0%A4%A4/ar-AA1An2uc?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/chandrashekhar-bawankule-open-challenge-to-rohit-pawar-in-cm-fadnavis-advertisement-case/articleshow/123777163.cms</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-shiv-bhojan-thali-scheme-to-continue-in-maharashtra-with-200-crore-approval-closed-centers-to-reopen-1385628/amp</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-obc-leader-and-revenue-minister-chandrashekhar-bawankule-s-reaction-to-atul-save-s-meeting-sparks-interest-in-maharashtra-politics-and-current-affairs-1382705</t>
+          <t>https://www.dainikprabhat.com/now-tribal-lands-will-be-available-on-lease-chandrashekhar-bawankule/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/gunaratna-sadavarte-warns-of-dragging-radhakrishna-vikhe-patil-to-court-if-cases-against-maratha-protesters-are-withdrawn/920375/</t>
+          <t>https://policenama.com/pune-navratri-mahotsav-pune-the-31st-pune-navratri-mahotsav-will-be-inaugurated-grandly-by-revenue-minister-chandrashekhar-bawankule-festival-organizer-aba-bagul-gave-this-information-in-a-press-c/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrashekhar-bawankule-on-obc-upsamiti-meeting-maratha-reservation-kunbi-certificate-marahi-news-1383083</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/private-companies-can-also-lease-wasteland-tribal-land-125092100014_1.html</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/sadavarte-targets-vikhepatil-and-jarange-what-did-he-say-after-meeting-minister-bawankule/videoshow/123811967.cms</t>
+          <t>https://www.marathiebatmya.com/political/obc-sub-committees-decision-thorough-verification-of-kunbi-bogus-certificates/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-chandrashekhar-bawankule-to-chair-crucial-maharashtra-cabinet-sub-committee-meeting-on-obc-and-maratha-reservation-on-september-10-1382547</t>
+          <t>https://www.dainikprabhat.com/pune-news-mine-owners-are-in-trouble-mining-in-mountains-and-hills-banned-revenue-minister-bawankules-firm-stance/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/minister-chandrashekhar-bawankule-on-ncp-sp-rohit-pawar-allegations/919482/</t>
+          <t>https://www.dainikprabhat.com/as-many-as-20-new-districts-and-81-talukas-have-been-created-in-the-state/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/agriculture/chief-minister-baliraja-panand-raste-yojana-good-news-for-farmers-a-big-announcement-by-revenue-minister-chandrashekar-bawankule-1488863.html</t>
+          <t>https://www.dainikprabhat.com/pune-news-exemption-from-the-fragmentation-law-sale-of-one-or-two-gunthas-is-now-possible-know-when-the-implementation-will-start/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/pankaja-munde-on-obc-reservation-and-chhagan-bhujbal-after-meeting-of-obc-subcommittee/920205/amp</t>
+          <t>https://www.dainikprabhat.com/shivbhojan-thali-the-shivbhojan-thali-of-uddhav-thackerays-era-will-continue-bawankule-clearly-stated/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/maharashtra-government-repaying-the-favour-of-electoral-bond-donations-says-mla-rohit-pawar-in-jibe-at-chandrashekhar-bawankule/</t>
+          <t>https://dainikekmat.com/%E0%A4%86%E0%A4%A6%E0%A4%BF%E0%A4%B5%E0%A4%BE%E0%A4%B8%E0%A5%80%E0%A4%82%E0%A4%9A%E0%A5%80-%E0%A4%9C%E0%A4%AE%E0%A5%80%E0%A4%A8-%E0%A4%AD%E0%A4%BE%E0%A4%A1%E0%A5%87%E0%A4%A4%E0%A4%A4%E0%A5%8D%E0%A4%A4/118039/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://telugu.getlokalapp.com/maharashtra-news/nagpur/kamthi/nagpur-artificial-sand-for-just-rs-200-information-about-bawankule-15367254</t>
+          <t>https://dainikekmat.com/%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%AD%E0%A4%B0%E0%A4%BE%E0%A4%A4%E0%A5%80%E0%A4%B2-%E0%A5%A7%E0%A5%A8-%E0%A4%B9%E0%A4%9C%E0%A4%BE%E0%A4%B0-%E0%A5%AC%E0%A5%A6%E0%A5%A6-%E0%A4%B8/118036/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-cabinet-sub-committee-meeting-tomorrow-at-11-am-with-pankaja-munde-chhagan-bhujbal-gulabrao-patil-to-address-obc-demands-and-doubts-1382731</t>
+          <t>https://www.msn.com/mr-in/news/other/banjara-reservation-%E0%A4%AC%E0%A4%82%E0%A4%9C-%E0%A4%B0-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%87%E0%A4%96%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%A3%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B9-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%9A-%E0%A4%A8-%E0%A4%82%E0%A4%A6/ar-AA1MArpW</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-obc-quota-row-maharashtra-gr-sparks-dispute-over-eligible-word-revenue-minister-bawankule-assures-no-harm-to-obc-reservation-vadettiwar-demands-clarity-1382623</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A8%E0%A4%B5%E0%A4%B0-%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A4%E0%A5%8D%E0%A4%B8%E0%A4%B5-%E0%A4%A4-%E0%A4%B2-%E0%A4%97%E0%A4%B0%E0%A4%AC-%E0%A4%AB%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%B9-%E0%A4%82%E0%A4%A6%E0%A5%82%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%86%E0%A4%A7-%E0%A4%B0-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%A1-%E0%A4%A4%E0%A4%AA-%E0%A4%B8-%E0%A4%B5-%E0%A4%B6%E0%A5%8D%E0%A4%B5-%E0%A4%B9-%E0%A4%82%E0%A4%A6%E0%A5%82-%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A4%A6%E0%A5%87%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD%E0%A5%82%E0%A4%AE-%E0%A4%95%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%B9-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1MWJzB</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://telugu.getlokalapp.com/amp/maharashtra-news/false-kunbi-registrations-will-not-be-allowed-bawankule-assures-obcs-15374678</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/rohit-pawar-medha-engineering-chandrashekhar-bawankule-saamana-online-news/</t>
+          <t>https://www.saamana.com/chhagan-bhujbal-demands-probe-into-fake-obc-certificates/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/chandrashekhar-bawankule-there-will-be-no-injustice-against-obcs-chandrashekhar-bawankule-made-it-clear/</t>
+          <t>https://www.lokmat.com/agriculture/news/revenue-ministers-big-announcement-on-the-excavation-of-murum-for-the-repair-of-panand-roads-in-the-state-a-a975/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/our-best-wishes-to-the-thackeray-brothers-minister-bawankules-suggestive-statement/</t>
+          <t>https://www.adharnewsnetwork.com/2025/09/aap-chandrapur.html</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/obc-cabinet-sub-committee-meeting-bawankule-instructions-regarding-incorrect-kunbi-entry-036919.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-local-body-polls-chandrashekhar-bawankule-on-ticket-distribution-public-opinion-to-decide-candidates-amidst-chandrapur-factionalism-1385673</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/sparks-ignited-in-mva-bjp-state-president-chandrashekhar-bawankules-scathing-criticism/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-chandrashekhar-bawankule-on-local-body-elections-tickets-via-internal-survey-public-opinion-to-decide-not-loyalty-to-leaders-amid-chandrapur-groupism-1385779</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/cm-fadnavis-inagurated-development-works-worth-rs-335-crore-in-yavatmal/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-obc-reservation-maharashtra-govt-to-prevent-forgery-in-maratha-kunbi-certificates-sub-committee-demands-2900-crore-for-obc-ministry-welfare-schemes-1384585</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/mou-between-tata-technology-and-govt-in-the-presence-of-cm-fadnavis-govt/amp/</t>
+          <t>https://www.navakal.in/maharashtra/vishwa-hindu-parishadno-muslims-allowed-in-garba-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/chief-minister-devendra-fadnavis-inaugurates-development-works-worth-rs-335-crore-in-yavatmal-125091400010_1.html</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/navratri-utsav-only-hindus-allowed-in-garbhas-vishva-hindu-parishad-takes-this-stand/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.berartimes.com/maharashtra/216432/</t>
+          <t>https://www.business-standard.com/amp/india-news/maha-govt-to-allow-tribal-farmers-to-lease-land-to-private-firms-minister-125092000372_1.html</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/maharashtra-news-injustice-to-obcs-important-decision-of-the-cabinet-sub-committee/</t>
+          <t>https://vsrsnews.in/pimpri-chinchwad/pune-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/there-will-be-a-radical-change-in-the-lives-of-tribals-devendra-fadnavis/</t>
+          <t>https://www.lokmat.com/agriculture/farming-ideas/latest-news-see-what-bhandara-district-farmers-did-to-control-the-khodkid-of-crops-read-in-detail-a-a993/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%AE%E0%A4%B9%E0%A4%B8%E0%A5%82%E0%A4%B2-%E0%A4%B2%E0%A5%8B%E0%A4%95-%E0%A4%85%E0%A4%A6%E0%A4%BE%E0%A4%B2%E0%A4%A4%E0%A5%80%E0%A4%B8-%E0%A4%A8%E0%A4%BE%E0%A4%97%E0%A4%B0%E0%A4%BF%E0%A4%95/117148/</t>
+          <t>https://marathi.abplive.com/news/revenue-servant-strike-eighth-day-government-not-even-a-simple-acknowledgement-protesters-warn-the-government-nagpur-news-maharashtra-marathi-news-1385371/amp</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/mr/chief-minister-devendra-fadnavis-41/</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-saturday-20-september-2025-1496545.html</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/chandrasehkhar-bawankule-chief-minister-baliraja-panand-road-scheme-chandrasekhar-bawankules-announcement-farmers-will-benefit/920043/</t>
+          <t>https://www.loksatta.com/pune/indian-railways-made-in-india-technology-locomotive-in-train-engine-pune-print-news-css-98-5381428/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/obc-reservation-there-will-be-no-injustice-to-obcs-no-false-entries-important-decisions-taken-in-the-meeting-chaired-by-bawankule/920275/</t>
+          <t>https://www.loksatta.com/pune/chairman-of-maharashtra-legislative-council-statement-on-ram-shinde-marathwada-backwardness-pune-print-news-zws-70-5381328/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%A4-%E0%A4%A1%E0%A4%AA-%E0%A4%A3-%E0%A4%95%E0%A4%B0%E0%A4%A4%E0%A4%82%E0%A4%AF-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A-%E0%A4%96%E0%A4%B3%E0%A4%AC%E0%A4%B3%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%86%E0%A4%B0-%E0%A4%AA-90-%E0%A4%95-%E0%A4%9F-%E0%A4%82%E0%A4%B5%E0%A4%B0%E0%A5%81%E0%A4%A8-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%B6-%E0%A4%AD-%E0%A4%A1%E0%A4%B2%E0%A5%87-%E0%A4%B8%E0%A4%82%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%98%E0%A5%87%E0%A4%8A%E0%A4%A8/ar-AA1M6js8</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-rain-live-mumbai-pune-nagpur-traffic-local-trains-flood-imd-alert-update-beed-crime-ex-sarpanch-govind-barge-death-pooja-gaikwad-latest-news-breaking-rak-94-5372752/lite/?liveblog_page=3&amp;liveblog_last=90890-1757948209</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/cm-devendra-fadnavis-maharashtra-is-my-adopted-state-committed-to-yavatmal-development-vsb99</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-rain-live-mumbai-pune-nagpur-traffic-local-trains-flood-imd-alert-update-beed-crime-ex-sarpanch-govind-barge-death-pooja-gaikwad-latest-news-breaking-rak-94-5372752/lite/?liveblog_page=2&amp;liveblog_last=90863-1757936847</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/there-will-be-no-injustice-to-obcs-kunbi-certificate-only-after-matching-the-lineage/116660/</t>
+          <t>https://www.loksatta.com/pune/cm-devendra-fadnavis-on-remark-on-maharashtra-revenue-department-pune-print-news-zws-70-5381326/lite/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-uddhav-thackeray-cricket-row-uddhav-thackeray-criticized-over-operation-sindoor-absence-pakistan-flags-and-politicizing-india-pakistan-match-maharashtra-government-firm-on-obc-reservation-1383972</t>
+          <t>https://saamtv.esakal.com/amp/story/maharashtra/tragic-incident-two-teen-boys-drown-in-pond-while-taking-photos-families-devastated-community-in-shock-latest-marathi-news-yps99</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/video/chandrashekhar-bawankule-post-on-x-targeting-mla-rohit-pawar/938538</t>
+          <t>https://saamtv.esakal.com/amp/story/maharashtra/buldhana-farmers-threaten-mass-movement-if-government-fails-to-announce-wet-drought-bdk97</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-megha-engineering-fine-waiver-row-rohit-pawar-bawankule-clash-intensifies-as-government-documents-reveal-fine-from-radhakrishna-vikhe-patil-s-tenure-1382711</t>
+          <t>https://vishwanewsmarathi.com/big-news-garba-only-for-hindus-vhps-conditions/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-thane-politics-ganesh-naik-s-ravana-attack-on-eknath-shinde-sparks-mahayuti-discord-ahead-of-thane-municipal-corporation-elections-1383104/amp</t>
+          <t>https://www.loksatta.com/nagpur/chandrashekhar-bawankule-interacted-with-reporters-at-the-district-collectors-office-phm-00-5387245/lite/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/maharashtra-revenue-minister-chandrashekhar-bawankule-on-maratha-reservation-there-will-be-no-injustice-with-obc/4135300/</t>
+          <t>https://saamtv.esakal.com/amp/story/sports/suryakumar-yadav-team-to-take-to-the-field-against-oman-today-will-the-players-on-the-bench-get-a-chance-sjk95</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.khabar24.tv/2025/09/14/chandrashekhar-bawankule-big-statement-there-will-be-no-injustice-with-obc-maratha-reservation-news-khabar-24-express/chandrashekhar-bawankule-big-statement-there-will-be-no-injustice-with-obc-maratha-reservation-news-khabar-24-express/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%B5-%E0%A4%B6%E0%A5%8D%E0%A4%B5-%E0%A4%B8%E0%A5%82-%E0%A4%85%E0%A4%A8%E0%A5%8D-rss-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%A4%E0%A4%B2%E0%A5%87-%E0%A4%B0%E0%A4%B5-%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%A3-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A5%87-%E0%A4%A8%E0%A4%B5%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%98-%E0%A4%B7%E0%A4%A3/ar-AA1HLd3n?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi</t>
+          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/agriculture/market-yard/latest-news-kanda-market-red-onions-arrive-in-lasalgaon-market-see-market-prices-a-a993/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-septembar-10-political-news-in-marathi-938172</t>
+          <t>https://www.ptinews.com/story/national/ajit-pawar-downplays-row-with-female-ips-officer/2925297</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-pankaja-munde-firm-stance-opposition-to-issuing-fake-kunbi-certificates-manoj-jarange-patil-maratha-reservation/articleshow/123806119.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/rs500cr-govt-land-grabbed-in-gadchiroli-with-fake-papers-minister/articleshow/124004750.cms</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/cm-devendra-fadnavis-and-nitin-gadkari-meet-shrikant-jichkar-mother-in-nagpur-program/articleshow/123854763.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/govt-to-fast-track-land-ownership-rights-for-bengali-families-in-gadchiroli/articleshow/124004837.cms</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/seven-friends-from-nagpur-returned-from-nepal-and-shared-their-thrilling-experience/articleshow/123848579.cms</t>
+          <t>https://www.lokmat.com/agriculture/weather/the-rains-will-stop-the-monsoons-return-journey-will-begin-how-do-you-know-when-the-monsoon-will-leave-a-a975/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/pimpri-chinchwad/todays-latest-marathi-news-pne25l38633-txt-pc-today-20250914110635</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-heavy-rain-traffic-disrupted-and-normal-life-affected-imd-issues-alert-for-next-24-hour/articleshow/123900789.cms</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/premier/naam-foundation-celebrates-its-10th-anniversary-in-presence-of-minitster-nitin-gadkari-entertainment-news-kds07</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/pankaja-munde-maratha-reservation-white-paper-demand-maratha-reservation-news-chhagan-bhujbal-9251415</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-news-case-registered-against-teacher-beating-girl-student-over-reason-of-refuse-to-clean-garbage/articleshow/123926192.cms</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-political-crime-sports-national-international-business-entertainment-lifestyle-breaking-news-982812.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-9th-september-2025-marathi-live-updates-ajit-pawar-lalbaugcha-raja-mandal-manoj-jarange-patil-maratha-reservation/liveblog/123776681.cms</t>
+          <t>https://marathi.indiatimes.com/e-paper/aam-aadmi-party-submits-memorandum-to-chief-minister-for-farmers-compensation/articleshow/123916578.cms</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/mahadev-koli-community-protests-hyderabad-gazette-black-flags-on-muktisangram-day-jp75</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/banjara-community-holds-two-big-rallies-munde-says-form-panel-to-grant-them-st-status-101757963085577.html</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/bhujbal-aggressive-in-obc-subcommittee-meeting-alleges-more-funds-given-to-maratha-community-objects-to-kunbi-records-gr-283714/</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/19/tatkare-terms-rahul-gandhis-vote-theft-allegation-childish.html</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/maharashtra-government-explanation-in-high-court-on-pil-file-against-ladki-bahin-yojana/articleshow/123832832.cms</t>
+          <t>https://www.devdiscourse.com/article/business/3634504-empowering-maharashtras-tribal-farmers-leasing-land-for-agriculture-and-mining</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/4/?m=0</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-presents-fake-documents-asks-for-committee-to-scrutinise-kunbi-certificates/articleshow/123927743.cms</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE-%E0%A4%9C-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%B6-11-%E0%A4%B5%E0%A4%B0%E0%A5%8D%E0%A4%B7-%E0%A4%82%E0%A4%9A-%E0%A4%B5-%E0%A4%A6-%E0%A4%95-%E0%A4%81%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B8%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%B0-%E0%A4%9C-%E0%A4%A8-%E0%A4%AE-%E0%A4%AD-%E0%A4%9C%E0%A4%AA-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%9A-%E0%A4%AE%E0%A5%81%E0%A4%B9%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%A4-%E0%A4%A0%E0%A4%B0%E0%A4%B2/ar-AA1MeDFB</t>
+          <t>https://ahmednagarlive24.com/spacial/maharashtra-news-at-this-time-20-districts-and-81-talukas-will-be-formed-in-the-state/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/mr/obc-reservation/</t>
+          <t>https://www.loksatta.com/nashik/ex-bjp-corporator-arrested-nashik-law-and-order-amid-political-unrest-panchvati-shooting-case-vsd-99-5388883/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/11/maratha-quota-mah-govt-starts-hyderabad-gazette-implementation-process-no-impact-on-obc-reservation.html</t>
+          <t>https://www.loksatta.com/nashik/nashik-traffic-diversions-announced-navratri-celebrations-kalika-mata-renuka-devi-temples-vsd-99-5388871/lite/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-crime-news-unknown-assailants-shot-on-businessman-and-robbed-him-of-cash-worth-lakhs/articleshow/123815444.cms</t>
+          <t>https://www.loksatta.com/nashik/uddhav-thackeray-shiv-sena-restructures-jalgaon-ahead-local-body-elections-new-appointments-vsd-99-5388810/lite/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://pib.gov.in/PressReleseDetailm.aspx?PRID=2166159</t>
+          <t>https://www.deccanherald.com/india/maharashtra/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister-3737045</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/maharashtra-govt-scheme-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%86%E0%A4%A3%E0%A4%96-%E0%A4%8F%E0%A4%95-%E0%A4%AE-%E0%A4%A0-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%A6-%E0%A4%B2-a-to-z-%E0%A4%AE-%E0%A4%B9-%E0%A4%A4/ar-AA1Mfl2g</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/farmers-in-tribal-areas-can-lease-land-to-private-parties-bawankule/amp_articleshow/124004941.cms</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/babanrao-lonikar-news-rohit-pawar-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%96-%E0%A4%9F-%E0%A4%AE-%E0%A4%B9-%E0%A4%A4-%E0%A4%AA%E0%A5%81%E0%A4%B0%E0%A4%B5%E0%A4%B2-%E0%A4%B2-%E0%A4%A3-%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A5%87%E0%A4%AE%E0%A4%95-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%95-%E0%A4%AF-n18v/vi-AA1Mbu5E</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/rs500cr-govt-land-grabbed-in-gadchiroli-with-fake-papers-minister/amp_articleshow/124004750.cms</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%A4-%E0%A4%A1%E0%A4%AA-%E0%A4%A3-%E0%A4%95%E0%A4%B0%E0%A4%A4%E0%A4%82%E0%A4%AF-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A-%E0%A4%96%E0%A4%B3%E0%A4%AC%E0%A4%B3%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%86%E0%A4%B0-%E0%A4%AA-90-%E0%A4%95-%E0%A4%9F-%E0%A4%82%E0%A4%B5%E0%A4%B0%E0%A5%81%E0%A4%A8-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%B6-%E0%A4%AD-%E0%A4%A1%E0%A4%B2%E0%A5%87-%E0%A4%B8%E0%A4%82%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%98%E0%A5%87%E0%A4%8A%E0%A4%A8/ar-AA1M6js8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.indiatimes.com/e-paper/ramtek-development-to-receive-major-boost-minister-shelkars-assurance/articleshow/123916582.cms</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://maharashtradesha.com/baliraja-panand-raste-scheme/</t>
+          <t>https://marathi.indiatimes.com/e-paper/leopard-spreads-terror-in-sinnar-forest-departments-capture-mission-fails/articleshow/123916817.cms</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://mondaytomondaynews.com/what-is-mukhyamantri-baliraja-panand-raste-yojana-maharashtra-government/</t>
+          <t>https://marathi.indiatimes.com/e-paper/amit-shah-declares-bokaro-in-jharkhand-maoist-free/articleshow/123916647.cms</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/how-many-obc-certificates-have-been-issued-so-far-release-all-the-information-by-publishing-a-white-paper/116657/</t>
+          <t>https://marathi.indiatimes.com/e-paper/trimbakeshwar-womens-pot-protest-against-water-shortage/articleshow/123916850.cms</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/obc-community-s-concerns-over-reservation-will-not-be-ignored-minister-pankaja-munde/2901852</t>
+          <t>https://marathi.indiatimes.com/e-paper/sinnar-17-25-percent-increase-in-water-bill-sima-organization-strongly-oppose/articleshow/123916891.cms</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/no-injustice-to-obcs-kunbi-certificates-to-be-issued-only-after-due-verification-bawankule-10084145</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-shiv-bhojan-thali-scheme-to-continue-in-maharashtra-with-200-crore-approval-closed-centers-to-reopen-1385628</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/cyber-criminals-cheated-bank-officer-and-his-family-of-rupees-39-lakh-in-nagpur/articleshow/123835223.cms</t>
+          <t>https://www.dainikprabhat.com/wagholi-news-wadebolhai-gram-panchayat-gets-aap-sarkar-seva-kendra/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/hsrp-number-plate-man-pil-dismissed-by-nagpur-court-over-extra-fee-in-maharashtra-than-other-states/articleshow/123805572.cms</t>
+          <t>https://www.marathi.hindusthanpost.com/social/maharashtra-action-will-be-taken-against-bogus-documents-decision-of-obc-cabinet-sub-committee-meeting-under-discussion/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/amravati-district-ajay-gaur-stranded-amid-nepal-violence-recounts-terrifying-experience/articleshow/123800988.cms</t>
+          <t>https://www.timemaharashtra.com/politics/a-conspiracy-has-been-hatched-to-defame-laxman-hake-vijay-vadettiwar-claims/133273/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/chhagan-bhujbal-opposes-maratha-caste-certificate-gr-maharashtra-1489591.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/jsym-to-host-amrit-mahotsavi-international-yoga-convention-in-nagpur-in-november/articleshow/124005000.cms</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/maharashtra-govt-a-new-revolutionary-decision-for-farmers-but-what-will-actually-happen/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-sudhir-khandare-dies-in-bathroom-after-allegedly-hit-by-tap-police-solved-murder-mystery-nabs-family/articleshow/123933510.cms</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/training-facility-for-3-thousand-students-skill-development-center-in-nagpur-by-tata-technology/132222/</t>
+          <t>https://mahasamvad.in/178604/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178359/</t>
+          <t>https://agrowon.esakal.com/agro-special/survey-of-654-rural-roads-completed-in-nagpur-gramin-taluka-maps-available-for-citizens-mj18</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/178382/</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/farmers-should-stay-strong-avoid-suicides-adopt-natural-farming-sri-sri-ravi-shankar-mj18</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/obc-activists-wave-black-flags-during-cms-speech-2-attempt-self-immolation-near-ajit-pawars-convoy/articleshow/123952613.cms</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/maha-revenue-dept-allocates-land-ib-s-residential-quarters-panvel-450341</t>
+          <t>https://www.businessworld.in/article/maharashtra-allows-tribal-farmers-to-lease-barren-land-to-firms-572455</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ramtek-to-host-farmers-fair-focused-on-sustainable-agriculture/articleshow/123793282.cms</t>
+          <t>https://agrowon.esakal.com/agro-special/bori-budruk-was-the-first-to-give-the-code-number-rat16</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/marathas-vs-obcs-reservation-issue-heads-to-courts-3717455</t>
+          <t>http://www.msn.com/mr-in/news/other/%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%86%E0%A4%A4-%E0%A4%95-%E0%A4%AF%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%B0-%E0%A4%AE-%E0%A4%A8%E0%A5%8D%E0%A4%AF%E0%A4%A4-%E0%A4%AA-%E0%A4%A3%E0%A4%82%E0%A4%A6-%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A5%87-%E0%A4%A1-%E0%A4%9C-%E0%A4%9F%E0%A4%B2-%E0%A4%B0%E0%A5%87%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%A1-%E0%A4%AB-%E0%A4%AF%E0%A4%A6%E0%A5%87-%E0%A4%B5-%E0%A4%9A%E0%A5%82%E0%A4%A8-%E0%A4%86%E0%A4%A8%E0%A4%82%E0%A4%A6%E0%A5%82%E0%A4%A8-%E0%A4%9C-%E0%A4%B2/ar-AA1MvyUA?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/reservation-issue-becomes-wider-in-maharashtra-even-as-govt-grapples-with-maratha-vs-obc-quota-problem-3723032</t>
+          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/10/there-will-be-no-injustice-to-obcs-no-false-records-important-decision-taken-in-the-cabinet-sub-committee-meet.amp.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/sharad-pawar-reaction-on-hyderabad-gazette-and-the-cabinet-sub-committee-formed-on-reservation/articleshow/123964633.cms</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ncp-chhagan-bhujbal-criticizes-governments-procedure-regarding-manoj-jarange-patil-maratha-reservation-gr/articleshow/123830074.cms</t>
+          <t>http://www.msn.com/en-in/news/India/maratha-quota-row-rumblings-in-mahayuti-alliance-chhagan-bhujbal-skips-cabinet-meet/ar-AA1LQ2jJ?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/maratha-community-should-not-be-given-bogus-certificates-pankaja-munde-stand-in-obc-subcommittee-meeting-283722/</t>
+          <t>https://www.msn.com/en-in/autos/photos/velhe-taluka-in-pune-renamed-after-chhatrapati-shivajis-first-capital-fort-rajgad/ar-AA1KZLQZ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/bhujbal-aggressive-in-obc-subcommittee-meeting-alleges-more-funds-given-to-maratha-community-objects-to-kunbi-records-gr-283714/amp/</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-rain-live-mumbai-pune-nagpur-traffic-local-trains-flood-imd-alert-update-beed-crime-ex-sarpanch-govind-barge-death-pooja-gaikwad-latest-news-breaking-rak-94-5372752/lite/?liveblog_page=2&amp;liveblog_last=90839-1757925166</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/obc-leaders-furious-over-maratha-reservation/</t>
+          <t>https://www.marathiebatmya.com/political/mou-signed-between-mahagenco-and-nmrda-in-the-presence-of-the-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/8/congresss-journey-is-a-history-of-injustice-against-the-obc-community.html</t>
+          <t>https://www.berartimes.com/vidarbha/216594/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/new-rotary-underground-market-planned-at-medical-square-gadkari/articleshow/123858415.cms</t>
+          <t>https://www.business-standard.com/amp/india-news/himachal-rains-death-toll-rises-to-427-243-rain-related-184-in-accidents-125092000391_1.html</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/gadkari-fadnavis-to-inaugurate-rto-flyover-today/articleshow/123836339.cms</t>
+          <t>https://thefocusindia.com/maharashtra-news/mou-between-maharashtra-government-and-naam-foundation-284511/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178345/</t>
+          <t>https://www.msn.com/mr-in/news/other/kunbi-caste-certificate-%E0%A4%95%E0%A5%81%E0%A4%A3%E0%A4%AC-%E0%A4%AC-%E0%A4%97%E0%A4%B8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AE-%E0%A4%A3%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%82%E0%A4%9A-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%B8%E0%A4%96-%E0%A4%B2-%E0%A4%AA%E0%A4%A1%E0%A4%A4-%E0%A4%B3%E0%A4%A3/ar-AA1MHcDS</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/178405/</t>
+          <t>https://news18marathi.com/agriculture/revenue-departments-lok-adalat-campaign-for-farmers-to-start-from-september-17-1480838.html</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178401/</t>
+          <t>https://agrowon.esakal.com/agro-special/khadgaon-farmer-suicide-case-inquiry-report-submitted-to-collector-mj18</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/state-government-help-loss-affected-farmers-cm-devendra-fadnavis/</t>
+          <t>https://www.devdiscourse.com/article/law-order/3634600-maharashtras-new-lease-law-a-boon-or-bane-for-tribal-farmers</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/after-bhujbal-sena-minister-gulabrao-patil-opposes-gr-on-marathas/articleshow/123724181.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/13/nagpur-to-be-hub-of-solar-panel-manufacturing-cm-fadnavis.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/anti-social-element-will-be-arrested-soon-cm-on-vandalism-of-meenatai-thackerays-statue-in-mumbai/articleshow/123955024.cms</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ramtek-to-get-rs115cr-skill-development-centre-tata-signs-mou-with-state/articleshow/123869977.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/state-has-received-no-complaint-of-denial-of-kunbi-certificate-to-eligible-candidates-cm/articleshow/123954996.cms</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://policenama.com/adachiwadi-village-news-pune-adachiwadi-in-purandar-taluka-a-new-example-emerged-as-a-model-village-videos/</t>
+          <t>https://www.newsdrum.in/national/maharashtra-obc-panel-orders-strict-scrutiny-of-caste-certificates-clears-rs-2933cr-pending-funds-10470839</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/new-nagpur-biz-hub-to-take-shape-in-phased-manner-over-15-years/articleshow/123772865.cms</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/global-level-tourist-destination-to-come-up-at-koradi-mou-signed-in-presence-of-cm-sdj87</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/marathas-should-not-be-given-fake-kunbi-certificates-maha-minister-450832</t>
+          <t>https://www.ptinews.com/detail/national/Maharashtra-OBC-panel-orders-strict-scrutiny-of-caste-certificates-clears-Rs-2-933cr-pending-funds/2920779</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178292/</t>
+          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/No-injustice-to-OBCs-Kunbi-certificates-to-be-issued-only-after-due-verification-Bawankule/2902881</t>
+          <t>https://www.freepressjournal.in/pune/videos-long-queues-outside-kopa-mall-in-punes-koregaon-park-as-iphone-17-series-goes-on-sale-in-india</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/the-free-press-journal/20250911/281595246673030</t>
+          <t>https://www.timemaharashtra.com/maharashtra/navratri-new-decision-from-vishwa-hindu-parishad-aadhaar-card-mandatory-to-watch-garba-during-navratri/133217/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/rohit-pawar-ncp-sp-allegations-of-200-crore-corruption-tagged-ajit-pawar/919533/</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/finally-rto-flyover-to-open-on-friday/articleshow/123793290.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>https://www.nagpurtoday.in/nagpur-court-cracks-down-on-underage-driving-woman-fined-%E2%82%B932500/09081750</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AF-%E0%A4%B6%E0%A4%B9%E0%A4%B0-%E0%A4%A4-%E0%A4%A4%E0%A4%AF-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4%E0%A4%82%E0%A4%AF-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%B8-%E0%A4%B0%E0%A4%96%E0%A4%82-%E0%A4%A8%E0%A4%B5%E0%A4%82-%E0%A4%B6%E0%A4%B9%E0%A4%B0-1710-%E0%A4%B9%E0%A5%87%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%B0%E0%A4%B5%E0%A4%B0-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%89%E0%A4%AD-%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%9C%E0%A4%97-%E0%A4%B0-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A8%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A4%82%E0%A4%A7/ar-AA1M6Vog</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/fix-the-loopholes-in-quota-gr-says-bhujbal-101757531207674.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/10/maratha-reservation-gr-to-be-implemented-in-a-time-bound-manner.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>https://news18marathi.com/agriculture/what-is-mukhyamantri-baliraja-panand-raste-yojana-marathi-agriculture-news-1476799.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>https://www.lokmat.com/agriculture/market-yard/latest-news-international-market-committee-will-be-built-in-ahilyanagar-district-cost-of-15-crores-a-a993/</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-8th-september-2025-marathi-batmya-lalbaugcha-raja-visarjan-raj-uddhav-thackeray-brothers-dasara-melava-chandra-grahan-lunar-eclipse/liveblog/123755669.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/deputy-cm-ajit-pawar-on-reports-of-cm-devendra-fadnavis-disappointment-over-ips-anjana-krishna-case/938959/amp</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/8/spontaneous-response-to-maha-bhandara-in-nallasopara-and-virar-on-the-occasion-of-anant-chaturdashi-more-than-.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/8/sanjay-raut-feels-blessed-to-visit-afzal-khans-grave.html</t>
+          <t>https://www.khabar24.tv/2025/09/17/chandrashekhar-bawankule-writes-emotional-letter-to-pm-modi-on-his-birthday-a-big-message-to-the-nation-khabar-24-express/</t>
         </is>
       </c>
     </row>

--- a/Output/Chandrashekhar Bawankule/extracted_links_Chandrashekhar Bawankule_failed_links.xlsx
+++ b/Output/Chandrashekhar Bawankule/extracted_links_Chandrashekhar Bawankule_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A151"/>
+  <dimension ref="A1:A121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,98 +438,98 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179502/</t>
+          <t>https://mahasamvad.in/178572/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/land-approved-for-bhandara-judges-residence-revenue-minister-chandrashekhar-bawankules-initiative.html</t>
+          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-revenue-minister-u-turn-on-his-statement-over-giving-tribal-land-on-lease-to-non-tribals-gadchiroli-maharashtra-politics-marathi-news-1385418</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AA-%E0%A4%A3%E0%A4%82%E0%A4%A6-%E0%A4%AE%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%9A-%E0%A4%AE%E0%A5%87%E0%A4%97-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AF-%E0%A4%97-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%9D%E0%A4%97%E0%A4%A1-%E0%A4%B8%E0%A5%81%E0%A4%9F%E0%A4%A3-%E0%A4%B0-%E0%A4%AE%E0%A4%B9%E0%A4%B8%E0%A5%82%E0%A4%B2-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AE-%E0%A4%A0-%E0%A4%98-%E0%A4%B7%E0%A4%A3/ar-AA1MeEni?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.abplive.com/news/revenue-servant-strike-eighth-day-government-not-even-a-simple-acknowledgement-protesters-warn-the-government-nagpur-news-maharashtra-marathi-news-1385371</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179430/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-live-blog-updates-19-september-2025-farmer-flood-rain-maharashtra-weather-maharashtra-politics-devendra-fadnavismumbai-rains-1385110</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/21/maharashtra-knows-what-lights-vadettiwar-lit-when-he-was-a-minister-minister-chandrashekhar-bawankule-criticiz.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/navratri-garba-only-for-hindus-check-aadhaar-of-participants-says-vhp-bawankule-comment-1385439</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178572/</t>
+          <t>https://www.adharnewsnetwork.com/2025/09/chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%AA%E0%A4%B9-%E0%A4%B2%E0%A4%82-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4%E0%A5%8D%E0%A4%AF%E0%A5%81%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B0-%E0%A4%95-%E0%A4%81%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B8%E0%A4%9A-%E0%A4%89%E0%A4%B2%E0%A5%8D%E0%A4%B2%E0%A5%87%E0%A4%96-%E0%A4%95%E0%A4%B0%E0%A4%A4-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1yazrQ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sena-ubt-criticises-govt-over-match-bawankule-hits-back/articleshow/123887314.cms</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-state-new-district-and-taluka-formation-the-map-of-maharashtra-will-change-81-new-talukas-and-20-districts-will-be-created-in-maharashtra/940852/amp</t>
+          <t>https://www.deccanherald.com/india/maharashtra/vhps-hindus-only-diktat-for-garba-bjp-leader-backs-organisers-rights-oppn-slams-move-3737006</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.adharnewsnetwork.com/2025/09/chandrashekhar-bawankule.html</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-encroachment-on-farm-roads-to-be-cleared-govt-to-map-such-pathways-says-bawankule/ar-AA1MXpLZ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/officials-should-act-without-condoning-any-wrongdoing/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/farmers-in-tribal-areas-can-lease-land-to-private-parties-bawankule/articleshow/124004941.cms</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/farmers-in-tribal-areas-can-lease-land-to-private-parties-bawankule/articleshow/124004941.cms</t>
+          <t>https://www.devdiscourse.com/article/headlines/3634796-maharashtras-road-to-prosperity-revamping-farm-access-for-farmers</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/entertainment/3634952-controversy-brews-over-garba-entry-restrictions-amidst-navratri-celebrations?amp</t>
+          <t>https://www.business-standard.com/india-news/maha-govt-to-allow-tribal-farmers-to-lease-land-to-private-firms-minister-125092000372_1.html</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/maha-govt-to-allow-tribal-farmers-to-lease-land-to-private-firms-minister-125092000372_1.html</t>
+          <t>https://www.ptinews.com/story/national/ajit-pawar-downplays-row-with-female-ips-officer/2925297</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Tribals-in-Maharashtra-can-now-lease-barren-land-to-private-entities;-govt-to-bring-law-Minister/2932964</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-minister-chhagan-bhujbal-demands-verification-of-obc-certificates-issued-to-maratha-community-23594340</t>
         </is>
       </c>
     </row>
@@ -543,945 +543,735 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maharashtra-obc-panel-orders-strict-scrutiny-of-caste-certificates-clears-rs-2-933cr-pending-funds/2920779</t>
+          <t>https://timesofindia.indiatimes.com/india/vhp-issues-hindus-only-diktat-for-garba-bawankule-backs-organisers-rights-wadettiwar-slams-move/articleshow/124014945.cms</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3634504-empowering-maharashtras-tribal-farmers-leasing-land-for-agriculture-and-mining?amp</t>
+          <t>https://www.socialnews.xyz/?p=6725428</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/vhp-issues-hindus-only-diktat-for-garba-bawankule-backs-organisers-rights-wadettiwar-slams-move/articleshow/124014945.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/new-nagpur-project-farmers-provide-proof-about-no-rr-rate-change-in-10-yrs/articleshow/124052183.cms</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/vhp-issues--hindus-only--diktat-for-garba;-bawankule-backs-organisers--rights--wadettiwar-slams-move/2932800</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/vhp-issues--hindus-only--diktat-for-garba;-bjp-minister-backs-organisers--rights--cong-slams-move/2934001</t>
+          <t>https://marathi.indiatimes.com/e-paper/chandrashekhar-bawankules-important-instructions-for-water-resource-conservation-in-nagpur/articleshow/123916999.cms</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/No-opposition-to-Badgujar-s-induction-into-BJP-Fadnavis/2655228</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/guardian-minister-chandrashekhar-bawankule-thanks-govt-for-upgrading-nagpurs-religious-sites-sdj87</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3634796-maharashtras-road-to-prosperity-revamping-farm-access-for-farmers?amp</t>
+          <t>https://mahasamvad.in/178575/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/20/bom22-mh-tribals-land-lease.amp.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-proposal-to-create-20-new-districts-81-talukas-process-chandrashekhar-bawankule-revenue-minister-news-1386089</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3634600-maharashtras-new-lease-law-a-boon-or-bane-for-tribal-farmers?amp</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/chandrashekhar-bawankule-criticizes-sharad-pawar-maratha-obc-upsamiti-135950317.html</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-minister-chhagan-bhujbal-demands-verification-of-obc-certificates-issued-to-maratha-community-23594340</t>
+          <t>https://www.saamana.com/chandrashekhar-bawankule-says-government-got-proposal-for-20-new-district/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/?p=6725428</t>
+          <t>https://marathi.abplive.com/news/gadchiroli/gadchiroli-non-tribals-will-able-to-take-tribal-lands-on-lease-revenue-minister-chandrashekhar-bawankule-marathi-news-1385320</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3634796-maharashtras-road-to-prosperity-revamping-farm-access-for-farmers</t>
+          <t>https://www.etvbharat.com/mr/!state/chandrashekhar-bawankule-gives-important-instructions-to-officers-chhagan-bhujbal-on-maratha-kunbi-certificate-distribution-and-obc-reservation-maharashtra-news-mhs25091605134</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-soon-allow-private-entities-to-lease-tribal-lands-101758396296809-amp.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/gadchiroli/revenue-minister-chandrashekhar-bawankule-announces-that-tribal-lands-can-be-given-on-lease/articleshow/124010200.cms</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/for-hindu-only-garba-vhp-sets-entry-norms-check-aadhaar-apply-tilak-101758363132840-amp.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/obc-upsamiti-meeting-chandrashekhar-bawankule-chhagan-bhujbal-opposed-flaw-evidence-to-kunbi-certificates-1384586</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/chandrashekhar-bawankule-%E0%A4%95%E0%A5%81%E0%A4%A3-%E0%A4%B9-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9C%E0%A4%96%E0%A4%AE%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%AE-%E0%A4%A0-%E0%A4%9A-%E0%A4%B3%E0%A5%82-%E0%A4%A8%E0%A4%AF%E0%A5%87-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%95-%E0%A4%9F%E0%A5%87-%E0%A4%95-%E0%A4%B9-%E0%A4%AC-%E0%A4%B2%E0%A4%B2%E0%A5%87-%E0%A4%85%E0%A4%B8%E0%A4%A4-%E0%A4%B2-%E0%A4%A4%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%A4%E0%A4%B0%E0%A5%8D%E0%A4%AB%E0%A5%87-%E0%A4%86%E0%A4%AE%E0%A5%8D%E0%A4%B9-%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%AE-%E0%A4%AE-%E0%A4%97%E0%A5%82-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%87%E0%A4%96%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87/ar-AA1Cn5Cg?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/minister-chandrashekhar-bawankule-gives-important-instructions-to-officers-about-maratha-kunbi-certificate-distribution/articleshow/123922415.cms</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A0%E0%A4%B0%E0%A4%B5%E0%A4%B2%E0%A4%82%E0%A4%AF-%E0%A4%95/ar-AA1NcvqY?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/chandrashekhar-bawankules-important-instructions-for-water-resource-conservation-in-nagpur/articleshow/123916999.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/22/relief-due-to-gst-reforms-common-people-benefit-from-reduction-in-tax-rates-on-daily-use-items-revenue-ministe.amp.html</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/guardian-minister-chandrashekhar-bawankule-thanks-govt-for-upgrading-nagpurs-religious-sites-sdj87</t>
+          <t>https://agrowon.esakal.com/agro-special/maharashtra-plans-20-new-districts-and-81-talukas-revenue-minister-bawankule-mj18</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178575/</t>
+          <t>https://marathi.ndtv.com/videos/bawankule-no-tickets-for-those-who-follow-leaders-bawankule-warns-997430</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%B8%E0%A5%81%E0%A4%B0%E0%A5%82%E0%A4%9A-%E0%A4%B0-%E0%A4%B9%E0%A4%A3-%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1zbVuE?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://mahasamvad.in/178893/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/nagpur-political-news-%E0%A4%95%E0%A5%87%E0%A4%B5%E0%A4%B3-%E0%A4%97%E0%A5%85%E0%A4%9D%E0%A5%87%E0%A4%9F%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%A8-%E0%A4%82%E0%A4%A6-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3%E0%A5%82%E0%A4%A8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AE-%E0%A4%A3%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%A8-%E0%A4%B9-%E0%A4%AE%E0%A4%B9%E0%A4%B8%E0%A5%82%E0%A4%B2%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87/ar-AA1LZyoY?cvid=68bc9315762a4b358cad5b270e1111ac&amp;ocid=wispr&amp;apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-obc-sub-committee-big-decision-on-kunbi-certificate-distribution-to-maratha-community/articleshow/123921757.cms</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/gadchiroli/gadchiroli-non-tribals-will-able-to-take-tribal-lands-on-lease-revenue-minister-chandrashekhar-bawankule-marathi-news-1385320</t>
+          <t>https://www.esakal.com/pune/vision-for-pune-transforming-into-indias-top-infrastructure-hub-chandrashekhar-bawankule-pjp78</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/gadchiroli/revenue-minister-chandrashekhar-bawankule-announces-that-tribal-lands-can-be-given-on-lease/articleshow/124010200.cms</t>
+          <t>https://agrowon.esakal.com/agro-special/maharashtra-to-make-1100-government-services-online-by-may-cm-fadnavis-mj18</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/minister-chandrashekhar-bawankule-gives-important-instructions-to-officers-about-maratha-kunbi-certificate-distribution/articleshow/123922415.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%97-%E0%A4%AF%E0%A4%95%E0%A4%B5-%E0%A4%A1-%E0%A4%AC-%E0%A4%B2%E0%A4%B2%E0%A5%87-%E0%A4%85%E0%A4%A8%E0%A5%8D-%E0%A4%AA%E0%A5%81%E0%A4%A8%E0%A5%8D%E0%A4%B9-%E0%A4%B5-%E0%A4%A6-%E0%A4%A4-%E0%A4%B8-%E0%A4%AA%E0%A4%A1%E0%A4%B2%E0%A5%87-%E0%A4%9D%E0%A5%87%E0%A4%A1%E0%A4%AA-%E0%A4%86%E0%A4%A3-%E0%A4%AA%E0%A4%82%E0%A4%9A-%E0%A4%AF%E0%A4%A4-%E0%A4%B8%E0%A4%AE-%E0%A4%A4-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%81%E0%A4%95-%E0%A4%82%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%B5-%E0%A4%A6%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B5%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A4%B5%E0%A5%8D%E0%A4%AF/ar-AA1N0sRo?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/maharashtra-plans-20-new-districts-and-81-talukas-revenue-minister-bawankule-mj18</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/chagan-bhujbal-obc-reservation-demands-135934860.html</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/bawankule-no-tickets-for-those-who-follow-leaders-bawankule-warns-997430</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-shivbhojan-thali-scheme-to-continue-minister-bawankule-announces-200-crore-approval-for-maharashtra-s-affordable-meal-program-1385482</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A8-%E0%A4%AF%E0%A4%AE-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%89%E0%A4%B2%E0%A5%8D%E0%A4%B2%E0%A4%82%E0%A4%98%E0%A4%A8-%E0%A4%95%E0%A5%87%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%B5-%E0%A4%B3%E0%A5%82-%E0%A4%A1%E0%A5%87%E0%A4%AA-%E0%A4%B0%E0%A4%A6%E0%A5%8D%E0%A4%A6/ar-AA1Df6na?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-chandrashekhar-bawankule-on-local-body-elections-tickets-via-internal-survey-public-opinion-to-decide-not-loyalty-to-leaders-amid-chandrapur-groupism-1385779</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178893/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-shiv-bhojan-thali-scheme-to-continue-in-maharashtra-with-200-crore-approval-closed-centers-to-reopen-1385628</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-obc-sub-committee-big-decision-on-kunbi-certificate-distribution-to-maratha-community/articleshow/123921757.cms</t>
+          <t>https://policenama.com/pune-navratri-mahotsav-pune-the-31st-pune-navratri-mahotsav-will-be-inaugurated-grandly-by-revenue-minister-chandrashekhar-bawankule-festival-organizer-aba-bagul-gave-this-information-in-a-press-c/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/revenue-minister-chandrashekhar-bawankule-has-made-murum-mining-royalty-free-1484899.html</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/private-companies-can-also-lease-wasteland-tribal-land-125092100014_1.html</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/maharashtra-to-make-1100-government-services-online-by-may-cm-fadnavis-mj18</t>
+          <t>https://www.marathiebatmya.com/political/obc-sub-committees-decision-thorough-verification-of-kunbi-bogus-certificates/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-chandrashekhar-bawankule-on-local-body-elections-tickets-via-internal-survey-public-opinion-to-decide-not-loyalty-to-leaders-amid-chandrapur-groupism-1385779/amp</t>
+          <t>https://www.dainikprabhat.com/no-registration-without-survey-big-decision-of-revenue-department-land-survey-mandatory-before-deed-registration-no-changes-without-registration/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-shivbhojan-thali-scheme-to-continue-minister-bawankule-announces-200-crore-approval-for-maharashtra-s-affordable-meal-program-1385482/amp</t>
+          <t>https://www.dainikprabhat.com/pune-news-mine-owners-are-in-trouble-mining-in-mountains-and-hills-banned-revenue-minister-bawankules-firm-stance/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/dhananjay-deshmukh-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%AD%E0%A5%82%E0%A4%AE-%E0%A4%95-%E0%A4%AE-%E0%A4%82%E0%A4%A1-%E0%A4%AF%E0%A4%B2-%E0%A4%B9%E0%A4%B5-%E0%A4%B9-%E0%A4%A4-%E0%A4%A7%E0%A4%A8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%A6%E0%A5%87%E0%A4%B6%E0%A4%AE%E0%A5%81%E0%A4%96-%E0%A4%82%E0%A4%A8-%E0%A4%B5%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%95%E0%A5%87%E0%A4%B2-%E0%A4%96%E0%A4%82%E0%A4%A4/ar-AA1An2uc?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.dainikprabhat.com/as-many-as-20-new-districts-and-81-talukas-have-been-created-in-the-state/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-shiv-bhojan-thali-scheme-to-continue-in-maharashtra-with-200-crore-approval-closed-centers-to-reopen-1385628/amp</t>
+          <t>https://www.dainikprabhat.com/pune-news-exemption-from-the-fragmentation-law-sale-of-one-or-two-gunthas-is-now-possible-know-when-the-implementation-will-start/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/now-tribal-lands-will-be-available-on-lease-chandrashekhar-bawankule/</t>
+          <t>https://www.timemaharashtra.com/maharashtra/chandrashekhar-bawankule-praises-new-gst-reform/133431/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://policenama.com/pune-navratri-mahotsav-pune-the-31st-pune-navratri-mahotsav-will-be-inaugurated-grandly-by-revenue-minister-chandrashekhar-bawankule-festival-organizer-aba-bagul-gave-this-information-in-a-press-c/</t>
+          <t>https://news34.in/2025/09/chandrapur-bjp-news-development-updates/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/private-companies-can-also-lease-wasteland-tribal-land-125092100014_1.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/obc-sub-committees-decision-thorough-verification-of-kunbi-bogus-certificates/</t>
+          <t>https://www.saamana.com/chhagan-bhujbal-demands-probe-into-fake-obc-certificates/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pune-news-mine-owners-are-in-trouble-mining-in-mountains-and-hills-banned-revenue-minister-bawankules-firm-stance/</t>
+          <t>https://www.adharnewsnetwork.com/2025/09/aap-chandrapur.html</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/as-many-as-20-new-districts-and-81-talukas-have-been-created-in-the-state/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-local-body-polls-chandrashekhar-bawankule-on-ticket-distribution-public-opinion-to-decide-candidates-amidst-chandrapur-factionalism-1385673</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pune-news-exemption-from-the-fragmentation-law-sale-of-one-or-two-gunthas-is-now-possible-know-when-the-implementation-will-start/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-obc-reservation-maharashtra-govt-to-prevent-forgery-in-maratha-kunbi-certificates-sub-committee-demands-2900-crore-for-obc-ministry-welfare-schemes-1384585</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/shivbhojan-thali-the-shivbhojan-thali-of-uddhav-thackerays-era-will-continue-bawankule-clearly-stated/</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-bawankule-says-private-companies-also-lease-barren-tribal-land-cm-fadnavis-government-enact-law-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%86%E0%A4%A6%E0%A4%BF%E0%A4%B5%E0%A4%BE%E0%A4%B8%E0%A5%80%E0%A4%82%E0%A4%9A%E0%A5%80-%E0%A4%9C%E0%A4%AE%E0%A5%80%E0%A4%A8-%E0%A4%AD%E0%A4%BE%E0%A4%A1%E0%A5%87%E0%A4%A4%E0%A4%A4%E0%A5%8D%E0%A4%A4/118039/</t>
+          <t>https://vsrsnews.in/pimpri-chinchwad/pune-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%AD%E0%A4%B0%E0%A4%BE%E0%A4%A4%E0%A5%80%E0%A4%B2-%E0%A5%A7%E0%A5%A8-%E0%A4%B9%E0%A4%9C%E0%A4%BE%E0%A4%B0-%E0%A5%AC%E0%A5%A6%E0%A5%A6-%E0%A4%B8/118036/</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-saturday-20-september-2025-1496545.html</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/banjara-reservation-%E0%A4%AC%E0%A4%82%E0%A4%9C-%E0%A4%B0-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%87%E0%A4%96%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%A3%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B9-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%9A-%E0%A4%A8-%E0%A4%82%E0%A4%A6/ar-AA1MArpW</t>
+          <t>https://news18marathi.com/agriculture/revenue-departments-lok-adalat-campaign-for-farmers-to-start-from-september-17-1480838.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A8%E0%A4%B5%E0%A4%B0-%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A4%E0%A5%8D%E0%A4%B8%E0%A4%B5-%E0%A4%A4-%E0%A4%B2-%E0%A4%97%E0%A4%B0%E0%A4%AC-%E0%A4%AB%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%B9-%E0%A4%82%E0%A4%A6%E0%A5%82%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%86%E0%A4%A7-%E0%A4%B0-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%A1-%E0%A4%A4%E0%A4%AA-%E0%A4%B8-%E0%A4%B5-%E0%A4%B6%E0%A5%8D%E0%A4%B5-%E0%A4%B9-%E0%A4%82%E0%A4%A6%E0%A5%82-%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A4%A6%E0%A5%87%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD%E0%A5%82%E0%A4%AE-%E0%A4%95%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%B9-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1MWJzB</t>
+          <t>https://www.loksatta.com/pune/indian-railways-made-in-india-technology-locomotive-in-train-engine-pune-print-news-css-98-5381428/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-rain-live-mumbai-pune-nagpur-traffic-local-trains-flood-imd-alert-update-beed-crime-ex-sarpanch-govind-barge-death-pooja-gaikwad-latest-news-breaking-rak-94-5372752/lite/?liveblog_page=3&amp;liveblog_last=90890-1757948209</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/chhagan-bhujbal-demands-probe-into-fake-obc-certificates/</t>
+          <t>https://www.loksatta.com/pune/chairman-of-maharashtra-legislative-council-statement-on-ram-shinde-marathwada-backwardness-pune-print-news-zws-70-5381328/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/agriculture/news/revenue-ministers-big-announcement-on-the-excavation-of-murum-for-the-repair-of-panand-roads-in-the-state-a-a975/</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-rain-live-mumbai-pune-nagpur-traffic-local-trains-flood-imd-alert-update-beed-crime-ex-sarpanch-govind-barge-death-pooja-gaikwad-latest-news-breaking-rak-94-5372752/lite/?liveblog_page=2&amp;liveblog_last=90863-1757936847</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.adharnewsnetwork.com/2025/09/aap-chandrapur.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/pandit-deendayal-upadhyay-employment-fair-organized.html</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-local-body-polls-chandrashekhar-bawankule-on-ticket-distribution-public-opinion-to-decide-candidates-amidst-chandrapur-factionalism-1385673</t>
+          <t>https://www.tv9marathi.com/videos/chhagan-bhujbal-accused-of-fake-maratha-kunbi-caste-certificate-documents-manoj-jarange-patil-1494274.html</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-chandrashekhar-bawankule-on-local-body-elections-tickets-via-internal-survey-public-opinion-to-decide-not-loyalty-to-leaders-amid-chandrapur-groupism-1385779</t>
+          <t>https://news18marathi.com/maharashtra/81-talukas-to-be-created-in-maharashtra-along-with-20-new-districts-marathi-news-1485490.html</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-obc-reservation-maharashtra-govt-to-prevent-forgery-in-maratha-kunbi-certificates-sub-committee-demands-2900-crore-for-obc-ministry-welfare-schemes-1384585</t>
+          <t>https://www.mymahanagar.com/desh-videsh/live-update-monsoon-2025-rain-update-maharashtra-rain-update-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-mumbai-news-cm-devendra-fadnavis-deputy-cm-eknath-shind-10/923721/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.navakal.in/maharashtra/vishwa-hindu-parishadno-muslims-allowed-in-garba-marathi-news/</t>
+          <t>https://puneprahar.com/2025/09/imd-weather-update-big-crisis-in-maharashtra-29-districts-on-high-alert-for-rain-today-step-out-of-the-house-only-if-necessary/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/navratri-utsav-only-hindus-allowed-in-garbhas-vishva-hindu-parishad-takes-this-stand/</t>
+          <t>https://puneprahar.com/2025/09/croma-launches-new-store-in-kothrud-pune-get-up-to-%E2%82%B930000-cashback-and-free-premium-gifts/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/amp/india-news/maha-govt-to-allow-tribal-farmers-to-lease-land-to-private-firms-minister-125092000372_1.html</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%B9-%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%97%E0%A4%9F-%E0%A4%B2-%E0%A4%A7%E0%A4%95%E0%A5%8D%E0%A4%95-%E0%A4%B8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%98-%E0%A4%9F%E0%A4%97%E0%A5%87-%E0%A4%85%E0%A4%82%E0%A4%AC%E0%A4%B0-%E0%A4%B7-%E0%A4%98-%E0%A4%9F%E0%A4%97%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6/ar-AA1CXkyZ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://vsrsnews.in/pimpri-chinchwad/pune-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival/</t>
+          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/agriculture/farming-ideas/latest-news-see-what-bhandara-district-farmers-did-to-control-the-khodkid-of-crops-read-in-detail-a-a993/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister-3737045</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/revenue-servant-strike-eighth-day-government-not-even-a-simple-acknowledgement-protesters-warn-the-government-nagpur-news-maharashtra-marathi-news-1385371/amp</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-saturday-20-september-2025-1496545.html</t>
+          <t>https://www.devdiscourse.com/article/business/3634504-empowering-maharashtras-tribal-farmers-leasing-land-for-agriculture-and-mining</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/indian-railways-made-in-india-technology-locomotive-in-train-engine-pune-print-news-css-98-5381428/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/rs500cr-govt-land-grabbed-in-gadchiroli-with-fake-papers-minister/articleshow/124004750.cms</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chairman-of-maharashtra-legislative-council-statement-on-ram-shinde-marathwada-backwardness-pune-print-news-zws-70-5381328/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/govt-to-fast-track-land-ownership-rights-for-bengali-families-in-gadchiroli/articleshow/124004837.cms</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-rain-live-mumbai-pune-nagpur-traffic-local-trains-flood-imd-alert-update-beed-crime-ex-sarpanch-govind-barge-death-pooja-gaikwad-latest-news-breaking-rak-94-5372752/lite/?liveblog_page=3&amp;liveblog_last=90890-1757948209</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-residents-question-plan-to-start-60-private-property-regn-centres-in-maha/articleshow/124055902.cms</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-rain-live-mumbai-pune-nagpur-traffic-local-trains-flood-imd-alert-update-beed-crime-ex-sarpanch-govind-barge-death-pooja-gaikwad-latest-news-breaking-rak-94-5372752/lite/?liveblog_page=2&amp;liveblog_last=90863-1757936847</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/govt-gives-rs-40-crore-loan-guarantee-to-sugar-mill-linked-to-ncp-sp-neta-prataprao-dhakne/articleshow/124061371.cms</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/cm-devendra-fadnavis-on-remark-on-maharashtra-revenue-department-pune-print-news-zws-70-5381326/lite/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-news-case-registered-against-teacher-beating-girl-student-over-reason-of-refuse-to-clean-garbage/articleshow/123926192.cms</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/maharashtra/tragic-incident-two-teen-boys-drown-in-pond-while-taking-photos-families-devastated-community-in-shock-latest-marathi-news-yps99</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/maharashtra/buldhana-farmers-threaten-mass-movement-if-government-fails-to-announce-wet-drought-bdk97</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/big-news-garba-only-for-hindus-vhps-conditions/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-presents-fake-documents-asks-for-committee-to-scrutinise-kunbi-certificates/articleshow/123927743.cms</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/chandrashekhar-bawankule-interacted-with-reporters-at-the-district-collectors-office-phm-00-5387245/lite/</t>
+          <t>https://www.dainikprabhat.com/wagholi-news-wadebolhai-gram-panchayat-gets-aap-sarkar-seva-kendra/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/sports/suryakumar-yadav-team-to-take-to-the-field-against-oman-today-will-the-players-on-the-bench-get-a-chance-sjk95</t>
+          <t>https://news34.in/2025/09/chandrapur-bjp-internal-conflict-2026/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%B5-%E0%A4%B6%E0%A5%8D%E0%A4%B5-%E0%A4%B8%E0%A5%82-%E0%A4%85%E0%A4%A8%E0%A5%8D-rss-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%A4%E0%A4%B2%E0%A5%87-%E0%A4%B0%E0%A4%B5-%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%A3-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A5%87-%E0%A4%A8%E0%A4%B5%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%98-%E0%A4%B7%E0%A4%A3/ar-AA1HLd3n?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A0%E0%A4%B0%E0%A4%B5%E0%A4%B2%E0%A4%82%E0%A4%AF-%E0%A4%95/ar-AA1NcvqY</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
+          <t>https://marathi.indiatimes.com/e-paper/aam-aadmi-party-submits-memorandum-to-chief-minister-for-farmers-compensation/articleshow/123916578.cms</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/pune-navratri-festival-inaugurates-this-year-135935585.html</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/ajit-pawar-downplays-row-with-female-ips-officer/2925297</t>
+          <t>https://divyamarathi.bhaskar.com/national/news/orders-to-sprinkle-cow-urine-on-people-during-garba-in-maharashtra-135974133.html</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/rs500cr-govt-land-grabbed-in-gadchiroli-with-fake-papers-minister/articleshow/124004750.cms</t>
+          <t>https://marathi.indiatimes.com/e-paper/ramtek-development-to-receive-major-boost-minister-shelkars-assurance/articleshow/123916582.cms</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/govt-to-fast-track-land-ownership-rights-for-bengali-families-in-gadchiroli/articleshow/124004837.cms</t>
+          <t>https://marathi.indiatimes.com/e-paper/leopard-spreads-terror-in-sinnar-forest-departments-capture-mission-fails/articleshow/123916817.cms</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/agriculture/weather/the-rains-will-stop-the-monsoons-return-journey-will-begin-how-do-you-know-when-the-monsoon-will-leave-a-a975/</t>
+          <t>https://marathi.indiatimes.com/e-paper/trimbakeshwar-womens-pot-protest-against-water-shortage/articleshow/123916850.cms</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-heavy-rain-traffic-disrupted-and-normal-life-affected-imd-issues-alert-for-next-24-hour/articleshow/123900789.cms</t>
+          <t>https://marathi.indiatimes.com/e-paper/sinnar-17-25-percent-increase-in-water-bill-sima-organization-strongly-oppose/articleshow/123916891.cms</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
+          <t>https://www.marathi.hindusthanpost.com/social/maharashtra-action-will-be-taken-against-bogus-documents-decision-of-obc-cabinet-sub-committee-meeting-under-discussion/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-news-case-registered-against-teacher-beating-girl-student-over-reason-of-refuse-to-clean-garbage/articleshow/123926192.cms</t>
+          <t>https://news34.in/2025/09/chandrapur-obc-leaders-statements-2025/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
+          <t>https://www.newsdrum.in/national/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister-10482393</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/aam-aadmi-party-submits-memorandum-to-chief-minister-for-farmers-compensation/articleshow/123916578.cms</t>
+          <t>https://telugu.getlokalapp.com/maharashtra-news/nagpur/ramtek/nagpur-bawankule-s-allegations-on-vadettiwar-s-allegations-15455305</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/banjara-community-holds-two-big-rallies-munde-says-form-panel-to-grant-them-st-status-101757963085577.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-sudhir-khandare-dies-in-bathroom-after-allegedly-hit-by-tap-police-solved-murder-mystery-nabs-family/articleshow/123933510.cms</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/19/tatkare-terms-rahul-gandhis-vote-theft-allegation-childish.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-heavy-rain-traffic-disrupted-and-normal-life-affected-imd-issues-alert-for-next-24-hour/articleshow/123900789.cms</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3634504-empowering-maharashtras-tribal-farmers-leasing-land-for-agriculture-and-mining</t>
+          <t>https://agrowon.esakal.com/agro-special/survey-of-654-rural-roads-completed-in-nagpur-gramin-taluka-maps-available-for-citizens-mj18</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-presents-fake-documents-asks-for-committee-to-scrutinise-kunbi-certificates/articleshow/123927743.cms</t>
+          <t>https://www.marathiebatmya.com/political/mou-signed-between-mahagenco-and-nmrda-in-the-presence-of-the-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://ahmednagarlive24.com/spacial/maharashtra-news-at-this-time-20-districts-and-81-talukas-will-be-formed-in-the-state/</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nashik/ex-bjp-corporator-arrested-nashik-law-and-order-amid-political-unrest-panchvati-shooting-case-vsd-99-5388883/</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/obc-activists-wave-black-flags-during-cms-speech-2-attempt-self-immolation-near-ajit-pawars-convoy/articleshow/123952613.cms</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nashik/nashik-traffic-diversions-announced-navratri-celebrations-kalika-mata-renuka-devi-temples-vsd-99-5388871/lite/</t>
+          <t>https://agrowon.esakal.com/agro-special/bori-budruk-was-the-first-to-give-the-code-number-rat16</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nashik/uddhav-thackeray-shiv-sena-restructures-jalgaon-ahead-local-body-elections-new-appointments-vsd-99-5388810/lite/</t>
+          <t>https://www.etvbharat.com/mr/!state/chhagan-bhujbal-question-to-sharad-pawar-over-obc-and-maratha-reservation-meeting-maharashtra-news-mhs25091803691</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister-3737045</t>
+          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/farmers-in-tribal-areas-can-lease-land-to-private-parties-bawankule/amp_articleshow/124004941.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/banjara-community-holds-two-big-rallies-munde-says-form-panel-to-grant-them-st-status-101757963085577.html</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/rs500cr-govt-land-grabbed-in-gadchiroli-with-fake-papers-minister/amp_articleshow/124004750.cms</t>
+          <t>https://www.oneindia.com/india/for-hindu-only-garba-vhp-sets-entry-rules-aadhaar-tilak-required-7866187.html</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/ramtek-development-to-receive-major-boost-minister-shelkars-assurance/articleshow/123916582.cms</t>
+          <t>https://www.newsdrum.in/national/maharashtra-obc-panel-orders-strict-scrutiny-of-caste-certificates-clears-rs-2933cr-pending-funds-10470839</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/leopard-spreads-terror-in-sinnar-forest-departments-capture-mission-fails/articleshow/123916817.cms</t>
+          <t>https://clarionindia.net/shiv-sena-fears-rigging-tampering-with-voter-list-in-maharashtra-local-polls/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/amit-shah-declares-bokaro-in-jharkhand-maoist-free/articleshow/123916647.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/trimbakeshwar-womens-pot-protest-against-water-shortage/articleshow/123916850.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/anti-social-element-will-be-arrested-soon-cm-on-vandalism-of-meenatai-thackerays-statue-in-mumbai/articleshow/123955024.cms</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/sinnar-17-25-percent-increase-in-water-bill-sima-organization-strongly-oppose/articleshow/123916891.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/state-has-received-no-complaint-of-denial-of-kunbi-certificate-to-eligible-candidates-cm/articleshow/123954996.cms</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-shiv-bhojan-thali-scheme-to-continue-in-maharashtra-with-200-crore-approval-closed-centers-to-reopen-1385628</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/govt-issued-gr-based-on-hyderabad-gazette-to-resolve-conflict-but-it-backfired-pawar/articleshow/123955159.cms</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/wagholi-news-wadebolhai-gram-panchayat-gets-aap-sarkar-seva-kendra/</t>
+          <t>https://mahasamvad.in/178604/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/maharashtra-action-will-be-taken-against-bogus-documents-decision-of-obc-cabinet-sub-committee-meeting-under-discussion/</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/global-level-tourist-destination-to-come-up-at-koradi-mou-signed-in-presence-of-cm-sdj87</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/a-conspiracy-has-been-hatched-to-defame-laxman-hake-vijay-vadettiwar-claims/133273/</t>
+          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/jsym-to-host-amrit-mahotsavi-international-yoga-convention-in-nagpur-in-november/articleshow/124005000.cms</t>
+          <t>https://www.freepressjournal.in/pune/videos-long-queues-outside-kopa-mall-in-punes-koregaon-park-as-iphone-17-series-goes-on-sale-in-india</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-sudhir-khandare-dies-in-bathroom-after-allegedly-hit-by-tap-police-solved-murder-mystery-nabs-family/articleshow/123933510.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/178604/</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>https://agrowon.esakal.com/agro-special/survey-of-654-rural-roads-completed-in-nagpur-gramin-taluka-maps-available-for-citizens-mj18</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/obc-activists-wave-black-flags-during-cms-speech-2-attempt-self-immolation-near-ajit-pawars-convoy/articleshow/123952613.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>https://www.businessworld.in/article/maharashtra-allows-tribal-farmers-to-lease-barren-land-to-firms-572455</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>https://agrowon.esakal.com/agro-special/bori-budruk-was-the-first-to-give-the-code-number-rat16</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>http://www.msn.com/mr-in/news/other/%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%86%E0%A4%A4-%E0%A4%95-%E0%A4%AF%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%B0-%E0%A4%AE-%E0%A4%A8%E0%A5%8D%E0%A4%AF%E0%A4%A4-%E0%A4%AA-%E0%A4%A3%E0%A4%82%E0%A4%A6-%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A5%87-%E0%A4%A1-%E0%A4%9C-%E0%A4%9F%E0%A4%B2-%E0%A4%B0%E0%A5%87%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%A1-%E0%A4%AB-%E0%A4%AF%E0%A4%A6%E0%A5%87-%E0%A4%B5-%E0%A4%9A%E0%A5%82%E0%A4%A8-%E0%A4%86%E0%A4%A8%E0%A4%82%E0%A4%A6%E0%A5%82%E0%A4%A8-%E0%A4%9C-%E0%A4%B2/ar-AA1MvyUA?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/sharad-pawar-reaction-on-hyderabad-gazette-and-the-cabinet-sub-committee-formed-on-reservation/articleshow/123964633.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>http://www.msn.com/en-in/news/India/maratha-quota-row-rumblings-in-mahayuti-alliance-chhagan-bhujbal-skips-cabinet-meet/ar-AA1LQ2jJ?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/en-in/autos/photos/velhe-taluka-in-pune-renamed-after-chhatrapati-shivajis-first-capital-fort-rajgad/ar-AA1KZLQZ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-rain-live-mumbai-pune-nagpur-traffic-local-trains-flood-imd-alert-update-beed-crime-ex-sarpanch-govind-barge-death-pooja-gaikwad-latest-news-breaking-rak-94-5372752/lite/?liveblog_page=2&amp;liveblog_last=90839-1757925166</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>https://www.marathiebatmya.com/political/mou-signed-between-mahagenco-and-nmrda-in-the-presence-of-the-chief-minister/</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>https://www.berartimes.com/vidarbha/216594/</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>https://www.business-standard.com/amp/india-news/himachal-rains-death-toll-rises-to-427-243-rain-related-184-in-accidents-125092000391_1.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>https://thefocusindia.com/maharashtra-news/mou-between-maharashtra-government-and-naam-foundation-284511/</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/kunbi-caste-certificate-%E0%A4%95%E0%A5%81%E0%A4%A3%E0%A4%AC-%E0%A4%AC-%E0%A4%97%E0%A4%B8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AE-%E0%A4%A3%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%82%E0%A4%9A-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%B8%E0%A4%96-%E0%A4%B2-%E0%A4%AA%E0%A4%A1%E0%A4%A4-%E0%A4%B3%E0%A4%A3/ar-AA1MHcDS</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>https://news18marathi.com/agriculture/revenue-departments-lok-adalat-campaign-for-farmers-to-start-from-september-17-1480838.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>https://agrowon.esakal.com/agro-special/khadgaon-farmer-suicide-case-inquiry-report-submitted-to-collector-mj18</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>https://www.devdiscourse.com/article/law-order/3634600-maharashtras-new-lease-law-a-boon-or-bane-for-tribal-farmers</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/anti-social-element-will-be-arrested-soon-cm-on-vandalism-of-meenatai-thackerays-statue-in-mumbai/articleshow/123955024.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/state-has-received-no-complaint-of-denial-of-kunbi-certificate-to-eligible-candidates-cm/articleshow/123954996.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>https://www.newsdrum.in/national/maharashtra-obc-panel-orders-strict-scrutiny-of-caste-certificates-clears-rs-2933cr-pending-funds-10470839</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/global-level-tourist-destination-to-come-up-at-koradi-mou-signed-in-presence-of-cm-sdj87</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>https://www.ptinews.com/detail/national/Maharashtra-OBC-panel-orders-strict-scrutiny-of-caste-certificates-clears-Rs-2-933cr-pending-funds/2920779</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>https://www.freepressjournal.in/pune/videos-long-queues-outside-kopa-mall-in-punes-koregaon-park-as-iphone-17-series-goes-on-sale-in-india</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
           <t>https://www.timemaharashtra.com/maharashtra/navratri-new-decision-from-vishwa-hindu-parishad-aadhaar-card-mandatory-to-watch-garba-during-navratri/133217/</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>https://www.khabar24.tv/2025/09/17/chandrashekhar-bawankule-writes-emotional-letter-to-pm-modi-on-his-birthday-a-big-message-to-the-nation-khabar-24-express/</t>
         </is>
       </c>
     </row>

--- a/Output/Chandrashekhar Bawankule/extracted_links_Chandrashekhar Bawankule_failed_links.xlsx
+++ b/Output/Chandrashekhar Bawankule/extracted_links_Chandrashekhar Bawankule_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A121"/>
+  <dimension ref="A1:A87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,7 +438,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178572/</t>
+          <t>https://mahasamvad.in/179502/</t>
         </is>
       </c>
     </row>
@@ -452,35 +452,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/revenue-servant-strike-eighth-day-government-not-even-a-simple-acknowledgement-protesters-warn-the-government-nagpur-news-maharashtra-marathi-news-1385371</t>
+          <t>https://mahasamvad.in/178572/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-live-blog-updates-19-september-2025-farmer-flood-rain-maharashtra-weather-maharashtra-politics-devendra-fadnavismumbai-rains-1385110</t>
+          <t>https://mahasamvad.in/179430/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/navratri-garba-only-for-hindus-check-aadhaar-of-participants-says-vhp-bawankule-comment-1385439</t>
+          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-live-blog-updates-19-september-2025-farmer-flood-rain-maharashtra-weather-maharashtra-politics-devendra-fadnavismumbai-rains-1385110</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.adharnewsnetwork.com/2025/09/chandrashekhar-bawankule.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sena-ubt-criticises-govt-over-match-bawankule-hits-back/articleshow/123887314.cms</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/sena-ubt-criticises-govt-over-match-bawankule-hits-back/articleshow/123887314.cms</t>
+          <t>https://www.msn.com/en-in/news/India/state-to-soon-allow-private-entities-to-lease-tribal-lands/ar-AA1MYFKc</t>
         </is>
       </c>
     </row>
@@ -494,784 +494,546 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-encroachment-on-farm-roads-to-be-cleared-govt-to-map-such-pathways-says-bawankule/ar-AA1MXpLZ</t>
+          <t>https://www.ptinews.com/story/national/vhp-issues-hindus-only-diktat-for-garba-bjp-minister-backs-organisers-rights-cong-slams-move/2934001</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/farmers-in-tribal-areas-can-lease-land-to-private-parties-bawankule/articleshow/124004941.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3634796-maharashtras-road-to-prosperity-revamping-farm-access-for-farmers</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-encroachment-on-farm-roads-to-be-cleared-govt-to-map-such-pathways-says-bawankule/ar-AA1MXpLZ</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/maha-govt-to-allow-tribal-farmers-to-lease-land-to-private-firms-minister-125092000372_1.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/farmers-in-tribal-areas-can-lease-land-to-private-parties-bawankule/articleshow/124004941.cms</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/ajit-pawar-downplays-row-with-female-ips-officer/2925297</t>
+          <t>https://www.business-standard.com/india-news/maha-govt-to-allow-tribal-farmers-to-lease-land-to-private-firms-minister-125092000372_1.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-minister-chhagan-bhujbal-demands-verification-of-obc-certificates-issued-to-maratha-community-23594340</t>
+          <t>https://www.ptinews.com/story/national/ajit-pawar-downplays-row-with-female-ips-officer/2925297</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
+          <t>https://timesofindia.indiatimes.com/india/vhp-issues-hindus-only-diktat-for-garba-bawankule-backs-organisers-rights-wadettiwar-slams-move/articleshow/124014945.cms</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/vhp-issues-hindus-only-diktat-for-garba-bawankule-backs-organisers-rights-wadettiwar-slams-move/articleshow/124014945.cms</t>
+          <t>https://www.hindustantimes.com/india-news/for-hindu-only-garba-vhp-sets-entry-norms-check-aadhaar-apply-tilak-101758363132840.html</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/?p=6725428</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/new-nagpur-project-farmers-provide-proof-about-no-rr-rate-change-in-10-yrs/articleshow/124052183.cms</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/new-nagpur-project-farmers-provide-proof-about-no-rr-rate-change-in-10-yrs/articleshow/124052183.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
+          <t>https://marathi.indiatimes.com/e-paper/chandrashekhar-bawankules-important-instructions-for-water-resource-conservation-in-nagpur/articleshow/123916999.cms</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/chandrashekhar-bawankules-important-instructions-for-water-resource-conservation-in-nagpur/articleshow/123916999.cms</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/guardian-minister-chandrashekhar-bawankule-thanks-govt-for-upgrading-nagpurs-religious-sites-sdj87</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/guardian-minister-chandrashekhar-bawankule-thanks-govt-for-upgrading-nagpurs-religious-sites-sdj87</t>
+          <t>https://mahasamvad.in/178575/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178575/</t>
+          <t>https://marathi.abplive.com/news/gadchiroli/gadchiroli-non-tribals-will-able-to-take-tribal-lands-on-lease-revenue-minister-chandrashekhar-bawankule-marathi-news-1385320</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-proposal-to-create-20-new-districts-81-talukas-process-chandrashekhar-bawankule-revenue-minister-news-1386089</t>
+          <t>https://marathi.indiatimes.com/maharashtra/gadchiroli/revenue-minister-chandrashekhar-bawankule-announces-that-tribal-lands-can-be-given-on-lease/articleshow/124010200.cms</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/chandrashekhar-bawankule-criticizes-sharad-pawar-maratha-obc-upsamiti-135950317.html</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/minister-chandrashekhar-bawankule-gives-important-instructions-to-officers-about-maratha-kunbi-certificate-distribution/articleshow/123922415.cms</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/chandrashekhar-bawankule-says-government-got-proposal-for-20-new-district/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AD-%E0%A4%9C%E0%A4%AA-%E0%A4%B8%E0%A4%A6%E0%A4%B8%E0%A5%8D%E0%A4%AF-%E0%A4%A8-%E0%A4%82%E0%A4%A6%E0%A4%A3-%E0%A4%A4-%E0%A4%B6%E0%A4%B9%E0%A4%B0-%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A5%E0%A4%AE/ar-AA1zoITs?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/gadchiroli/gadchiroli-non-tribals-will-able-to-take-tribal-lands-on-lease-revenue-minister-chandrashekhar-bawankule-marathi-news-1385320</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A0%E0%A4%B0%E0%A4%B5%E0%A4%B2%E0%A4%82%E0%A4%AF-%E0%A4%95/ar-AA1NcvqY</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/chandrashekhar-bawankule-gives-important-instructions-to-officers-chhagan-bhujbal-on-maratha-kunbi-certificate-distribution-and-obc-reservation-maharashtra-news-mhs25091605134</t>
+          <t>https://marathi.ndtv.com/videos/bawankule-no-tickets-for-those-who-follow-leaders-bawankule-warns-997430</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/gadchiroli/revenue-minister-chandrashekhar-bawankule-announces-that-tribal-lands-can-be-given-on-lease/articleshow/124010200.cms</t>
+          <t>https://agrowon.esakal.com/agro-special/maharashtra-plans-20-new-districts-and-81-talukas-revenue-minister-bawankule-mj18</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/obc-upsamiti-meeting-chandrashekhar-bawankule-chhagan-bhujbal-opposed-flaw-evidence-to-kunbi-certificates-1384586</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/maharashtra-obc-sub-committee-big-decision-on-kunbi-certificate-distribution-to-maratha-community/articleshow/123921757.cms</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/minister-chandrashekhar-bawankule-gives-important-instructions-to-officers-about-maratha-kunbi-certificate-distribution/articleshow/123922415.cms</t>
+          <t>https://mahasamvad.in/178893/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A0%E0%A4%B0%E0%A4%B5%E0%A4%B2%E0%A4%82%E0%A4%AF-%E0%A4%95/ar-AA1NcvqY?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://marathi.abplive.com/news/maharashtra/obc-upsamiti-meeting-chandrashekhar-bawankule-chhagan-bhujbal-opposed-flaw-evidence-to-kunbi-certificates-1384586</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/22/relief-due-to-gst-reforms-common-people-benefit-from-reduction-in-tax-rates-on-daily-use-items-revenue-ministe.amp.html</t>
+          <t>https://news18marathi.com/maharashtra/revenue-minister-chandrashekhar-bawankule-has-made-murum-mining-royalty-free-1484899.html</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/maharashtra-plans-20-new-districts-and-81-talukas-revenue-minister-bawankule-mj18</t>
+          <t>https://agrowon.esakal.com/agro-special/maharashtra-to-make-1100-government-services-online-by-may-cm-fadnavis-mj18</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/bawankule-no-tickets-for-those-who-follow-leaders-bawankule-warns-997430</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-shivbhojan-thali-scheme-to-continue-minister-bawankule-announces-200-crore-approval-for-maharashtra-s-affordable-meal-program-1385482</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178893/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-chandrashekhar-bawankule-on-local-body-elections-tickets-via-internal-survey-public-opinion-to-decide-not-loyalty-to-leaders-amid-chandrapur-groupism-1385779</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-obc-sub-committee-big-decision-on-kunbi-certificate-distribution-to-maratha-community/articleshow/123921757.cms</t>
+          <t>https://policenama.com/pune-navratri-mahotsav-pune-the-31st-pune-navratri-mahotsav-will-be-inaugurated-grandly-by-revenue-minister-chandrashekhar-bawankule-festival-organizer-aba-bagul-gave-this-information-in-a-press-c/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/vision-for-pune-transforming-into-indias-top-infrastructure-hub-chandrashekhar-bawankule-pjp78</t>
+          <t>https://www.adharnewsnetwork.com/2025/09/chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/maharashtra-to-make-1100-government-services-online-by-may-cm-fadnavis-mj18</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/private-companies-can-also-lease-wasteland-tribal-land-125092100014_1.html</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%97-%E0%A4%AF%E0%A4%95%E0%A4%B5-%E0%A4%A1-%E0%A4%AC-%E0%A4%B2%E0%A4%B2%E0%A5%87-%E0%A4%85%E0%A4%A8%E0%A5%8D-%E0%A4%AA%E0%A5%81%E0%A4%A8%E0%A5%8D%E0%A4%B9-%E0%A4%B5-%E0%A4%A6-%E0%A4%A4-%E0%A4%B8-%E0%A4%AA%E0%A4%A1%E0%A4%B2%E0%A5%87-%E0%A4%9D%E0%A5%87%E0%A4%A1%E0%A4%AA-%E0%A4%86%E0%A4%A3-%E0%A4%AA%E0%A4%82%E0%A4%9A-%E0%A4%AF%E0%A4%A4-%E0%A4%B8%E0%A4%AE-%E0%A4%A4-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%81%E0%A4%95-%E0%A4%82%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%B5-%E0%A4%A6%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B5%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A4%B5%E0%A5%8D%E0%A4%AF/ar-AA1N0sRo?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://www.marathiebatmya.com/political/obc-sub-committees-decision-thorough-verification-of-kunbi-bogus-certificates/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/chagan-bhujbal-obc-reservation-demands-135934860.html</t>
+          <t>https://www.dainikprabhat.com/no-registration-without-survey-big-decision-of-revenue-department-land-survey-mandatory-before-deed-registration-no-changes-without-registration/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-shivbhojan-thali-scheme-to-continue-minister-bawankule-announces-200-crore-approval-for-maharashtra-s-affordable-meal-program-1385482</t>
+          <t>https://www.dainikprabhat.com/as-many-as-20-new-districts-and-81-talukas-have-been-created-in-the-state/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-chandrashekhar-bawankule-on-local-body-elections-tickets-via-internal-survey-public-opinion-to-decide-not-loyalty-to-leaders-amid-chandrapur-groupism-1385779</t>
+          <t>https://www.dainikprabhat.com/pune-news-exemption-from-the-fragmentation-law-sale-of-one-or-two-gunthas-is-now-possible-know-when-the-implementation-will-start/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-shiv-bhojan-thali-scheme-to-continue-in-maharashtra-with-200-crore-approval-closed-centers-to-reopen-1385628</t>
+          <t>https://marathi.ndtv.com/videos/gautam-adani-sebi-has-dismissed-all-allegations-thanks-to-everyone-who-was-with-us-998035</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://policenama.com/pune-navratri-mahotsav-pune-the-31st-pune-navratri-mahotsav-will-be-inaugurated-grandly-by-revenue-minister-chandrashekhar-bawankule-festival-organizer-aba-bagul-gave-this-information-in-a-press-c/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/rs500cr-govt-land-grabbed-in-gadchiroli-with-fake-papers-minister/articleshow/124004750.cms</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/private-companies-can-also-lease-wasteland-tribal-land-125092100014_1.html</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-bawankule-says-private-companies-also-lease-barren-tribal-land-cm-fadnavis-government-enact-law-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/obc-sub-committees-decision-thorough-verification-of-kunbi-bogus-certificates/</t>
+          <t>https://vsrsnews.in/pimpri-chinchwad/pune-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/no-registration-without-survey-big-decision-of-revenue-department-land-survey-mandatory-before-deed-registration-no-changes-without-registration/</t>
+          <t>https://news18marathi.com/maharashtra/81-talukas-to-be-created-in-maharashtra-along-with-20-new-districts-marathi-news-1485490.html</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pune-news-mine-owners-are-in-trouble-mining-in-mountains-and-hills-banned-revenue-minister-bawankules-firm-stance/</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-saturday-20-september-2025-1496545.html</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/as-many-as-20-new-districts-and-81-talukas-have-been-created-in-the-state/</t>
+          <t>https://news18marathi.com/agriculture/revenue-departments-lok-adalat-campaign-for-farmers-to-start-from-september-17-1480838.html</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pune-news-exemption-from-the-fragmentation-law-sale-of-one-or-two-gunthas-is-now-possible-know-when-the-implementation-will-start/</t>
+          <t>https://www.loksatta.com/pune/indian-railways-made-in-india-technology-locomotive-in-train-engine-pune-print-news-css-98-5381428/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/chandrashekhar-bawankule-praises-new-gst-reform/133431/</t>
+          <t>https://www.loksatta.com/pune/chairman-of-maharashtra-legislative-council-statement-on-ram-shinde-marathwada-backwardness-pune-print-news-zws-70-5381328/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://news34.in/2025/09/chandrapur-bjp-news-development-updates/</t>
+          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister-3737045</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/chhagan-bhujbal-demands-probe-into-fake-obc-certificates/</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.adharnewsnetwork.com/2025/09/aap-chandrapur.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/jsym-to-host-amrit-mahotsavi-international-yoga-convention-in-nagpur-in-november/articleshow/124005000.cms</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-local-body-polls-chandrashekhar-bawankule-on-ticket-distribution-public-opinion-to-decide-candidates-amidst-chandrapur-factionalism-1385673</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/govt-to-fast-track-land-ownership-rights-for-bengali-families-in-gadchiroli/articleshow/124004837.cms</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-obc-reservation-maharashtra-govt-to-prevent-forgery-in-maratha-kunbi-certificates-sub-committee-demands-2900-crore-for-obc-ministry-welfare-schemes-1384585</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-bawankule-says-private-companies-also-lease-barren-tribal-land-cm-fadnavis-government-enact-law-2025-09-20</t>
+          <t>https://www.devdiscourse.com/article/business/3634504-empowering-maharashtras-tribal-farmers-leasing-land-for-agriculture-and-mining</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://vsrsnews.in/pimpri-chinchwad/pune-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival/</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-heavy-rain-traffic-disrupted-and-normal-life-affected-imd-issues-alert-for-next-24-hour/articleshow/123900789.cms</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-saturday-20-september-2025-1496545.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/revenue-departments-lok-adalat-campaign-for-farmers-to-start-from-september-17-1480838.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/indian-railways-made-in-india-technology-locomotive-in-train-engine-pune-print-news-css-98-5381428/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-presents-fake-documents-asks-for-committee-to-scrutinise-kunbi-certificates/articleshow/123927743.cms</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-rain-live-mumbai-pune-nagpur-traffic-local-trains-flood-imd-alert-update-beed-crime-ex-sarpanch-govind-barge-death-pooja-gaikwad-latest-news-breaking-rak-94-5372752/lite/?liveblog_page=3&amp;liveblog_last=90890-1757948209</t>
+          <t>https://ahmednagarlive24.com/maharashtra/maharashtra-news-at-this-time-20-districts-and-81-talukas-will-be-formed-in-the-state/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chairman-of-maharashtra-legislative-council-statement-on-ram-shinde-marathwada-backwardness-pune-print-news-zws-70-5381328/</t>
+          <t>https://www.oneindia.com/india/for-hindu-only-garba-vhp-sets-entry-rules-aadhaar-tilak-required-7866187.html</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-rain-live-mumbai-pune-nagpur-traffic-local-trains-flood-imd-alert-update-beed-crime-ex-sarpanch-govind-barge-death-pooja-gaikwad-latest-news-breaking-rak-94-5372752/lite/?liveblog_page=2&amp;liveblog_last=90863-1757936847</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-minister-chhagan-bhujbal-demands-verification-of-obc-certificates-issued-to-maratha-community-23594340</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/pandit-deendayal-upadhyay-employment-fair-organized.html</t>
+          <t>https://marathi.indiatimes.com/e-paper/aam-aadmi-party-submits-memorandum-to-chief-minister-for-farmers-compensation/articleshow/123916578.cms</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/chhagan-bhujbal-accused-of-fake-maratha-kunbi-caste-certificate-documents-manoj-jarange-patil-1494274.html</t>
+          <t>https://marathi.indiatimes.com/e-paper/ramtek-development-to-receive-major-boost-minister-shelkars-assurance/articleshow/123916582.cms</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/81-talukas-to-be-created-in-maharashtra-along-with-20-new-districts-marathi-news-1485490.html</t>
+          <t>https://marathi.indiatimes.com/e-paper/leopard-spreads-terror-in-sinnar-forest-departments-capture-mission-fails/articleshow/123916817.cms</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-update-monsoon-2025-rain-update-maharashtra-rain-update-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-mumbai-news-cm-devendra-fadnavis-deputy-cm-eknath-shind-10/923721/</t>
+          <t>https://marathi.indiatimes.com/e-paper/sinnar-17-25-percent-increase-in-water-bill-sima-organization-strongly-oppose/articleshow/123916891.cms</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://puneprahar.com/2025/09/imd-weather-update-big-crisis-in-maharashtra-29-districts-on-high-alert-for-rain-today-step-out-of-the-house-only-if-necessary/</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://puneprahar.com/2025/09/croma-launches-new-store-in-kothrud-pune-get-up-to-%E2%82%B930000-cashback-and-free-premium-gifts/</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/obc-activists-wave-black-flags-during-cms-speech-2-attempt-self-immolation-near-ajit-pawars-convoy/articleshow/123952613.cms</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%B9-%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%97%E0%A4%9F-%E0%A4%B2-%E0%A4%A7%E0%A4%95%E0%A5%8D%E0%A4%95-%E0%A4%B8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%98-%E0%A4%9F%E0%A4%97%E0%A5%87-%E0%A4%85%E0%A4%82%E0%A4%AC%E0%A4%B0-%E0%A4%B7-%E0%A4%98-%E0%A4%9F%E0%A4%97%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6/ar-AA1CXkyZ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/state-has-received-no-complaint-of-denial-of-kunbi-certificate-to-eligible-candidates-cm/articleshow/123954996.cms</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
+          <t>https://mumbaimirror.indiatimes.com/mumbai/unveiled-uniform-rules-for-hoardings-on-government-land/articleshow/123907327.html</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister-3737045</t>
+          <t>https://agrowon.esakal.com/agro-special/bori-budruk-was-the-first-to-give-the-code-number-rat16</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
+          <t>https://www.tribuneindia.com/news/india/vhp-issues-hindus-only-diktat-for-garba-events-congress-slams-move/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3634504-empowering-maharashtras-tribal-farmers-leasing-land-for-agriculture-and-mining</t>
+          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/rs500cr-govt-land-grabbed-in-gadchiroli-with-fake-papers-minister/articleshow/124004750.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/govt-to-fast-track-land-ownership-rights-for-bengali-families-in-gadchiroli/articleshow/124004837.cms</t>
+          <t>https://clarionindia.net/shiv-sena-fears-rigging-tampering-with-voter-list-in-maharashtra-local-polls/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-residents-question-plan-to-start-60-private-property-regn-centres-in-maha/articleshow/124055902.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/govt-gives-rs-40-crore-loan-guarantee-to-sugar-mill-linked-to-ncp-sp-neta-prataprao-dhakne/articleshow/124061371.cms</t>
+          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-news-case-registered-against-teacher-beating-girl-student-over-reason-of-refuse-to-clean-garbage/articleshow/123926192.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/banjara-community-holds-two-big-rallies-munde-says-form-panel-to-grant-them-st-status-101757963085577.html</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/20/bom27-mh-tribals-ld-land-lease.html</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/anti-social-element-will-be-arrested-soon-cm-on-vandalism-of-meenatai-thackerays-statue-in-mumbai/articleshow/123955024.cms</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-presents-fake-documents-asks-for-committee-to-scrutinise-kunbi-certificates/articleshow/123927743.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/govt-issued-gr-based-on-hyderabad-gazette-to-resolve-conflict-but-it-backfired-pawar/articleshow/123955159.cms</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/wagholi-news-wadebolhai-gram-panchayat-gets-aap-sarkar-seva-kendra/</t>
+          <t>https://mahasamvad.in/178604/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://news34.in/2025/09/chandrapur-bjp-internal-conflict-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A0%E0%A4%B0%E0%A4%B5%E0%A4%B2%E0%A4%82%E0%A4%AF-%E0%A4%95/ar-AA1NcvqY</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/e-paper/aam-aadmi-party-submits-memorandum-to-chief-minister-for-farmers-compensation/articleshow/123916578.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/pune-navratri-festival-inaugurates-this-year-135935585.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>https://divyamarathi.bhaskar.com/national/news/orders-to-sprinkle-cow-urine-on-people-during-garba-in-maharashtra-135974133.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/e-paper/ramtek-development-to-receive-major-boost-minister-shelkars-assurance/articleshow/123916582.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/e-paper/leopard-spreads-terror-in-sinnar-forest-departments-capture-mission-fails/articleshow/123916817.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/e-paper/trimbakeshwar-womens-pot-protest-against-water-shortage/articleshow/123916850.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/e-paper/sinnar-17-25-percent-increase-in-water-bill-sima-organization-strongly-oppose/articleshow/123916891.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>https://www.marathi.hindusthanpost.com/social/maharashtra-action-will-be-taken-against-bogus-documents-decision-of-obc-cabinet-sub-committee-meeting-under-discussion/</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>https://news34.in/2025/09/chandrapur-obc-leaders-statements-2025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>https://www.newsdrum.in/national/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister-10482393</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>https://telugu.getlokalapp.com/maharashtra-news/nagpur/ramtek/nagpur-bawankule-s-allegations-on-vadettiwar-s-allegations-15455305</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-sudhir-khandare-dies-in-bathroom-after-allegedly-hit-by-tap-police-solved-murder-mystery-nabs-family/articleshow/123933510.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-heavy-rain-traffic-disrupted-and-normal-life-affected-imd-issues-alert-for-next-24-hour/articleshow/123900789.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>https://agrowon.esakal.com/agro-special/survey-of-654-rural-roads-completed-in-nagpur-gramin-taluka-maps-available-for-citizens-mj18</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>https://www.marathiebatmya.com/political/mou-signed-between-mahagenco-and-nmrda-in-the-presence-of-the-chief-minister/</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/obc-activists-wave-black-flags-during-cms-speech-2-attempt-self-immolation-near-ajit-pawars-convoy/articleshow/123952613.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>https://agrowon.esakal.com/agro-special/bori-budruk-was-the-first-to-give-the-code-number-rat16</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/chhagan-bhujbal-question-to-sharad-pawar-over-obc-and-maratha-reservation-meeting-maharashtra-news-mhs25091803691</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/banjara-community-holds-two-big-rallies-munde-says-form-panel-to-grant-them-st-status-101757963085577.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>https://www.oneindia.com/india/for-hindu-only-garba-vhp-sets-entry-rules-aadhaar-tilak-required-7866187.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>https://www.newsdrum.in/national/maharashtra-obc-panel-orders-strict-scrutiny-of-caste-certificates-clears-rs-2933cr-pending-funds-10470839</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>https://clarionindia.net/shiv-sena-fears-rigging-tampering-with-voter-list-in-maharashtra-local-polls/</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/anti-social-element-will-be-arrested-soon-cm-on-vandalism-of-meenatai-thackerays-statue-in-mumbai/articleshow/123955024.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/state-has-received-no-complaint-of-denial-of-kunbi-certificate-to-eligible-candidates-cm/articleshow/123954996.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/govt-issued-gr-based-on-hyderabad-gazette-to-resolve-conflict-but-it-backfired-pawar/articleshow/123955159.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/178604/</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/global-level-tourist-destination-to-come-up-at-koradi-mou-signed-in-presence-of-cm-sdj87</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
           <t>https://www.freepressjournal.in/pune/videos-long-queues-outside-kopa-mall-in-punes-koregaon-park-as-iphone-17-series-goes-on-sale-in-india</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>https://www.timemaharashtra.com/maharashtra/navratri-new-decision-from-vishwa-hindu-parishad-aadhaar-card-mandatory-to-watch-garba-during-navratri/133217/</t>
         </is>
       </c>
     </row>

--- a/Output/Chandrashekhar Bawankule/extracted_links_Chandrashekhar Bawankule_failed_links.xlsx
+++ b/Output/Chandrashekhar Bawankule/extracted_links_Chandrashekhar Bawankule_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A87"/>
+  <dimension ref="A1:A81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,49 +438,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179502/</t>
+          <t>https://mahasamvad.in/178572/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-revenue-minister-u-turn-on-his-statement-over-giving-tribal-land-on-lease-to-non-tribals-gadchiroli-maharashtra-politics-marathi-news-1385418</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178572/</t>
+          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-revenue-minister-u-turn-on-his-statement-over-giving-tribal-land-on-lease-to-non-tribals-gadchiroli-maharashtra-politics-marathi-news-1385418</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179430/</t>
+          <t>https://marathi.abplive.com/news/revenue-servant-strike-eighth-day-government-not-even-a-simple-acknowledgement-protesters-warn-the-government-nagpur-news-maharashtra-marathi-news-1385371</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-live-blog-updates-19-september-2025-farmer-flood-rain-maharashtra-weather-maharashtra-politics-devendra-fadnavismumbai-rains-1385110</t>
+          <t>https://www.loksatta.com/pune/land-measurement-mandatory-for-registration-maharashtra-revenue-bawankule-pune-print-news-ocd-94-5385238/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/sena-ubt-criticises-govt-over-match-bawankule-hits-back/articleshow/123887314.cms</t>
+          <t>https://deshonnati.com/officials-should-act-without-condoning-any-wrongdoing/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/state-to-soon-allow-private-entities-to-lease-tribal-lands/ar-AA1MYFKc</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sena-ubt-criticises-govt-over-match-bawankule-hits-back/articleshow/123887314.cms</t>
         </is>
       </c>
     </row>
@@ -494,56 +494,56 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/vhp-issues-hindus-only-diktat-for-garba-bjp-minister-backs-organisers-rights-cong-slams-move/2934001</t>
+          <t>https://www.ptinews.com/editor-detail/vhp-issues--hindus-only--diktat-for-garba;-bawankule-backs-organisers--rights--wadettiwar-slams-move/2932800</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/farmers-in-tribal-areas-can-lease-land-to-private-parties-bawankule/articleshow/124004941.cms</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-encroachment-on-farm-roads-to-be-cleared-govt-to-map-such-pathways-says-bawankule/ar-AA1MXpLZ</t>
+          <t>https://www.businessworld.in/article/maharashtra-allows-tribal-farmers-to-lease-barren-land-to-firms-572455</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/farmers-in-tribal-areas-can-lease-land-to-private-parties-bawankule/articleshow/124004941.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/maha-govt-to-allow-tribal-farmers-to-lease-land-to-private-firms-minister-125092000372_1.html</t>
+          <t>https://www.newsdrum.in/national/tribal-farmers-in-maharashtra-can-now-lease-land-to-private-entities-govt-to-bring-law-minister-10482095</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/ajit-pawar-downplays-row-with-female-ips-officer/2925297</t>
+          <t>https://www.deccanherald.com/india/maharashtra/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister-3737045</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/vhp-issues-hindus-only-diktat-for-garba-bawankule-backs-organisers-rights-wadettiwar-slams-move/articleshow/124014945.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/for-hindu-only-garba-vhp-sets-entry-norms-check-aadhaar-apply-tilak-101758363132840.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/govt-to-fast-track-land-ownership-rights-for-bengali-families-in-gadchiroli/articleshow/124004837.cms</t>
         </is>
       </c>
     </row>
@@ -557,481 +557,439 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
+          <t>https://maharashtratimes.com/e-paper/chandrashekhar-bawankules-important-instructions-for-water-resource-conservation-in-nagpur/articleshow/123916999.cms</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/chandrashekhar-bawankules-important-instructions-for-water-resource-conservation-in-nagpur/articleshow/123916999.cms</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/guardian-minister-chandrashekhar-bawankule-thanks-govt-for-upgrading-nagpurs-religious-sites-sdj87</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/guardian-minister-chandrashekhar-bawankule-thanks-govt-for-upgrading-nagpurs-religious-sites-sdj87</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/minister-chandrashekhar-bawankule-gives-important-instructions-to-officers-about-maratha-kunbi-certificate-distribution/articleshow/123922415.cms</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178575/</t>
+          <t>https://marathi.abplive.com/news/gadchiroli/gadchiroli-non-tribals-will-able-to-take-tribal-lands-on-lease-revenue-minister-chandrashekhar-bawankule-marathi-news-1385320</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/gadchiroli/gadchiroli-non-tribals-will-able-to-take-tribal-lands-on-lease-revenue-minister-chandrashekhar-bawankule-marathi-news-1385320</t>
+          <t>https://maharashtratimes.com/maharashtra/gadchiroli/revenue-minister-chandrashekhar-bawankule-announces-that-tribal-lands-can-be-given-on-lease/articleshow/124010200.cms</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/gadchiroli/revenue-minister-chandrashekhar-bawankule-announces-that-tribal-lands-can-be-given-on-lease/articleshow/124010200.cms</t>
+          <t>https://www.tarunbharat.net/Encyc/2025/9/15/bjp-nagpur-chandrashekhar-bawankule-2025-panchayat-to-parliament-election-strategy-.html</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/minister-chandrashekhar-bawankule-gives-important-instructions-to-officers-about-maratha-kunbi-certificate-distribution/articleshow/123922415.cms</t>
+          <t>https://agrowon.esakal.com/agro-special/maharashtra-plans-20-new-districts-and-81-talukas-revenue-minister-bawankule-mj18</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AD-%E0%A4%9C%E0%A4%AA-%E0%A4%B8%E0%A4%A6%E0%A4%B8%E0%A5%8D%E0%A4%AF-%E0%A4%A8-%E0%A4%82%E0%A4%A6%E0%A4%A3-%E0%A4%A4-%E0%A4%B6%E0%A4%B9%E0%A4%B0-%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A5%E0%A4%AE/ar-AA1zoITs?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.abplive.com/news/maharashtra/obc-upsamiti-meeting-chandrashekhar-bawankule-chhagan-bhujbal-opposed-flaw-evidence-to-kunbi-certificates-1384586</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A0%E0%A4%B0%E0%A4%B5%E0%A4%B2%E0%A4%82%E0%A4%AF-%E0%A4%95/ar-AA1NcvqY</t>
+          <t>https://marathi.abplive.com/news/maharashtra/navratri-garba-only-for-hindus-check-aadhaar-of-participants-says-vhp-bawankule-comment-1385439</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/bawankule-no-tickets-for-those-who-follow-leaders-bawankule-warns-997430</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/maharashtra-obc-sub-committee-big-decision-on-kunbi-certificate-distribution-to-maratha-community/articleshow/123921757.cms</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/maharashtra-plans-20-new-districts-and-81-talukas-revenue-minister-bawankule-mj18</t>
+          <t>https://www.nagpurtoday.in/bawankules-initiative-five-nagpur-pilgrimage-sites-granted-b-category-status/09191501</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/maharashtra-obc-sub-committee-big-decision-on-kunbi-certificate-distribution-to-maratha-community/articleshow/123921757.cms</t>
+          <t>https://www.tarunbharat.net/Encyc/2025/9/16/yogesh-kumbhejkar-seva-pandharvada.html</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178893/</t>
+          <t>https://agrowon.esakal.com/agro-special/maharashtra-to-make-1100-government-services-online-by-may-cm-fadnavis-mj18</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/obc-upsamiti-meeting-chandrashekhar-bawankule-chhagan-bhujbal-opposed-flaw-evidence-to-kunbi-certificates-1384586</t>
+          <t>https://news18marathi.com/maharashtra/81-talukas-to-be-created-in-maharashtra-along-with-20-new-districts-marathi-news-1485490.html</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/revenue-minister-chandrashekhar-bawankule-has-made-murum-mining-royalty-free-1484899.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-shivbhojan-thali-scheme-to-continue-minister-bawankule-announces-200-crore-approval-for-maharashtra-s-affordable-meal-program-1385482</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/maharashtra-to-make-1100-government-services-online-by-may-cm-fadnavis-mj18</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-chandrashekhar-bawankule-on-local-body-elections-tickets-via-internal-survey-public-opinion-to-decide-not-loyalty-to-leaders-amid-chandrapur-groupism-1385779</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-shivbhojan-thali-scheme-to-continue-minister-bawankule-announces-200-crore-approval-for-maharashtra-s-affordable-meal-program-1385482</t>
+          <t>https://www.mahasamvad.in/page/52/?m=0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-chandrashekhar-bawankule-on-local-body-elections-tickets-via-internal-survey-public-opinion-to-decide-not-loyalty-to-leaders-amid-chandrapur-groupism-1385779</t>
+          <t>https://news18marathi.com/agriculture/revenue-minister-bawankule-has-given-information-about-the-documents-in-the-tukdebandi-1482532.html</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://policenama.com/pune-navratri-mahotsav-pune-the-31st-pune-navratri-mahotsav-will-be-inaugurated-grandly-by-revenue-minister-chandrashekhar-bawankule-festival-organizer-aba-bagul-gave-this-information-in-a-press-c/</t>
+          <t>https://www.adharnewsnetwork.com/2025/09/chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.adharnewsnetwork.com/2025/09/chandrashekhar-bawankule.html</t>
+          <t>https://policenama.com/pune-navratri-mahotsav-pune-the-31st-pune-navratri-mahotsav-will-be-inaugurated-grandly-by-revenue-minister-chandrashekhar-bawankule-festival-organizer-aba-bagul-gave-this-information-in-a-press-c/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/private-companies-can-also-lease-wasteland-tribal-land-125092100014_1.html</t>
+          <t>https://www.marathiebatmya.com/political/obc-sub-committees-decision-thorough-verification-of-kunbi-bogus-certificates/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/obc-sub-committees-decision-thorough-verification-of-kunbi-bogus-certificates/</t>
+          <t>https://www.dainikprabhat.com/no-registration-without-survey-big-decision-of-revenue-department-land-survey-mandatory-before-deed-registration-no-changes-without-registration/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/no-registration-without-survey-big-decision-of-revenue-department-land-survey-mandatory-before-deed-registration-no-changes-without-registration/</t>
+          <t>https://www.dainikprabhat.com/as-many-as-20-new-districts-and-81-talukas-have-been-created-in-the-state/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/as-many-as-20-new-districts-and-81-talukas-have-been-created-in-the-state/</t>
+          <t>https://www.tarunbharat.net/Encyc/2025/9/17/devendra-fadnavis-seva-pandharwada.html</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pune-news-exemption-from-the-fragmentation-law-sale-of-one-or-two-gunthas-is-now-possible-know-when-the-implementation-will-start/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/rs500cr-govt-land-grabbed-in-gadchiroli-with-fake-papers-minister/articleshow/124004750.cms</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/gautam-adani-sebi-has-dismissed-all-allegations-thanks-to-everyone-who-was-with-us-998035</t>
+          <t>https://www.business-standard.com/india-news/maha-govt-to-allow-tribal-farmers-to-lease-land-to-private-firms-minister-125092000372_1.html</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/rs500cr-govt-land-grabbed-in-gadchiroli-with-fake-papers-minister/articleshow/124004750.cms</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-bawankule-says-private-companies-also-lease-barren-tribal-land-cm-fadnavis-government-enact-law-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-bawankule-says-private-companies-also-lease-barren-tribal-land-cm-fadnavis-government-enact-law-2025-09-20</t>
+          <t>https://www.khabar24.tv/2025/09/25/chandrashekhar-bawankule-wrote-a-thank-you-letter-to-pm-modi-khabar-24-express/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://vsrsnews.in/pimpri-chinchwad/pune-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival/</t>
+          <t>https://www.khabar24.tv/2025/09/17/chandrashekhar-bawankule-writes-emotional-letter-to-pm-modi-on-his-birthday-a-big-message-to-the-nation-khabar-24-express/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/81-talukas-to-be-created-in-maharashtra-along-with-20-new-districts-marathi-news-1485490.html</t>
+          <t>https://www.loksatta.com/pune/indian-railways-made-in-india-technology-locomotive-in-train-engine-pune-print-news-css-98-5381428/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-saturday-20-september-2025-1496545.html</t>
+          <t>https://www.loksatta.com/pune/chairman-of-maharashtra-legislative-council-statement-on-ram-shinde-marathwada-backwardness-pune-print-news-zws-70-5381328/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/revenue-departments-lok-adalat-campaign-for-farmers-to-start-from-september-17-1480838.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/seva-pandharvada-organized-across-the-state-on-the-occasion-of-prime-minister-modis-birthday-information-from-.html</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/indian-railways-made-in-india-technology-locomotive-in-train-engine-pune-print-news-css-98-5381428/</t>
+          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chairman-of-maharashtra-legislative-council-statement-on-ram-shinde-marathwada-backwardness-pune-print-news-zws-70-5381328/</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/jsym-to-host-amrit-mahotsavi-international-yoga-convention-in-nagpur-in-november/articleshow/124005000.cms</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister-3737045</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/state-has-received-no-complaint-of-denial-of-kunbi-certificate-to-eligible-candidates-cm/articleshow/123954996.cms</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/jsym-to-host-amrit-mahotsavi-international-yoga-convention-in-nagpur-in-november/articleshow/124005000.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-news-case-registered-against-teacher-beating-girl-student-over-reason-of-refuse-to-clean-garbage/articleshow/123926192.cms</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/govt-to-fast-track-land-ownership-rights-for-bengali-families-in-gadchiroli/articleshow/124004837.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3634504-empowering-maharashtras-tribal-farmers-leasing-land-for-agriculture-and-mining</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/banjara-community-holds-two-big-rallies-munde-says-form-panel-to-grant-them-st-status-101757963085577.html</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-heavy-rain-traffic-disrupted-and-normal-life-affected-imd-issues-alert-for-next-24-hour/articleshow/123900789.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-presents-fake-documents-asks-for-committee-to-scrutinise-kunbi-certificates/articleshow/123927743.cms</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
+          <t>https://www.hindustantimes.com/india-news/for-hindu-only-garba-vhp-sets-entry-norms-check-aadhaar-apply-tilak-101758363132840.html</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-presents-fake-documents-asks-for-committee-to-scrutinise-kunbi-certificates/articleshow/123927743.cms</t>
+          <t>https://timesofindia.indiatimes.com/india/vhp-issues-hindus-only-diktat-for-garba-bawankule-backs-organisers-rights-wadettiwar-slams-move/articleshow/124014945.cms</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://ahmednagarlive24.com/maharashtra/maharashtra-news-at-this-time-20-districts-and-81-talukas-will-be-formed-in-the-state/</t>
+          <t>https://news34.in/2025/09/chandrapur-bjp-internal-conflict-2026/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.oneindia.com/india/for-hindu-only-garba-vhp-sets-entry-rules-aadhaar-tilak-required-7866187.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-minister-chhagan-bhujbal-demands-verification-of-obc-certificates-issued-to-maratha-community-23594340</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-minister-chhagan-bhujbal-demands-verification-of-obc-certificates-issued-to-maratha-community-23594340</t>
+          <t>https://maharashtratimes.com/e-paper/aam-aadmi-party-submits-memorandum-to-chief-minister-for-farmers-compensation/articleshow/123916578.cms</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/aam-aadmi-party-submits-memorandum-to-chief-minister-for-farmers-compensation/articleshow/123916578.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-heavy-rain-traffic-disrupted-and-normal-life-affected-imd-issues-alert-for-next-24-hour/articleshow/123900789.cms</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/ramtek-development-to-receive-major-boost-minister-shelkars-assurance/articleshow/123916582.cms</t>
+          <t>https://thelivenagpur.com/2025/09/15/guardian-minister-reviews-preparations-for-deekshabhoomi-and-navratri/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/leopard-spreads-terror-in-sinnar-forest-departments-capture-mission-fails/articleshow/123916817.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/obc-activists-wave-black-flags-during-cms-speech-2-attempt-self-immolation-near-ajit-pawars-convoy/articleshow/123952613.cms</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/sinnar-17-25-percent-increase-in-water-bill-sima-organization-strongly-oppose/articleshow/123916891.cms</t>
+          <t>https://agrowon.esakal.com/agro-special/survey-of-654-rural-roads-completed-in-nagpur-gramin-taluka-maps-available-for-citizens-mj18</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
+          <t>https://mumbaimirror.indiatimes.com/mumbai/unveiled-uniform-rules-for-hoardings-on-government-land/articleshow/123907327.html</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/obc-activists-wave-black-flags-during-cms-speech-2-attempt-self-immolation-near-ajit-pawars-convoy/articleshow/123952613.cms</t>
+          <t>https://agrowon.esakal.com/agro-special/bori-budruk-was-the-first-to-give-the-code-number-rat16</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/state-has-received-no-complaint-of-denial-of-kunbi-certificate-to-eligible-candidates-cm/articleshow/123954996.cms</t>
+          <t>https://www.tribuneindia.com/news/india/vhp-issues-hindus-only-diktat-for-garba-events-congress-slams-move/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://mumbaimirror.indiatimes.com/mumbai/unveiled-uniform-rules-for-hoardings-on-government-land/articleshow/123907327.html</t>
+          <t>https://maharashtratimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/bori-budruk-was-the-first-to-give-the-code-number-rat16</t>
+          <t>https://clarionindia.net/shiv-sena-fears-rigging-tampering-with-voter-list-in-maharashtra-local-polls/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/india/vhp-issues-hindus-only-diktat-for-garba-events-congress-slams-move/</t>
+          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/cleanliness-campaign-launched-in-the-state-on-the-occasion-of-prime-minister-narendra-modis-birthday-thousands.html</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/anti-social-element-will-be-arrested-soon-cm-on-vandalism-of-meenatai-thackerays-statue-in-mumbai/articleshow/123955024.cms</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://clarionindia.net/shiv-sena-fears-rigging-tampering-with-voter-list-in-maharashtra-local-polls/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/govt-issued-gr-based-on-hyderabad-gazette-to-resolve-conflict-but-it-backfired-pawar/articleshow/123955159.cms</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
+          <t>https://mahasamvad.in/178604/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
-        <is>
-          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/banjara-community-holds-two-big-rallies-munde-says-form-panel-to-grant-them-st-status-101757963085577.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/20/bom27-mh-tribals-ld-land-lease.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/anti-social-element-will-be-arrested-soon-cm-on-vandalism-of-meenatai-thackerays-statue-in-mumbai/articleshow/123955024.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/govt-issued-gr-based-on-hyderabad-gazette-to-resolve-conflict-but-it-backfired-pawar/articleshow/123955159.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/178604/</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
         <is>
           <t>https://www.freepressjournal.in/pune/videos-long-queues-outside-kopa-mall-in-punes-koregaon-park-as-iphone-17-series-goes-on-sale-in-india</t>
         </is>

--- a/Output/Chandrashekhar Bawankule/extracted_links_Chandrashekhar Bawankule_failed_links.xlsx
+++ b/Output/Chandrashekhar Bawankule/extracted_links_Chandrashekhar Bawankule_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A81"/>
+  <dimension ref="A1:A82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,7 +438,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178572/</t>
+          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-revenue-minister-u-turn-on-his-statement-over-giving-tribal-land-on-lease-to-non-tribals-gadchiroli-maharashtra-politics-marathi-news-1385418</t>
         </is>
       </c>
     </row>
@@ -452,49 +452,49 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-revenue-minister-u-turn-on-his-statement-over-giving-tribal-land-on-lease-to-non-tribals-gadchiroli-maharashtra-politics-marathi-news-1385418</t>
+          <t>https://marathi.abplive.com/news/revenue-servant-strike-eighth-day-government-not-even-a-simple-acknowledgement-protesters-warn-the-government-nagpur-news-maharashtra-marathi-news-1385371</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/revenue-servant-strike-eighth-day-government-not-even-a-simple-acknowledgement-protesters-warn-the-government-nagpur-news-maharashtra-marathi-news-1385371</t>
+          <t>https://marathi.abplive.com/news/maharashtra/navratri-garba-only-for-hindus-check-aadhaar-of-participants-says-vhp-bawankule-comment-1385439</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/land-measurement-mandatory-for-registration-maharashtra-revenue-bawankule-pune-print-news-ocd-94-5385238/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-live-blog-updates-19-september-2025-farmer-flood-rain-maharashtra-weather-maharashtra-politics-devendra-fadnavismumbai-rains-1385110</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/officials-should-act-without-condoning-any-wrongdoing/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sena-ubt-criticises-govt-over-match-bawankule-hits-back/articleshow/123887314.cms</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/sena-ubt-criticises-govt-over-match-bawankule-hits-back/articleshow/123887314.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-soon-allow-private-entities-to-lease-tribal-lands-101758396296809.html</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/vhps-hindus-only-diktat-for-garba-bjp-leader-backs-organisers-rights-oppn-slams-move-3737006</t>
+          <t>https://www.deccanherald.com/india/maharashtra/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister-3737045</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/vhp-issues--hindus-only--diktat-for-garba;-bawankule-backs-organisers--rights--wadettiwar-slams-move/2932800</t>
+          <t>https://www.ptinews.com/editor-detail/tribal-farmers-in-maharashtra-can-now-lease-land-to-private-entities;-govt-to-bring-law--minister/2932661</t>
         </is>
       </c>
     </row>
@@ -515,42 +515,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
+          <t>https://www.ptinews.com/story/national/vhp-issues-hindus-only-diktat-for-garba-bjp-minister-backs-organisers-rights-cong-slams-move/2934001</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/tribal-farmers-in-maharashtra-can-now-lease-land-to-private-entities-govt-to-bring-law-minister-10482095</t>
+          <t>https://timesofindia.indiatimes.com/india/vhp-issues-hindus-only-diktat-for-garba-bawankule-backs-organisers-rights-wadettiwar-slams-move/articleshow/124014945.cms</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister-3737045</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
+          <t>https://www.newsdrum.in/national/tribal-farmers-in-maharashtra-can-now-lease-land-to-private-entities-govt-to-bring-law-minister-10482095</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/govt-to-fast-track-land-ownership-rights-for-bengali-families-in-gadchiroli/articleshow/124004837.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/new-nagpur-project-farmers-provide-proof-about-no-rr-rate-change-in-10-yrs/articleshow/124052183.cms</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/new-nagpur-project-farmers-provide-proof-about-no-rr-rate-change-in-10-yrs/articleshow/124052183.cms</t>
+          <t>https://www.loksatta.com/maharashtra/chandrashekhar-bawankule-on-obc-sub-committee-meeting-and-obc-maratha-kunbi-certificate-politics-gkt-96-5376634/</t>
         </is>
       </c>
     </row>
@@ -564,385 +564,385 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/guardian-minister-chandrashekhar-bawankule-thanks-govt-for-upgrading-nagpurs-religious-sites-sdj87</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/minister-chandrashekhar-bawankule-gives-important-instructions-to-officers-about-maratha-kunbi-certificate-distribution/articleshow/123922415.cms</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/minister-chandrashekhar-bawankule-gives-important-instructions-to-officers-about-maratha-kunbi-certificate-distribution/articleshow/123922415.cms</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/guardian-minister-chandrashekhar-bawankule-thanks-govt-for-upgrading-nagpurs-religious-sites-sdj87</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/gadchiroli/gadchiroli-non-tribals-will-able-to-take-tribal-lands-on-lease-revenue-minister-chandrashekhar-bawankule-marathi-news-1385320</t>
+          <t>https://maharashtratimes.com/maharashtra/gadchiroli/revenue-minister-chandrashekhar-bawankule-announces-that-tribal-lands-can-be-given-on-lease/articleshow/124010200.cms</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/gadchiroli/revenue-minister-chandrashekhar-bawankule-announces-that-tribal-lands-can-be-given-on-lease/articleshow/124010200.cms</t>
+          <t>https://agrowon.esakal.com/agro-special/maharashtra-plans-20-new-districts-and-81-talukas-revenue-minister-bawankule-mj18</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.net/Encyc/2025/9/15/bjp-nagpur-chandrashekhar-bawankule-2025-panchayat-to-parliament-election-strategy-.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/obc-upsamiti-meeting-chandrashekhar-bawankule-chhagan-bhujbal-opposed-flaw-evidence-to-kunbi-certificates-1384586</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/maharashtra-plans-20-new-districts-and-81-talukas-revenue-minister-bawankule-mj18</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/maharashtra-obc-sub-committee-big-decision-on-kunbi-certificate-distribution-to-maratha-community/articleshow/123921757.cms</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/obc-upsamiti-meeting-chandrashekhar-bawankule-chhagan-bhujbal-opposed-flaw-evidence-to-kunbi-certificates-1384586</t>
+          <t>https://marathi.ndtv.com/videos/bawankule-no-tickets-for-those-who-follow-leaders-bawankule-warns-997430</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/navratri-garba-only-for-hindus-check-aadhaar-of-participants-says-vhp-bawankule-comment-1385439</t>
+          <t>https://www.tarunbharat.net/Encyc/2025/9/15/bjp-nagpur-chandrashekhar-bawankule-2025-panchayat-to-parliament-election-strategy-.html</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/maharashtra-obc-sub-committee-big-decision-on-kunbi-certificate-distribution-to-maratha-community/articleshow/123921757.cms</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-chandrashekhar-bawankule-on-local-body-elections-tickets-via-internal-survey-public-opinion-to-decide-not-loyalty-to-leaders-amid-chandrapur-groupism-1385779</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankules-initiative-five-nagpur-pilgrimage-sites-granted-b-category-status/09191501</t>
+          <t>https://www.tarunbharat.net/Encyc/2025/9/16/yogesh-kumbhejkar-seva-pandharvada.html</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.net/Encyc/2025/9/16/yogesh-kumbhejkar-seva-pandharvada.html</t>
+          <t>https://agrowon.esakal.com/agro-special/maharashtra-to-make-1100-government-services-online-by-may-cm-fadnavis-mj18</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/maharashtra-to-make-1100-government-services-online-by-may-cm-fadnavis-mj18</t>
+          <t>https://news18marathi.com/maharashtra/81-talukas-to-be-created-in-maharashtra-along-with-20-new-districts-marathi-news-1485490.html</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/81-talukas-to-be-created-in-maharashtra-along-with-20-new-districts-marathi-news-1485490.html</t>
+          <t>https://www.saamana.com/shiv-bhojan-thali-started-by-uddhav-thackeray-gets-200-crore-fund-by-government/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-shivbhojan-thali-scheme-to-continue-minister-bawankule-announces-200-crore-approval-for-maharashtra-s-affordable-meal-program-1385482</t>
+          <t>https://www.nagpurtoday.in/sharadiya-navratri-ritual-worship-of-guardian-minister-chandrashekhar-bawankule-at-koradi-mata-temple/09221722</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-chandrashekhar-bawankule-on-local-body-elections-tickets-via-internal-survey-public-opinion-to-decide-not-loyalty-to-leaders-amid-chandrapur-groupism-1385779</t>
+          <t>https://www.adharnewsnetwork.com/2025/09/chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/52/?m=0</t>
+          <t>https://policenama.com/pune-navratri-mahotsav-pune-the-31st-pune-navratri-mahotsav-will-be-inaugurated-grandly-by-revenue-minister-chandrashekhar-bawankule-festival-organizer-aba-bagul-gave-this-information-in-a-press-c/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/revenue-minister-bawankule-has-given-information-about-the-documents-in-the-tukdebandi-1482532.html</t>
+          <t>https://www.dainikprabhat.com/no-registration-without-survey-big-decision-of-revenue-department-land-survey-mandatory-before-deed-registration-no-changes-without-registration/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.adharnewsnetwork.com/2025/09/chandrashekhar-bawankule.html</t>
+          <t>https://www.marathiebatmya.com/political/obc-sub-committees-decision-thorough-verification-of-kunbi-bogus-certificates/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://policenama.com/pune-navratri-mahotsav-pune-the-31st-pune-navratri-mahotsav-will-be-inaugurated-grandly-by-revenue-minister-chandrashekhar-bawankule-festival-organizer-aba-bagul-gave-this-information-in-a-press-c/</t>
+          <t>https://www.dainikprabhat.com/pune-news-exemption-from-the-fragmentation-law-sale-of-one-or-two-gunthas-is-now-possible-know-when-the-implementation-will-start/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/obc-sub-committees-decision-thorough-verification-of-kunbi-bogus-certificates/</t>
+          <t>https://www.tarunbharat.net/Encyc/2025/9/17/devendra-fadnavis-seva-pandharwada.html</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/no-registration-without-survey-big-decision-of-revenue-department-land-survey-mandatory-before-deed-registration-no-changes-without-registration/</t>
+          <t>https://www.business-standard.com/india-news/maha-govt-to-allow-tribal-farmers-to-lease-land-to-private-firms-minister-125092000372_1.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/as-many-as-20-new-districts-and-81-talukas-have-been-created-in-the-state/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/rs500cr-govt-land-grabbed-in-gadchiroli-with-fake-papers-minister/articleshow/124004750.cms</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.net/Encyc/2025/9/17/devendra-fadnavis-seva-pandharwada.html</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-bawankule-says-private-companies-also-lease-barren-tribal-land-cm-fadnavis-government-enact-law-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/rs500cr-govt-land-grabbed-in-gadchiroli-with-fake-papers-minister/articleshow/124004750.cms</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-saturday-20-september-2025-1496545.html</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/maha-govt-to-allow-tribal-farmers-to-lease-land-to-private-firms-minister-125092000372_1.html</t>
+          <t>https://www.loksatta.com/pune/chairman-of-maharashtra-legislative-council-statement-on-ram-shinde-marathwada-backwardness-pune-print-news-zws-70-5381328/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-bawankule-says-private-companies-also-lease-barren-tribal-land-cm-fadnavis-government-enact-law-2025-09-20</t>
+          <t>https://www.loksatta.com/pune/indian-railways-made-in-india-technology-locomotive-in-train-engine-pune-print-news-css-98-5381428/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.khabar24.tv/2025/09/25/chandrashekhar-bawankule-wrote-a-thank-you-letter-to-pm-modi-khabar-24-express/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/seva-pandharvada-organized-across-the-state-on-the-occasion-of-prime-minister-modis-birthday-information-from-.html</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.khabar24.tv/2025/09/17/chandrashekhar-bawankule-writes-emotional-letter-to-pm-modi-on-his-birthday-a-big-message-to-the-nation-khabar-24-express/</t>
+          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/indian-railways-made-in-india-technology-locomotive-in-train-engine-pune-print-news-css-98-5381428/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chairman-of-maharashtra-legislative-council-statement-on-ram-shinde-marathwada-backwardness-pune-print-news-zws-70-5381328/</t>
+          <t>https://www.nagpurtoday.in/nagpur-officials-review-preparations-for-dhammachakra-pravartan-din/09161920</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/seva-pandharvada-organized-across-the-state-on-the-occasion-of-prime-minister-modis-birthday-information-from-.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-rain-manoj-jarange-chhagan-bhujbal-obc-reservation-devendra-fadnavis-tuesday-16-september-2025-1493374.html</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-news-case-registered-against-teacher-beating-girl-student-over-reason-of-refuse-to-clean-garbage/articleshow/123926192.cms</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-sudhir-khandare-dies-in-bathroom-after-allegedly-hit-by-tap-police-solved-murder-mystery-nabs-family/articleshow/123933510.cms</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/jsym-to-host-amrit-mahotsavi-international-yoga-convention-in-nagpur-in-november/articleshow/124005000.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/vhps-hindus-only-diktat-for-garba-bjp-leader-backs-organisers-rights-oppn-slams-move-3737006</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/state-has-received-no-complaint-of-denial-of-kunbi-certificate-to-eligible-candidates-cm/articleshow/123954996.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/banjara-community-holds-two-big-rallies-munde-says-form-panel-to-grant-them-st-status-101757963085577.html</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-news-case-registered-against-teacher-beating-girl-student-over-reason-of-refuse-to-clean-garbage/articleshow/123926192.cms</t>
+          <t>https://www.hindustantimes.com/india-news/for-hindu-only-garba-vhp-sets-entry-norms-check-aadhaar-apply-tilak-101758363132840.html</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
+          <t>https://www.oneindia.com/india/for-hindu-only-garba-vhp-sets-entry-rules-aadhaar-tilak-required-7866187.html</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/banjara-community-holds-two-big-rallies-munde-says-form-panel-to-grant-them-st-status-101757963085577.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-minister-chhagan-bhujbal-demands-verification-of-obc-certificates-issued-to-maratha-community-23594340</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-presents-fake-documents-asks-for-committee-to-scrutinise-kunbi-certificates/articleshow/123927743.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/kolhapur/sharad-pawar-reaction-on-hyderabad-gazette-and-the-cabinet-sub-committee-formed-on-reservation/articleshow/123964633.cms</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/for-hindu-only-garba-vhp-sets-entry-norms-check-aadhaar-apply-tilak-101758363132840.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/jsym-to-host-amrit-mahotsavi-international-yoga-convention-in-nagpur-in-november/articleshow/124005000.cms</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/vhp-issues-hindus-only-diktat-for-garba-bawankule-backs-organisers-rights-wadettiwar-slams-move/articleshow/124014945.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/obc-activists-wave-black-flags-during-cms-speech-2-attempt-self-immolation-near-ajit-pawars-convoy/articleshow/123952613.cms</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://news34.in/2025/09/chandrapur-bjp-internal-conflict-2026/</t>
+          <t>https://agrowon.esakal.com/agro-special/survey-of-654-rural-roads-completed-in-nagpur-gramin-taluka-maps-available-for-citizens-mj18</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-minister-chhagan-bhujbal-demands-verification-of-obc-certificates-issued-to-maratha-community-23594340</t>
+          <t>https://www.nagpurtoday.in/burglary-in-nagpurs-wathoda-cash-along-with-jewellery-worth-over-rs-6-lakhs-looted/09221724</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/e-paper/aam-aadmi-party-submits-memorandum-to-chief-minister-for-farmers-compensation/articleshow/123916578.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/state-has-received-no-complaint-of-denial-of-kunbi-certificate-to-eligible-candidates-cm/articleshow/123954996.cms</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-heavy-rain-traffic-disrupted-and-normal-life-affected-imd-issues-alert-for-next-24-hour/articleshow/123900789.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/govt-to-fast-track-land-ownership-rights-for-bengali-families-in-gadchiroli/articleshow/124004837.cms</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/09/15/guardian-minister-reviews-preparations-for-deekshabhoomi-and-navratri/</t>
+          <t>https://mumbaimirror.indiatimes.com/mumbai/unveiled-uniform-rules-for-hoardings-on-government-land/articleshow/123907327.html</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/obc-activists-wave-black-flags-during-cms-speech-2-attempt-self-immolation-near-ajit-pawars-convoy/articleshow/123952613.cms</t>
+          <t>https://www.business-standard.com/india-news/punjab-records-27-stubble-burning-cases-as-govt-boosts-awareness-drive-125092000441_1.html</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/survey-of-654-rural-roads-completed-in-nagpur-gramin-taluka-maps-available-for-citizens-mj18</t>
+          <t>https://civicmirror.in/maharashtra/1100-services-will-be-digitized-under-the-service-guarantee-act-by-may-1st-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://mumbaimirror.indiatimes.com/mumbai/unveiled-uniform-rules-for-hoardings-on-government-land/articleshow/123907327.html</t>
+          <t>https://agrowon.esakal.com/agro-special/bori-budruk-was-the-first-to-give-the-code-number-rat16</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/bori-budruk-was-the-first-to-give-the-code-number-rat16</t>
+          <t>https://maharashtratimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/india/vhp-issues-hindus-only-diktat-for-garba-events-congress-slams-move/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-presents-fake-documents-asks-for-committee-to-scrutinise-kunbi-certificates/articleshow/123927743.cms</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
+          <t>https://www.loksatta.com/nagpur/chandrapur-jiwati-taluka-deforestation-credit-war-between-bjp-congress-mla-css-98-5372937/</t>
         </is>
       </c>
     </row>
@@ -956,40 +956,47 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/cleanliness-campaign-launched-in-the-state-on-the-occasion-of-prime-minister-narendra-modis-birthday-thousands.html</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/cleanliness-campaign-launched-in-the-state-on-the-occasion-of-prime-minister-narendra-modis-birthday-thousands.html</t>
+          <t>https://punemirror.com/city/pune/7500-students-take-cleanliness-pledge-in-pune-to-mark-pm-modis-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/anti-social-element-will-be-arrested-soon-cm-on-vandalism-of-meenatai-thackerays-statue-in-mumbai/articleshow/123955024.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/govt-issued-gr-based-on-hyderabad-gazette-to-resolve-conflict-but-it-backfired-pawar/articleshow/123955159.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/anti-social-element-will-be-arrested-soon-cm-on-vandalism-of-meenatai-thackerays-statue-in-mumbai/articleshow/123955024.cms</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178604/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/govt-issued-gr-based-on-hyderabad-gazette-to-resolve-conflict-but-it-backfired-pawar/articleshow/123955159.cms</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
+        <is>
+          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>https://www.freepressjournal.in/pune/videos-long-queues-outside-kopa-mall-in-punes-koregaon-park-as-iphone-17-series-goes-on-sale-in-india</t>
         </is>

--- a/Output/Chandrashekhar Bawankule/extracted_links_Chandrashekhar Bawankule_failed_links.xlsx
+++ b/Output/Chandrashekhar Bawankule/extracted_links_Chandrashekhar Bawankule_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A82"/>
+  <dimension ref="A1:A75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,56 +445,56 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
+          <t>https://marathi.abplive.com/news/revenue-servant-strike-eighth-day-government-not-even-a-simple-acknowledgement-protesters-warn-the-government-nagpur-news-maharashtra-marathi-news-1385371</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/revenue-servant-strike-eighth-day-government-not-even-a-simple-acknowledgement-protesters-warn-the-government-nagpur-news-maharashtra-marathi-news-1385371</t>
+          <t>https://marathi.abplive.com/news/maharashtra/navratri-garba-only-for-hindus-check-aadhaar-of-participants-says-vhp-bawankule-comment-1385439</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/navratri-garba-only-for-hindus-check-aadhaar-of-participants-says-vhp-bawankule-comment-1385439</t>
+          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-live-blog-updates-19-september-2025-farmer-flood-rain-maharashtra-weather-maharashtra-politics-devendra-fadnavismumbai-rains-1385110</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-live-blog-updates-19-september-2025-farmer-flood-rain-maharashtra-weather-maharashtra-politics-devendra-fadnavismumbai-rains-1385110</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sena-ubt-criticises-govt-over-match-bawankule-hits-back/articleshow/123887314.cms</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/sena-ubt-criticises-govt-over-match-bawankule-hits-back/articleshow/123887314.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-soon-allow-private-entities-to-lease-tribal-lands-101758396296809.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-soon-allow-private-entities-to-lease-tribal-lands-101758396296809.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister-3737045</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister-3737045</t>
+          <t>https://timesofindia.indiatimes.com/india/vhp-issues-hindus-only-diktat-for-garba-bawankule-backs-organisers-rights-wadettiwar-slams-move/articleshow/124014945.cms</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/tribal-farmers-in-maharashtra-can-now-lease-land-to-private-entities;-govt-to-bring-law--minister/2932661</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
         </is>
       </c>
     </row>
@@ -508,495 +508,446 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/maharashtra-allows-tribal-farmers-to-lease-barren-land-to-firms-572455</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/new-nagpur-project-farmers-provide-proof-about-no-rr-rate-change-in-10-yrs/articleshow/124052183.cms</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/vhp-issues-hindus-only-diktat-for-garba-bjp-minister-backs-organisers-rights-cong-slams-move/2934001</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/minister-chandrashekhar-bawankule-gives-important-instructions-to-officers-about-maratha-kunbi-certificate-distribution/articleshow/123922415.cms</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/vhp-issues-hindus-only-diktat-for-garba-bawankule-backs-organisers-rights-wadettiwar-slams-move/articleshow/124014945.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-proposal-to-create-20-new-districts-81-talukas-process-chandrashekhar-bawankule-revenue-minister-news-1386089</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
+          <t>https://www.loksatta.com/pune/revenue-minister-chandrashekhar-bawankule-order-minor-mineral-plan-of-each-district-in-the-state-pune-print-news-asj-82-5381503/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/tribal-farmers-in-maharashtra-can-now-lease-land-to-private-entities-govt-to-bring-law-minister-10482095</t>
+          <t>https://www.loksatta.com/maharashtra/chandrashekhar-bawankule-on-obc-sub-committee-meeting-and-obc-maratha-kunbi-certificate-politics-gkt-96-5376634/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/new-nagpur-project-farmers-provide-proof-about-no-rr-rate-change-in-10-yrs/articleshow/124052183.cms</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/guardian-minister-chandrashekhar-bawankule-thanks-govt-for-upgrading-nagpurs-religious-sites-sdj87</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/chandrashekhar-bawankule-on-obc-sub-committee-meeting-and-obc-maratha-kunbi-certificate-politics-gkt-96-5376634/</t>
+          <t>https://maharashtratimes.com/maharashtra/gadchiroli/revenue-minister-chandrashekhar-bawankule-announces-that-tribal-lands-can-be-given-on-lease/articleshow/124010200.cms</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/e-paper/chandrashekhar-bawankules-important-instructions-for-water-resource-conservation-in-nagpur/articleshow/123916999.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/obc-upsamiti-meeting-chandrashekhar-bawankule-chhagan-bhujbal-opposed-flaw-evidence-to-kunbi-certificates-1384586</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/minister-chandrashekhar-bawankule-gives-important-instructions-to-officers-about-maratha-kunbi-certificate-distribution/articleshow/123922415.cms</t>
+          <t>https://marathi.abplive.com/news/gadchiroli/gadchiroli-non-tribals-will-able-to-take-tribal-lands-on-lease-revenue-minister-chandrashekhar-bawankule-marathi-news-1385320</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/guardian-minister-chandrashekhar-bawankule-thanks-govt-for-upgrading-nagpurs-religious-sites-sdj87</t>
+          <t>https://www.tarunbharat.net/Encyc/2025/9/15/bjp-nagpur-chandrashekhar-bawankule-2025-panchayat-to-parliament-election-strategy-.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/gadchiroli/revenue-minister-chandrashekhar-bawankule-announces-that-tribal-lands-can-be-given-on-lease/articleshow/124010200.cms</t>
+          <t>https://agrowon.esakal.com/agro-special/maharashtra-plans-20-new-districts-and-81-talukas-revenue-minister-bawankule-mj18</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/maharashtra-plans-20-new-districts-and-81-talukas-revenue-minister-bawankule-mj18</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/maharashtra-obc-sub-committee-big-decision-on-kunbi-certificate-distribution-to-maratha-community/articleshow/123921757.cms</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/obc-upsamiti-meeting-chandrashekhar-bawankule-chhagan-bhujbal-opposed-flaw-evidence-to-kunbi-certificates-1384586</t>
+          <t>https://marathi.ndtv.com/videos/bawankule-no-tickets-for-those-who-follow-leaders-bawankule-warns-997430</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/maharashtra-obc-sub-committee-big-decision-on-kunbi-certificate-distribution-to-maratha-community/articleshow/123921757.cms</t>
+          <t>https://www.tarunbharat.net/Encyc/2025/9/16/yogesh-kumbhejkar-seva-pandharvada.html</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/bawankule-no-tickets-for-those-who-follow-leaders-bawankule-warns-997430</t>
+          <t>https://agrowon.esakal.com/agro-special/maharashtra-to-make-1100-government-services-online-by-may-cm-fadnavis-mj18</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.net/Encyc/2025/9/15/bjp-nagpur-chandrashekhar-bawankule-2025-panchayat-to-parliament-election-strategy-.html</t>
+          <t>https://news18marathi.com/maharashtra/81-talukas-to-be-created-in-maharashtra-along-with-20-new-districts-marathi-news-1485490.html</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-chandrashekhar-bawankule-on-local-body-elections-tickets-via-internal-survey-public-opinion-to-decide-not-loyalty-to-leaders-amid-chandrapur-groupism-1385779</t>
+          <t>https://www.nagpurtoday.in/sharadiya-navratri-ritual-worship-of-guardian-minister-chandrashekhar-bawankule-at-koradi-mata-temple/09221722</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.net/Encyc/2025/9/16/yogesh-kumbhejkar-seva-pandharvada.html</t>
+          <t>https://policenama.com/pune-navratri-mahotsav-pune-the-31st-pune-navratri-mahotsav-will-be-inaugurated-grandly-by-revenue-minister-chandrashekhar-bawankule-festival-organizer-aba-bagul-gave-this-information-in-a-press-c/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/maharashtra-to-make-1100-government-services-online-by-may-cm-fadnavis-mj18</t>
+          <t>https://www.marathiebatmya.com/political/obc-sub-committees-decision-thorough-verification-of-kunbi-bogus-certificates/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/81-talukas-to-be-created-in-maharashtra-along-with-20-new-districts-marathi-news-1485490.html</t>
+          <t>https://marathi.timesnownews.com/maharashtra/ladki-bahin-yojana-e-kyc-verification-mandatory-for-all-beneficiary-at-ladakibahin-maharashtra-gov-in-article-152850258</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/shiv-bhojan-thali-started-by-uddhav-thackeray-gets-200-crore-fund-by-government/</t>
+          <t>https://www.business-standard.com/india-news/maha-govt-to-allow-tribal-farmers-to-lease-land-to-private-firms-minister-125092000372_1.html</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/sharadiya-navratri-ritual-worship-of-guardian-minister-chandrashekhar-bawankule-at-koradi-mata-temple/09221722</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/rs500cr-govt-land-grabbed-in-gadchiroli-with-fake-papers-minister/articleshow/124004750.cms</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.adharnewsnetwork.com/2025/09/chandrashekhar-bawankule.html</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-bawankule-says-private-companies-also-lease-barren-tribal-land-cm-fadnavis-government-enact-law-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://policenama.com/pune-navratri-mahotsav-pune-the-31st-pune-navratri-mahotsav-will-be-inaugurated-grandly-by-revenue-minister-chandrashekhar-bawankule-festival-organizer-aba-bagul-gave-this-information-in-a-press-c/</t>
+          <t>https://www.khabar24.tv/2025/09/17/chandrashekhar-bawankule-writes-emotional-letter-to-pm-modi-on-his-birthday-a-big-message-to-the-nation-khabar-24-express/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/no-registration-without-survey-big-decision-of-revenue-department-land-survey-mandatory-before-deed-registration-no-changes-without-registration/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/seva-pandharvada-organized-across-the-state-on-the-occasion-of-prime-minister-modis-birthday-information-from-.html</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/obc-sub-committees-decision-thorough-verification-of-kunbi-bogus-certificates/</t>
+          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pune-news-exemption-from-the-fragmentation-law-sale-of-one-or-two-gunthas-is-now-possible-know-when-the-implementation-will-start/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.net/Encyc/2025/9/17/devendra-fadnavis-seva-pandharwada.html</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-sudhir-khandare-dies-in-bathroom-after-allegedly-hit-by-tap-police-solved-murder-mystery-nabs-family/articleshow/123933510.cms</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/maha-govt-to-allow-tribal-farmers-to-lease-land-to-private-firms-minister-125092000372_1.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-rain-manoj-jarange-chhagan-bhujbal-obc-reservation-devendra-fadnavis-tuesday-16-september-2025-1493374.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/rs500cr-govt-land-grabbed-in-gadchiroli-with-fake-papers-minister/articleshow/124004750.cms</t>
+          <t>https://www.tarunbharat.net/Encyc/2025/9/16/flood-news-ashti.html</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-bawankule-says-private-companies-also-lease-barren-tribal-land-cm-fadnavis-government-enact-law-2025-09-20</t>
+          <t>https://www.tarunbharat.net/Encyc/2025/9/16/crime-news-maulana-arrested.html</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-saturday-20-september-2025-1496545.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-presents-fake-documents-asks-for-committee-to-scrutinise-kunbi-certificates/articleshow/123927743.cms</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chairman-of-maharashtra-legislative-council-statement-on-ram-shinde-marathwada-backwardness-pune-print-news-zws-70-5381328/</t>
+          <t>https://www.freepressjournal.in/entertainment/ajey-the-untold-story-of-a-yogi-review-anant-vijay-joshi-wins-over-with-his-sincere-attempt</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/indian-railways-made-in-india-technology-locomotive-in-train-engine-pune-print-news-css-98-5381428/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/seva-pandharvada-organized-across-the-state-on-the-occasion-of-prime-minister-modis-birthday-information-from-.html</t>
+          <t>https://www.oneindia.com/india/for-hindu-only-garba-vhp-sets-entry-rules-aadhaar-tilak-required-7866187.html</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
+          <t>https://www.freepressjournal.in/entertainment/bigg-boss-19-contestants-fees-gaurav-khanna-earns-175-lakh-per-week-know-how-much-amaal-mallik-kunickaa-sadanand-others-charged</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-minister-chhagan-bhujbal-demands-verification-of-obc-certificates-issued-to-maratha-community-23594340</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/nagpur-officials-review-preparations-for-dhammachakra-pravartan-din/09161920</t>
+          <t>https://maharashtratimes.com/maharashtra/kolhapur/sharad-pawar-reaction-on-hyderabad-gazette-and-the-cabinet-sub-committee-formed-on-reservation/articleshow/123964633.cms</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-rain-manoj-jarange-chhagan-bhujbal-obc-reservation-devendra-fadnavis-tuesday-16-september-2025-1493374.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/jsym-to-host-amrit-mahotsavi-international-yoga-convention-in-nagpur-in-november/articleshow/124005000.cms</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-news-case-registered-against-teacher-beating-girl-student-over-reason-of-refuse-to-clean-garbage/articleshow/123926192.cms</t>
+          <t>https://www.nagpurtoday.in/burglary-in-nagpurs-wathoda-cash-along-with-jewellery-worth-over-rs-6-lakhs-looted/09221724</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-sudhir-khandare-dies-in-bathroom-after-allegedly-hit-by-tap-police-solved-murder-mystery-nabs-family/articleshow/123933510.cms</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/obc-activists-wave-black-flags-during-cms-speech-2-attempt-self-immolation-near-ajit-pawars-convoy/articleshow/123952613.cms</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/vhps-hindus-only-diktat-for-garba-bjp-leader-backs-organisers-rights-oppn-slams-move-3737006</t>
+          <t>https://agrowon.esakal.com/agro-special/survey-of-654-rural-roads-completed-in-nagpur-gramin-taluka-maps-available-for-citizens-mj18</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/banjara-community-holds-two-big-rallies-munde-says-form-panel-to-grant-them-st-status-101757963085577.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/govt-to-fast-track-land-ownership-rights-for-bengali-families-in-gadchiroli/articleshow/124004837.cms</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/for-hindu-only-garba-vhp-sets-entry-norms-check-aadhaar-apply-tilak-101758363132840.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/state-has-received-no-complaint-of-denial-of-kunbi-certificate-to-eligible-candidates-cm/articleshow/123954996.cms</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
+          <t>https://www.navarashtra.com/automobile/how-to-increase-electric-car-range-which-mistakes-should-be-avoided-991242.html</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.oneindia.com/india/for-hindu-only-garba-vhp-sets-entry-rules-aadhaar-tilak-required-7866187.html</t>
+          <t>https://www.businessworld.in/article/maharashtra-allows-tribal-farmers-to-lease-barren-land-to-firms-572455</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-minister-chhagan-bhujbal-demands-verification-of-obc-certificates-issued-to-maratha-community-23594340</t>
+          <t>https://www.business-standard.com/india-news/punjab-records-27-stubble-burning-cases-as-govt-boosts-awareness-drive-125092000441_1.html</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/kolhapur/sharad-pawar-reaction-on-hyderabad-gazette-and-the-cabinet-sub-committee-formed-on-reservation/articleshow/123964633.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/vhps-hindus-only-diktat-for-garba-bjp-leader-backs-organisers-rights-oppn-slams-move-3737006</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/jsym-to-host-amrit-mahotsavi-international-yoga-convention-in-nagpur-in-november/articleshow/124005000.cms</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/19/tatkare-terms-rahul-gandhis-vote-theft-allegation-childish.html</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
+          <t>https://www.etvbharat.com/mr/!videos/vanjari-samaj-leader-balasaheb-sanap-demends-reservation-for-vanjari-in-st-as-per-hyderabad-gazette-watch-video-mhs25091903949</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/obc-activists-wave-black-flags-during-cms-speech-2-attempt-self-immolation-near-ajit-pawars-convoy/articleshow/123952613.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/survey-of-654-rural-roads-completed-in-nagpur-gramin-taluka-maps-available-for-citizens-mj18</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/banjara-community-holds-two-big-rallies-munde-says-form-panel-to-grant-them-st-status-101757963085577.html</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/burglary-in-nagpurs-wathoda-cash-along-with-jewellery-worth-over-rs-6-lakhs-looted/09221724</t>
+          <t>https://www.freepressjournal.in/entertainment/emmy-awards-2025-fk-ice-and-free-palestine-hacks-actress-hannah-einbinder-speech-goes-viral-watch-video</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/state-has-received-no-complaint-of-denial-of-kunbi-certificate-to-eligible-candidates-cm/articleshow/123954996.cms</t>
+          <t>https://www.freepressjournal.in/entertainment/homebound-review-neeraj-ghaywans-film-hits-hard-with-ishaan-khatter-vishal-jethwas-career-defining-performances</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/govt-to-fast-track-land-ownership-rights-for-bengali-families-in-gadchiroli/articleshow/124004837.cms</t>
+          <t>https://www.freepressjournal.in/entertainment/nishaanchi-review-anurag-kashyaps-film-is-full-on-desi-but-very-long-actors-take-the-movie-a-notch-higher</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://mumbaimirror.indiatimes.com/mumbai/unveiled-uniform-rules-for-hoardings-on-government-land/articleshow/123907327.html</t>
+          <t>https://www.freepressjournal.in/entertainment/the-trial-season-2-review-kajols-series-is-about-pyaar-kanoon-dhokha-and-a-few-loose-ends-tied-up</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/punjab-records-27-stubble-burning-cases-as-govt-boosts-awareness-drive-125092000441_1.html</t>
+          <t>https://www.freepressjournal.in/entertainment/mohanlal-wins-dadasaheb-phalke-award-malayalam-actors-daughter-vismaya-pens-heartfelt-note-says-were-all-proud-of-you</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/1100-services-will-be-digitized-under-the-service-guarantee-act-by-may-1st-chief-minister-devendra-fadnavis/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/anti-social-element-will-be-arrested-soon-cm-on-vandalism-of-meenatai-thackerays-statue-in-mumbai/articleshow/123955024.cms</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/bori-budruk-was-the-first-to-give-the-code-number-rat16</t>
+          <t>https://www.etvbharat.com/mr/!state/sewa-pakhwada-in-the-maharashtra-on-the-occasion-of-prime-minister-narendra-modis-75th-birthday-iti-students-to-carry-out-cleanliness-drive-in-750-villages-maharashtra-news-mhs25091603490</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/cleanliness-campaign-launched-in-the-state-on-the-occasion-of-prime-minister-narendra-modis-birthday-thousands.html</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-presents-fake-documents-asks-for-committee-to-scrutinise-kunbi-certificates/articleshow/123927743.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/chandrapur-jiwati-taluka-deforestation-credit-war-between-bjp-congress-mla-css-98-5372937/</t>
+          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
-        <is>
-          <t>https://clarionindia.net/shiv-sena-fears-rigging-tampering-with-voter-list-in-maharashtra-local-polls/</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/cleanliness-campaign-launched-in-the-state-on-the-occasion-of-prime-minister-narendra-modis-birthday-thousands.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>https://punemirror.com/city/pune/7500-students-take-cleanliness-pledge-in-pune-to-mark-pm-modis-75th-birthday/</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/anti-social-element-will-be-arrested-soon-cm-on-vandalism-of-meenatai-thackerays-statue-in-mumbai/articleshow/123955024.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/govt-issued-gr-based-on-hyderabad-gazette-to-resolve-conflict-but-it-backfired-pawar/articleshow/123955159.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
         <is>
           <t>https://www.freepressjournal.in/pune/videos-long-queues-outside-kopa-mall-in-punes-koregaon-park-as-iphone-17-series-goes-on-sale-in-india</t>
         </is>
